--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA75CE6-B471-457F-8BF5-222ED4BDB67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AC1ED9-0989-44DD-9C8B-98452ED23E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="799">
   <si>
     <t>Id</t>
   </si>
@@ -2720,10 +2720,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{"Count":1,"UnitId":"猫"}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>猫</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2771,10 +2767,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>#猫诱导</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>猫牢笼</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2796,6 +2788,10 @@
   </si>
   <si>
     <t>{"UnitId":"猫牢笼","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"FixedDirection"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Count":1,"UnitId":"猫诱导"}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3580,7 +3576,7 @@
         <v>51</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="BA1" t="s">
         <v>52</v>
@@ -3750,7 +3746,7 @@
         <v>105</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="BA2" t="s">
         <v>106</v>
@@ -5783,7 +5779,7 @@
         <v>689</v>
       </c>
       <c r="AI22" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AK22">
         <v>0</v>
@@ -5983,7 +5979,7 @@
     </row>
     <row r="25" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="B25" t="s">
         <v>139</v>
@@ -6041,13 +6037,13 @@
         <v>-1</v>
       </c>
       <c r="AG25" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AH25" t="s">
         <v>135</v>
       </c>
       <c r="AI25" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AK25">
         <v>3</v>
@@ -6114,7 +6110,7 @@
     </row>
     <row r="26" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B26" t="s">
         <v>139</v>
@@ -6172,7 +6168,7 @@
         <v>1</v>
       </c>
       <c r="AG26" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AH26" t="s">
         <v>135</v>
@@ -12997,7 +12993,7 @@
       <c r="BT73"/>
       <c r="CJ73" s="3"/>
       <c r="CS73" s="8" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
     </row>
     <row r="74" spans="1:110" x14ac:dyDescent="0.25">
@@ -13015,7 +13011,7 @@
     </row>
     <row r="75" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>760</v>
@@ -13040,7 +13036,7 @@
       </c>
       <c r="CJ75" s="3"/>
       <c r="CS75" s="8" t="s">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="DB75">
         <v>1</v>
@@ -13319,7 +13315,7 @@
     </row>
     <row r="84" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>684</v>
@@ -13328,7 +13324,7 @@
         <v>1</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>707</v>
@@ -13387,10 +13383,10 @@
     </row>
     <row r="85" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>784</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>785</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -13408,7 +13404,7 @@
         <v>708</v>
       </c>
       <c r="AR85" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="BB85">
         <v>4</v>
@@ -13418,10 +13414,10 @@
       </c>
       <c r="CJ85" s="3"/>
       <c r="CS85" s="8" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="CW85" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="86" spans="1:110" x14ac:dyDescent="0.25">
@@ -13429,7 +13425,7 @@
     </row>
     <row r="87" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>759</v>
@@ -13444,12 +13440,12 @@
         <v>1</v>
       </c>
       <c r="AR87" s="8" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="BT87"/>
       <c r="CJ87" s="3"/>
       <c r="CS87" s="8" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
     </row>
     <row r="88" spans="1:110" x14ac:dyDescent="0.25">

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6AC1ED9-0989-44DD-9C8B-98452ED23E26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA75CE6-B471-457F-8BF5-222ED4BDB67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="800">
   <si>
     <t>Id</t>
   </si>
@@ -2720,6 +2720,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>{"Count":1,"UnitId":"猫"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>猫</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2767,6 +2771,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
+    <t>#猫诱导</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
     <t>猫牢笼</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2788,10 +2796,6 @@
   </si>
   <si>
     <t>{"UnitId":"猫牢笼","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"FixedDirection"}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>{"Count":1,"UnitId":"猫诱导"}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3576,7 +3580,7 @@
         <v>51</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="BA1" t="s">
         <v>52</v>
@@ -3746,7 +3750,7 @@
         <v>105</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="BA2" t="s">
         <v>106</v>
@@ -5779,7 +5783,7 @@
         <v>689</v>
       </c>
       <c r="AI22" s="8" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="AK22">
         <v>0</v>
@@ -5979,7 +5983,7 @@
     </row>
     <row r="25" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>783</v>
+        <v>793</v>
       </c>
       <c r="B25" t="s">
         <v>139</v>
@@ -6037,13 +6041,13 @@
         <v>-1</v>
       </c>
       <c r="AG25" s="8" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AH25" t="s">
         <v>135</v>
       </c>
       <c r="AI25" s="8" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="AK25">
         <v>3</v>
@@ -6110,7 +6114,7 @@
     </row>
     <row r="26" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="B26" t="s">
         <v>139</v>
@@ -6168,7 +6172,7 @@
         <v>1</v>
       </c>
       <c r="AG26" s="8" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AH26" t="s">
         <v>135</v>
@@ -12993,7 +12997,7 @@
       <c r="BT73"/>
       <c r="CJ73" s="3"/>
       <c r="CS73" s="8" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
     </row>
     <row r="74" spans="1:110" x14ac:dyDescent="0.25">
@@ -13011,7 +13015,7 @@
     </row>
     <row r="75" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>760</v>
@@ -13036,7 +13040,7 @@
       </c>
       <c r="CJ75" s="3"/>
       <c r="CS75" s="8" t="s">
-        <v>798</v>
+        <v>780</v>
       </c>
       <c r="DB75">
         <v>1</v>
@@ -13315,7 +13319,7 @@
     </row>
     <row r="84" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>684</v>
@@ -13324,7 +13328,7 @@
         <v>1</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>707</v>
@@ -13383,10 +13387,10 @@
     </row>
     <row r="85" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="C85" s="8" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -13404,7 +13408,7 @@
         <v>708</v>
       </c>
       <c r="AR85" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="BB85">
         <v>4</v>
@@ -13414,10 +13418,10 @@
       </c>
       <c r="CJ85" s="3"/>
       <c r="CS85" s="8" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="CW85" s="8" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="86" spans="1:110" x14ac:dyDescent="0.25">
@@ -13425,7 +13429,7 @@
     </row>
     <row r="87" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>759</v>
@@ -13440,12 +13444,12 @@
         <v>1</v>
       </c>
       <c r="AR87" s="8" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="BT87"/>
       <c r="CJ87" s="3"/>
       <c r="CS87" s="8" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
     </row>
     <row r="88" spans="1:110" x14ac:dyDescent="0.25">

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FA75CE6-B471-457F-8BF5-222ED4BDB67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2661733-A701-4A63-B409-FF4279875D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="799">
   <si>
     <t>Id</t>
   </si>
@@ -2720,10 +2720,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{"Count":1,"UnitId":"猫"}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>猫</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2771,10 +2767,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>#猫诱导</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>猫牢笼</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2791,11 +2783,15 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{"UnitId":"影哨","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"先锋型斯卡蒂"}</t>
+    <t>{"UnitId":"猫牢笼","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"FixedDirection"}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{"UnitId":"猫牢笼","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"FixedDirection"}</t>
+    <t>{"UnitId":"先锋型斯卡蒂","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"先锋型斯卡蒂"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"Count":1,"UnitId":"猫诱导"}</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3580,7 +3576,7 @@
         <v>51</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="BA1" t="s">
         <v>52</v>
@@ -3750,7 +3746,7 @@
         <v>105</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="BA2" t="s">
         <v>106</v>
@@ -5783,7 +5779,7 @@
         <v>689</v>
       </c>
       <c r="AI22" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AK22">
         <v>0</v>
@@ -5796,6 +5792,9 @@
       </c>
       <c r="AP22">
         <v>0.5</v>
+      </c>
+      <c r="AQ22">
+        <v>1</v>
       </c>
       <c r="AW22">
         <v>0.25</v>
@@ -5983,7 +5982,7 @@
     </row>
     <row r="25" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>793</v>
+        <v>783</v>
       </c>
       <c r="B25" t="s">
         <v>139</v>
@@ -6041,13 +6040,13 @@
         <v>-1</v>
       </c>
       <c r="AG25" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AH25" t="s">
         <v>135</v>
       </c>
       <c r="AI25" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="AK25">
         <v>3</v>
@@ -6114,7 +6113,7 @@
     </row>
     <row r="26" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B26" t="s">
         <v>139</v>
@@ -6172,7 +6171,7 @@
         <v>1</v>
       </c>
       <c r="AG26" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AH26" t="s">
         <v>135</v>
@@ -12997,7 +12996,7 @@
       <c r="BT73"/>
       <c r="CJ73" s="3"/>
       <c r="CS73" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
     </row>
     <row r="74" spans="1:110" x14ac:dyDescent="0.25">
@@ -13015,7 +13014,7 @@
     </row>
     <row r="75" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="C75" s="8" t="s">
         <v>760</v>
@@ -13040,7 +13039,7 @@
       </c>
       <c r="CJ75" s="3"/>
       <c r="CS75" s="8" t="s">
-        <v>780</v>
+        <v>798</v>
       </c>
       <c r="DB75">
         <v>1</v>
@@ -13319,7 +13318,7 @@
     </row>
     <row r="84" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>684</v>
@@ -13328,7 +13327,7 @@
         <v>1</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>707</v>
@@ -13387,10 +13386,10 @@
     </row>
     <row r="85" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
+        <v>783</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>784</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>785</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -13408,7 +13407,7 @@
         <v>708</v>
       </c>
       <c r="AR85" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="BB85">
         <v>4</v>
@@ -13418,10 +13417,10 @@
       </c>
       <c r="CJ85" s="3"/>
       <c r="CS85" s="8" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="CW85" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
     </row>
     <row r="86" spans="1:110" x14ac:dyDescent="0.25">
@@ -13429,7 +13428,7 @@
     </row>
     <row r="87" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="C87" s="8" t="s">
         <v>759</v>
@@ -13444,12 +13443,12 @@
         <v>1</v>
       </c>
       <c r="AR87" s="8" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="BT87"/>
       <c r="CJ87" s="3"/>
       <c r="CS87" s="8" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
     </row>
     <row r="88" spans="1:110" x14ac:dyDescent="0.25">

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D2661733-A701-4A63-B409-FF4279875D21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C42F1ED-B937-4005-A9A8-18D5972E00B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="799">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="811">
   <si>
     <t>Id</t>
   </si>
@@ -2751,10 +2751,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>猫诱导,猫自毁</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>充能释放</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2792,6 +2788,52 @@
   </si>
   <si>
     <t>{"Count":1,"UnitId":"猫诱导"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫爆炸</t>
+  </si>
+  <si>
+    <t>猫死亡</t>
+  </si>
+  <si>
+    <t>{"Sanity":100}</t>
+  </si>
+  <si>
+    <t>减速</t>
+  </si>
+  <si>
+    <t>Real</t>
+  </si>
+  <si>
+    <t>撤退</t>
+  </si>
+  <si>
+    <t>猫索敌</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫爆炸</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫死亡</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫撤退爆炸</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫死亡爆炸</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>猫索敌,猫爆炸,猫死亡,猫撤退爆炸,猫死亡爆炸,猫诱导</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2799,7 +2841,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2885,6 +2927,44 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF00B0F0"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -2920,7 +3000,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2953,6 +3033,24 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3576,7 +3674,7 @@
         <v>51</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="BA1" t="s">
         <v>52</v>
@@ -3746,7 +3844,7 @@
         <v>105</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="BA2" t="s">
         <v>106</v>
@@ -6036,6 +6134,9 @@
       <c r="AC25">
         <v>0</v>
       </c>
+      <c r="AD25">
+        <v>1</v>
+      </c>
       <c r="AE25">
         <v>-1</v>
       </c>
@@ -6046,7 +6147,7 @@
         <v>135</v>
       </c>
       <c r="AI25" s="8" t="s">
-        <v>788</v>
+        <v>809</v>
       </c>
       <c r="AK25">
         <v>3</v>
@@ -6113,7 +6214,7 @@
     </row>
     <row r="26" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="B26" t="s">
         <v>139</v>
@@ -9019,7 +9120,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:DH899"/>
+  <dimension ref="A1:DH905"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.08203125" customWidth="1"/>
@@ -9068,7 +9169,10 @@
     <col min="52" max="52" width="9.75" customWidth="1"/>
     <col min="53" max="53" width="5.08203125" customWidth="1"/>
     <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="58" width="8.25" customWidth="1"/>
+    <col min="55" max="55" width="13.5" customWidth="1"/>
+    <col min="56" max="56" width="14.6640625" customWidth="1"/>
+    <col min="57" max="57" width="10.1640625" customWidth="1"/>
+    <col min="58" max="58" width="8.25" customWidth="1"/>
     <col min="59" max="65" width="8.33203125" customWidth="1"/>
     <col min="66" max="68" width="11.25" customWidth="1"/>
     <col min="69" max="69" width="6.58203125" customWidth="1"/>
@@ -12996,7 +13100,7 @@
       <c r="BT73"/>
       <c r="CJ73" s="3"/>
       <c r="CS73" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
     </row>
     <row r="74" spans="1:110" x14ac:dyDescent="0.25">
@@ -13039,7 +13143,7 @@
       </c>
       <c r="CJ75" s="3"/>
       <c r="CS75" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="DB75">
         <v>1</v>
@@ -13327,7 +13431,7 @@
         <v>1</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>707</v>
@@ -13417,106 +13521,494 @@
       </c>
       <c r="CJ85" s="3"/>
       <c r="CS85" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="CW85" s="8" t="s">
         <v>785</v>
       </c>
     </row>
     <row r="86" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A86" s="8"/>
+      <c r="C86" s="8"/>
+      <c r="AO86" s="8"/>
       <c r="CJ86" s="3"/>
+      <c r="CS86" s="8"/>
+      <c r="CW86" s="8"/>
     </row>
     <row r="87" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
+        <v>804</v>
+      </c>
+      <c r="C87" t="s">
+        <v>424</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87" s="13"/>
+      <c r="K87" s="13"/>
+      <c r="L87" s="13"/>
+      <c r="M87"/>
+      <c r="N87"/>
+      <c r="O87" s="13"/>
+      <c r="P87"/>
+      <c r="Q87"/>
+      <c r="R87" s="13"/>
+      <c r="S87" s="13"/>
+      <c r="T87" s="13"/>
+      <c r="U87" s="13"/>
+      <c r="V87" s="13"/>
+      <c r="W87" s="13"/>
+      <c r="X87" s="13"/>
+      <c r="Y87" s="13"/>
+      <c r="AC87">
+        <v>2</v>
+      </c>
+      <c r="AD87">
+        <v>1</v>
+      </c>
+      <c r="AT87" s="12">
+        <v>0.5</v>
+      </c>
+      <c r="BB87">
+        <v>1</v>
+      </c>
+      <c r="BN87" s="12" t="s">
+        <v>798</v>
+      </c>
+      <c r="BT87" s="14"/>
+      <c r="BU87" s="14"/>
+      <c r="BV87" s="14"/>
+      <c r="BW87" s="14"/>
+      <c r="BX87" s="14"/>
+      <c r="BY87" s="14"/>
+      <c r="BZ87" s="12"/>
+      <c r="CH87" s="12"/>
+      <c r="CK87" s="12"/>
+      <c r="CR87" s="12"/>
+      <c r="CU87" s="12"/>
+      <c r="CV87" s="12"/>
+      <c r="DF87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A88" s="8" t="s">
+        <v>805</v>
+      </c>
+      <c r="C88" t="s">
+        <v>424</v>
+      </c>
+      <c r="I88">
+        <v>1</v>
+      </c>
+      <c r="K88" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="L88" s="13"/>
+      <c r="M88"/>
+      <c r="N88"/>
+      <c r="O88" s="13"/>
+      <c r="P88"/>
+      <c r="Q88"/>
+      <c r="R88" s="13"/>
+      <c r="S88" s="13"/>
+      <c r="T88" s="13"/>
+      <c r="U88" s="13"/>
+      <c r="V88" s="13"/>
+      <c r="W88" s="13"/>
+      <c r="X88" s="13"/>
+      <c r="Y88" s="13"/>
+      <c r="AC88">
+        <v>2</v>
+      </c>
+      <c r="AD88">
+        <v>1</v>
+      </c>
+      <c r="AR88" t="s">
+        <v>782</v>
+      </c>
+      <c r="AV88" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="AX88">
+        <v>1</v>
+      </c>
+      <c r="BB88">
+        <v>99</v>
+      </c>
+      <c r="BM88" s="12"/>
+      <c r="BN88" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="BR88">
+        <v>0.5</v>
+      </c>
+      <c r="BT88" s="14">
+        <v>12</v>
+      </c>
+      <c r="BU88" s="14">
+        <v>1</v>
+      </c>
+      <c r="BV88" s="14">
+        <v>12</v>
+      </c>
+      <c r="BW88" s="17" t="s">
+        <v>810</v>
+      </c>
+      <c r="BX88" s="14"/>
+      <c r="BY88" s="14"/>
+      <c r="BZ88" s="12"/>
+      <c r="CH88" s="12"/>
+      <c r="CJ88" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="CK88" s="12"/>
+      <c r="CL88" t="s">
+        <v>801</v>
+      </c>
+      <c r="CM88">
+        <v>-0.8</v>
+      </c>
+      <c r="CP88">
+        <v>6</v>
+      </c>
+      <c r="CR88" s="12"/>
+      <c r="CU88" s="12"/>
+      <c r="CV88" s="12"/>
+      <c r="CW88" t="s">
+        <v>516</v>
+      </c>
+      <c r="DF88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A89" s="8" t="s">
+        <v>806</v>
+      </c>
+      <c r="C89" s="12" t="s">
+        <v>424</v>
+      </c>
+      <c r="I89">
+        <v>1</v>
+      </c>
+      <c r="J89" s="12"/>
+      <c r="K89" s="15" t="s">
+        <v>425</v>
+      </c>
+      <c r="L89" s="15"/>
+      <c r="M89" s="15"/>
+      <c r="N89" s="15"/>
+      <c r="O89" s="15"/>
+      <c r="P89" s="15"/>
+      <c r="Q89" s="15"/>
+      <c r="R89" s="15"/>
+      <c r="S89" s="15"/>
+      <c r="T89" s="15"/>
+      <c r="U89" s="15"/>
+      <c r="V89" s="15"/>
+      <c r="W89" s="15"/>
+      <c r="X89" s="15"/>
+      <c r="AC89">
+        <v>1</v>
+      </c>
+      <c r="AG89" s="12" t="s">
+        <v>428</v>
+      </c>
+      <c r="AJ89" s="12"/>
+      <c r="AR89" t="s">
+        <v>440</v>
+      </c>
+      <c r="AV89" s="12" t="s">
+        <v>802</v>
+      </c>
+      <c r="AX89">
+        <v>9</v>
+      </c>
+      <c r="AZ89">
+        <v>2</v>
+      </c>
+      <c r="BB89">
+        <v>1</v>
+      </c>
+      <c r="BT89"/>
+      <c r="BU89" s="16"/>
+      <c r="BV89" s="16"/>
+      <c r="BW89" s="16"/>
+      <c r="BX89" s="16"/>
+      <c r="BY89" s="16"/>
+      <c r="CE89" s="12"/>
+      <c r="CJ89" s="15"/>
+      <c r="CL89" s="12"/>
+      <c r="DB89">
+        <v>1</v>
+      </c>
+      <c r="DE89">
+        <v>1</v>
+      </c>
+      <c r="DF89">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="90" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A90" s="8" t="s">
+        <v>807</v>
+      </c>
+      <c r="C90" t="s">
+        <v>424</v>
+      </c>
+      <c r="I90">
+        <v>1</v>
+      </c>
+      <c r="K90" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="L90" s="13" t="s">
+        <v>803</v>
+      </c>
+      <c r="M90"/>
+      <c r="N90"/>
+      <c r="O90" s="13"/>
+      <c r="P90"/>
+      <c r="Q90"/>
+      <c r="R90" s="13"/>
+      <c r="S90" s="13"/>
+      <c r="T90" s="13"/>
+      <c r="U90" s="13"/>
+      <c r="V90" s="13"/>
+      <c r="W90" s="13"/>
+      <c r="X90" s="13"/>
+      <c r="Y90" s="13"/>
+      <c r="AC90">
+        <v>2</v>
+      </c>
+      <c r="AD90">
+        <v>1</v>
+      </c>
+      <c r="AR90" t="s">
+        <v>782</v>
+      </c>
+      <c r="AV90" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="AX90">
+        <v>1</v>
+      </c>
+      <c r="BB90">
+        <v>99</v>
+      </c>
+      <c r="BC90">
+        <v>11</v>
+      </c>
+      <c r="BM90" s="12"/>
+      <c r="BN90" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="BT90" s="14"/>
+      <c r="BU90" s="14"/>
+      <c r="BV90" s="14"/>
+      <c r="BW90" s="14"/>
+      <c r="BX90" s="14"/>
+      <c r="BY90" s="14"/>
+      <c r="BZ90" s="12"/>
+      <c r="CH90" s="12"/>
+      <c r="CJ90" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="CK90" s="12"/>
+      <c r="CL90" t="s">
+        <v>801</v>
+      </c>
+      <c r="CM90">
+        <v>-0.8</v>
+      </c>
+      <c r="CP90">
+        <v>6</v>
+      </c>
+      <c r="CR90" s="12"/>
+      <c r="CU90" s="12"/>
+      <c r="CV90" s="12"/>
+      <c r="CW90" t="s">
+        <v>516</v>
+      </c>
+      <c r="DF90">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="91" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A91" s="8" t="s">
+        <v>808</v>
+      </c>
+      <c r="C91" t="s">
+        <v>424</v>
+      </c>
+      <c r="I91">
+        <v>1</v>
+      </c>
+      <c r="K91" s="13" t="s">
+        <v>425</v>
+      </c>
+      <c r="L91" s="13" t="s">
+        <v>510</v>
+      </c>
+      <c r="M91"/>
+      <c r="N91"/>
+      <c r="O91" s="13"/>
+      <c r="P91"/>
+      <c r="Q91"/>
+      <c r="R91" s="13"/>
+      <c r="S91" s="13"/>
+      <c r="T91" s="13"/>
+      <c r="U91" s="13"/>
+      <c r="V91" s="13"/>
+      <c r="W91" s="13"/>
+      <c r="X91" s="13"/>
+      <c r="Y91" s="13"/>
+      <c r="AC91">
+        <v>2</v>
+      </c>
+      <c r="AD91">
+        <v>1</v>
+      </c>
+      <c r="AR91" t="s">
+        <v>782</v>
+      </c>
+      <c r="AV91" s="12" t="s">
+        <v>439</v>
+      </c>
+      <c r="AX91">
+        <v>1</v>
+      </c>
+      <c r="BB91">
+        <v>99</v>
+      </c>
+      <c r="BC91">
+        <v>11</v>
+      </c>
+      <c r="BM91" s="12"/>
+      <c r="BN91" s="12" t="s">
+        <v>799</v>
+      </c>
+      <c r="BT91" s="14"/>
+      <c r="BU91" s="14"/>
+      <c r="BV91" s="14"/>
+      <c r="BW91" s="14"/>
+      <c r="BX91" s="14"/>
+      <c r="BY91" s="14"/>
+      <c r="BZ91" s="12"/>
+      <c r="CH91" s="12"/>
+      <c r="CJ91" s="15" t="s">
+        <v>800</v>
+      </c>
+      <c r="CK91" s="12"/>
+      <c r="CL91" t="s">
+        <v>801</v>
+      </c>
+      <c r="CM91">
+        <v>-0.8</v>
+      </c>
+      <c r="CP91">
+        <v>6</v>
+      </c>
+      <c r="CR91" s="12"/>
+      <c r="CU91" s="12"/>
+      <c r="CV91" s="12"/>
+      <c r="CW91" t="s">
+        <v>516</v>
+      </c>
+      <c r="DF91">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="92" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="CJ92" s="3"/>
+    </row>
+    <row r="93" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="A93" s="8" t="s">
+        <v>792</v>
+      </c>
+      <c r="C93" s="8" t="s">
+        <v>759</v>
+      </c>
+      <c r="I93">
+        <v>1</v>
+      </c>
+      <c r="K93" s="3" t="s">
+        <v>703</v>
+      </c>
+      <c r="AC93">
+        <v>1</v>
+      </c>
+      <c r="AR93" s="8" t="s">
         <v>793</v>
       </c>
-      <c r="C87" s="8" t="s">
-        <v>759</v>
-      </c>
-      <c r="I87">
-        <v>1</v>
-      </c>
-      <c r="K87" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="AC87">
-        <v>1</v>
-      </c>
-      <c r="AR87" s="8" t="s">
-        <v>794</v>
-      </c>
-      <c r="BT87"/>
-      <c r="CJ87" s="3"/>
-      <c r="CS87" s="8" t="s">
-        <v>796</v>
-      </c>
-    </row>
-    <row r="88" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BT88"/>
-      <c r="CJ88" s="3"/>
-    </row>
-    <row r="89" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BT89"/>
-      <c r="CJ89" s="3"/>
-    </row>
-    <row r="90" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="BT90"/>
-      <c r="CJ90" s="3"/>
-    </row>
-    <row r="91" spans="1:110" x14ac:dyDescent="0.25">
-      <c r="CJ91" s="3"/>
-    </row>
-    <row r="93" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BT93"/>
       <c r="CJ93" s="3"/>
+      <c r="CS93" s="8" t="s">
+        <v>795</v>
+      </c>
     </row>
     <row r="94" spans="1:110" x14ac:dyDescent="0.25">
       <c r="BT94"/>
+      <c r="CJ94" s="3"/>
     </row>
     <row r="95" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BT95"/>
       <c r="CJ95" s="3"/>
     </row>
     <row r="96" spans="1:110" x14ac:dyDescent="0.25">
+      <c r="BT96"/>
       <c r="CJ96" s="3"/>
     </row>
     <row r="97" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ97" s="3"/>
     </row>
+    <row r="99" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ99" s="3"/>
+    </row>
     <row r="100" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ100" s="3"/>
+      <c r="BT100"/>
     </row>
     <row r="101" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ101" s="3"/>
     </row>
-    <row r="105" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT105"/>
+    <row r="102" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ102" s="3"/>
+    </row>
+    <row r="103" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ103" s="3"/>
     </row>
     <row r="106" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ106" s="3"/>
     </row>
+    <row r="107" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ107" s="3"/>
+    </row>
     <row r="111" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT111"/>
     </row>
-    <row r="114" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT114"/>
-      <c r="CJ114" s="3"/>
-    </row>
-    <row r="115" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT115"/>
+    <row r="112" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ112" s="3"/>
     </row>
     <row r="117" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT117"/>
     </row>
-    <row r="118" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ118" s="3"/>
-    </row>
-    <row r="119" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ119" s="3"/>
-    </row>
     <row r="120" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT120"/>
       <c r="CJ120" s="3"/>
     </row>
     <row r="121" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ121" s="3"/>
+      <c r="BT121"/>
+    </row>
+    <row r="123" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT123"/>
+    </row>
+    <row r="124" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ124" s="3"/>
+    </row>
+    <row r="125" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ125" s="3"/>
     </row>
     <row r="126" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ126" s="3"/>
@@ -13524,84 +14016,72 @@
     <row r="127" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ127" s="3"/>
     </row>
-    <row r="133" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="132" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ132" s="3"/>
+    </row>
+    <row r="133" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ133" s="3"/>
     </row>
-    <row r="134" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ134" s="3"/>
-    </row>
-    <row r="136" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ136" s="3"/>
-    </row>
-    <row r="137" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ137" s="3"/>
-    </row>
-    <row r="138" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ138" s="3"/>
-    </row>
-    <row r="139" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="139" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ139" s="3"/>
     </row>
-    <row r="140" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT140"/>
-    </row>
-    <row r="141" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT141"/>
-    </row>
-    <row r="142" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT142"/>
+    <row r="140" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ140" s="3"/>
+    </row>
+    <row r="142" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ142" s="3"/>
     </row>
-    <row r="143" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="143" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ143" s="3"/>
     </row>
-    <row r="144" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="144" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ144" s="3"/>
     </row>
     <row r="145" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT145"/>
+      <c r="CJ145" s="3"/>
     </row>
     <row r="146" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ146" s="3"/>
+      <c r="BT146"/>
+    </row>
+    <row r="147" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT147"/>
+    </row>
+    <row r="148" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT148"/>
+      <c r="CJ148" s="3"/>
+    </row>
+    <row r="149" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ149" s="3"/>
     </row>
     <row r="150" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT150"/>
+      <c r="CJ150" s="3"/>
     </row>
     <row r="151" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ151" s="3"/>
-    </row>
-    <row r="159" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ159" s="3"/>
-    </row>
-    <row r="160" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ160" s="3"/>
-    </row>
-    <row r="161" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT161"/>
+      <c r="BT151"/>
+    </row>
+    <row r="152" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ152" s="3"/>
+    </row>
+    <row r="156" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT156"/>
+    </row>
+    <row r="157" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ157" s="3"/>
+    </row>
+    <row r="165" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ165" s="3"/>
     </row>
     <row r="166" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT166"/>
+      <c r="CJ166" s="3"/>
     </row>
     <row r="167" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT167"/>
-      <c r="CJ167" s="3"/>
-    </row>
-    <row r="168" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ168" s="3"/>
-    </row>
-    <row r="169" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ169" s="3"/>
-    </row>
-    <row r="170" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ170" s="3"/>
-    </row>
-    <row r="171" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ171" s="3"/>
     </row>
     <row r="172" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT172"/>
     </row>
     <row r="173" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT173"/>
       <c r="CJ173" s="3"/>
     </row>
     <row r="174" spans="72:88" x14ac:dyDescent="0.25">
@@ -13614,10 +14094,10 @@
       <c r="CJ176" s="3"/>
     </row>
     <row r="177" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT177"/>
+      <c r="CJ177" s="3"/>
     </row>
     <row r="178" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ178" s="3"/>
+      <c r="BT178"/>
     </row>
     <row r="179" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ179" s="3"/>
@@ -13628,6 +14108,12 @@
     <row r="181" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ181" s="3"/>
     </row>
+    <row r="182" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ182" s="3"/>
+    </row>
+    <row r="183" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT183"/>
+    </row>
     <row r="184" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ184" s="3"/>
     </row>
@@ -13640,11 +14126,8 @@
     <row r="187" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ187" s="3"/>
     </row>
-    <row r="188" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ188" s="3"/>
-    </row>
     <row r="190" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT190"/>
+      <c r="CJ190" s="3"/>
     </row>
     <row r="191" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ191" s="3"/>
@@ -13658,30 +14141,30 @@
     <row r="194" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ194" s="3"/>
     </row>
+    <row r="196" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT196"/>
+    </row>
+    <row r="197" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ197" s="3"/>
+    </row>
     <row r="198" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ198" s="3"/>
     </row>
+    <row r="199" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ199" s="3"/>
+    </row>
     <row r="200" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT200"/>
-    </row>
-    <row r="201" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT201"/>
-      <c r="CJ201" s="3"/>
-    </row>
-    <row r="202" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ202" s="3"/>
-    </row>
-    <row r="203" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ203" s="3"/>
+      <c r="CJ200" s="3"/>
     </row>
     <row r="204" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ204" s="3"/>
     </row>
-    <row r="205" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ205" s="3"/>
+    <row r="206" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT206"/>
     </row>
     <row r="207" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT207"/>
+      <c r="CJ207" s="3"/>
     </row>
     <row r="208" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ208" s="3"/>
@@ -13689,35 +14172,38 @@
     <row r="209" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ209" s="3"/>
     </row>
+    <row r="210" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ210" s="3"/>
+    </row>
     <row r="211" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ211" s="3"/>
     </row>
-    <row r="212" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ212" s="3"/>
+    <row r="213" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT213"/>
     </row>
     <row r="214" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT214"/>
+      <c r="CJ214" s="3"/>
     </row>
     <row r="215" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ215" s="3"/>
     </row>
+    <row r="217" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ217" s="3"/>
+    </row>
     <row r="218" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ218" s="3"/>
     </row>
-    <row r="219" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ219" s="3"/>
-    </row>
-    <row r="222" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ222" s="3"/>
+    <row r="220" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT220"/>
+    </row>
+    <row r="221" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ221" s="3"/>
     </row>
     <row r="224" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ224" s="3"/>
     </row>
-    <row r="226" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT226"/>
-    </row>
-    <row r="227" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ227" s="3"/>
+    <row r="225" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ225" s="3"/>
     </row>
     <row r="228" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ228" s="3"/>
@@ -13725,11 +14211,17 @@
     <row r="230" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ230" s="3"/>
     </row>
-    <row r="231" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ231" s="3"/>
-    </row>
     <row r="232" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ232" s="3"/>
+      <c r="BT232"/>
+    </row>
+    <row r="233" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ233" s="3"/>
+    </row>
+    <row r="234" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ234" s="3"/>
+    </row>
+    <row r="236" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ236" s="3"/>
     </row>
     <row r="237" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ237" s="3"/>
@@ -13737,192 +14229,180 @@
     <row r="238" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ238" s="3"/>
     </row>
-    <row r="241" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ241" s="3"/>
-    </row>
-    <row r="242" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ242" s="3"/>
-    </row>
-    <row r="246" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ246" s="3"/>
-    </row>
-    <row r="250" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ250" s="3"/>
+    <row r="243" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ243" s="3"/>
+    </row>
+    <row r="244" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ244" s="3"/>
+    </row>
+    <row r="247" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ247" s="3"/>
+    </row>
+    <row r="248" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ248" s="3"/>
     </row>
     <row r="252" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ252" s="3"/>
     </row>
-    <row r="253" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ253" s="3"/>
-    </row>
-    <row r="255" spans="88:88" x14ac:dyDescent="0.25">
-      <c r="CJ255" s="3"/>
-    </row>
     <row r="256" spans="88:88" x14ac:dyDescent="0.25">
       <c r="CJ256" s="3"/>
     </row>
     <row r="258" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT258"/>
+      <c r="CJ258" s="3"/>
     </row>
     <row r="259" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT259"/>
       <c r="CJ259" s="3"/>
     </row>
-    <row r="260" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ260" s="3"/>
+    <row r="261" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ261" s="3"/>
     </row>
     <row r="262" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ262" s="3"/>
     </row>
-    <row r="271" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT271"/>
-    </row>
-    <row r="272" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT272"/>
-      <c r="CJ272" s="3"/>
-    </row>
-    <row r="273" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ273" s="3"/>
-    </row>
-    <row r="274" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ274" s="3"/>
-    </row>
-    <row r="275" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT275"/>
-    </row>
-    <row r="276" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT276"/>
-      <c r="CJ276" s="3"/>
+    <row r="264" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT264"/>
+    </row>
+    <row r="265" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT265"/>
+      <c r="CJ265" s="3"/>
+    </row>
+    <row r="266" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ266" s="3"/>
+    </row>
+    <row r="268" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ268" s="3"/>
     </row>
     <row r="277" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ277" s="3"/>
+      <c r="BT277"/>
+    </row>
+    <row r="278" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT278"/>
+      <c r="CJ278" s="3"/>
     </row>
     <row r="279" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT279"/>
+      <c r="CJ279" s="3"/>
     </row>
     <row r="280" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT280"/>
       <c r="CJ280" s="3"/>
     </row>
     <row r="281" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ281" s="3"/>
+      <c r="BT281"/>
+    </row>
+    <row r="282" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT282"/>
+      <c r="CJ282" s="3"/>
     </row>
     <row r="283" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT283"/>
-    </row>
-    <row r="284" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ284" s="3"/>
+      <c r="CJ283" s="3"/>
+    </row>
+    <row r="285" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT285"/>
+    </row>
+    <row r="286" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT286"/>
+      <c r="CJ286" s="3"/>
     </row>
     <row r="287" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ287" s="3"/>
     </row>
-    <row r="291" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ291" s="3"/>
+    <row r="289" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT289"/>
+    </row>
+    <row r="290" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ290" s="3"/>
     </row>
     <row r="293" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT293"/>
-    </row>
-    <row r="294" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ294" s="3"/>
-    </row>
-    <row r="301" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT301"/>
-    </row>
-    <row r="302" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ302" s="3"/>
-    </row>
-    <row r="303" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ303" s="3"/>
-    </row>
-    <row r="305" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT305"/>
-    </row>
-    <row r="306" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT306"/>
-      <c r="CJ306" s="3"/>
+      <c r="CJ293" s="3"/>
+    </row>
+    <row r="297" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ297" s="3"/>
+    </row>
+    <row r="299" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT299"/>
+    </row>
+    <row r="300" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ300" s="3"/>
     </row>
     <row r="307" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ307" s="3"/>
+      <c r="BT307"/>
+    </row>
+    <row r="308" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ308" s="3"/>
+    </row>
+    <row r="309" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ309" s="3"/>
+    </row>
+    <row r="311" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT311"/>
+    </row>
+    <row r="312" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT312"/>
+      <c r="CJ312" s="3"/>
     </row>
     <row r="313" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT313"/>
-    </row>
-    <row r="314" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT314"/>
-      <c r="CJ314" s="3"/>
-    </row>
-    <row r="315" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT315"/>
-      <c r="CJ315" s="3"/>
-    </row>
-    <row r="316" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ316" s="3"/>
+      <c r="CJ313" s="3"/>
+    </row>
+    <row r="319" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT319"/>
+    </row>
+    <row r="320" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT320"/>
+      <c r="CJ320" s="3"/>
     </row>
     <row r="321" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT321"/>
+      <c r="CJ321" s="3"/>
     </row>
     <row r="322" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT322"/>
-    </row>
-    <row r="326" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT326"/>
+      <c r="CJ322" s="3"/>
     </row>
     <row r="327" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ327" s="3"/>
+      <c r="BT327"/>
     </row>
     <row r="328" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT328"/>
     </row>
-    <row r="329" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ329" s="3"/>
-    </row>
-    <row r="339" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT339"/>
-    </row>
-    <row r="340" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ340" s="3"/>
-    </row>
-    <row r="342" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT342"/>
-    </row>
-    <row r="343" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ343" s="3"/>
-    </row>
-    <row r="351" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT351"/>
-    </row>
-    <row r="352" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ352" s="3"/>
-    </row>
-    <row r="356" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT356"/>
+    <row r="332" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT332"/>
+    </row>
+    <row r="333" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ333" s="3"/>
+    </row>
+    <row r="334" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT334"/>
+    </row>
+    <row r="335" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ335" s="3"/>
+    </row>
+    <row r="345" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT345"/>
+    </row>
+    <row r="346" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ346" s="3"/>
+    </row>
+    <row r="348" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT348"/>
+    </row>
+    <row r="349" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ349" s="3"/>
     </row>
     <row r="357" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ357" s="3"/>
-    </row>
-    <row r="359" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT359"/>
-    </row>
-    <row r="360" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ360" s="3"/>
-    </row>
-    <row r="376" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT376"/>
-    </row>
-    <row r="377" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT377"/>
-      <c r="CJ377" s="3"/>
-    </row>
-    <row r="378" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT378"/>
-      <c r="CJ378" s="3"/>
-    </row>
-    <row r="379" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT379"/>
-      <c r="CJ379" s="3"/>
-    </row>
-    <row r="380" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT380"/>
+      <c r="BT357"/>
+    </row>
+    <row r="358" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ358" s="3"/>
+    </row>
+    <row r="362" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT362"/>
+    </row>
+    <row r="363" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ363" s="3"/>
+    </row>
+    <row r="365" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT365"/>
+    </row>
+    <row r="366" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ366" s="3"/>
     </row>
     <row r="382" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT382"/>
@@ -13936,60 +14416,62 @@
       <c r="CJ384" s="3"/>
     </row>
     <row r="385" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT385"/>
       <c r="CJ385" s="3"/>
+    </row>
+    <row r="386" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT386"/>
+    </row>
+    <row r="388" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT388"/>
     </row>
     <row r="389" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT389"/>
+      <c r="CJ389" s="3"/>
     </row>
     <row r="390" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT390"/>
       <c r="CJ390" s="3"/>
     </row>
-    <row r="392" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT392"/>
-    </row>
-    <row r="393" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT393"/>
-      <c r="CJ393" s="3"/>
-    </row>
-    <row r="394" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT394"/>
-      <c r="CJ394" s="3"/>
+    <row r="391" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ391" s="3"/>
     </row>
     <row r="395" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ395" s="3"/>
-    </row>
-    <row r="411" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT411"/>
-    </row>
-    <row r="412" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ412" s="3"/>
-    </row>
-    <row r="420" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ420" s="3"/>
-    </row>
-    <row r="421" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ421" s="3"/>
-    </row>
-    <row r="422" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ422" s="3"/>
-    </row>
-    <row r="423" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ423" s="3"/>
-    </row>
-    <row r="424" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ424" s="3"/>
+      <c r="BT395"/>
+    </row>
+    <row r="396" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ396" s="3"/>
+    </row>
+    <row r="398" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT398"/>
+    </row>
+    <row r="399" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT399"/>
+      <c r="CJ399" s="3"/>
+    </row>
+    <row r="400" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT400"/>
+      <c r="CJ400" s="3"/>
+    </row>
+    <row r="401" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ401" s="3"/>
+    </row>
+    <row r="417" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT417"/>
+    </row>
+    <row r="418" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ418" s="3"/>
     </row>
     <row r="426" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT426"/>
+      <c r="CJ426" s="3"/>
     </row>
     <row r="427" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ427" s="3"/>
     </row>
     <row r="428" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT428"/>
+      <c r="CJ428" s="3"/>
     </row>
     <row r="429" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT429"/>
       <c r="CJ429" s="3"/>
     </row>
     <row r="430" spans="72:88" x14ac:dyDescent="0.25">
@@ -13999,52 +14481,48 @@
       <c r="BT432"/>
     </row>
     <row r="433" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT433"/>
       <c r="CJ433" s="3"/>
     </row>
     <row r="434" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT434"/>
-      <c r="CJ434" s="3"/>
     </row>
     <row r="435" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT435"/>
       <c r="CJ435" s="3"/>
     </row>
-    <row r="437" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ437" s="3"/>
+    <row r="436" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ436" s="3"/>
+    </row>
+    <row r="438" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT438"/>
     </row>
     <row r="439" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT439"/>
       <c r="CJ439" s="3"/>
+    </row>
+    <row r="440" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT440"/>
+      <c r="CJ440" s="3"/>
     </row>
     <row r="441" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ441" s="3"/>
     </row>
-    <row r="444" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ444" s="3"/>
+    <row r="443" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ443" s="3"/>
     </row>
     <row r="445" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ445" s="3"/>
     </row>
-    <row r="446" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ446" s="3"/>
-    </row>
     <row r="447" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ447" s="3"/>
     </row>
-    <row r="448" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ448" s="3"/>
-    </row>
-    <row r="449" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ449" s="3"/>
-    </row>
     <row r="450" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT450"/>
+      <c r="CJ450" s="3"/>
     </row>
     <row r="451" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT451"/>
       <c r="CJ451" s="3"/>
     </row>
     <row r="452" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT452"/>
       <c r="CJ452" s="3"/>
     </row>
     <row r="453" spans="72:88" x14ac:dyDescent="0.25">
@@ -14057,35 +14535,39 @@
       <c r="CJ455" s="3"/>
     </row>
     <row r="456" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ456" s="3"/>
+      <c r="BT456"/>
+    </row>
+    <row r="457" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT457"/>
+      <c r="CJ457" s="3"/>
     </row>
     <row r="458" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT458"/>
       <c r="CJ458" s="3"/>
     </row>
     <row r="459" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ459" s="3"/>
     </row>
     <row r="460" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT460"/>
+      <c r="CJ460" s="3"/>
     </row>
     <row r="461" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT461"/>
       <c r="CJ461" s="3"/>
     </row>
     <row r="462" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT462"/>
       <c r="CJ462" s="3"/>
-    </row>
-    <row r="463" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ463" s="3"/>
     </row>
     <row r="464" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ464" s="3"/>
     </row>
+    <row r="465" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ465" s="3"/>
+    </row>
     <row r="466" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ466" s="3"/>
+      <c r="BT466"/>
     </row>
     <row r="467" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT467"/>
       <c r="CJ467" s="3"/>
     </row>
     <row r="468" spans="72:88" x14ac:dyDescent="0.25">
@@ -14093,190 +14575,182 @@
       <c r="CJ468" s="3"/>
     </row>
     <row r="469" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT469"/>
       <c r="CJ469" s="3"/>
     </row>
     <row r="470" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ470" s="3"/>
     </row>
-    <row r="471" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ471" s="3"/>
-    </row>
     <row r="472" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ472" s="3"/>
+    </row>
+    <row r="473" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ473" s="3"/>
     </row>
     <row r="474" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT474"/>
       <c r="CJ474" s="3"/>
     </row>
     <row r="475" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT475"/>
       <c r="CJ475" s="3"/>
     </row>
     <row r="476" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ476" s="3"/>
     </row>
+    <row r="477" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ477" s="3"/>
+    </row>
     <row r="478" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT478"/>
       <c r="CJ478" s="3"/>
     </row>
-    <row r="479" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT479"/>
-      <c r="CJ479" s="3"/>
-    </row>
     <row r="480" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT480"/>
       <c r="CJ480" s="3"/>
+    </row>
+    <row r="481" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ481" s="3"/>
     </row>
     <row r="482" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ482" s="3"/>
     </row>
     <row r="484" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT484"/>
       <c r="CJ484" s="3"/>
     </row>
-    <row r="487" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ487" s="3"/>
+    <row r="485" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT485"/>
+      <c r="CJ485" s="3"/>
+    </row>
+    <row r="486" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ486" s="3"/>
     </row>
     <row r="488" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ488" s="3"/>
     </row>
-    <row r="492" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT492"/>
+    <row r="490" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ490" s="3"/>
     </row>
     <row r="493" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT493"/>
       <c r="CJ493" s="3"/>
     </row>
     <row r="494" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT494"/>
       <c r="CJ494" s="3"/>
     </row>
-    <row r="495" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ495" s="3"/>
-    </row>
-    <row r="496" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ496" s="3"/>
-    </row>
-    <row r="497" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT497"/>
-    </row>
     <row r="498" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ498" s="3"/>
+      <c r="BT498"/>
+    </row>
+    <row r="499" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT499"/>
+      <c r="CJ499" s="3"/>
     </row>
     <row r="500" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT500"/>
       <c r="CJ500" s="3"/>
     </row>
     <row r="501" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ501" s="3"/>
     </row>
+    <row r="502" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ502" s="3"/>
+    </row>
     <row r="503" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ503" s="3"/>
+      <c r="BT503"/>
     </row>
     <row r="504" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ504" s="3"/>
     </row>
-    <row r="505" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ505" s="3"/>
-    </row>
     <row r="506" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ506" s="3"/>
     </row>
     <row r="507" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ507" s="3"/>
     </row>
-    <row r="508" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ508" s="3"/>
-    </row>
     <row r="509" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ509" s="3"/>
     </row>
+    <row r="510" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ510" s="3"/>
+    </row>
     <row r="511" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT511"/>
+      <c r="CJ511" s="3"/>
     </row>
     <row r="512" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ512" s="3"/>
     </row>
-    <row r="513" spans="88:88" x14ac:dyDescent="0.25">
+    <row r="513" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ513" s="3"/>
     </row>
-    <row r="546" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS546" s="10"/>
-      <c r="BT546" s="11"/>
-    </row>
-    <row r="547" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H547" s="10"/>
-      <c r="CJ547" s="10"/>
+    <row r="514" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ514" s="3"/>
+    </row>
+    <row r="515" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ515" s="3"/>
+    </row>
+    <row r="517" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT517"/>
+    </row>
+    <row r="518" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ518" s="3"/>
+    </row>
+    <row r="519" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ519" s="3"/>
+    </row>
+    <row r="552" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS552" s="10"/>
+      <c r="BT552" s="11"/>
     </row>
     <row r="553" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT553"/>
-    </row>
-    <row r="554" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT554"/>
-      <c r="CJ554" s="3"/>
-    </row>
-    <row r="555" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT555"/>
-      <c r="CJ555" s="3"/>
-    </row>
-    <row r="556" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ556" s="3"/>
-    </row>
-    <row r="573" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT573"/>
-    </row>
-    <row r="574" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ574" s="3"/>
-    </row>
-    <row r="606" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT606"/>
-    </row>
-    <row r="607" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT607"/>
-      <c r="CJ607" s="3"/>
-    </row>
-    <row r="608" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ608" s="3"/>
-    </row>
-    <row r="624" spans="72:72" x14ac:dyDescent="0.25">
-      <c r="BT624"/>
-    </row>
-    <row r="625" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ625" s="3"/>
+      <c r="H553" s="10"/>
+      <c r="CJ553" s="10"/>
+    </row>
+    <row r="559" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT559"/>
+    </row>
+    <row r="560" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT560"/>
+      <c r="CJ560" s="3"/>
+    </row>
+    <row r="561" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT561"/>
+      <c r="CJ561" s="3"/>
+    </row>
+    <row r="562" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ562" s="3"/>
+    </row>
+    <row r="579" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT579"/>
+    </row>
+    <row r="580" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ580" s="3"/>
+    </row>
+    <row r="612" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT612"/>
+    </row>
+    <row r="613" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT613"/>
+      <c r="CJ613" s="3"/>
+    </row>
+    <row r="614" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ614" s="3"/>
+    </row>
+    <row r="630" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT630"/>
     </row>
     <row r="631" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT631"/>
-    </row>
-    <row r="632" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT632"/>
-      <c r="CJ632" s="3"/>
-    </row>
-    <row r="633" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ633" s="3"/>
+      <c r="CJ631" s="3"/>
+    </row>
+    <row r="637" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT637"/>
     </row>
     <row r="638" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT638"/>
+      <c r="CJ638" s="3"/>
     </row>
     <row r="639" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT639"/>
       <c r="CJ639" s="3"/>
-    </row>
-    <row r="640" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT640"/>
-      <c r="CJ640" s="3"/>
-    </row>
-    <row r="641" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT641"/>
-      <c r="CJ641" s="3"/>
-    </row>
-    <row r="642" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT642"/>
-      <c r="CJ642" s="3"/>
-    </row>
-    <row r="643" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT643"/>
-      <c r="CJ643" s="3"/>
     </row>
     <row r="644" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT644"/>
-      <c r="CJ644" s="3"/>
     </row>
     <row r="645" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT645"/>
@@ -14315,10 +14789,24 @@
       <c r="CJ653" s="3"/>
     </row>
     <row r="654" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT654"/>
       <c r="CJ654" s="3"/>
+    </row>
+    <row r="655" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT655"/>
+      <c r="CJ655" s="3"/>
+    </row>
+    <row r="656" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT656"/>
+      <c r="CJ656" s="3"/>
+    </row>
+    <row r="657" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT657"/>
+      <c r="CJ657" s="3"/>
     </row>
     <row r="658" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT658"/>
+      <c r="CJ658" s="3"/>
     </row>
     <row r="659" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT659"/>
@@ -14327,109 +14815,101 @@
     <row r="660" spans="72:88" x14ac:dyDescent="0.25">
       <c r="CJ660" s="3"/>
     </row>
-    <row r="661" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT661"/>
-    </row>
-    <row r="662" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ662" s="3"/>
+    <row r="664" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT664"/>
     </row>
     <row r="665" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT665"/>
+      <c r="CJ665" s="3"/>
     </row>
     <row r="666" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT666"/>
       <c r="CJ666" s="3"/>
     </row>
     <row r="667" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ667" s="3"/>
-    </row>
-    <row r="698" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT698"/>
-    </row>
-    <row r="699" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT699"/>
-      <c r="CJ699" s="3"/>
-    </row>
-    <row r="700" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT700"/>
-      <c r="CJ700" s="3"/>
-    </row>
-    <row r="701" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT701"/>
-      <c r="CJ701" s="3"/>
-    </row>
-    <row r="702" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT702"/>
-      <c r="CJ702" s="3"/>
-    </row>
-    <row r="703" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT703"/>
-      <c r="CJ703" s="3"/>
-    </row>
-    <row r="704" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT667"/>
+    </row>
+    <row r="668" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ668" s="3"/>
+    </row>
+    <row r="671" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT671"/>
+    </row>
+    <row r="672" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT672"/>
+      <c r="CJ672" s="3"/>
+    </row>
+    <row r="673" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ673" s="3"/>
+    </row>
+    <row r="704" spans="72:72" x14ac:dyDescent="0.25">
       <c r="BT704"/>
-      <c r="CJ704" s="3"/>
     </row>
     <row r="705" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT705"/>
       <c r="CJ705" s="3"/>
     </row>
     <row r="706" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT706"/>
       <c r="CJ706" s="3"/>
+    </row>
+    <row r="707" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT707"/>
+      <c r="CJ707" s="3"/>
     </row>
     <row r="708" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT708"/>
+      <c r="CJ708" s="3"/>
     </row>
     <row r="709" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT709"/>
       <c r="CJ709" s="3"/>
     </row>
-    <row r="713" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT713"/>
+    <row r="710" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT710"/>
+      <c r="CJ710" s="3"/>
+    </row>
+    <row r="711" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT711"/>
+      <c r="CJ711" s="3"/>
+    </row>
+    <row r="712" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ712" s="3"/>
     </row>
     <row r="714" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ714" s="3"/>
-    </row>
-    <row r="717" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT717"/>
-    </row>
-    <row r="718" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT718"/>
-      <c r="CJ718" s="3"/>
+      <c r="BT714"/>
+    </row>
+    <row r="715" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ715" s="3"/>
     </row>
     <row r="719" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT719"/>
-      <c r="CJ719" s="3"/>
     </row>
     <row r="720" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT720"/>
       <c r="CJ720" s="3"/>
     </row>
-    <row r="721" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ721" s="3"/>
-    </row>
-    <row r="728" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT728"/>
-    </row>
-    <row r="729" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ729" s="3"/>
-    </row>
-    <row r="732" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT732"/>
-    </row>
-    <row r="733" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT733"/>
-      <c r="CJ733" s="3"/>
+    <row r="723" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT723"/>
+    </row>
+    <row r="724" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT724"/>
+      <c r="CJ724" s="3"/>
+    </row>
+    <row r="725" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT725"/>
+      <c r="CJ725" s="3"/>
+    </row>
+    <row r="726" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT726"/>
+      <c r="CJ726" s="3"/>
+    </row>
+    <row r="727" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ727" s="3"/>
     </row>
     <row r="734" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT734"/>
-      <c r="CJ734" s="3"/>
     </row>
     <row r="735" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT735"/>
       <c r="CJ735" s="3"/>
-    </row>
-    <row r="736" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ736" s="3"/>
     </row>
     <row r="738" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT738"/>
@@ -14439,84 +14919,78 @@
       <c r="CJ739" s="3"/>
     </row>
     <row r="740" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT740"/>
       <c r="CJ740" s="3"/>
     </row>
     <row r="741" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ741">
+      <c r="BT741"/>
+      <c r="CJ741" s="3"/>
+    </row>
+    <row r="742" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ742" s="3"/>
+    </row>
+    <row r="744" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT744"/>
+    </row>
+    <row r="745" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT745"/>
+      <c r="CJ745" s="3"/>
+    </row>
+    <row r="746" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ746" s="3"/>
+    </row>
+    <row r="747" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ747">
         <v>0.15</v>
       </c>
     </row>
-    <row r="743" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ743">
+    <row r="749" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ749">
         <v>0.2</v>
       </c>
     </row>
-    <row r="744" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ744">
+    <row r="750" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ750">
         <v>0.1</v>
       </c>
     </row>
-    <row r="746" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ746">
+    <row r="752" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ752">
         <v>0.2</v>
       </c>
     </row>
-    <row r="753" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ753">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="755" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ755">
+    <row r="759" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ759">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="761" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ761">
         <v>0.4</v>
       </c>
     </row>
-    <row r="756" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ756">
+    <row r="762" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ762">
         <v>0.6</v>
       </c>
     </row>
-    <row r="759" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ759">
+    <row r="765" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ765">
         <v>0.5</v>
       </c>
     </row>
-    <row r="760" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ760">
+    <row r="766" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ766">
         <v>0.66700000000000004</v>
       </c>
     </row>
-    <row r="761" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ761">
+    <row r="767" spans="88:88" x14ac:dyDescent="0.25">
+      <c r="CJ767">
         <v>0.2</v>
       </c>
-    </row>
-    <row r="764" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT764"/>
-    </row>
-    <row r="765" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT765"/>
-      <c r="CJ765" s="3"/>
-    </row>
-    <row r="766" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT766"/>
-      <c r="CJ766" s="3"/>
-    </row>
-    <row r="767" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT767"/>
-      <c r="CJ767" s="3"/>
-    </row>
-    <row r="768" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT768"/>
-      <c r="CJ768" s="3"/>
-    </row>
-    <row r="769" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT769"/>
-      <c r="CJ769" s="3"/>
     </row>
     <row r="770" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT770"/>
-      <c r="CJ770" s="3"/>
     </row>
     <row r="771" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT771"/>
@@ -14527,73 +15001,77 @@
       <c r="CJ772" s="3"/>
     </row>
     <row r="773" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT773"/>
       <c r="CJ773" s="3"/>
     </row>
     <row r="774" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT774"/>
+      <c r="CJ774" s="3"/>
     </row>
     <row r="775" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT775"/>
       <c r="CJ775" s="3"/>
     </row>
-    <row r="784" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT784"/>
-    </row>
-    <row r="785" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT785"/>
-      <c r="CJ785" s="3"/>
-    </row>
-    <row r="786" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT786"/>
-      <c r="CJ786" s="3"/>
-    </row>
-    <row r="787" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT787"/>
-      <c r="CJ787" s="3"/>
-    </row>
-    <row r="788" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT788"/>
-      <c r="CJ788" s="3"/>
-    </row>
-    <row r="789" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT789"/>
-      <c r="CJ789" s="3"/>
+    <row r="776" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT776"/>
+      <c r="CJ776" s="3"/>
+    </row>
+    <row r="777" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT777"/>
+      <c r="CJ777" s="3"/>
+    </row>
+    <row r="778" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT778"/>
+      <c r="CJ778" s="3"/>
+    </row>
+    <row r="779" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ779" s="3"/>
+    </row>
+    <row r="780" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT780"/>
+    </row>
+    <row r="781" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ781" s="3"/>
     </row>
     <row r="790" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT790"/>
-      <c r="CJ790" s="3"/>
     </row>
     <row r="791" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT791"/>
       <c r="CJ791" s="3"/>
     </row>
     <row r="792" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT792"/>
       <c r="CJ792" s="3"/>
     </row>
     <row r="793" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT793"/>
+      <c r="CJ793" s="3"/>
     </row>
     <row r="794" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT794"/>
       <c r="CJ794" s="3"/>
+    </row>
+    <row r="795" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT795"/>
+      <c r="CJ795" s="3"/>
+    </row>
+    <row r="796" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT796"/>
+      <c r="CJ796" s="3"/>
+    </row>
+    <row r="797" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT797"/>
+      <c r="CJ797" s="3"/>
+    </row>
+    <row r="798" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ798" s="3"/>
     </row>
     <row r="799" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT799"/>
     </row>
     <row r="800" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT800"/>
       <c r="CJ800" s="3"/>
-    </row>
-    <row r="801" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ801" s="3"/>
-    </row>
-    <row r="802" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT802"/>
-    </row>
-    <row r="803" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT803"/>
-      <c r="CJ803" s="3"/>
-    </row>
-    <row r="804" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ804" s="3"/>
     </row>
     <row r="805" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT805"/>
@@ -14603,140 +15081,138 @@
       <c r="CJ806" s="3"/>
     </row>
     <row r="807" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT807"/>
       <c r="CJ807" s="3"/>
     </row>
     <row r="808" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT808"/>
-      <c r="CJ808" s="3"/>
     </row>
     <row r="809" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT809"/>
       <c r="CJ809" s="3"/>
+    </row>
+    <row r="810" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ810" s="3"/>
+    </row>
+    <row r="811" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT811"/>
+    </row>
+    <row r="812" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT812"/>
+      <c r="CJ812" s="3"/>
     </row>
     <row r="813" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT813"/>
+      <c r="CJ813" s="3"/>
     </row>
     <row r="814" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT814"/>
       <c r="CJ814" s="3"/>
     </row>
     <row r="815" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT815"/>
       <c r="CJ815" s="3"/>
     </row>
-    <row r="816" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ816" s="3"/>
-    </row>
-    <row r="817" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT817"/>
-    </row>
-    <row r="818" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ818" s="3"/>
-    </row>
     <row r="819" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS819" s="10"/>
-      <c r="BT819" s="11"/>
+      <c r="BT819"/>
     </row>
     <row r="820" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H820" s="10"/>
-      <c r="CJ820" s="10"/>
-    </row>
-    <row r="837" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT837"/>
-    </row>
-    <row r="838" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT838"/>
-      <c r="CJ838" s="3"/>
-    </row>
-    <row r="839" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT839"/>
-      <c r="CJ839" s="3"/>
-    </row>
-    <row r="840" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT840"/>
-      <c r="CJ840" s="3"/>
-    </row>
-    <row r="841" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="CJ841" s="3"/>
-    </row>
-    <row r="842" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BT842"/>
-    </row>
-    <row r="843" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT820"/>
+      <c r="CJ820" s="3"/>
+    </row>
+    <row r="821" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT821"/>
+      <c r="CJ821" s="3"/>
+    </row>
+    <row r="822" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ822" s="3"/>
+    </row>
+    <row r="823" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT823"/>
+    </row>
+    <row r="824" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="CJ824" s="3"/>
+    </row>
+    <row r="825" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS825" s="10"/>
+      <c r="BT825" s="11"/>
+    </row>
+    <row r="826" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H826" s="10"/>
+      <c r="CJ826" s="10"/>
+    </row>
+    <row r="843" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT843"/>
-      <c r="CJ843" s="3"/>
-    </row>
-    <row r="844" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="BS844" s="10"/>
-      <c r="BT844" s="11"/>
+    </row>
+    <row r="844" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT844"/>
       <c r="CJ844" s="3"/>
     </row>
-    <row r="845" spans="8:88" x14ac:dyDescent="0.25">
-      <c r="H845" s="10"/>
-      <c r="CJ845" s="10"/>
-    </row>
-    <row r="848" spans="8:88" x14ac:dyDescent="0.25">
+    <row r="845" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT845"/>
+      <c r="CJ845" s="3"/>
+    </row>
+    <row r="846" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT846"/>
+      <c r="CJ846" s="3"/>
+    </row>
+    <row r="847" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ847" s="3"/>
+    </row>
+    <row r="848" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT848"/>
     </row>
-    <row r="849" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="849" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT849"/>
       <c r="CJ849" s="3"/>
     </row>
-    <row r="850" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT850"/>
+    <row r="850" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BS850" s="10"/>
+      <c r="BT850" s="11"/>
       <c r="CJ850" s="3"/>
     </row>
-    <row r="851" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT851"/>
-      <c r="CJ851" s="3"/>
-    </row>
-    <row r="852" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT852"/>
-      <c r="CJ852" s="3"/>
-    </row>
-    <row r="853" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT853"/>
-      <c r="CJ853" s="3"/>
-    </row>
-    <row r="854" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="851" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="H851" s="10"/>
+      <c r="CJ851" s="10"/>
+    </row>
+    <row r="854" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT854"/>
-      <c r="CJ854" s="3"/>
-    </row>
-    <row r="855" spans="72:88" x14ac:dyDescent="0.25">
+    </row>
+    <row r="855" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT855"/>
       <c r="CJ855" s="3"/>
     </row>
-    <row r="856" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="856" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT856"/>
       <c r="CJ856" s="3"/>
     </row>
-    <row r="858" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="857" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT857"/>
+      <c r="CJ857" s="3"/>
+    </row>
+    <row r="858" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT858"/>
-    </row>
-    <row r="859" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ858" s="3"/>
+    </row>
+    <row r="859" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT859"/>
       <c r="CJ859" s="3"/>
     </row>
-    <row r="860" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="860" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT860"/>
       <c r="CJ860" s="3"/>
     </row>
-    <row r="861" spans="72:88" x14ac:dyDescent="0.25">
+    <row r="861" spans="8:88" x14ac:dyDescent="0.25">
       <c r="BT861"/>
       <c r="CJ861" s="3"/>
     </row>
-    <row r="862" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT862"/>
+    <row r="862" spans="8:88" x14ac:dyDescent="0.25">
       <c r="CJ862" s="3"/>
     </row>
-    <row r="863" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT863"/>
-      <c r="CJ863" s="3"/>
-    </row>
-    <row r="864" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="CJ864" s="3"/>
+    <row r="864" spans="8:88" x14ac:dyDescent="0.25">
+      <c r="BT864"/>
     </row>
     <row r="865" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT865"/>
+      <c r="CJ865" s="3"/>
     </row>
     <row r="866" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT866"/>
@@ -14755,12 +15231,10 @@
       <c r="CJ869" s="3"/>
     </row>
     <row r="870" spans="72:88" x14ac:dyDescent="0.25">
-      <c r="BT870"/>
       <c r="CJ870" s="3"/>
     </row>
     <row r="871" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT871"/>
-      <c r="CJ871" s="3"/>
     </row>
     <row r="872" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT872"/>
@@ -14855,10 +15329,12 @@
       <c r="CJ894" s="3"/>
     </row>
     <row r="895" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT895"/>
       <c r="CJ895" s="3"/>
     </row>
     <row r="896" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT896"/>
+      <c r="CJ896" s="3"/>
     </row>
     <row r="897" spans="72:88" x14ac:dyDescent="0.25">
       <c r="BT897"/>
@@ -14869,7 +15345,29 @@
       <c r="CJ898" s="3"/>
     </row>
     <row r="899" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT899"/>
       <c r="CJ899" s="3"/>
+    </row>
+    <row r="900" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT900"/>
+      <c r="CJ900" s="3"/>
+    </row>
+    <row r="901" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ901" s="3"/>
+    </row>
+    <row r="902" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT902"/>
+    </row>
+    <row r="903" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT903"/>
+      <c r="CJ903" s="3"/>
+    </row>
+    <row r="904" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="BT904"/>
+      <c r="CJ904" s="3"/>
+    </row>
+    <row r="905" spans="72:88" x14ac:dyDescent="0.25">
+      <c r="CJ905" s="3"/>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4C42F1ED-B937-4005-A9A8-18D5972E00B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{508C92D4-B45D-4708-929A-B24BA34F6542}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1612" uniqueCount="812">
   <si>
     <t>Id</t>
   </si>
@@ -2507,10 +2507,6 @@
     <phoneticPr fontId="11" type="noConversion"/>
   </si>
   <si>
-    <t>前锋剑术攻击,先锋型斯卡蒂普通攻击,前锋剑术获取闪避</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>固定间隔</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2830,6 +2826,14 @@
   </si>
   <si>
     <t>猫索敌,猫爆炸,猫死亡,猫撤退爆炸,猫死亡爆炸,猫诱导</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻击</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>先锋型斯卡蒂普通攻击,前锋剑术获取闪避</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -2841,7 +2845,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2965,6 +2969,12 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="4">
     <fill>
@@ -3000,7 +3010,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3051,6 +3061,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3674,7 +3687,7 @@
         <v>51</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="BA1" t="s">
         <v>52</v>
@@ -3844,7 +3857,7 @@
         <v>105</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="BA2" t="s">
         <v>106</v>
@@ -3886,7 +3899,7 @@
         <v>118</v>
       </c>
       <c r="BN2" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="BO2" t="s">
         <v>119</v>
@@ -5865,7 +5878,7 @@
         <v>0.05</v>
       </c>
       <c r="Z22">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AC22">
         <v>1</v>
@@ -5877,7 +5890,7 @@
         <v>689</v>
       </c>
       <c r="AI22" s="8" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="AK22">
         <v>0</v>
@@ -5946,19 +5959,19 @@
     </row>
     <row r="24" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="B24" t="s">
         <v>139</v>
       </c>
       <c r="D24" t="s">
+        <v>725</v>
+      </c>
+      <c r="E24" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>728</v>
       </c>
       <c r="G24">
         <v>0.01</v>
@@ -6007,13 +6020,13 @@
         <v>-1</v>
       </c>
       <c r="AG24" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AH24" t="s">
         <v>135</v>
       </c>
       <c r="AI24" s="8" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="AK24">
         <v>3</v>
@@ -6040,10 +6053,10 @@
         <v>1</v>
       </c>
       <c r="BB24" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="BD24" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="BE24" t="str">
         <f t="shared" ref="BE24" si="40">"half_"&amp;D24</f>
@@ -6080,19 +6093,19 @@
     </row>
     <row r="25" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A25" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B25" t="s">
         <v>139</v>
       </c>
       <c r="D25" t="s">
+        <v>725</v>
+      </c>
+      <c r="E25" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="E25" s="1" t="s">
+      <c r="F25" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="F25" s="8" t="s">
-        <v>728</v>
       </c>
       <c r="G25">
         <v>1</v>
@@ -6134,20 +6147,17 @@
       <c r="AC25">
         <v>0</v>
       </c>
-      <c r="AD25">
-        <v>1</v>
-      </c>
       <c r="AE25">
         <v>-1</v>
       </c>
       <c r="AG25" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AH25" t="s">
         <v>135</v>
       </c>
       <c r="AI25" s="8" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="AK25">
         <v>3</v>
@@ -6174,10 +6184,10 @@
         <v>1</v>
       </c>
       <c r="BB25" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="BD25" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="BE25" t="str">
         <f t="shared" ref="BE25" si="42">"half_"&amp;D25</f>
@@ -6214,19 +6224,19 @@
     </row>
     <row r="26" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A26" s="8" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="B26" t="s">
         <v>139</v>
       </c>
       <c r="D26" t="s">
+        <v>725</v>
+      </c>
+      <c r="E26" s="1" t="s">
         <v>726</v>
       </c>
-      <c r="E26" s="1" t="s">
+      <c r="F26" s="8" t="s">
         <v>727</v>
-      </c>
-      <c r="F26" s="8" t="s">
-        <v>728</v>
       </c>
       <c r="G26">
         <v>1</v>
@@ -6272,7 +6282,7 @@
         <v>1</v>
       </c>
       <c r="AG26" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="AH26" t="s">
         <v>135</v>
@@ -6303,10 +6313,10 @@
         <v>1</v>
       </c>
       <c r="BB26" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="BD26" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="BE26" t="str">
         <f t="shared" ref="BE26" si="44">"half_"&amp;D26</f>
@@ -9217,7 +9227,7 @@
         <v>210</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="I1" t="s">
         <v>211</v>
@@ -9403,10 +9413,10 @@
         <v>269</v>
       </c>
       <c r="BS1" s="8" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="BT1" s="4" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="BU1" s="4" t="s">
         <v>270</v>
@@ -9454,7 +9464,7 @@
         <v>284</v>
       </c>
       <c r="CJ1" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="CK1" t="s">
         <v>285</v>
@@ -9546,7 +9556,7 @@
         <v>63</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="I2" t="s">
         <v>308</v>
@@ -9735,10 +9745,10 @@
         <v>368</v>
       </c>
       <c r="BS2" s="8" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="BT2" s="4" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="BU2" s="4" t="s">
         <v>369</v>
@@ -9786,7 +9796,7 @@
         <v>383</v>
       </c>
       <c r="CJ2" s="8" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="CK2" t="s">
         <v>384</v>
@@ -9878,7 +9888,7 @@
         <v>126</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="I3" t="s">
         <v>124</v>
@@ -9890,7 +9900,7 @@
         <v>408</v>
       </c>
       <c r="L3" s="3" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>126</v>
@@ -10067,7 +10077,7 @@
         <v>125</v>
       </c>
       <c r="BS3" s="8" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="BT3" s="4" t="s">
         <v>125</v>
@@ -10118,7 +10128,7 @@
         <v>420</v>
       </c>
       <c r="CJ3" s="8" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="CK3" t="s">
         <v>128</v>
@@ -12173,6 +12183,9 @@
       <c r="BR53">
         <v>25</v>
       </c>
+      <c r="BS53">
+        <v>1</v>
+      </c>
       <c r="BT53" s="4">
         <v>25</v>
       </c>
@@ -12184,6 +12197,9 @@
       </c>
       <c r="BW53" s="4" t="s">
         <v>429</v>
+      </c>
+      <c r="BY53" s="4" t="s">
+        <v>809</v>
       </c>
       <c r="BZ53" t="s">
         <v>509</v>
@@ -12940,13 +12956,13 @@
       <c r="K69" s="9"/>
       <c r="L69" s="9"/>
       <c r="AR69" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="BM69" s="8" t="s">
-        <v>723</v>
+        <v>810</v>
       </c>
       <c r="CS69" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="70" spans="1:110" x14ac:dyDescent="0.25">
@@ -12968,7 +12984,7 @@
         <v>708</v>
       </c>
       <c r="AR70" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AV70" t="s">
         <v>436</v>
@@ -12979,6 +12995,12 @@
       <c r="BB70">
         <v>1</v>
       </c>
+      <c r="BC70">
+        <v>1</v>
+      </c>
+      <c r="BD70">
+        <v>0.3</v>
+      </c>
       <c r="BZ70" s="8" t="s">
         <v>710</v>
       </c>
@@ -12986,7 +13008,7 @@
         <v>711</v>
       </c>
       <c r="CJ70" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="CK70" s="8"/>
       <c r="CW70" t="s">
@@ -13014,7 +13036,7 @@
         <v>708</v>
       </c>
       <c r="AR71" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="AV71" t="s">
         <v>436</v>
@@ -13033,7 +13055,7 @@
       </c>
       <c r="BZ71" s="8"/>
       <c r="CE71" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="CW71" t="s">
         <v>547</v>
@@ -13079,16 +13101,16 @@
     </row>
     <row r="73" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C73" s="8" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="K73" s="3" t="s">
         <v>703</v>
       </c>
       <c r="L73" s="3" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AC73">
         <v>1</v>
@@ -13100,7 +13122,7 @@
       <c r="BT73"/>
       <c r="CJ73" s="3"/>
       <c r="CS73" s="8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
     </row>
     <row r="74" spans="1:110" x14ac:dyDescent="0.25">
@@ -13118,16 +13140,16 @@
     </row>
     <row r="75" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A75" s="8" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="C75" s="8" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="K75" s="3" t="s">
         <v>703</v>
       </c>
       <c r="L75" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AC75">
         <v>1</v>
@@ -13143,7 +13165,7 @@
       </c>
       <c r="CJ75" s="3"/>
       <c r="CS75" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="DB75">
         <v>1</v>
@@ -13169,10 +13191,10 @@
     </row>
     <row r="78" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="I78">
         <v>1</v>
@@ -13187,7 +13209,7 @@
         <v>705</v>
       </c>
       <c r="AR78" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="BB78">
         <v>1</v>
@@ -13201,7 +13223,7 @@
     </row>
     <row r="79" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C79" s="8" t="s">
         <v>684</v>
@@ -13220,7 +13242,7 @@
         <v>708</v>
       </c>
       <c r="AR79" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="BB79">
         <v>99</v>
@@ -13233,13 +13255,13 @@
       <c r="CE79" s="8"/>
       <c r="CJ79" s="3"/>
       <c r="CL79" s="8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="CP79">
         <v>0.02</v>
       </c>
       <c r="CS79" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="DB79">
         <v>1</v>
@@ -13250,7 +13272,7 @@
     </row>
     <row r="80" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C80" s="8" t="s">
         <v>684</v>
@@ -13264,7 +13286,7 @@
         <v>703</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="AC80">
         <v>1</v>
@@ -13281,7 +13303,7 @@
         <v>99</v>
       </c>
       <c r="AV80" s="8" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="AX80">
         <v>1</v>
@@ -13293,16 +13315,16 @@
       <c r="BN80" s="8"/>
       <c r="BP80" s="8"/>
       <c r="CE80" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="CF80" s="8" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="CG80" s="8" t="s">
         <v>689</v>
       </c>
       <c r="CL80" s="8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="CP80">
         <v>6</v>
@@ -13313,7 +13335,7 @@
     </row>
     <row r="81" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C81" s="8" t="s">
         <v>684</v>
@@ -13350,7 +13372,7 @@
       <c r="CE81" s="8"/>
       <c r="CJ81" s="3"/>
       <c r="CL81" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="CP81">
         <v>99999</v>
@@ -13365,7 +13387,7 @@
     </row>
     <row r="82" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C82" s="8" t="s">
         <v>684</v>
@@ -13377,20 +13399,20 @@
         <v>703</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="AC82">
         <v>1</v>
       </c>
       <c r="AG82" s="8"/>
       <c r="AJ82" s="8" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AT82">
         <v>99</v>
       </c>
       <c r="AV82" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AX82">
         <v>99999</v>
@@ -13403,7 +13425,7 @@
       </c>
       <c r="BT82"/>
       <c r="CE82" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="CJ82" s="3"/>
       <c r="CL82" s="8"/>
@@ -13422,7 +13444,7 @@
     </row>
     <row r="84" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A84" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C84" s="8" t="s">
         <v>684</v>
@@ -13431,7 +13453,7 @@
         <v>1</v>
       </c>
       <c r="J84" s="8" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K84" s="3" t="s">
         <v>707</v>
@@ -13447,7 +13469,7 @@
         <v>99</v>
       </c>
       <c r="AV84" s="8" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AX84">
         <v>99999</v>
@@ -13474,7 +13496,7 @@
         <v>707</v>
       </c>
       <c r="CE84" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="CJ84" s="3"/>
       <c r="CL84" s="8"/>
@@ -13490,10 +13512,10 @@
     </row>
     <row r="85" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A85" s="8" t="s">
+        <v>782</v>
+      </c>
+      <c r="C85" s="8" t="s">
         <v>783</v>
-      </c>
-      <c r="C85" s="8" t="s">
-        <v>784</v>
       </c>
       <c r="I85">
         <v>1</v>
@@ -13511,7 +13533,7 @@
         <v>708</v>
       </c>
       <c r="AR85" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="BB85">
         <v>4</v>
@@ -13521,10 +13543,10 @@
       </c>
       <c r="CJ85" s="3"/>
       <c r="CS85" s="8" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="CW85" s="8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
     </row>
     <row r="86" spans="1:110" x14ac:dyDescent="0.25">
@@ -13537,7 +13559,7 @@
     </row>
     <row r="87" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A87" s="8" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="C87" t="s">
         <v>424</v>
@@ -13545,8 +13567,12 @@
       <c r="I87">
         <v>1</v>
       </c>
-      <c r="J87" s="13"/>
-      <c r="K87" s="13"/>
+      <c r="J87" s="18" t="s">
+        <v>787</v>
+      </c>
+      <c r="K87" s="18" t="s">
+        <v>707</v>
+      </c>
       <c r="L87" s="13"/>
       <c r="M87"/>
       <c r="N87"/>
@@ -13574,15 +13600,29 @@
         <v>1</v>
       </c>
       <c r="BN87" s="12" t="s">
-        <v>798</v>
-      </c>
-      <c r="BT87" s="14"/>
-      <c r="BU87" s="14"/>
-      <c r="BV87" s="14"/>
-      <c r="BW87" s="14"/>
+        <v>797</v>
+      </c>
+      <c r="BR87">
+        <v>6</v>
+      </c>
+      <c r="BT87" s="14">
+        <v>1</v>
+      </c>
+      <c r="BU87" s="14">
+        <v>1</v>
+      </c>
+      <c r="BV87" s="14">
+        <v>1</v>
+      </c>
+      <c r="BW87" s="17" t="s">
+        <v>811</v>
+      </c>
       <c r="BX87" s="14"/>
       <c r="BY87" s="14"/>
       <c r="BZ87" s="12"/>
+      <c r="CE87" s="8" t="s">
+        <v>723</v>
+      </c>
       <c r="CH87" s="12"/>
       <c r="CK87" s="12"/>
       <c r="CR87" s="12"/>
@@ -13594,7 +13634,7 @@
     </row>
     <row r="88" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A88" s="8" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C88" t="s">
         <v>424</v>
@@ -13626,7 +13666,7 @@
         <v>1</v>
       </c>
       <c r="AR88" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AV88" s="12" t="s">
         <v>439</v>
@@ -13637,35 +13677,36 @@
       <c r="BB88">
         <v>99</v>
       </c>
+      <c r="BC88">
+        <v>11</v>
+      </c>
+      <c r="BD88">
+        <v>0.5</v>
+      </c>
       <c r="BM88" s="12"/>
       <c r="BN88" s="12" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="BR88">
-        <v>0.5</v>
-      </c>
-      <c r="BT88" s="14">
-        <v>12</v>
-      </c>
-      <c r="BU88" s="14">
-        <v>1</v>
-      </c>
-      <c r="BV88" s="14">
-        <v>12</v>
-      </c>
-      <c r="BW88" s="17" t="s">
-        <v>810</v>
-      </c>
+        <v>5.5</v>
+      </c>
+      <c r="BT88" s="14"/>
+      <c r="BU88" s="14"/>
+      <c r="BV88" s="14"/>
+      <c r="BW88" s="17"/>
       <c r="BX88" s="14"/>
       <c r="BY88" s="14"/>
       <c r="BZ88" s="12"/>
+      <c r="CE88" s="8" t="s">
+        <v>723</v>
+      </c>
       <c r="CH88" s="12"/>
       <c r="CJ88" s="15" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="CK88" s="12"/>
       <c r="CL88" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="CM88">
         <v>-0.8</v>
@@ -13685,7 +13726,7 @@
     </row>
     <row r="89" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A89" s="8" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C89" s="12" t="s">
         <v>424</v>
@@ -13721,7 +13762,7 @@
         <v>440</v>
       </c>
       <c r="AV89" s="12" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AX89">
         <v>9</v>
@@ -13731,6 +13772,15 @@
       </c>
       <c r="BB89">
         <v>1</v>
+      </c>
+      <c r="BC89">
+        <v>11</v>
+      </c>
+      <c r="BD89">
+        <v>0.5</v>
+      </c>
+      <c r="BR89">
+        <v>5.5</v>
       </c>
       <c r="BT89"/>
       <c r="BU89" s="16"/>
@@ -13738,7 +13788,9 @@
       <c r="BW89" s="16"/>
       <c r="BX89" s="16"/>
       <c r="BY89" s="16"/>
-      <c r="CE89" s="12"/>
+      <c r="CE89" s="8" t="s">
+        <v>723</v>
+      </c>
       <c r="CJ89" s="15"/>
       <c r="CL89" s="12"/>
       <c r="DB89">
@@ -13753,7 +13805,7 @@
     </row>
     <row r="90" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A90" s="8" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C90" t="s">
         <v>424</v>
@@ -13765,7 +13817,7 @@
         <v>425</v>
       </c>
       <c r="L90" s="13" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="M90"/>
       <c r="N90"/>
@@ -13787,7 +13839,7 @@
         <v>1</v>
       </c>
       <c r="AR90" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AV90" s="12" t="s">
         <v>439</v>
@@ -13803,7 +13855,7 @@
       </c>
       <c r="BM90" s="12"/>
       <c r="BN90" s="12" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="BT90" s="14"/>
       <c r="BU90" s="14"/>
@@ -13814,11 +13866,11 @@
       <c r="BZ90" s="12"/>
       <c r="CH90" s="12"/>
       <c r="CJ90" s="15" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="CK90" s="12"/>
       <c r="CL90" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="CM90">
         <v>-0.8</v>
@@ -13838,7 +13890,7 @@
     </row>
     <row r="91" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A91" s="8" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C91" t="s">
         <v>424</v>
@@ -13872,7 +13924,7 @@
         <v>1</v>
       </c>
       <c r="AR91" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AV91" s="12" t="s">
         <v>439</v>
@@ -13888,7 +13940,7 @@
       </c>
       <c r="BM91" s="12"/>
       <c r="BN91" s="12" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="BT91" s="14"/>
       <c r="BU91" s="14"/>
@@ -13899,11 +13951,11 @@
       <c r="BZ91" s="12"/>
       <c r="CH91" s="12"/>
       <c r="CJ91" s="15" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="CK91" s="12"/>
       <c r="CL91" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="CM91">
         <v>-0.8</v>
@@ -13926,10 +13978,10 @@
     </row>
     <row r="93" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A93" s="8" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="C93" s="8" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="I93">
         <v>1</v>
@@ -13941,12 +13993,12 @@
         <v>1</v>
       </c>
       <c r="AR93" s="8" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="BT93"/>
       <c r="CJ93" s="3"/>
       <c r="CS93" s="8" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
     </row>
     <row r="94" spans="1:110" x14ac:dyDescent="0.25">
@@ -15529,7 +15581,7 @@
         <v>472</v>
       </c>
       <c r="C4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -15544,7 +15596,7 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
@@ -15552,16 +15604,16 @@
         <v>487</v>
       </c>
       <c r="C5" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="J5" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="K5">
         <v>0.01</v>
       </c>
       <c r="P5" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
@@ -15569,7 +15621,7 @@
         <v>488</v>
       </c>
       <c r="C6" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -15578,7 +15630,7 @@
         <v>0.01</v>
       </c>
       <c r="P6" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
@@ -15586,7 +15638,7 @@
         <v>623</v>
       </c>
       <c r="C7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="J7" t="s">
         <v>623</v>
@@ -15598,15 +15650,15 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>747</v>
+      </c>
+      <c r="C8" t="s">
         <v>748</v>
-      </c>
-      <c r="C8" t="s">
-        <v>749</v>
       </c>
       <c r="J8" t="s">
         <v>624</v>
@@ -15617,21 +15669,21 @@
         <v>601</v>
       </c>
       <c r="C9" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="J9" t="s">
+        <v>752</v>
+      </c>
+      <c r="P9" t="s">
         <v>753</v>
-      </c>
-      <c r="P9" t="s">
-        <v>754</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>764</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>765</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>766</v>
       </c>
     </row>
   </sheetData>
@@ -15776,19 +15828,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>737</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>738</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" t="s">
         <v>739</v>
-      </c>
-      <c r="C4" t="s">
-        <v>740</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2840A6B-FE8C-4EA0-8C79-C89DBF1F27BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9510506D-EE60-47D2-8D09-42E497DD8D9D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="781" uniqueCount="494">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="788" uniqueCount="501">
   <si>
     <t>Id</t>
   </si>
@@ -828,9 +828,6 @@
   </si>
   <si>
     <t>倍率乘以cd</t>
-  </si>
-  <si>
-    <t>伤害基准</t>
   </si>
   <si>
     <t>吸血</t>
@@ -1850,6 +1847,37 @@
   </si>
   <si>
     <t>{"MoveHeight":0,"MaxLinkNum":10,"CanBack":"false","SkillId":"链式弹道索敌"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>受击治疗</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>事件目标替换</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>被击</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>放置降序</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>伤害基准</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>治疗2</t>
+  </si>
+  <si>
+    <t>CCB普攻,受击治疗</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2411,10 +2439,10 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
     </row>
   </sheetData>
@@ -2583,7 +2611,7 @@
         <v>39</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="BA1" t="s">
         <v>40</v>
@@ -2753,7 +2781,7 @@
         <v>93</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="BA2" t="s">
         <v>94</v>
@@ -2795,7 +2823,7 @@
         <v>106</v>
       </c>
       <c r="BN2" s="8" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="BO2" t="s">
         <v>107</v>
@@ -3032,14 +3060,14 @@
     </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="E5" s="1"/>
       <c r="F5" s="8" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G5">
         <v>1</v>
@@ -3081,13 +3109,13 @@
         <v>1</v>
       </c>
       <c r="AG5" s="8" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="AH5" s="8" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>486</v>
+        <v>500</v>
       </c>
       <c r="AK5">
         <v>0</v>
@@ -3105,44 +3133,44 @@
         <v>0.25</v>
       </c>
       <c r="BB5" s="8" t="s">
+        <v>411</v>
+      </c>
+      <c r="BD5" s="8" t="s">
         <v>412</v>
       </c>
-      <c r="BD5" s="8" t="s">
+      <c r="BE5" s="8" t="s">
         <v>413</v>
       </c>
-      <c r="BE5" s="8" t="s">
+      <c r="BF5" s="8" t="s">
         <v>414</v>
       </c>
-      <c r="BF5" s="8" t="s">
+      <c r="BG5" s="8" t="s">
         <v>415</v>
-      </c>
-      <c r="BG5" s="8" t="s">
-        <v>416</v>
       </c>
       <c r="BH5">
         <v>6</v>
       </c>
       <c r="BI5" s="8" t="s">
+        <v>416</v>
+      </c>
+      <c r="BJ5" s="8" t="s">
         <v>417</v>
-      </c>
-      <c r="BJ5" s="8" t="s">
-        <v>418</v>
       </c>
       <c r="BK5" s="5"/>
       <c r="BM5" s="8" t="s">
+        <v>418</v>
+      </c>
+      <c r="BN5" s="8" t="s">
         <v>419</v>
       </c>
-      <c r="BN5" s="8" t="s">
+      <c r="BP5" s="8" t="s">
         <v>420</v>
       </c>
-      <c r="BP5" s="8" t="s">
+      <c r="BQ5" s="8" t="s">
+        <v>420</v>
+      </c>
+      <c r="BR5" s="8" t="s">
         <v>421</v>
-      </c>
-      <c r="BQ5" s="8" t="s">
-        <v>421</v>
-      </c>
-      <c r="BR5" s="8" t="s">
-        <v>422</v>
       </c>
       <c r="BS5">
         <v>1</v>
@@ -3162,19 +3190,19 @@
     </row>
     <row r="8" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="B8" t="s">
         <v>127</v>
       </c>
       <c r="D8" t="s">
+        <v>430</v>
+      </c>
+      <c r="E8" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E8" s="1" t="s">
+      <c r="F8" s="8" t="s">
         <v>432</v>
-      </c>
-      <c r="F8" s="8" t="s">
-        <v>433</v>
       </c>
       <c r="G8">
         <v>1</v>
@@ -3220,13 +3248,13 @@
         <v>-1</v>
       </c>
       <c r="AG8" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AH8" t="s">
         <v>123</v>
       </c>
       <c r="AI8" s="8" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="AK8">
         <v>3</v>
@@ -3253,10 +3281,10 @@
         <v>1</v>
       </c>
       <c r="BB8" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="BD8" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="BE8" t="str">
         <f t="shared" ref="BE8" si="0">"half_"&amp;D8</f>
@@ -3293,19 +3321,19 @@
     </row>
     <row r="9" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="B9" t="s">
         <v>127</v>
       </c>
       <c r="D9" t="s">
+        <v>430</v>
+      </c>
+      <c r="E9" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="E9" s="1" t="s">
+      <c r="F9" s="8" t="s">
         <v>432</v>
-      </c>
-      <c r="F9" s="8" t="s">
-        <v>433</v>
       </c>
       <c r="G9">
         <v>1</v>
@@ -3351,7 +3379,7 @@
         <v>1</v>
       </c>
       <c r="AG9" s="8" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AH9" t="s">
         <v>123</v>
@@ -3382,10 +3410,10 @@
         <v>1</v>
       </c>
       <c r="BB9" s="8" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="BD9" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="BE9" t="str">
         <f t="shared" ref="BE9" si="2">"half_"&amp;D9</f>
@@ -6245,7 +6273,7 @@
     <col min="48" max="48" width="12.6640625" customWidth="1"/>
     <col min="50" max="50" width="7" customWidth="1"/>
     <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="9.75" customWidth="1"/>
+    <col min="52" max="52" width="19.75" customWidth="1"/>
     <col min="53" max="53" width="5.08203125" customWidth="1"/>
     <col min="54" max="54" width="8.5" customWidth="1"/>
     <col min="55" max="55" width="13.5" customWidth="1"/>
@@ -6296,7 +6324,7 @@
         <v>134</v>
       </c>
       <c r="H1" s="8" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="I1" t="s">
         <v>135</v>
@@ -6427,182 +6455,182 @@
       <c r="AY1" t="s">
         <v>176</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="AZ1" s="8" t="s">
+        <v>498</v>
+      </c>
+      <c r="BA1" t="s">
         <v>177</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>178</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>179</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>180</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>181</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>182</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
+        <v>182</v>
+      </c>
+      <c r="BI1" t="s">
         <v>183</v>
       </c>
-      <c r="BH1" t="s">
-        <v>183</v>
-      </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>184</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>185</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>186</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>187</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>188</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>189</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>190</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>191</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>192</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" s="8" t="s">
+        <v>442</v>
+      </c>
+      <c r="BT1" s="4" t="s">
+        <v>445</v>
+      </c>
+      <c r="BU1" s="4" t="s">
         <v>193</v>
       </c>
-      <c r="BS1" s="8" t="s">
-        <v>443</v>
-      </c>
-      <c r="BT1" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="BU1" s="4" t="s">
+      <c r="BV1" s="4" t="s">
         <v>194</v>
       </c>
-      <c r="BV1" s="4" t="s">
+      <c r="BW1" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="BW1" s="4" t="s">
+      <c r="BX1" s="4" t="s">
         <v>196</v>
       </c>
-      <c r="BX1" s="4" t="s">
+      <c r="BY1" s="4" t="s">
         <v>197</v>
       </c>
-      <c r="BY1" s="4" t="s">
+      <c r="BZ1" t="s">
         <v>198</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" s="4" t="s">
         <v>199</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CB1" t="s">
         <v>200</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>201</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>202</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>203</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>204</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>205</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>206</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>207</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" s="8" t="s">
+        <v>447</v>
+      </c>
+      <c r="CK1" t="s">
         <v>208</v>
       </c>
-      <c r="CJ1" s="8" t="s">
-        <v>448</v>
-      </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>209</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>210</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>211</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>212</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
+        <v>192</v>
+      </c>
+      <c r="CQ1" t="s">
         <v>213</v>
       </c>
-      <c r="CP1" t="s">
-        <v>193</v>
-      </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>214</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>215</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>216</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>217</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>218</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>219</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
+        <v>218</v>
+      </c>
+      <c r="CY1" t="s">
         <v>220</v>
       </c>
-      <c r="CX1" t="s">
-        <v>219</v>
-      </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>221</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>222</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>223</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>224</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>225</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>226</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>227</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>228</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>229</v>
       </c>
     </row>
     <row r="2" spans="1:111" x14ac:dyDescent="0.25">
@@ -6616,325 +6644,325 @@
         <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>229</v>
+      </c>
+      <c r="F2" t="s">
         <v>230</v>
-      </c>
-      <c r="F2" t="s">
-        <v>231</v>
       </c>
       <c r="G2" t="s">
         <v>51</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="I2" t="s">
+        <v>231</v>
+      </c>
+      <c r="J2" t="s">
         <v>232</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>237</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>238</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>239</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>245</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>246</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" t="s">
         <v>247</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>248</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AB2" t="s">
         <v>250</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>251</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>252</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>253</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>254</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>255</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>256</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>257</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>258</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>259</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>260</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>261</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>262</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>263</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>264</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>265</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>266</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>267</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>268</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>269</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>270</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>271</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>272</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>273</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>274</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>275</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>276</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>277</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>278</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>279</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>280</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>281</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>282</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>283</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>284</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>285</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>286</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>287</v>
       </c>
       <c r="BM2" t="s">
         <v>77</v>
       </c>
       <c r="BN2" t="s">
+        <v>287</v>
+      </c>
+      <c r="BO2" t="s">
         <v>288</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BP2" t="s">
         <v>289</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>290</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>291</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" s="8" t="s">
+        <v>443</v>
+      </c>
+      <c r="BT2" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="BU2" s="4" t="s">
         <v>292</v>
       </c>
-      <c r="BS2" s="8" t="s">
-        <v>444</v>
-      </c>
-      <c r="BT2" s="4" t="s">
-        <v>447</v>
-      </c>
-      <c r="BU2" s="4" t="s">
+      <c r="BV2" s="4" t="s">
         <v>293</v>
       </c>
-      <c r="BV2" s="4" t="s">
+      <c r="BW2" s="4" t="s">
         <v>294</v>
       </c>
-      <c r="BW2" s="4" t="s">
+      <c r="BX2" s="4" t="s">
         <v>295</v>
       </c>
-      <c r="BX2" s="4" t="s">
+      <c r="BY2" s="4" t="s">
         <v>296</v>
       </c>
-      <c r="BY2" s="4" t="s">
+      <c r="BZ2" t="s">
         <v>297</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>298</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>299</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>300</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>301</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>302</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>303</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>304</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>305</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>306</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" s="8" t="s">
+        <v>448</v>
+      </c>
+      <c r="CK2" t="s">
         <v>307</v>
       </c>
-      <c r="CJ2" s="8" t="s">
-        <v>449</v>
-      </c>
-      <c r="CK2" t="s">
+      <c r="CL2" t="s">
         <v>308</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CM2" t="s">
         <v>309</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>310</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>311</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>312</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>313</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>314</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>315</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>316</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>317</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>318</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>319</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>320</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>321</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>322</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>323</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>324</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>325</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>326</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>327</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>328</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>329</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>330</v>
       </c>
     </row>
     <row r="3" spans="1:111" x14ac:dyDescent="0.25">
@@ -6957,19 +6985,19 @@
         <v>114</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I3" t="s">
         <v>112</v>
       </c>
       <c r="J3" t="s">
+        <v>330</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>331</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>332</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>114</v>
@@ -7032,7 +7060,7 @@
         <v>112</v>
       </c>
       <c r="AG3" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="AH3" t="s">
         <v>112</v>
@@ -7056,16 +7084,16 @@
         <v>112</v>
       </c>
       <c r="AO3" t="s">
+        <v>333</v>
+      </c>
+      <c r="AP3" t="s">
         <v>334</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>335</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="AS3" t="s">
         <v>112</v>
@@ -7077,7 +7105,7 @@
         <v>112</v>
       </c>
       <c r="AV3" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="AW3" t="s">
         <v>112</v>
@@ -7107,7 +7135,7 @@
         <v>112</v>
       </c>
       <c r="BF3" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="BG3" t="s">
         <v>112</v>
@@ -7134,10 +7162,10 @@
         <v>115</v>
       </c>
       <c r="BO3" t="s">
+        <v>337</v>
+      </c>
+      <c r="BP3" t="s">
         <v>338</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>339</v>
       </c>
       <c r="BQ3" t="s">
         <v>113</v>
@@ -7146,7 +7174,7 @@
         <v>113</v>
       </c>
       <c r="BS3" s="8" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="BT3" s="4" t="s">
         <v>113</v>
@@ -7158,19 +7186,19 @@
         <v>114</v>
       </c>
       <c r="BW3" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BX3" s="4" t="s">
         <v>112</v>
       </c>
       <c r="BY3" s="4" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="BZ3" t="s">
         <v>120</v>
       </c>
       <c r="CA3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="CB3" t="s">
         <v>120</v>
@@ -7182,22 +7210,22 @@
         <v>120</v>
       </c>
       <c r="CE3" t="s">
+        <v>341</v>
+      </c>
+      <c r="CF3" t="s">
         <v>342</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>343</v>
       </c>
       <c r="CG3" t="s">
         <v>2</v>
       </c>
       <c r="CH3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="CI3" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="CJ3" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="CK3" t="s">
         <v>116</v>
@@ -7215,7 +7243,7 @@
         <v>119</v>
       </c>
       <c r="CP3" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="CQ3" t="s">
         <v>119</v>
@@ -7227,28 +7255,28 @@
         <v>121</v>
       </c>
       <c r="CT3" t="s">
+        <v>344</v>
+      </c>
+      <c r="CU3" t="s">
         <v>345</v>
       </c>
-      <c r="CU3" t="s">
-        <v>346</v>
-      </c>
       <c r="CV3" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="CW3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="CX3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="CY3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="CZ3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="DA3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="DB3" t="s">
         <v>112</v>
@@ -7271,7 +7299,7 @@
     </row>
     <row r="4" spans="1:111" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
     </row>
     <row r="5" spans="1:111" x14ac:dyDescent="0.25">
@@ -7284,13 +7312,13 @@
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="C6" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="K6" s="9" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="O6" s="9"/>
       <c r="P6"/>
@@ -7298,13 +7326,13 @@
         <v>2</v>
       </c>
       <c r="AO6" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AR6" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AV6" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="AX6">
         <v>1</v>
@@ -7313,31 +7341,31 @@
         <v>1</v>
       </c>
       <c r="BZ6" s="8" t="s">
+        <v>426</v>
+      </c>
+      <c r="CE6" s="8" t="s">
         <v>427</v>
       </c>
-      <c r="CE6" s="8" t="s">
-        <v>428</v>
-      </c>
       <c r="CF6" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="CG6" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="CJ6" s="8" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="CK6" s="8"/>
       <c r="CW6" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="C7" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="J7" s="8"/>
       <c r="O7"/>
@@ -7348,7 +7376,7 @@
         <v>1</v>
       </c>
       <c r="AO7" s="8" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="AT7">
         <v>2.5</v>
@@ -7357,13 +7385,49 @@
       <c r="CE7" s="8"/>
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
-      <c r="A8" s="8"/>
-      <c r="C8" s="8"/>
-      <c r="K8" s="9"/>
-      <c r="L8" s="9"/>
+      <c r="A8" s="8" t="s">
+        <v>493</v>
+      </c>
+      <c r="C8" s="8" t="s">
+        <v>494</v>
+      </c>
+      <c r="K8" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L8" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="AC8">
+        <v>1</v>
+      </c>
+      <c r="AF8">
+        <v>1</v>
+      </c>
       <c r="AG8" s="8"/>
+      <c r="AO8" s="8" t="s">
+        <v>496</v>
+      </c>
+      <c r="AV8" s="8" t="s">
+        <v>497</v>
+      </c>
+      <c r="AW8">
+        <v>1</v>
+      </c>
+      <c r="AX8">
+        <v>500</v>
+      </c>
+      <c r="AZ8">
+        <v>2</v>
+      </c>
+      <c r="BB8">
+        <v>1</v>
+      </c>
+      <c r="CE8" s="8"/>
       <c r="CL8" s="8"/>
       <c r="CM8" s="8"/>
+      <c r="CW8" t="s">
+        <v>499</v>
+      </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A9" s="8"/>
@@ -7380,16 +7444,16 @@
     </row>
     <row r="10" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="C10" s="8" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="K10" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L10" s="3" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="AC10">
         <v>1</v>
@@ -7398,14 +7462,14 @@
         <v>1</v>
       </c>
       <c r="AG10" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="BB10">
         <v>1</v>
       </c>
       <c r="CJ10" s="3"/>
       <c r="CS10" s="8" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="DB10">
         <v>1</v>
@@ -7419,32 +7483,32 @@
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="C11" s="8" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I11">
         <v>1</v>
       </c>
       <c r="J11" s="8" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K11" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AC11">
         <v>1</v>
       </c>
       <c r="AG11" s="8" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="AJ11" s="8"/>
       <c r="AT11">
         <v>99</v>
       </c>
       <c r="AV11" s="8" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AX11">
         <v>99999</v>
@@ -7468,10 +7532,10 @@
         <v>1</v>
       </c>
       <c r="BW11" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="CE11" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="CJ11" s="3"/>
       <c r="CL11" s="8"/>
@@ -7487,28 +7551,28 @@
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>458</v>
+      </c>
+      <c r="C12" s="8" t="s">
         <v>459</v>
-      </c>
-      <c r="C12" s="8" t="s">
-        <v>460</v>
       </c>
       <c r="I12">
         <v>1</v>
       </c>
       <c r="K12" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="L12" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC12">
         <v>2</v>
       </c>
       <c r="AO12" s="8" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AR12" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="BB12">
         <v>4</v>
@@ -7518,10 +7582,10 @@
       </c>
       <c r="CJ12" s="3"/>
       <c r="CS12" s="8" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="CW12" s="8" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
@@ -7534,19 +7598,19 @@
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="C14" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I14">
         <v>1</v>
       </c>
       <c r="J14" s="18" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="K14" s="18" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L14" s="13"/>
       <c r="M14"/>
@@ -7575,7 +7639,7 @@
         <v>1</v>
       </c>
       <c r="BN14" s="12" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="BR14">
         <v>6</v>
@@ -7590,13 +7654,13 @@
         <v>1</v>
       </c>
       <c r="BW14" s="17" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="BX14" s="14"/>
       <c r="BY14" s="14"/>
       <c r="BZ14" s="12"/>
       <c r="CE14" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="CH14" s="12"/>
       <c r="CK14" s="12"/>
@@ -7609,16 +7673,16 @@
     </row>
     <row r="15" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="C15" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I15">
         <v>1</v>
       </c>
       <c r="K15" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L15" s="13"/>
       <c r="M15"/>
@@ -7641,10 +7705,10 @@
         <v>1</v>
       </c>
       <c r="AR15" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AV15" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AX15">
         <v>1</v>
@@ -7660,7 +7724,7 @@
       </c>
       <c r="BM15" s="12"/>
       <c r="BN15" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="BR15">
         <v>5.5</v>
@@ -7673,15 +7737,15 @@
       <c r="BY15" s="14"/>
       <c r="BZ15" s="12"/>
       <c r="CE15" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="CH15" s="12"/>
       <c r="CJ15" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="CK15" s="12"/>
       <c r="CL15" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="CM15">
         <v>-0.8</v>
@@ -7693,7 +7757,7 @@
       <c r="CU15" s="12"/>
       <c r="CV15" s="12"/>
       <c r="CW15" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="DF15">
         <v>1</v>
@@ -7701,17 +7765,17 @@
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="C16" s="12" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I16">
         <v>1</v>
       </c>
       <c r="J16" s="12"/>
       <c r="K16" s="15" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L16" s="15"/>
       <c r="M16" s="15"/>
@@ -7730,14 +7794,14 @@
         <v>1</v>
       </c>
       <c r="AG16" s="12" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="AJ16" s="12"/>
       <c r="AR16" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="AV16" s="12" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="AX16">
         <v>9</v>
@@ -7764,7 +7828,7 @@
       <c r="BX16" s="16"/>
       <c r="BY16" s="16"/>
       <c r="CE16" s="8" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="CJ16" s="15"/>
       <c r="CL16" s="12"/>
@@ -7780,19 +7844,19 @@
     </row>
     <row r="17" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="C17" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I17">
         <v>1</v>
       </c>
       <c r="K17" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L17" s="13" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="M17"/>
       <c r="N17"/>
@@ -7814,10 +7878,10 @@
         <v>1</v>
       </c>
       <c r="AR17" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AV17" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AX17">
         <v>1</v>
@@ -7830,7 +7894,7 @@
       </c>
       <c r="BM17" s="12"/>
       <c r="BN17" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="BT17" s="14"/>
       <c r="BU17" s="14"/>
@@ -7841,11 +7905,11 @@
       <c r="BZ17" s="12"/>
       <c r="CH17" s="12"/>
       <c r="CJ17" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="CK17" s="12"/>
       <c r="CL17" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="CM17">
         <v>-0.8</v>
@@ -7857,7 +7921,7 @@
       <c r="CU17" s="12"/>
       <c r="CV17" s="12"/>
       <c r="CW17" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="DF17">
         <v>1</v>
@@ -7865,19 +7929,19 @@
     </row>
     <row r="18" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="C18" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="I18">
         <v>1</v>
       </c>
       <c r="K18" s="13" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="L18" s="13" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="M18"/>
       <c r="N18"/>
@@ -7899,10 +7963,10 @@
         <v>1</v>
       </c>
       <c r="AR18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="AV18" s="12" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="AX18">
         <v>1</v>
@@ -7915,7 +7979,7 @@
       </c>
       <c r="BM18" s="12"/>
       <c r="BN18" s="12" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="BT18" s="14"/>
       <c r="BU18" s="14"/>
@@ -7926,11 +7990,11 @@
       <c r="BZ18" s="12"/>
       <c r="CH18" s="12"/>
       <c r="CJ18" s="15" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="CK18" s="12"/>
       <c r="CL18" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="CM18">
         <v>-0.8</v>
@@ -7942,7 +8006,7 @@
       <c r="CU18" s="12"/>
       <c r="CV18" s="12"/>
       <c r="CW18" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="DF18">
         <v>1</v>
@@ -7953,27 +8017,27 @@
     </row>
     <row r="20" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="C20" s="8" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="I20">
         <v>1</v>
       </c>
       <c r="K20" s="3" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="AC20">
         <v>1</v>
       </c>
       <c r="AR20" s="8" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="BT20"/>
       <c r="CJ20" s="3"/>
       <c r="CS20" s="8" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
     </row>
     <row r="21" spans="1:110" x14ac:dyDescent="0.25">
@@ -9427,34 +9491,34 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
+        <v>356</v>
+      </c>
+      <c r="F1" t="s">
         <v>357</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>358</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>359</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>360</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>361</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>362</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>363</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>364</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>365</v>
-      </c>
-      <c r="O1" t="s">
-        <v>366</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -9468,40 +9532,40 @@
         <v>75</v>
       </c>
       <c r="E2" t="s">
+        <v>366</v>
+      </c>
+      <c r="F2" t="s">
         <v>367</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>368</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>369</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>370</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>371</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>372</v>
-      </c>
-      <c r="K2" t="s">
-        <v>373</v>
       </c>
       <c r="L2" t="s">
         <v>51</v>
       </c>
       <c r="M2" t="s">
+        <v>373</v>
+      </c>
+      <c r="N2" t="s">
         <v>374</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>375</v>
       </c>
-      <c r="O2" t="s">
-        <v>376</v>
-      </c>
       <c r="P2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -9530,13 +9594,13 @@
         <v>112</v>
       </c>
       <c r="J3" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="K3" t="s">
         <v>113</v>
       </c>
       <c r="L3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="M3" t="s">
         <v>112</v>
@@ -9545,7 +9609,7 @@
         <v>112</v>
       </c>
       <c r="O3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="P3" t="s">
         <v>121</v>
@@ -9577,7 +9641,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9588,10 +9652,10 @@
         <v>46</v>
       </c>
       <c r="C2" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9602,7 +9666,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="D3" t="s">
         <v>121</v>
@@ -9637,22 +9701,22 @@
         <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E2" t="s">
         <v>70</v>
       </c>
       <c r="F2" t="s">
+        <v>379</v>
+      </c>
+      <c r="G2" t="s">
         <v>380</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>381</v>
       </c>
-      <c r="H2" t="s">
-        <v>382</v>
-      </c>
       <c r="I2" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -9681,24 +9745,24 @@
         <v>114</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C4" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
     </row>
   </sheetData>
@@ -9725,34 +9789,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>382</v>
+      </c>
+      <c r="C1" t="s">
         <v>383</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>384</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>385</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>386</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>387</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>388</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>389</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>390</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>391</v>
-      </c>
-      <c r="L1" t="s">
-        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -9760,34 +9824,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>392</v>
+      </c>
+      <c r="C2" t="s">
         <v>393</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>394</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>395</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>396</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>397</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>398</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>399</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>400</v>
       </c>
-      <c r="J2" t="s">
-        <v>401</v>
-      </c>
       <c r="K2" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="L2" t="s">
         <v>94</v>
@@ -9804,7 +9868,7 @@
         <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -9858,28 +9922,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="C2" t="s">
         <v>75</v>
       </c>
       <c r="D2" t="s">
+        <v>402</v>
+      </c>
+      <c r="E2" t="s">
         <v>403</v>
-      </c>
-      <c r="E2" t="s">
-        <v>404</v>
       </c>
       <c r="F2" t="s">
         <v>77</v>
       </c>
       <c r="G2" t="s">
+        <v>404</v>
+      </c>
+      <c r="H2" t="s">
+        <v>257</v>
+      </c>
+      <c r="I2" t="s">
         <v>405</v>
-      </c>
-      <c r="H2" t="s">
-        <v>258</v>
-      </c>
-      <c r="I2" t="s">
-        <v>406</v>
       </c>
       <c r="J2" t="s">
         <v>52</v>
@@ -9908,7 +9972,7 @@
         <v>114</v>
       </c>
       <c r="H3" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="I3" t="s">
         <v>114</v>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{42C3D0A5-2231-4B77-8250-919F33AF3B40}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6DD850-D562-4C36-AA9C-DBE2B3301640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -297,7 +297,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1510" uniqueCount="784">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="783">
   <si>
     <t>Id</t>
   </si>
@@ -699,9 +699,6 @@
   </si>
   <si>
     <t>System.Collections.Generic.Dictionary&lt;string,object&gt;</t>
-  </si>
-  <si>
-    <t>不要删！</t>
   </si>
   <si>
     <t>Hip</t>
@@ -3294,7 +3291,7 @@
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
@@ -3307,7 +3304,7 @@
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
     </row>
     <row r="7" spans="1:2" x14ac:dyDescent="0.25">
@@ -3336,7 +3333,7 @@
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -3373,7 +3370,7 @@
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -3394,7 +3391,7 @@
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
@@ -3415,10 +3412,10 @@
     </row>
     <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
     </row>
   </sheetData>
@@ -3587,7 +3584,7 @@
         <v>51</v>
       </c>
       <c r="AZ1" s="8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="BA1" t="s">
         <v>52</v>
@@ -3757,7 +3754,7 @@
         <v>105</v>
       </c>
       <c r="AZ2" s="8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="BA2" t="s">
         <v>106</v>
@@ -3799,7 +3796,7 @@
         <v>118</v>
       </c>
       <c r="BN2" s="8" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="BO2" t="s">
         <v>119</v>
@@ -4023,26 +4020,15 @@
         <v>125</v>
       </c>
     </row>
-    <row r="4" spans="1:71" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>0</v>
-      </c>
-      <c r="D4" t="s">
-        <v>134</v>
-      </c>
-      <c r="K4">
-        <v>1</v>
-      </c>
-    </row>
     <row r="5" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D5" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="E5">
         <v>502</v>
@@ -4103,10 +4089,10 @@
         <v>4</v>
       </c>
       <c r="AH5" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI5" s="8" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AN5">
         <v>1</v>
@@ -4121,10 +4107,10 @@
         <v>0.25</v>
       </c>
       <c r="BB5" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC5" t="s">
         <v>143</v>
-      </c>
-      <c r="BC5" t="s">
-        <v>144</v>
       </c>
       <c r="BD5" t="str">
         <f t="shared" ref="BD5" si="1">"icon_"&amp;D5</f>
@@ -4139,34 +4125,34 @@
         <v>nblade</v>
       </c>
       <c r="BG5" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH5">
         <v>2</v>
       </c>
       <c r="BI5" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ5" t="s">
+        <v>144</v>
+      </c>
+      <c r="BK5" t="s">
         <v>145</v>
       </c>
-      <c r="BK5" t="s">
+      <c r="BL5" t="s">
         <v>146</v>
       </c>
-      <c r="BL5" t="s">
-        <v>147</v>
-      </c>
       <c r="BM5" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN5" t="s">
         <v>136</v>
       </c>
-      <c r="BN5" t="s">
+      <c r="BP5" t="s">
         <v>137</v>
       </c>
-      <c r="BP5" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ5" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS5">
         <v>1</v>
@@ -4177,10 +4163,10 @@
         <v>5</v>
       </c>
       <c r="B7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D7" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="E7">
         <v>123</v>
@@ -4241,13 +4227,13 @@
         <v>5</v>
       </c>
       <c r="AH7" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI7" t="s">
+        <v>149</v>
+      </c>
+      <c r="AJ7" t="s">
         <v>150</v>
-      </c>
-      <c r="AJ7" t="s">
-        <v>151</v>
       </c>
       <c r="AN7">
         <v>1</v>
@@ -4262,10 +4248,10 @@
         <v>0.25</v>
       </c>
       <c r="BB7" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC7" t="s">
         <v>143</v>
-      </c>
-      <c r="BC7" t="s">
-        <v>144</v>
       </c>
       <c r="BD7" t="str">
         <f t="shared" ref="BD7:BD9" si="5">"icon_"&amp;D7</f>
@@ -4280,34 +4266,34 @@
         <v>fang</v>
       </c>
       <c r="BG7" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH7">
         <v>3</v>
       </c>
       <c r="BI7" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ7" t="s">
+        <v>151</v>
+      </c>
+      <c r="BK7" t="s">
+        <v>145</v>
+      </c>
+      <c r="BL7" t="s">
         <v>152</v>
       </c>
-      <c r="BK7" t="s">
-        <v>146</v>
-      </c>
-      <c r="BL7" t="s">
-        <v>153</v>
-      </c>
       <c r="BM7" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN7" t="s">
         <v>136</v>
       </c>
-      <c r="BN7" t="s">
+      <c r="BP7" t="s">
         <v>137</v>
       </c>
-      <c r="BP7" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ7" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS7">
         <v>1</v>
@@ -4318,10 +4304,10 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="E8">
         <v>240</v>
@@ -4382,13 +4368,13 @@
         <v>6</v>
       </c>
       <c r="AH8" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI8" t="s">
+        <v>154</v>
+      </c>
+      <c r="AJ8" t="s">
         <v>155</v>
-      </c>
-      <c r="AJ8" t="s">
-        <v>156</v>
       </c>
       <c r="AN8">
         <v>1</v>
@@ -4403,10 +4389,10 @@
         <v>0.25</v>
       </c>
       <c r="BB8" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC8" t="s">
         <v>143</v>
-      </c>
-      <c r="BC8" t="s">
-        <v>144</v>
       </c>
       <c r="BD8" t="str">
         <f t="shared" si="5"/>
@@ -4421,34 +4407,34 @@
         <v>wyvern</v>
       </c>
       <c r="BG8" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH8">
         <v>3</v>
       </c>
       <c r="BI8" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BK8" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BL8" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BM8" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN8" t="s">
         <v>136</v>
       </c>
-      <c r="BN8" t="s">
+      <c r="BP8" t="s">
         <v>137</v>
       </c>
-      <c r="BP8" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ8" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS8">
         <v>1</v>
@@ -4459,10 +4445,10 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D9" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="E9">
         <v>192</v>
@@ -4523,13 +4509,13 @@
         <v>7</v>
       </c>
       <c r="AH9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI9" t="s">
+        <v>158</v>
+      </c>
+      <c r="AJ9" t="s">
         <v>159</v>
-      </c>
-      <c r="AJ9" t="s">
-        <v>160</v>
       </c>
       <c r="AN9">
         <v>1</v>
@@ -4544,10 +4530,10 @@
         <v>0.25</v>
       </c>
       <c r="BB9" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BC9" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BD9" t="str">
         <f t="shared" si="5"/>
@@ -4562,34 +4548,34 @@
         <v>falco</v>
       </c>
       <c r="BG9" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH9">
         <v>3</v>
       </c>
       <c r="BI9" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ9" t="s">
+        <v>161</v>
+      </c>
+      <c r="BK9" t="s">
         <v>162</v>
       </c>
-      <c r="BK9" t="s">
-        <v>163</v>
-      </c>
       <c r="BL9" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="BM9" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN9" t="s">
         <v>136</v>
       </c>
-      <c r="BN9" t="s">
+      <c r="BP9" t="s">
         <v>137</v>
       </c>
-      <c r="BP9" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ9" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS9">
         <v>1</v>
@@ -4600,10 +4586,10 @@
         <v>8</v>
       </c>
       <c r="B11" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D11" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="E11">
         <v>198</v>
@@ -4664,13 +4650,13 @@
         <v>8</v>
       </c>
       <c r="AH11" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI11" t="s">
+        <v>164</v>
+      </c>
+      <c r="AJ11" t="s">
         <v>165</v>
-      </c>
-      <c r="AJ11" t="s">
-        <v>166</v>
       </c>
       <c r="AN11">
         <v>1</v>
@@ -4685,10 +4671,10 @@
         <v>0.25</v>
       </c>
       <c r="BB11" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC11" t="s">
         <v>143</v>
-      </c>
-      <c r="BC11" t="s">
-        <v>144</v>
       </c>
       <c r="BD11" t="str">
         <f t="shared" ref="BD11" si="9">"icon_"&amp;D11</f>
@@ -4703,34 +4689,34 @@
         <v>blackd</v>
       </c>
       <c r="BG11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH11">
         <v>4</v>
       </c>
       <c r="BI11" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ11" t="s">
+        <v>166</v>
+      </c>
+      <c r="BK11" t="s">
+        <v>145</v>
+      </c>
+      <c r="BL11" t="s">
         <v>167</v>
       </c>
-      <c r="BK11" t="s">
-        <v>146</v>
-      </c>
-      <c r="BL11" t="s">
-        <v>168</v>
-      </c>
       <c r="BM11" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN11" t="s">
         <v>136</v>
       </c>
-      <c r="BN11" t="s">
+      <c r="BP11" t="s">
         <v>137</v>
       </c>
-      <c r="BP11" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ11" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS11">
         <v>1</v>
@@ -4741,10 +4727,10 @@
         <v>9</v>
       </c>
       <c r="B12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D12" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E12">
         <v>149</v>
@@ -4805,13 +4791,13 @@
         <v>9</v>
       </c>
       <c r="AH12" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI12" t="s">
+        <v>169</v>
+      </c>
+      <c r="AJ12" t="s">
         <v>170</v>
-      </c>
-      <c r="AJ12" t="s">
-        <v>171</v>
       </c>
       <c r="AN12">
         <v>1</v>
@@ -4826,10 +4812,10 @@
         <v>0.25</v>
       </c>
       <c r="BB12" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC12" t="s">
         <v>143</v>
-      </c>
-      <c r="BC12" t="s">
-        <v>144</v>
       </c>
       <c r="BD12" t="str">
         <f t="shared" ref="BD12" si="13">"icon_"&amp;D12</f>
@@ -4844,34 +4830,34 @@
         <v>scave</v>
       </c>
       <c r="BG12" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH12">
         <v>4</v>
       </c>
       <c r="BI12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ12" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="BK12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BL12" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="BM12" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN12" t="s">
         <v>136</v>
       </c>
-      <c r="BN12" t="s">
+      <c r="BP12" t="s">
         <v>137</v>
       </c>
-      <c r="BP12" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS12">
         <v>1</v>
@@ -4882,10 +4868,10 @@
         <v>10</v>
       </c>
       <c r="B13" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D13" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="E13">
         <v>290</v>
@@ -4946,13 +4932,13 @@
         <v>10</v>
       </c>
       <c r="AH13" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI13" t="s">
+        <v>173</v>
+      </c>
+      <c r="AJ13" t="s">
         <v>174</v>
-      </c>
-      <c r="AJ13" t="s">
-        <v>175</v>
       </c>
       <c r="AN13">
         <v>1</v>
@@ -4967,10 +4953,10 @@
         <v>0.25</v>
       </c>
       <c r="BB13" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BC13" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BD13" t="str">
         <f t="shared" ref="BD13" si="17">"icon_"&amp;D13</f>
@@ -4985,34 +4971,34 @@
         <v>vigna</v>
       </c>
       <c r="BG13" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH13">
         <v>4</v>
       </c>
       <c r="BI13" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ13" t="s">
+        <v>161</v>
+      </c>
+      <c r="BK13" t="s">
         <v>162</v>
       </c>
-      <c r="BK13" t="s">
-        <v>163</v>
-      </c>
       <c r="BL13" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="BM13" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN13" t="s">
         <v>136</v>
       </c>
-      <c r="BN13" t="s">
+      <c r="BP13" t="s">
         <v>137</v>
       </c>
-      <c r="BP13" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ13" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS13">
         <v>1</v>
@@ -5023,10 +5009,10 @@
         <v>11</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D14" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="E14">
         <v>151</v>
@@ -5087,13 +5073,13 @@
         <v>11</v>
       </c>
       <c r="AH14" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI14" t="s">
+        <v>177</v>
+      </c>
+      <c r="AJ14" t="s">
         <v>178</v>
-      </c>
-      <c r="AJ14" t="s">
-        <v>179</v>
       </c>
       <c r="AN14">
         <v>1</v>
@@ -5108,10 +5094,10 @@
         <v>0.25</v>
       </c>
       <c r="BB14" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BC14" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="BD14" t="str">
         <f t="shared" ref="BD14" si="21">"icon_"&amp;D14</f>
@@ -5126,34 +5112,34 @@
         <v>myrtle</v>
       </c>
       <c r="BG14" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH14">
         <v>4</v>
       </c>
       <c r="BI14" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ14" t="s">
+        <v>180</v>
+      </c>
+      <c r="BK14" t="s">
         <v>181</v>
       </c>
-      <c r="BK14" t="s">
+      <c r="BL14" t="s">
         <v>182</v>
       </c>
-      <c r="BL14" t="s">
-        <v>183</v>
-      </c>
       <c r="BM14" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN14" t="s">
         <v>136</v>
       </c>
-      <c r="BN14" t="s">
+      <c r="BP14" t="s">
         <v>137</v>
       </c>
-      <c r="BP14" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ14" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS14">
         <v>1.1000000000000001</v>
@@ -5164,10 +5150,10 @@
         <v>12</v>
       </c>
       <c r="B16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D16" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E16">
         <v>115</v>
@@ -5228,13 +5214,13 @@
         <v>12</v>
       </c>
       <c r="AH16" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI16" t="s">
+        <v>184</v>
+      </c>
+      <c r="AJ16" t="s">
         <v>185</v>
-      </c>
-      <c r="AJ16" t="s">
-        <v>186</v>
       </c>
       <c r="AN16">
         <v>1</v>
@@ -5249,10 +5235,10 @@
         <v>0.25</v>
       </c>
       <c r="BB16" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC16" t="s">
         <v>143</v>
-      </c>
-      <c r="BC16" t="s">
-        <v>144</v>
       </c>
       <c r="BD16" t="str">
         <f t="shared" ref="BD16" si="25">"icon_"&amp;D16</f>
@@ -5267,34 +5253,34 @@
         <v>headbr</v>
       </c>
       <c r="BG16" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH16">
         <v>5</v>
       </c>
       <c r="BI16" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ16" t="s">
+        <v>186</v>
+      </c>
+      <c r="BK16" t="s">
+        <v>145</v>
+      </c>
+      <c r="BL16" t="s">
         <v>187</v>
       </c>
-      <c r="BK16" t="s">
-        <v>146</v>
-      </c>
-      <c r="BL16" t="s">
-        <v>188</v>
-      </c>
       <c r="BM16" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN16" t="s">
         <v>136</v>
       </c>
-      <c r="BN16" t="s">
+      <c r="BP16" t="s">
         <v>137</v>
       </c>
-      <c r="BP16" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ16" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS16">
         <v>1</v>
@@ -5305,10 +5291,10 @@
         <v>13</v>
       </c>
       <c r="B17" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D17" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="E17">
         <v>102</v>
@@ -5369,13 +5355,13 @@
         <v>13</v>
       </c>
       <c r="AH17" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI17" t="s">
+        <v>189</v>
+      </c>
+      <c r="AJ17" t="s">
         <v>190</v>
-      </c>
-      <c r="AJ17" t="s">
-        <v>191</v>
       </c>
       <c r="AN17">
         <v>1</v>
@@ -5390,10 +5376,10 @@
         <v>0.25</v>
       </c>
       <c r="BB17" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC17" t="s">
         <v>143</v>
-      </c>
-      <c r="BC17" t="s">
-        <v>144</v>
       </c>
       <c r="BD17" t="str">
         <f t="shared" ref="BD17" si="29">"icon_"&amp;D17</f>
@@ -5408,37 +5394,37 @@
         <v>texas</v>
       </c>
       <c r="BG17" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH17">
         <v>5</v>
       </c>
       <c r="BI17" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ17" t="s">
+        <v>191</v>
+      </c>
+      <c r="BK17" t="s">
+        <v>145</v>
+      </c>
+      <c r="BL17" t="s">
         <v>192</v>
       </c>
-      <c r="BK17" t="s">
-        <v>146</v>
-      </c>
-      <c r="BL17" t="s">
+      <c r="BM17" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN17" t="s">
+        <v>136</v>
+      </c>
+      <c r="BP17" t="s">
+        <v>137</v>
+      </c>
+      <c r="BQ17" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR17" t="s">
         <v>193</v>
-      </c>
-      <c r="BM17" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN17" t="s">
-        <v>137</v>
-      </c>
-      <c r="BP17" t="s">
-        <v>138</v>
-      </c>
-      <c r="BQ17" t="s">
-        <v>138</v>
-      </c>
-      <c r="BR17" t="s">
-        <v>194</v>
       </c>
       <c r="BS17">
         <v>1.05</v>
@@ -5449,13 +5435,13 @@
         <v>14</v>
       </c>
       <c r="B19" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D19" t="s">
+        <v>194</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>195</v>
-      </c>
-      <c r="E19" s="1" t="s">
-        <v>196</v>
       </c>
       <c r="F19" t="str">
         <f t="shared" ref="F19" si="32">"char_"&amp;E19&amp;"_"&amp;D19</f>
@@ -5516,13 +5502,13 @@
         <v>14</v>
       </c>
       <c r="AH19" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI19" t="s">
+        <v>196</v>
+      </c>
+      <c r="AJ19" t="s">
         <v>197</v>
-      </c>
-      <c r="AJ19" t="s">
-        <v>198</v>
       </c>
       <c r="AN19">
         <v>1</v>
@@ -5537,10 +5523,10 @@
         <v>0.25</v>
       </c>
       <c r="BB19" t="s">
+        <v>142</v>
+      </c>
+      <c r="BC19" t="s">
         <v>143</v>
-      </c>
-      <c r="BC19" t="s">
-        <v>144</v>
       </c>
       <c r="BD19" t="str">
         <f t="shared" ref="BD19" si="33">"icon_"&amp;D19</f>
@@ -5555,37 +5541,37 @@
         <v>siege</v>
       </c>
       <c r="BG19" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH19">
         <v>6</v>
       </c>
       <c r="BI19" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ19" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="BK19" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="BL19" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="BM19" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN19" t="s">
         <v>136</v>
       </c>
-      <c r="BN19" t="s">
+      <c r="BP19" t="s">
         <v>137</v>
       </c>
-      <c r="BP19" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BR19" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="BS19">
         <v>1</v>
@@ -5596,13 +5582,13 @@
         <v>15</v>
       </c>
       <c r="B20" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="D20" t="s">
+        <v>200</v>
+      </c>
+      <c r="E20" s="1" t="s">
         <v>201</v>
-      </c>
-      <c r="E20" s="1" t="s">
-        <v>202</v>
       </c>
       <c r="F20" t="str">
         <f t="shared" ref="F20" si="36">"char_"&amp;E20&amp;"_"&amp;D20</f>
@@ -5657,13 +5643,13 @@
         <v>15</v>
       </c>
       <c r="AH20" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI20" t="s">
+        <v>202</v>
+      </c>
+      <c r="AJ20" t="s">
         <v>203</v>
-      </c>
-      <c r="AJ20" t="s">
-        <v>204</v>
       </c>
       <c r="AN20">
         <v>1</v>
@@ -5678,10 +5664,10 @@
         <v>0.25</v>
       </c>
       <c r="BB20" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BC20" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="BD20" t="str">
         <f t="shared" ref="BD20" si="37">"icon_"&amp;D20</f>
@@ -5696,34 +5682,34 @@
         <v>bpipe</v>
       </c>
       <c r="BG20" s="8" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="BH20">
         <v>6</v>
       </c>
       <c r="BI20" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BJ20" t="s">
+        <v>161</v>
+      </c>
+      <c r="BK20" t="s">
         <v>162</v>
       </c>
-      <c r="BK20" t="s">
-        <v>163</v>
-      </c>
       <c r="BL20" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="BM20" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN20" t="s">
         <v>136</v>
       </c>
-      <c r="BN20" t="s">
+      <c r="BP20" t="s">
         <v>137</v>
       </c>
-      <c r="BP20" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ20" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS20">
         <v>2</v>
@@ -5735,14 +5721,14 @@
     </row>
     <row r="22" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A22" s="8" t="s">
+        <v>685</v>
+      </c>
+      <c r="B22" s="8" t="s">
         <v>686</v>
-      </c>
-      <c r="B22" s="8" t="s">
-        <v>687</v>
       </c>
       <c r="E22" s="1"/>
       <c r="F22" s="8" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G22">
         <v>1</v>
@@ -5784,13 +5770,13 @@
         <v>1</v>
       </c>
       <c r="AG22" s="8" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AH22" s="8" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AI22" s="8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="AK22">
         <v>0</v>
@@ -5811,44 +5797,44 @@
         <v>0.25</v>
       </c>
       <c r="BB22" s="8" t="s">
+        <v>689</v>
+      </c>
+      <c r="BD22" s="8" t="s">
         <v>690</v>
       </c>
-      <c r="BD22" s="8" t="s">
+      <c r="BE22" s="8" t="s">
         <v>691</v>
       </c>
-      <c r="BE22" s="8" t="s">
+      <c r="BF22" s="8" t="s">
         <v>692</v>
       </c>
-      <c r="BF22" s="8" t="s">
+      <c r="BG22" s="8" t="s">
         <v>693</v>
-      </c>
-      <c r="BG22" s="8" t="s">
-        <v>694</v>
       </c>
       <c r="BH22">
         <v>6</v>
       </c>
       <c r="BI22" s="8" t="s">
+        <v>694</v>
+      </c>
+      <c r="BJ22" s="8" t="s">
         <v>695</v>
-      </c>
-      <c r="BJ22" s="8" t="s">
-        <v>696</v>
       </c>
       <c r="BK22" s="5"/>
       <c r="BM22" s="8" t="s">
+        <v>696</v>
+      </c>
+      <c r="BN22" s="8" t="s">
         <v>697</v>
       </c>
-      <c r="BN22" s="8" t="s">
+      <c r="BP22" s="8" t="s">
         <v>698</v>
       </c>
-      <c r="BP22" s="8" t="s">
+      <c r="BQ22" s="8" t="s">
+        <v>698</v>
+      </c>
+      <c r="BR22" s="8" t="s">
         <v>699</v>
-      </c>
-      <c r="BQ22" s="8" t="s">
-        <v>699</v>
-      </c>
-      <c r="BR22" s="8" t="s">
-        <v>700</v>
       </c>
       <c r="BS22">
         <v>1</v>
@@ -5859,19 +5845,19 @@
     </row>
     <row r="24" spans="1:71" x14ac:dyDescent="0.25">
       <c r="A24" s="8" t="s">
+        <v>723</v>
+      </c>
+      <c r="B24" t="s">
+        <v>138</v>
+      </c>
+      <c r="D24" t="s">
         <v>724</v>
       </c>
-      <c r="B24" t="s">
-        <v>139</v>
-      </c>
-      <c r="D24" t="s">
+      <c r="E24" s="1" t="s">
         <v>725</v>
       </c>
-      <c r="E24" s="1" t="s">
+      <c r="F24" s="8" t="s">
         <v>726</v>
-      </c>
-      <c r="F24" s="8" t="s">
-        <v>727</v>
       </c>
       <c r="G24">
         <v>0.01</v>
@@ -5920,13 +5906,13 @@
         <v>-1</v>
       </c>
       <c r="AG24" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AH24" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="AI24" s="8" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AK24">
         <v>3</v>
@@ -5953,10 +5939,10 @@
         <v>1</v>
       </c>
       <c r="BB24" s="8" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="BD24" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="BE24" t="str">
         <f t="shared" ref="BE24" si="40">"half_"&amp;D24</f>
@@ -5967,25 +5953,25 @@
         <v>otter</v>
       </c>
       <c r="BG24" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="BH24">
         <v>5</v>
       </c>
       <c r="BI24" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="BM24" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN24" t="s">
         <v>136</v>
       </c>
-      <c r="BN24" t="s">
+      <c r="BP24" t="s">
         <v>137</v>
       </c>
-      <c r="BP24" t="s">
-        <v>138</v>
-      </c>
       <c r="BQ24" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="BS24">
         <v>1</v>
@@ -8870,328 +8856,328 @@
   <sheetData>
     <row r="1" spans="1:111" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
+        <v>205</v>
+      </c>
+      <c r="D1" t="s">
         <v>206</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>207</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>208</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>209</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" s="8" t="s">
+        <v>772</v>
+      </c>
+      <c r="I1" t="s">
         <v>210</v>
       </c>
-      <c r="H1" s="8" t="s">
-        <v>773</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>211</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" s="3" t="s">
         <v>212</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="L1" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="M1" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="N1" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="O1" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="P1" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="Q1" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="R1" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="R1" s="3" t="s">
+      <c r="S1" s="3" t="s">
         <v>220</v>
       </c>
-      <c r="S1" s="3" t="s">
+      <c r="T1" s="3" t="s">
         <v>221</v>
       </c>
-      <c r="T1" s="3" t="s">
+      <c r="U1" s="3" t="s">
+        <v>221</v>
+      </c>
+      <c r="V1" s="3" t="s">
         <v>222</v>
       </c>
-      <c r="U1" s="3" t="s">
-        <v>222</v>
-      </c>
-      <c r="V1" s="3" t="s">
+      <c r="W1" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="W1" s="3" t="s">
+      <c r="X1" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="X1" s="3" t="s">
+      <c r="Y1" t="s">
         <v>225</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>226</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="AA1" s="3" t="s">
+      <c r="AB1" t="s">
         <v>228</v>
       </c>
-      <c r="AB1" t="s">
+      <c r="AC1" t="s">
         <v>229</v>
       </c>
-      <c r="AC1" t="s">
+      <c r="AD1" t="s">
         <v>230</v>
       </c>
-      <c r="AD1" t="s">
+      <c r="AE1" t="s">
         <v>231</v>
       </c>
-      <c r="AE1" t="s">
+      <c r="AF1" t="s">
         <v>232</v>
       </c>
-      <c r="AF1" t="s">
+      <c r="AG1" t="s">
         <v>233</v>
       </c>
-      <c r="AG1" t="s">
+      <c r="AH1" t="s">
         <v>234</v>
       </c>
-      <c r="AH1" t="s">
+      <c r="AI1" t="s">
         <v>235</v>
       </c>
-      <c r="AI1" t="s">
+      <c r="AJ1" t="s">
         <v>236</v>
       </c>
-      <c r="AJ1" t="s">
+      <c r="AK1" t="s">
         <v>237</v>
       </c>
-      <c r="AK1" t="s">
+      <c r="AL1" t="s">
         <v>238</v>
       </c>
-      <c r="AL1" t="s">
+      <c r="AM1" t="s">
         <v>239</v>
       </c>
-      <c r="AM1" t="s">
+      <c r="AN1" t="s">
         <v>240</v>
       </c>
-      <c r="AN1" t="s">
+      <c r="AO1" t="s">
         <v>241</v>
       </c>
-      <c r="AO1" t="s">
+      <c r="AP1" t="s">
         <v>242</v>
       </c>
-      <c r="AP1" t="s">
+      <c r="AQ1" t="s">
         <v>243</v>
       </c>
-      <c r="AQ1" t="s">
+      <c r="AR1" t="s">
         <v>244</v>
       </c>
-      <c r="AR1" t="s">
+      <c r="AS1" t="s">
         <v>245</v>
       </c>
-      <c r="AS1" t="s">
+      <c r="AT1" t="s">
         <v>246</v>
       </c>
-      <c r="AT1" t="s">
+      <c r="AU1" t="s">
         <v>247</v>
       </c>
-      <c r="AU1" t="s">
+      <c r="AV1" t="s">
         <v>248</v>
       </c>
-      <c r="AV1" t="s">
+      <c r="AW1" t="s">
         <v>249</v>
       </c>
-      <c r="AW1" t="s">
+      <c r="AX1" t="s">
         <v>250</v>
       </c>
-      <c r="AX1" t="s">
+      <c r="AY1" t="s">
         <v>251</v>
       </c>
-      <c r="AY1" t="s">
+      <c r="AZ1" t="s">
         <v>252</v>
       </c>
-      <c r="AZ1" t="s">
+      <c r="BA1" t="s">
         <v>253</v>
       </c>
-      <c r="BA1" t="s">
+      <c r="BB1" t="s">
         <v>254</v>
       </c>
-      <c r="BB1" t="s">
+      <c r="BC1" t="s">
         <v>255</v>
       </c>
-      <c r="BC1" t="s">
+      <c r="BD1" t="s">
         <v>256</v>
       </c>
-      <c r="BD1" t="s">
+      <c r="BE1" t="s">
         <v>257</v>
       </c>
-      <c r="BE1" t="s">
+      <c r="BF1" t="s">
         <v>258</v>
       </c>
-      <c r="BF1" t="s">
+      <c r="BH1" t="s">
+        <v>258</v>
+      </c>
+      <c r="BI1" t="s">
         <v>259</v>
       </c>
-      <c r="BH1" t="s">
-        <v>259</v>
-      </c>
-      <c r="BI1" t="s">
+      <c r="BJ1" t="s">
         <v>260</v>
       </c>
-      <c r="BJ1" t="s">
+      <c r="BK1" t="s">
         <v>261</v>
       </c>
-      <c r="BK1" t="s">
+      <c r="BL1" t="s">
         <v>262</v>
       </c>
-      <c r="BL1" t="s">
+      <c r="BM1" t="s">
         <v>263</v>
       </c>
-      <c r="BM1" t="s">
+      <c r="BN1" t="s">
         <v>264</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>265</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>266</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>267</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>268</v>
       </c>
-      <c r="BR1" t="s">
+      <c r="BS1" s="8" t="s">
+        <v>764</v>
+      </c>
+      <c r="BT1" s="4" t="s">
+        <v>767</v>
+      </c>
+      <c r="BU1" s="4" t="s">
         <v>269</v>
       </c>
-      <c r="BS1" s="8" t="s">
-        <v>765</v>
-      </c>
-      <c r="BT1" s="4" t="s">
-        <v>768</v>
-      </c>
-      <c r="BU1" s="4" t="s">
+      <c r="BV1" s="4" t="s">
         <v>270</v>
       </c>
-      <c r="BV1" s="4" t="s">
+      <c r="BW1" s="4" t="s">
         <v>271</v>
       </c>
-      <c r="BW1" s="4" t="s">
+      <c r="BX1" s="4" t="s">
         <v>272</v>
       </c>
-      <c r="BX1" s="4" t="s">
+      <c r="BY1" s="4" t="s">
         <v>273</v>
       </c>
-      <c r="BY1" s="4" t="s">
+      <c r="BZ1" t="s">
         <v>274</v>
       </c>
-      <c r="BZ1" t="s">
+      <c r="CA1" s="4" t="s">
         <v>275</v>
       </c>
-      <c r="CA1" s="4" t="s">
+      <c r="CB1" t="s">
         <v>276</v>
       </c>
-      <c r="CB1" t="s">
+      <c r="CC1" t="s">
         <v>277</v>
       </c>
-      <c r="CC1" t="s">
+      <c r="CD1" t="s">
         <v>278</v>
       </c>
-      <c r="CD1" t="s">
+      <c r="CE1" t="s">
         <v>279</v>
       </c>
-      <c r="CE1" t="s">
+      <c r="CF1" t="s">
         <v>280</v>
       </c>
-      <c r="CF1" t="s">
+      <c r="CG1" t="s">
         <v>281</v>
       </c>
-      <c r="CG1" t="s">
+      <c r="CH1" t="s">
         <v>282</v>
       </c>
-      <c r="CH1" t="s">
+      <c r="CI1" t="s">
         <v>283</v>
       </c>
-      <c r="CI1" t="s">
+      <c r="CJ1" s="8" t="s">
+        <v>769</v>
+      </c>
+      <c r="CK1" t="s">
         <v>284</v>
       </c>
-      <c r="CJ1" s="8" t="s">
-        <v>770</v>
-      </c>
-      <c r="CK1" t="s">
+      <c r="CL1" t="s">
         <v>285</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>286</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>287</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>288</v>
       </c>
-      <c r="CO1" t="s">
+      <c r="CP1" t="s">
+        <v>268</v>
+      </c>
+      <c r="CQ1" t="s">
         <v>289</v>
       </c>
-      <c r="CP1" t="s">
-        <v>269</v>
-      </c>
-      <c r="CQ1" t="s">
+      <c r="CR1" t="s">
         <v>290</v>
       </c>
-      <c r="CR1" t="s">
+      <c r="CS1" t="s">
         <v>291</v>
       </c>
-      <c r="CS1" t="s">
+      <c r="CT1" t="s">
         <v>292</v>
       </c>
-      <c r="CT1" t="s">
+      <c r="CU1" t="s">
         <v>293</v>
       </c>
-      <c r="CU1" t="s">
+      <c r="CV1" t="s">
         <v>294</v>
       </c>
-      <c r="CV1" t="s">
+      <c r="CW1" t="s">
         <v>295</v>
       </c>
-      <c r="CW1" t="s">
+      <c r="CX1" t="s">
+        <v>294</v>
+      </c>
+      <c r="CY1" t="s">
         <v>296</v>
       </c>
-      <c r="CX1" t="s">
-        <v>295</v>
-      </c>
-      <c r="CY1" t="s">
+      <c r="CZ1" t="s">
         <v>297</v>
       </c>
-      <c r="CZ1" t="s">
+      <c r="DA1" t="s">
         <v>298</v>
       </c>
-      <c r="DA1" t="s">
+      <c r="DB1" t="s">
         <v>299</v>
       </c>
-      <c r="DB1" t="s">
+      <c r="DC1" t="s">
         <v>300</v>
       </c>
-      <c r="DC1" t="s">
+      <c r="DD1" t="s">
         <v>301</v>
       </c>
-      <c r="DD1" t="s">
+      <c r="DE1" t="s">
         <v>302</v>
       </c>
-      <c r="DE1" t="s">
+      <c r="DF1" t="s">
         <v>303</v>
       </c>
-      <c r="DF1" t="s">
+      <c r="DG1" t="s">
         <v>304</v>
-      </c>
-      <c r="DG1" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="2" spans="1:111" x14ac:dyDescent="0.25">
@@ -9205,325 +9191,325 @@
         <v>87</v>
       </c>
       <c r="E2" t="s">
+        <v>305</v>
+      </c>
+      <c r="F2" t="s">
         <v>306</v>
-      </c>
-      <c r="F2" t="s">
-        <v>307</v>
       </c>
       <c r="G2" t="s">
         <v>63</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="I2" t="s">
+        <v>307</v>
+      </c>
+      <c r="J2" t="s">
         <v>308</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" s="3" t="s">
         <v>309</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>310</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>311</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>312</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>313</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>314</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>315</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>316</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>317</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>318</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>319</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>320</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>321</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>322</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" t="s">
         <v>323</v>
       </c>
-      <c r="Y2" t="s">
+      <c r="Z2" t="s">
         <v>324</v>
       </c>
-      <c r="Z2" t="s">
+      <c r="AA2" s="3" t="s">
         <v>325</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AB2" t="s">
         <v>326</v>
       </c>
-      <c r="AB2" t="s">
+      <c r="AC2" t="s">
         <v>327</v>
       </c>
-      <c r="AC2" t="s">
+      <c r="AD2" t="s">
         <v>328</v>
       </c>
-      <c r="AD2" t="s">
+      <c r="AE2" t="s">
         <v>329</v>
       </c>
-      <c r="AE2" t="s">
+      <c r="AF2" t="s">
         <v>330</v>
       </c>
-      <c r="AF2" t="s">
+      <c r="AG2" t="s">
         <v>331</v>
       </c>
-      <c r="AG2" t="s">
+      <c r="AH2" t="s">
         <v>332</v>
       </c>
-      <c r="AH2" t="s">
+      <c r="AI2" t="s">
         <v>333</v>
       </c>
-      <c r="AI2" t="s">
+      <c r="AJ2" t="s">
         <v>334</v>
       </c>
-      <c r="AJ2" t="s">
+      <c r="AK2" t="s">
         <v>335</v>
       </c>
-      <c r="AK2" t="s">
+      <c r="AL2" t="s">
         <v>336</v>
       </c>
-      <c r="AL2" t="s">
+      <c r="AM2" t="s">
         <v>337</v>
       </c>
-      <c r="AM2" t="s">
+      <c r="AN2" t="s">
         <v>338</v>
       </c>
-      <c r="AN2" t="s">
+      <c r="AO2" t="s">
         <v>339</v>
       </c>
-      <c r="AO2" t="s">
+      <c r="AP2" t="s">
         <v>340</v>
       </c>
-      <c r="AP2" t="s">
+      <c r="AQ2" t="s">
         <v>341</v>
       </c>
-      <c r="AQ2" t="s">
+      <c r="AR2" t="s">
         <v>342</v>
       </c>
-      <c r="AR2" t="s">
+      <c r="AS2" t="s">
         <v>343</v>
       </c>
-      <c r="AS2" t="s">
+      <c r="AT2" t="s">
         <v>344</v>
       </c>
-      <c r="AT2" t="s">
+      <c r="AU2" t="s">
         <v>345</v>
       </c>
-      <c r="AU2" t="s">
+      <c r="AV2" t="s">
         <v>346</v>
       </c>
-      <c r="AV2" t="s">
+      <c r="AW2" t="s">
         <v>347</v>
       </c>
-      <c r="AW2" t="s">
+      <c r="AX2" t="s">
         <v>348</v>
       </c>
-      <c r="AX2" t="s">
+      <c r="AY2" t="s">
         <v>349</v>
       </c>
-      <c r="AY2" t="s">
+      <c r="AZ2" t="s">
         <v>350</v>
       </c>
-      <c r="AZ2" t="s">
+      <c r="BA2" t="s">
         <v>351</v>
       </c>
-      <c r="BA2" t="s">
+      <c r="BB2" t="s">
         <v>352</v>
       </c>
-      <c r="BB2" t="s">
+      <c r="BC2" t="s">
         <v>353</v>
       </c>
-      <c r="BC2" t="s">
+      <c r="BD2" t="s">
         <v>354</v>
       </c>
-      <c r="BD2" t="s">
+      <c r="BE2" t="s">
         <v>355</v>
       </c>
-      <c r="BE2" t="s">
+      <c r="BF2" t="s">
         <v>356</v>
       </c>
-      <c r="BF2" t="s">
+      <c r="BG2" t="s">
         <v>357</v>
       </c>
-      <c r="BG2" t="s">
+      <c r="BH2" t="s">
         <v>358</v>
       </c>
-      <c r="BH2" t="s">
+      <c r="BI2" t="s">
         <v>359</v>
       </c>
-      <c r="BI2" t="s">
+      <c r="BJ2" t="s">
         <v>360</v>
       </c>
-      <c r="BJ2" t="s">
+      <c r="BK2" t="s">
         <v>361</v>
       </c>
-      <c r="BK2" t="s">
+      <c r="BL2" t="s">
         <v>362</v>
-      </c>
-      <c r="BL2" t="s">
-        <v>363</v>
       </c>
       <c r="BM2" t="s">
         <v>89</v>
       </c>
       <c r="BN2" t="s">
+        <v>363</v>
+      </c>
+      <c r="BO2" t="s">
         <v>364</v>
       </c>
-      <c r="BO2" t="s">
+      <c r="BP2" t="s">
         <v>365</v>
       </c>
-      <c r="BP2" t="s">
+      <c r="BQ2" t="s">
         <v>366</v>
       </c>
-      <c r="BQ2" t="s">
+      <c r="BR2" t="s">
         <v>367</v>
       </c>
-      <c r="BR2" t="s">
+      <c r="BS2" s="8" t="s">
+        <v>765</v>
+      </c>
+      <c r="BT2" s="4" t="s">
+        <v>768</v>
+      </c>
+      <c r="BU2" s="4" t="s">
         <v>368</v>
       </c>
-      <c r="BS2" s="8" t="s">
-        <v>766</v>
-      </c>
-      <c r="BT2" s="4" t="s">
-        <v>769</v>
-      </c>
-      <c r="BU2" s="4" t="s">
+      <c r="BV2" s="4" t="s">
         <v>369</v>
       </c>
-      <c r="BV2" s="4" t="s">
+      <c r="BW2" s="4" t="s">
         <v>370</v>
       </c>
-      <c r="BW2" s="4" t="s">
+      <c r="BX2" s="4" t="s">
         <v>371</v>
       </c>
-      <c r="BX2" s="4" t="s">
+      <c r="BY2" s="4" t="s">
         <v>372</v>
       </c>
-      <c r="BY2" s="4" t="s">
+      <c r="BZ2" t="s">
         <v>373</v>
       </c>
-      <c r="BZ2" t="s">
+      <c r="CA2" t="s">
         <v>374</v>
       </c>
-      <c r="CA2" t="s">
+      <c r="CB2" t="s">
         <v>375</v>
       </c>
-      <c r="CB2" t="s">
+      <c r="CC2" t="s">
         <v>376</v>
       </c>
-      <c r="CC2" t="s">
+      <c r="CD2" t="s">
         <v>377</v>
       </c>
-      <c r="CD2" t="s">
+      <c r="CE2" t="s">
         <v>378</v>
       </c>
-      <c r="CE2" t="s">
+      <c r="CF2" t="s">
         <v>379</v>
       </c>
-      <c r="CF2" t="s">
+      <c r="CG2" t="s">
         <v>380</v>
       </c>
-      <c r="CG2" t="s">
+      <c r="CH2" t="s">
         <v>381</v>
       </c>
-      <c r="CH2" t="s">
+      <c r="CI2" t="s">
         <v>382</v>
       </c>
-      <c r="CI2" t="s">
+      <c r="CJ2" s="8" t="s">
+        <v>770</v>
+      </c>
+      <c r="CK2" t="s">
         <v>383</v>
       </c>
-      <c r="CJ2" s="8" t="s">
-        <v>771</v>
-      </c>
-      <c r="CK2" t="s">
+      <c r="CL2" t="s">
         <v>384</v>
       </c>
-      <c r="CL2" t="s">
+      <c r="CM2" t="s">
         <v>385</v>
       </c>
-      <c r="CM2" t="s">
+      <c r="CN2" t="s">
         <v>386</v>
       </c>
-      <c r="CN2" t="s">
+      <c r="CO2" t="s">
         <v>387</v>
       </c>
-      <c r="CO2" t="s">
+      <c r="CP2" t="s">
         <v>388</v>
       </c>
-      <c r="CP2" t="s">
+      <c r="CQ2" t="s">
         <v>389</v>
       </c>
-      <c r="CQ2" t="s">
+      <c r="CR2" t="s">
         <v>390</v>
       </c>
-      <c r="CR2" t="s">
+      <c r="CS2" t="s">
         <v>391</v>
       </c>
-      <c r="CS2" t="s">
+      <c r="CT2" t="s">
         <v>392</v>
       </c>
-      <c r="CT2" t="s">
+      <c r="CU2" t="s">
         <v>393</v>
       </c>
-      <c r="CU2" t="s">
+      <c r="CV2" t="s">
         <v>394</v>
       </c>
-      <c r="CV2" t="s">
+      <c r="CW2" t="s">
         <v>395</v>
       </c>
-      <c r="CW2" t="s">
+      <c r="CX2" t="s">
         <v>396</v>
       </c>
-      <c r="CX2" t="s">
+      <c r="CY2" t="s">
         <v>397</v>
       </c>
-      <c r="CY2" t="s">
+      <c r="CZ2" t="s">
         <v>398</v>
       </c>
-      <c r="CZ2" t="s">
+      <c r="DA2" t="s">
         <v>399</v>
       </c>
-      <c r="DA2" t="s">
+      <c r="DB2" t="s">
         <v>400</v>
       </c>
-      <c r="DB2" t="s">
+      <c r="DC2" t="s">
         <v>401</v>
       </c>
-      <c r="DC2" t="s">
+      <c r="DD2" t="s">
         <v>402</v>
       </c>
-      <c r="DD2" t="s">
+      <c r="DE2" t="s">
         <v>403</v>
       </c>
-      <c r="DE2" t="s">
+      <c r="DF2" t="s">
         <v>404</v>
       </c>
-      <c r="DF2" t="s">
+      <c r="DG2" t="s">
         <v>405</v>
-      </c>
-      <c r="DG2" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="3" spans="1:111" x14ac:dyDescent="0.25">
@@ -9546,19 +9532,19 @@
         <v>126</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="I3" t="s">
         <v>124</v>
       </c>
       <c r="J3" t="s">
+        <v>406</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>407</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>408</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="M3" s="3" t="s">
         <v>126</v>
@@ -9621,7 +9607,7 @@
         <v>124</v>
       </c>
       <c r="AG3" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="AH3" t="s">
         <v>124</v>
@@ -9645,16 +9631,16 @@
         <v>124</v>
       </c>
       <c r="AO3" t="s">
+        <v>409</v>
+      </c>
+      <c r="AP3" t="s">
         <v>410</v>
-      </c>
-      <c r="AP3" t="s">
-        <v>411</v>
       </c>
       <c r="AQ3" t="s">
         <v>2</v>
       </c>
       <c r="AR3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AS3" t="s">
         <v>124</v>
@@ -9666,7 +9652,7 @@
         <v>124</v>
       </c>
       <c r="AV3" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AW3" t="s">
         <v>124</v>
@@ -9696,7 +9682,7 @@
         <v>124</v>
       </c>
       <c r="BF3" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="BG3" t="s">
         <v>124</v>
@@ -9723,10 +9709,10 @@
         <v>127</v>
       </c>
       <c r="BO3" t="s">
+        <v>413</v>
+      </c>
+      <c r="BP3" t="s">
         <v>414</v>
-      </c>
-      <c r="BP3" t="s">
-        <v>415</v>
       </c>
       <c r="BQ3" t="s">
         <v>125</v>
@@ -9735,7 +9721,7 @@
         <v>125</v>
       </c>
       <c r="BS3" s="8" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="BT3" s="4" t="s">
         <v>125</v>
@@ -9747,19 +9733,19 @@
         <v>126</v>
       </c>
       <c r="BW3" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="BX3" s="4" t="s">
         <v>124</v>
       </c>
       <c r="BY3" s="4" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="BZ3" t="s">
         <v>132</v>
       </c>
       <c r="CA3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="CB3" t="s">
         <v>132</v>
@@ -9771,22 +9757,22 @@
         <v>132</v>
       </c>
       <c r="CE3" t="s">
+        <v>417</v>
+      </c>
+      <c r="CF3" t="s">
         <v>418</v>
-      </c>
-      <c r="CF3" t="s">
-        <v>419</v>
       </c>
       <c r="CG3" t="s">
         <v>2</v>
       </c>
       <c r="CH3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="CI3" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="CJ3" s="8" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="CK3" t="s">
         <v>128</v>
@@ -9804,7 +9790,7 @@
         <v>131</v>
       </c>
       <c r="CP3" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="CQ3" t="s">
         <v>131</v>
@@ -9816,28 +9802,28 @@
         <v>133</v>
       </c>
       <c r="CT3" t="s">
+        <v>420</v>
+      </c>
+      <c r="CU3" t="s">
         <v>421</v>
       </c>
-      <c r="CU3" t="s">
-        <v>422</v>
-      </c>
       <c r="CV3" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="CW3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CX3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CY3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="CZ3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="DA3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="DB3" t="s">
         <v>124</v>
@@ -9860,27 +9846,27 @@
     </row>
     <row r="4" spans="1:111" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
     </row>
     <row r="5" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A5" s="8" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C5" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC5">
         <v>2</v>
       </c>
       <c r="AO5" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR5" t="s">
         <v>434</v>
       </c>
-      <c r="AR5" t="s">
+      <c r="AV5" t="s">
         <v>435</v>
-      </c>
-      <c r="AV5" t="s">
-        <v>436</v>
       </c>
       <c r="AX5">
         <v>1</v>
@@ -9893,10 +9879,10 @@
         <v>67</v>
       </c>
       <c r="CE5" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CW5" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
     </row>
     <row r="6" spans="1:111" x14ac:dyDescent="0.25">
@@ -9920,22 +9906,22 @@
     </row>
     <row r="7" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C7" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC7">
         <v>2</v>
       </c>
       <c r="AO7" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR7" t="s">
         <v>434</v>
       </c>
-      <c r="AR7" t="s">
+      <c r="AV7" t="s">
         <v>435</v>
-      </c>
-      <c r="AV7" t="s">
-        <v>436</v>
       </c>
       <c r="AX7">
         <v>1</v>
@@ -9947,30 +9933,30 @@
         <v>67</v>
       </c>
       <c r="CE7" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="8" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C8" t="s">
+        <v>453</v>
+      </c>
+      <c r="D8" t="s">
         <v>454</v>
       </c>
-      <c r="D8" t="s">
+      <c r="E8" t="s">
         <v>455</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>456</v>
       </c>
-      <c r="F8" t="s">
-        <v>457</v>
-      </c>
       <c r="J8" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="W8" s="3">
         <v>1</v>
@@ -9997,30 +9983,30 @@
         <v>1</v>
       </c>
       <c r="BW8" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CV8" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="9" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="C9" t="s">
+        <v>423</v>
+      </c>
+      <c r="K9" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K9" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L9" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AC9">
         <v>1</v>
       </c>
       <c r="AG9" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AW9" s="3"/>
       <c r="BB9">
@@ -10042,7 +10028,7 @@
       <c r="CI9" s="3"/>
       <c r="CK9" s="3"/>
       <c r="CL9" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="CM9">
         <v>-2</v>
@@ -10071,22 +10057,22 @@
     </row>
     <row r="11" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="C11" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC11">
         <v>2</v>
       </c>
       <c r="AO11" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR11" t="s">
         <v>434</v>
       </c>
-      <c r="AR11" t="s">
+      <c r="AV11" t="s">
         <v>435</v>
-      </c>
-      <c r="AV11" t="s">
-        <v>436</v>
       </c>
       <c r="AX11">
         <v>1</v>
@@ -10098,21 +10084,21 @@
         <v>67</v>
       </c>
       <c r="CE11" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
     </row>
     <row r="12" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
+        <v>461</v>
+      </c>
+      <c r="C12" t="s">
+        <v>453</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L12" s="3" t="s">
         <v>462</v>
-      </c>
-      <c r="C12" t="s">
-        <v>454</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>463</v>
       </c>
       <c r="AC12">
         <v>1</v>
@@ -10126,25 +10112,25 @@
     </row>
     <row r="13" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="C13" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D13" t="s">
+        <v>449</v>
+      </c>
+      <c r="E13" t="s">
         <v>450</v>
       </c>
-      <c r="E13" t="s">
-        <v>451</v>
-      </c>
       <c r="F13" t="s">
+        <v>444</v>
+      </c>
+      <c r="J13" t="s">
         <v>445</v>
       </c>
-      <c r="J13" t="s">
-        <v>446</v>
-      </c>
       <c r="K13" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AC13">
         <v>1</v>
@@ -10154,7 +10140,7 @@
         <v>1</v>
       </c>
       <c r="BN13" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="BR13">
         <v>25</v>
@@ -10169,7 +10155,7 @@
         <v>1</v>
       </c>
       <c r="BW13" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ13" s="3"/>
       <c r="CA13" s="3"/>
@@ -10182,7 +10168,7 @@
       <c r="CI13" s="3"/>
       <c r="CK13" s="3"/>
       <c r="CL13" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="CM13">
         <v>0.25</v>
@@ -10193,16 +10179,16 @@
     </row>
     <row r="14" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="C14" t="s">
+        <v>423</v>
+      </c>
+      <c r="K14" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K14" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L14" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC14">
         <v>1</v>
@@ -10227,7 +10213,7 @@
       <c r="CI14" s="3"/>
       <c r="CK14" s="3"/>
       <c r="CL14" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="CM14">
         <v>25</v>
@@ -10257,22 +10243,22 @@
     </row>
     <row r="16" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="C16" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC16">
         <v>2</v>
       </c>
       <c r="AO16" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR16" t="s">
         <v>434</v>
       </c>
-      <c r="AR16" t="s">
+      <c r="AV16" t="s">
         <v>435</v>
-      </c>
-      <c r="AV16" t="s">
-        <v>436</v>
       </c>
       <c r="AX16">
         <v>1</v>
@@ -10284,31 +10270,31 @@
         <v>67</v>
       </c>
       <c r="CE16" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CJ16" s="3"/>
     </row>
     <row r="17" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C17" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D17" t="s">
+        <v>465</v>
+      </c>
+      <c r="E17" t="s">
         <v>466</v>
       </c>
-      <c r="E17" t="s">
+      <c r="F17" t="s">
         <v>467</v>
       </c>
-      <c r="F17" t="s">
-        <v>468</v>
-      </c>
       <c r="J17" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K17" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AC17">
         <v>1</v>
@@ -10318,7 +10304,7 @@
         <v>1</v>
       </c>
       <c r="BN17" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="BR17">
         <v>10</v>
@@ -10333,7 +10319,7 @@
         <v>1</v>
       </c>
       <c r="BW17" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ17" s="3"/>
       <c r="CA17" s="3"/>
@@ -10346,7 +10332,7 @@
       <c r="CI17" s="3"/>
       <c r="CK17" s="3"/>
       <c r="CL17" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="CM17">
         <v>0.35</v>
@@ -10357,22 +10343,22 @@
     </row>
     <row r="18" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="C18" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E18" s="5"/>
       <c r="G18" s="5"/>
       <c r="I18" s="5"/>
       <c r="K18" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="AC18">
         <v>1</v>
       </c>
       <c r="AG18" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BB18">
         <v>1</v>
@@ -10382,27 +10368,27 @@
       </c>
       <c r="BT18"/>
       <c r="CV18" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="19" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="C19" t="s">
+        <v>423</v>
+      </c>
+      <c r="K19" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K19" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L19" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AC19">
         <v>1</v>
       </c>
       <c r="AG19" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AH19">
         <v>1</v>
@@ -10429,7 +10415,7 @@
       <c r="CJ19" s="3"/>
       <c r="CK19" s="3"/>
       <c r="CL19" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="CM19">
         <v>0.08</v>
@@ -10443,22 +10429,22 @@
     </row>
     <row r="21" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C21" t="s">
+        <v>423</v>
+      </c>
+      <c r="K21" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K21" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L21" s="3" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="AC21">
         <v>1</v>
       </c>
       <c r="AG21" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="AH21">
         <v>1</v>
@@ -10484,7 +10470,7 @@
       <c r="CI21" s="3"/>
       <c r="CK21" s="3"/>
       <c r="CL21" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="CM21">
         <v>0.19</v>
@@ -10495,22 +10481,22 @@
     </row>
     <row r="22" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="C22" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC22">
         <v>2</v>
       </c>
       <c r="AO22" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR22" t="s">
         <v>434</v>
       </c>
-      <c r="AR22" t="s">
+      <c r="AV22" t="s">
         <v>435</v>
-      </c>
-      <c r="AV22" t="s">
-        <v>436</v>
       </c>
       <c r="AX22">
         <v>1</v>
@@ -10522,40 +10508,40 @@
         <v>67</v>
       </c>
       <c r="CE22" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CJ22" s="3"/>
       <c r="CU22" t="s">
+        <v>473</v>
+      </c>
+      <c r="CW22" t="s">
         <v>474</v>
-      </c>
-      <c r="CW22" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="23" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>475</v>
+      </c>
+      <c r="C23" t="s">
+        <v>453</v>
+      </c>
+      <c r="D23" t="s">
         <v>476</v>
       </c>
-      <c r="C23" t="s">
-        <v>454</v>
-      </c>
-      <c r="D23" t="s">
+      <c r="E23" t="s">
         <v>477</v>
       </c>
-      <c r="E23" t="s">
+      <c r="F23" t="s">
         <v>478</v>
-      </c>
-      <c r="F23" t="s">
-        <v>479</v>
       </c>
       <c r="G23">
         <v>3</v>
       </c>
       <c r="J23" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="W23" s="3">
         <v>1</v>
@@ -10582,36 +10568,36 @@
         <v>1</v>
       </c>
       <c r="BW23" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CV23" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="24" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
+        <v>479</v>
+      </c>
+      <c r="C24" t="s">
         <v>480</v>
       </c>
-      <c r="C24" t="s">
+      <c r="D24" t="s">
         <v>481</v>
       </c>
-      <c r="D24" t="s">
+      <c r="E24" t="s">
         <v>482</v>
       </c>
-      <c r="E24" t="s">
+      <c r="F24" t="s">
         <v>483</v>
-      </c>
-      <c r="F24" t="s">
-        <v>484</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
       <c r="J24" t="s">
+        <v>440</v>
+      </c>
+      <c r="K24" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="AC24">
         <v>1</v>
@@ -10623,7 +10609,7 @@
         <v>8</v>
       </c>
       <c r="BM24" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="BR24">
         <v>15</v>
@@ -10638,24 +10624,24 @@
         <v>1</v>
       </c>
       <c r="BW24" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CV24" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="25" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="C25" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K25" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L25" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC25">
         <v>1</v>
@@ -10668,7 +10654,7 @@
       </c>
       <c r="BT25"/>
       <c r="CL25" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="CM25">
         <v>0.8</v>
@@ -10683,25 +10669,25 @@
     </row>
     <row r="27" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C27" t="s">
+        <v>423</v>
+      </c>
+      <c r="K27" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K27" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L27" s="3" t="s">
+        <v>426</v>
+      </c>
+      <c r="AC27">
+        <v>1</v>
+      </c>
+      <c r="AF27">
+        <v>1</v>
+      </c>
+      <c r="AG27" t="s">
         <v>427</v>
-      </c>
-      <c r="AC27">
-        <v>1</v>
-      </c>
-      <c r="AF27">
-        <v>1</v>
-      </c>
-      <c r="AG27" t="s">
-        <v>428</v>
       </c>
       <c r="AH27">
         <v>1</v>
@@ -10728,10 +10714,10 @@
       <c r="CJ27" s="3"/>
       <c r="CK27" s="3"/>
       <c r="CL27" t="s">
+        <v>487</v>
+      </c>
+      <c r="CM27" t="s">
         <v>488</v>
-      </c>
-      <c r="CM27" t="s">
-        <v>489</v>
       </c>
       <c r="CP27">
         <v>99999</v>
@@ -10742,23 +10728,23 @@
     </row>
     <row r="28" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="C28" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC28">
         <v>2</v>
       </c>
       <c r="AO28" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR28" t="s">
         <v>434</v>
       </c>
-      <c r="AR28" t="s">
+      <c r="AV28" t="s">
         <v>435</v>
       </c>
-      <c r="AV28" t="s">
-        <v>436</v>
-      </c>
       <c r="AX28">
         <v>1</v>
       </c>
@@ -10766,43 +10752,43 @@
         <v>1</v>
       </c>
       <c r="BZ28" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="CE28" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CJ28" s="3"/>
       <c r="CU28" t="s">
+        <v>491</v>
+      </c>
+      <c r="CW28" t="s">
         <v>492</v>
-      </c>
-      <c r="CW28" t="s">
-        <v>493</v>
       </c>
     </row>
     <row r="29" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>493</v>
+      </c>
+      <c r="C29" t="s">
+        <v>423</v>
+      </c>
+      <c r="D29" t="s">
         <v>494</v>
       </c>
-      <c r="C29" t="s">
-        <v>424</v>
-      </c>
-      <c r="D29" t="s">
+      <c r="E29" t="s">
         <v>495</v>
       </c>
-      <c r="E29" t="s">
+      <c r="F29" t="s">
         <v>496</v>
-      </c>
-      <c r="F29" t="s">
-        <v>497</v>
       </c>
       <c r="G29">
         <v>3</v>
       </c>
       <c r="J29" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AC29">
         <v>1</v>
@@ -10812,7 +10798,7 @@
         <v>1</v>
       </c>
       <c r="BN29" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="BR29">
         <v>15</v>
@@ -10827,7 +10813,7 @@
         <v>1</v>
       </c>
       <c r="BW29" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ29" s="3"/>
       <c r="CA29" s="3"/>
@@ -10840,7 +10826,7 @@
       <c r="CI29" s="3"/>
       <c r="CK29" s="3"/>
       <c r="CL29" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="CM29">
         <v>0.7</v>
@@ -10851,19 +10837,19 @@
     </row>
     <row r="30" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="C30" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="E30" s="5"/>
       <c r="G30" s="5"/>
       <c r="I30" s="5"/>
       <c r="K30" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L30" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="BL30">
         <v>11</v>
@@ -10871,7 +10857,7 @@
       <c r="BT30"/>
       <c r="CJ30" s="3"/>
       <c r="CV30" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="31" spans="1:106" x14ac:dyDescent="0.25">
@@ -10883,22 +10869,22 @@
     </row>
     <row r="32" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="C32" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC32">
         <v>2</v>
       </c>
       <c r="AO32" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR32" t="s">
         <v>434</v>
       </c>
-      <c r="AR32" t="s">
+      <c r="AV32" t="s">
         <v>435</v>
-      </c>
-      <c r="AV32" t="s">
-        <v>436</v>
       </c>
       <c r="AX32">
         <v>1</v>
@@ -10911,43 +10897,43 @@
         <v>67</v>
       </c>
       <c r="CE32" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CH32" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="CJ32" s="3"/>
       <c r="CU32" t="s">
+        <v>500</v>
+      </c>
+      <c r="CW32" t="s">
         <v>501</v>
-      </c>
-      <c r="CW32" t="s">
-        <v>502</v>
       </c>
     </row>
     <row r="33" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
+        <v>502</v>
+      </c>
+      <c r="C33" t="s">
+        <v>423</v>
+      </c>
+      <c r="D33" t="s">
         <v>503</v>
       </c>
-      <c r="C33" t="s">
-        <v>424</v>
-      </c>
-      <c r="D33" t="s">
+      <c r="E33" t="s">
         <v>504</v>
       </c>
-      <c r="E33" t="s">
+      <c r="F33" t="s">
         <v>505</v>
-      </c>
-      <c r="F33" t="s">
-        <v>506</v>
       </c>
       <c r="G33">
         <v>3</v>
       </c>
       <c r="J33" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K33" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AC33">
         <v>1</v>
@@ -10969,7 +10955,7 @@
         <v>1</v>
       </c>
       <c r="BW33" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ33" s="3"/>
       <c r="CA33" s="3"/>
@@ -10979,16 +10965,16 @@
       <c r="CF33" s="3"/>
       <c r="CG33" s="3"/>
       <c r="CH33" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="CI33" s="3"/>
       <c r="CJ33" s="3"/>
       <c r="CK33" s="3"/>
       <c r="CL33" t="s">
+        <v>506</v>
+      </c>
+      <c r="CM33" t="s">
         <v>507</v>
-      </c>
-      <c r="CM33" t="s">
-        <v>508</v>
       </c>
       <c r="CP33">
         <v>30</v>
@@ -10996,22 +10982,22 @@
     </row>
     <row r="35" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="C35" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC35">
         <v>2</v>
       </c>
       <c r="AO35" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR35" t="s">
         <v>434</v>
       </c>
-      <c r="AR35" t="s">
+      <c r="AV35" t="s">
         <v>435</v>
-      </c>
-      <c r="AV35" t="s">
-        <v>436</v>
       </c>
       <c r="AX35">
         <v>1</v>
@@ -11024,27 +11010,27 @@
         <v>67</v>
       </c>
       <c r="CE35" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CU35" t="s">
+        <v>514</v>
+      </c>
+      <c r="CW35" t="s">
         <v>515</v>
-      </c>
-      <c r="CW35" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="36" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="C36" t="s">
+        <v>423</v>
+      </c>
+      <c r="K36" t="s">
         <v>424</v>
       </c>
-      <c r="K36" t="s">
-        <v>425</v>
-      </c>
       <c r="L36" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="M36"/>
       <c r="N36"/>
@@ -11068,7 +11054,7 @@
         <v>1</v>
       </c>
       <c r="AI36" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BU36"/>
       <c r="BV36"/>
@@ -11076,7 +11062,7 @@
       <c r="BX36"/>
       <c r="BY36"/>
       <c r="CL36" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="CM36">
         <v>-1</v>
@@ -11084,28 +11070,28 @@
     </row>
     <row r="37" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
+        <v>518</v>
+      </c>
+      <c r="C37" t="s">
+        <v>453</v>
+      </c>
+      <c r="D37" t="s">
         <v>519</v>
       </c>
-      <c r="C37" t="s">
-        <v>454</v>
-      </c>
-      <c r="D37" t="s">
+      <c r="E37" t="s">
         <v>520</v>
       </c>
-      <c r="E37" t="s">
+      <c r="F37" t="s">
         <v>521</v>
-      </c>
-      <c r="F37" t="s">
-        <v>522</v>
       </c>
       <c r="G37">
         <v>3</v>
       </c>
       <c r="J37" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="W37" s="3">
         <v>1</v>
@@ -11132,36 +11118,36 @@
         <v>1</v>
       </c>
       <c r="BW37" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CV37" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="38" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
+        <v>522</v>
+      </c>
+      <c r="C38" t="s">
+        <v>480</v>
+      </c>
+      <c r="D38" t="s">
         <v>523</v>
       </c>
-      <c r="C38" t="s">
-        <v>481</v>
-      </c>
-      <c r="D38" t="s">
+      <c r="E38" t="s">
         <v>524</v>
       </c>
-      <c r="E38" t="s">
+      <c r="F38" t="s">
         <v>525</v>
-      </c>
-      <c r="F38" t="s">
-        <v>526</v>
       </c>
       <c r="G38">
         <v>3</v>
       </c>
       <c r="J38" t="s">
+        <v>440</v>
+      </c>
+      <c r="K38" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="K38" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="AC38">
         <v>1</v>
@@ -11173,7 +11159,7 @@
         <v>9</v>
       </c>
       <c r="BM38" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="BR38">
         <v>10</v>
@@ -11188,25 +11174,25 @@
         <v>1</v>
       </c>
       <c r="BW38" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CJ38" s="3"/>
       <c r="CV38" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
     </row>
     <row r="39" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C39" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AC39">
         <v>1</v>
@@ -11221,22 +11207,22 @@
     </row>
     <row r="40" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C40" t="s">
+        <v>423</v>
+      </c>
+      <c r="K40" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K40" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L40" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC40">
         <v>1</v>
       </c>
       <c r="AI40" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AT40">
         <v>99</v>
@@ -11256,10 +11242,10 @@
       <c r="CI40" s="3"/>
       <c r="CK40" s="3"/>
       <c r="CL40" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="CM40" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="CP40">
         <v>10</v>
@@ -11273,25 +11259,25 @@
     </row>
     <row r="42" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="C42" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC42">
         <v>2</v>
       </c>
       <c r="AO42" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR42" t="s">
         <v>434</v>
       </c>
-      <c r="AR42" t="s">
+      <c r="AV42" t="s">
         <v>435</v>
-      </c>
-      <c r="AV42" t="s">
-        <v>436</v>
       </c>
       <c r="AX42">
         <v>1</v>
@@ -11301,32 +11287,32 @@
       </c>
       <c r="BT42"/>
       <c r="BZ42" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="CE42" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CJ42" s="3"/>
       <c r="CU42" t="s">
+        <v>531</v>
+      </c>
+      <c r="CW42" t="s">
         <v>532</v>
-      </c>
-      <c r="CW42" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="43" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
+        <v>533</v>
+      </c>
+      <c r="C43" t="s">
+        <v>453</v>
+      </c>
+      <c r="K43" s="3" t="s">
+        <v>424</v>
+      </c>
+      <c r="L43" s="3" t="s">
         <v>534</v>
       </c>
-      <c r="C43" t="s">
-        <v>454</v>
-      </c>
-      <c r="K43" s="3" t="s">
-        <v>425</v>
-      </c>
-      <c r="L43" s="3" t="s">
-        <v>535</v>
-      </c>
       <c r="X43" s="3">
         <v>1</v>
       </c>
@@ -11334,7 +11320,7 @@
         <v>1</v>
       </c>
       <c r="AG43" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="BB43">
         <v>1</v>
@@ -11346,16 +11332,16 @@
     </row>
     <row r="44" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="C44" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L44" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC44">
         <v>1</v>
@@ -11369,28 +11355,28 @@
     </row>
     <row r="45" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
+        <v>536</v>
+      </c>
+      <c r="C45" t="s">
+        <v>423</v>
+      </c>
+      <c r="D45" t="s">
         <v>537</v>
       </c>
-      <c r="C45" t="s">
-        <v>424</v>
-      </c>
-      <c r="D45" t="s">
+      <c r="E45" t="s">
         <v>538</v>
       </c>
-      <c r="E45" t="s">
+      <c r="F45" t="s">
         <v>539</v>
-      </c>
-      <c r="F45" t="s">
-        <v>540</v>
       </c>
       <c r="G45">
         <v>3</v>
       </c>
       <c r="J45" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K45" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="X45" s="3">
         <v>1</v>
@@ -11405,13 +11391,13 @@
         <v>2</v>
       </c>
       <c r="AO45" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AR45" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="AV45" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="AX45">
         <v>1.7</v>
@@ -11426,7 +11412,7 @@
         <v>0.8</v>
       </c>
       <c r="BM45" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="BQ45">
         <v>2.1669999999999998</v>
@@ -11444,29 +11430,29 @@
         <v>1</v>
       </c>
       <c r="BW45" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ45" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="CA45">
         <v>0.5</v>
       </c>
       <c r="CE45" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="CJ45" s="3"/>
       <c r="CL45" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="CP45">
         <v>3</v>
       </c>
       <c r="CU45" t="s">
+        <v>541</v>
+      </c>
+      <c r="CW45" t="s">
         <v>542</v>
-      </c>
-      <c r="CW45" t="s">
-        <v>543</v>
       </c>
     </row>
     <row r="46" spans="1:106" x14ac:dyDescent="0.25">
@@ -11475,22 +11461,22 @@
     </row>
     <row r="47" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="C47" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC47">
         <v>2</v>
       </c>
       <c r="AO47" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR47" t="s">
         <v>434</v>
       </c>
-      <c r="AR47" t="s">
+      <c r="AV47" t="s">
         <v>435</v>
-      </c>
-      <c r="AV47" t="s">
-        <v>436</v>
       </c>
       <c r="AX47">
         <v>1</v>
@@ -11503,38 +11489,38 @@
         <v>67</v>
       </c>
       <c r="CE47" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CJ47" s="3"/>
       <c r="CU47" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
     </row>
     <row r="48" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="C48" t="s">
+        <v>423</v>
+      </c>
+      <c r="K48" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K48" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L48" s="3" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AC48">
         <v>1</v>
       </c>
       <c r="AI48" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AW48" s="3"/>
       <c r="BB48">
         <v>99</v>
       </c>
       <c r="BM48" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="BU48"/>
       <c r="BV48"/>
@@ -11553,10 +11539,10 @@
       <c r="CJ48" s="3"/>
       <c r="CK48" s="3"/>
       <c r="CL48" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="CM48" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="CP48">
         <v>99999</v>
@@ -11567,16 +11553,16 @@
     </row>
     <row r="49" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="C49" t="s">
+        <v>423</v>
+      </c>
+      <c r="K49" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K49" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L49" s="3" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="AC49">
         <v>1</v>
@@ -11585,10 +11571,10 @@
         <v>1</v>
       </c>
       <c r="AG49" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AI49" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AW49" s="3"/>
       <c r="BB49">
@@ -11610,10 +11596,10 @@
       <c r="CI49" s="3"/>
       <c r="CK49" s="3"/>
       <c r="CL49" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="CM49" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="CP49">
         <v>99999</v>
@@ -11624,16 +11610,16 @@
     </row>
     <row r="50" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C50" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L50" s="3" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="AC50">
         <v>2</v>
@@ -11642,7 +11628,7 @@
         <v>1</v>
       </c>
       <c r="AR50" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AW50" s="3"/>
       <c r="BT50"/>
@@ -11657,33 +11643,33 @@
       <c r="CI50" s="3"/>
       <c r="CK50" s="3"/>
       <c r="CS50" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
     </row>
     <row r="51" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C51" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D51" t="s">
+        <v>519</v>
+      </c>
+      <c r="E51" t="s">
         <v>520</v>
       </c>
-      <c r="E51" t="s">
+      <c r="F51" t="s">
         <v>521</v>
-      </c>
-      <c r="F51" t="s">
-        <v>522</v>
       </c>
       <c r="G51">
         <v>3</v>
       </c>
       <c r="J51" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="W51" s="3">
         <v>1</v>
@@ -11710,49 +11696,49 @@
         <v>1</v>
       </c>
       <c r="BW51" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CJ51" s="3"/>
       <c r="CV51" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
     </row>
     <row r="52" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
+        <v>557</v>
+      </c>
+      <c r="C52" t="s">
+        <v>453</v>
+      </c>
+      <c r="D52" t="s">
         <v>558</v>
       </c>
-      <c r="C52" t="s">
-        <v>454</v>
-      </c>
-      <c r="D52" t="s">
+      <c r="E52" t="s">
         <v>559</v>
       </c>
-      <c r="E52" t="s">
+      <c r="F52" t="s">
         <v>560</v>
-      </c>
-      <c r="F52" t="s">
-        <v>561</v>
       </c>
       <c r="G52">
         <v>3</v>
       </c>
       <c r="J52" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC52">
         <v>2</v>
       </c>
       <c r="AO52" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="AR52" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="AV52" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AX52">
         <v>3.4</v>
@@ -11779,55 +11765,55 @@
         <v>3</v>
       </c>
       <c r="BW52" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ52" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="CE52" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CJ52" s="3"/>
       <c r="CU52" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
     </row>
     <row r="53" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
+        <v>562</v>
+      </c>
+      <c r="C53" t="s">
+        <v>432</v>
+      </c>
+      <c r="D53" t="s">
         <v>563</v>
       </c>
-      <c r="C53" t="s">
-        <v>433</v>
-      </c>
-      <c r="D53" t="s">
+      <c r="E53" t="s">
         <v>564</v>
       </c>
-      <c r="E53" t="s">
+      <c r="F53" t="s">
         <v>565</v>
-      </c>
-      <c r="F53" t="s">
-        <v>566</v>
       </c>
       <c r="G53">
         <v>3</v>
       </c>
       <c r="J53" t="s">
+        <v>440</v>
+      </c>
+      <c r="K53" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="K53" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="AC53">
         <v>2</v>
       </c>
       <c r="AO53" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR53" t="s">
         <v>434</v>
       </c>
-      <c r="AR53" t="s">
+      <c r="AV53" t="s">
         <v>435</v>
-      </c>
-      <c r="AV53" t="s">
-        <v>436</v>
       </c>
       <c r="AX53">
         <v>3.8</v>
@@ -11836,7 +11822,7 @@
         <v>1</v>
       </c>
       <c r="BM53" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="BR53">
         <v>25</v>
@@ -11854,19 +11840,19 @@
         <v>1</v>
       </c>
       <c r="BW53" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BY53" s="4" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="BZ53" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="CE53" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CL53" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="CP53">
         <v>1.5</v>
@@ -11875,24 +11861,24 @@
         <v>0.4</v>
       </c>
       <c r="CU53" t="s">
+        <v>567</v>
+      </c>
+      <c r="CV53" t="s">
         <v>568</v>
-      </c>
-      <c r="CV53" t="s">
-        <v>569</v>
       </c>
     </row>
     <row r="54" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="C54" t="s">
+        <v>423</v>
+      </c>
+      <c r="K54" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K54" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L54" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC54">
         <v>1</v>
@@ -11913,7 +11899,7 @@
       <c r="CI54" s="3"/>
       <c r="CK54" s="3"/>
       <c r="CL54" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="CM54">
         <v>1</v>
@@ -11942,22 +11928,22 @@
     </row>
     <row r="56" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="C56" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC56">
         <v>2</v>
       </c>
       <c r="AO56" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR56" t="s">
         <v>434</v>
       </c>
-      <c r="AR56" t="s">
+      <c r="AV56" t="s">
         <v>435</v>
-      </c>
-      <c r="AV56" t="s">
-        <v>436</v>
       </c>
       <c r="AX56">
         <v>1</v>
@@ -11969,34 +11955,34 @@
         <v>67</v>
       </c>
       <c r="CE56" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CJ56" s="3"/>
       <c r="CV56" t="s">
+        <v>572</v>
+      </c>
+      <c r="CW56" t="s">
         <v>573</v>
-      </c>
-      <c r="CW56" t="s">
-        <v>574</v>
       </c>
     </row>
     <row r="57" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C57" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="I57">
         <v>1</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC57">
         <v>1</v>
       </c>
       <c r="AI57" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="AT57">
         <v>99</v>
@@ -12037,34 +12023,34 @@
     </row>
     <row r="58" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
+        <v>575</v>
+      </c>
+      <c r="C58" t="s">
+        <v>480</v>
+      </c>
+      <c r="D58" t="s">
         <v>576</v>
       </c>
-      <c r="C58" t="s">
-        <v>481</v>
-      </c>
-      <c r="D58" t="s">
+      <c r="E58" t="s">
         <v>577</v>
       </c>
-      <c r="E58" t="s">
+      <c r="F58" t="s">
         <v>578</v>
-      </c>
-      <c r="F58" t="s">
-        <v>579</v>
       </c>
       <c r="G58">
         <v>3</v>
       </c>
       <c r="J58" t="s">
+        <v>440</v>
+      </c>
+      <c r="K58" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="K58" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="AC58">
         <v>1</v>
       </c>
       <c r="AR58" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="BB58">
         <v>1</v>
@@ -12088,23 +12074,23 @@
         <v>1</v>
       </c>
       <c r="BW58" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ58" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="CA58">
         <v>0</v>
       </c>
       <c r="CC58" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="CE58" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="CJ58" s="3"/>
       <c r="CL58" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="CN58">
         <v>-1</v>
@@ -12118,34 +12104,34 @@
     </row>
     <row r="59" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
+        <v>580</v>
+      </c>
+      <c r="C59" t="s">
+        <v>480</v>
+      </c>
+      <c r="D59" t="s">
         <v>581</v>
       </c>
-      <c r="C59" t="s">
-        <v>481</v>
-      </c>
-      <c r="D59" t="s">
+      <c r="E59" t="s">
         <v>582</v>
       </c>
-      <c r="E59" t="s">
+      <c r="F59" t="s">
         <v>583</v>
-      </c>
-      <c r="F59" t="s">
-        <v>584</v>
       </c>
       <c r="G59">
         <v>3</v>
       </c>
       <c r="J59" t="s">
+        <v>440</v>
+      </c>
+      <c r="K59" s="3" t="s">
         <v>441</v>
       </c>
-      <c r="K59" s="3" t="s">
-        <v>442</v>
-      </c>
       <c r="AC59">
         <v>1</v>
       </c>
       <c r="AR59" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="BB59">
         <v>1</v>
@@ -12154,7 +12140,7 @@
         <v>16</v>
       </c>
       <c r="BM59" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="BQ59">
         <v>0.01</v>
@@ -12172,23 +12158,23 @@
         <v>1</v>
       </c>
       <c r="BW59" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ59" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="CA59">
         <v>0</v>
       </c>
       <c r="CC59" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="CE59" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="CJ59" s="3"/>
       <c r="CL59" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="CN59">
         <v>-1</v>
@@ -12200,33 +12186,33 @@
         <v>1</v>
       </c>
       <c r="DA59" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
     </row>
     <row r="60" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="C60" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="J60" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="K60" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="AB60">
+        <v>1</v>
+      </c>
+      <c r="AC60">
+        <v>1</v>
+      </c>
+      <c r="AO60" t="s">
         <v>429</v>
       </c>
-      <c r="AB60">
-        <v>1</v>
-      </c>
-      <c r="AC60">
-        <v>1</v>
-      </c>
-      <c r="AO60" t="s">
-        <v>430</v>
-      </c>
       <c r="AR60" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="AW60">
         <v>1</v>
@@ -12244,22 +12230,22 @@
     </row>
     <row r="62" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C62" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="AC62">
         <v>2</v>
       </c>
       <c r="AO62" t="s">
+        <v>433</v>
+      </c>
+      <c r="AR62" t="s">
         <v>434</v>
       </c>
-      <c r="AR62" t="s">
+      <c r="AV62" t="s">
         <v>435</v>
-      </c>
-      <c r="AV62" t="s">
-        <v>436</v>
       </c>
       <c r="AX62">
         <v>1</v>
@@ -12269,28 +12255,28 @@
       </c>
       <c r="BT62"/>
       <c r="BZ62" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="CE62" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CH62" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="CJ62" s="3"/>
     </row>
     <row r="63" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="C63" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="K63" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="L63" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="M63"/>
       <c r="N63"/>
@@ -12314,7 +12300,7 @@
         <v>1</v>
       </c>
       <c r="AI63" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="BB63">
         <v>1</v>
@@ -12327,30 +12313,30 @@
       <c r="BY63"/>
       <c r="CJ63" s="3"/>
       <c r="CS63" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
     </row>
     <row r="64" spans="1:106" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
+        <v>589</v>
+      </c>
+      <c r="C64" t="s">
+        <v>423</v>
+      </c>
+      <c r="D64" t="s">
+        <v>543</v>
+      </c>
+      <c r="E64" t="s">
+        <v>544</v>
+      </c>
+      <c r="F64" t="s">
         <v>590</v>
       </c>
-      <c r="C64" t="s">
-        <v>424</v>
-      </c>
-      <c r="D64" t="s">
-        <v>544</v>
-      </c>
-      <c r="E64" t="s">
-        <v>545</v>
-      </c>
-      <c r="F64" t="s">
-        <v>591</v>
-      </c>
       <c r="J64" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="AC64">
         <v>1</v>
@@ -12372,7 +12358,7 @@
         <v>1</v>
       </c>
       <c r="BW64" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ64" s="3"/>
       <c r="CA64" s="3"/>
@@ -12386,10 +12372,10 @@
       <c r="CJ64" s="3"/>
       <c r="CK64" s="3"/>
       <c r="CL64" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="CM64" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="CP64">
         <v>35</v>
@@ -12397,34 +12383,34 @@
     </row>
     <row r="65" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
+        <v>592</v>
+      </c>
+      <c r="C65" t="s">
+        <v>432</v>
+      </c>
+      <c r="D65" t="s">
         <v>593</v>
       </c>
-      <c r="C65" t="s">
-        <v>433</v>
-      </c>
-      <c r="D65" t="s">
+      <c r="E65" t="s">
         <v>594</v>
       </c>
-      <c r="E65" t="s">
+      <c r="F65" t="s">
         <v>595</v>
       </c>
-      <c r="F65" t="s">
-        <v>596</v>
-      </c>
       <c r="J65" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="AC65">
         <v>2</v>
       </c>
       <c r="AR65" t="s">
+        <v>434</v>
+      </c>
+      <c r="AV65" t="s">
         <v>435</v>
-      </c>
-      <c r="AV65" t="s">
-        <v>436</v>
       </c>
       <c r="AW65" s="3"/>
       <c r="AX65">
@@ -12452,47 +12438,47 @@
         <v>3</v>
       </c>
       <c r="BW65" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ65" s="3" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="CA65" s="3"/>
       <c r="CB65" s="3"/>
       <c r="CC65" s="3"/>
       <c r="CD65" s="3"/>
       <c r="CE65" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CF65" s="3"/>
       <c r="CG65" s="3"/>
       <c r="CH65" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="CI65" s="3"/>
       <c r="CK65" s="3"/>
     </row>
     <row r="66" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
+        <v>596</v>
+      </c>
+      <c r="C66" t="s">
+        <v>432</v>
+      </c>
+      <c r="D66" t="s">
         <v>597</v>
       </c>
-      <c r="C66" t="s">
-        <v>433</v>
-      </c>
-      <c r="D66" t="s">
+      <c r="E66" t="s">
         <v>598</v>
       </c>
-      <c r="E66" t="s">
+      <c r="F66" t="s">
         <v>599</v>
       </c>
-      <c r="F66" t="s">
-        <v>600</v>
-      </c>
       <c r="J66" t="s">
+        <v>440</v>
+      </c>
+      <c r="K66" s="3" t="s">
         <v>441</v>
-      </c>
-      <c r="K66" s="3" t="s">
-        <v>442</v>
       </c>
       <c r="AB66">
         <v>1</v>
@@ -12501,10 +12487,10 @@
         <v>2</v>
       </c>
       <c r="AR66" t="s">
+        <v>434</v>
+      </c>
+      <c r="AV66" t="s">
         <v>435</v>
-      </c>
-      <c r="AV66" t="s">
-        <v>436</v>
       </c>
       <c r="AW66" s="3"/>
       <c r="AX66">
@@ -12520,7 +12506,7 @@
         <v>0.1</v>
       </c>
       <c r="BM66" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="BR66">
         <v>20</v>
@@ -12538,22 +12524,22 @@
         <v>1</v>
       </c>
       <c r="BW66" s="4" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="BZ66" s="3" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="CA66" s="3"/>
       <c r="CB66" s="3"/>
       <c r="CC66" s="3"/>
       <c r="CD66" s="3"/>
       <c r="CE66" t="s">
-        <v>431</v>
+        <v>430</v>
       </c>
       <c r="CF66" s="3"/>
       <c r="CG66" s="3"/>
       <c r="CH66" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="CI66" s="3"/>
       <c r="CJ66" s="3"/>
@@ -12561,16 +12547,16 @@
     </row>
     <row r="67" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C67" t="s">
+        <v>423</v>
+      </c>
+      <c r="K67" s="3" t="s">
         <v>424</v>
       </c>
-      <c r="K67" s="3" t="s">
-        <v>425</v>
-      </c>
       <c r="L67" s="3" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="AC67">
         <v>1</v>
@@ -12592,10 +12578,10 @@
       <c r="CJ67" s="3"/>
       <c r="CK67" s="3"/>
       <c r="CL67" t="s">
+        <v>600</v>
+      </c>
+      <c r="CM67" t="s">
         <v>601</v>
-      </c>
-      <c r="CM67" t="s">
-        <v>602</v>
       </c>
       <c r="CP67">
         <v>20</v>
@@ -12606,32 +12592,32 @@
     </row>
     <row r="69" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A69" s="8" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C69" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="K69" s="9"/>
       <c r="L69" s="9"/>
       <c r="AR69" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="BM69" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="CS69" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
     </row>
     <row r="70" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A70" s="8" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="C70" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="K70" s="9" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="O70" s="9"/>
       <c r="P70"/>
@@ -12639,13 +12625,13 @@
         <v>2</v>
       </c>
       <c r="AO70" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AR70" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AV70" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AX70">
         <v>1</v>
@@ -12660,44 +12646,44 @@
         <v>0.3</v>
       </c>
       <c r="BZ70" s="8" t="s">
+        <v>709</v>
+      </c>
+      <c r="CE70" s="8" t="s">
         <v>710</v>
       </c>
-      <c r="CE70" s="8" t="s">
-        <v>711</v>
-      </c>
       <c r="CJ70" s="8" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="CK70" s="8"/>
       <c r="CW70" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="71" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A71" s="8" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C71" s="8" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="K71" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="L71" s="3" t="s">
         <v>703</v>
-      </c>
-      <c r="L71" s="3" t="s">
-        <v>704</v>
       </c>
       <c r="O71"/>
       <c r="AC71">
         <v>2</v>
       </c>
       <c r="AO71" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AR71" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="AV71" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="AX71">
         <v>2</v>
@@ -12713,45 +12699,45 @@
       </c>
       <c r="BZ71" s="8"/>
       <c r="CE71" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="CW71" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
     </row>
     <row r="72" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A72" s="8" t="s">
+        <v>712</v>
+      </c>
+      <c r="C72" s="8" t="s">
+        <v>683</v>
+      </c>
+      <c r="I72">
+        <v>1</v>
+      </c>
+      <c r="K72" s="9" t="s">
+        <v>702</v>
+      </c>
+      <c r="L72" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="C72" s="8" t="s">
-        <v>684</v>
-      </c>
-      <c r="I72">
-        <v>1</v>
-      </c>
-      <c r="K72" s="9" t="s">
-        <v>703</v>
-      </c>
-      <c r="L72" s="9" t="s">
+      <c r="AC72">
+        <v>1</v>
+      </c>
+      <c r="AF72">
+        <v>1</v>
+      </c>
+      <c r="AG72" s="8" t="s">
+        <v>704</v>
+      </c>
+      <c r="BB72">
+        <v>1</v>
+      </c>
+      <c r="CL72" s="8" t="s">
         <v>714</v>
       </c>
-      <c r="AC72">
-        <v>1</v>
-      </c>
-      <c r="AF72">
-        <v>1</v>
-      </c>
-      <c r="AG72" s="8" t="s">
-        <v>705</v>
-      </c>
-      <c r="BB72">
-        <v>1</v>
-      </c>
-      <c r="CL72" s="8" t="s">
+      <c r="CM72" s="8" t="s">
         <v>715</v>
-      </c>
-      <c r="CM72" s="8" t="s">
-        <v>716</v>
       </c>
       <c r="CP72">
         <v>99999</v>
@@ -12759,16 +12745,16 @@
     </row>
     <row r="73" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A73" s="8" t="s">
+        <v>758</v>
+      </c>
+      <c r="C73" s="8" t="s">
+        <v>757</v>
+      </c>
+      <c r="K73" s="3" t="s">
+        <v>702</v>
+      </c>
+      <c r="L73" s="3" t="s">
         <v>759</v>
-      </c>
-      <c r="C73" s="8" t="s">
-        <v>758</v>
-      </c>
-      <c r="K73" s="3" t="s">
-        <v>703</v>
-      </c>
-      <c r="L73" s="3" t="s">
-        <v>760</v>
       </c>
       <c r="AC73">
         <v>1</v>
@@ -12780,7 +12766,7 @@
       <c r="BT73"/>
       <c r="CJ73" s="3"/>
       <c r="CS73" s="8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="74" spans="1:109" x14ac:dyDescent="0.25">
@@ -12817,25 +12803,25 @@
     </row>
     <row r="78" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A78" s="8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C78" s="8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="I78">
         <v>1</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AC78">
         <v>1</v>
       </c>
       <c r="AG78" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AR78" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="BB78">
         <v>1</v>
@@ -12849,26 +12835,26 @@
     </row>
     <row r="79" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A79" s="8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C79" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I79">
         <v>1</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="AC79">
         <v>2</v>
       </c>
       <c r="AG79" s="8"/>
       <c r="AO79" s="8" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AR79" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="BB79">
         <v>99</v>
@@ -12881,13 +12867,13 @@
       <c r="CE79" s="8"/>
       <c r="CJ79" s="3"/>
       <c r="CL79" s="8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="CP79">
         <v>0.02</v>
       </c>
       <c r="CS79" s="8" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="DB79">
         <v>1</v>
@@ -12898,10 +12884,10 @@
     </row>
     <row r="80" spans="1:109" x14ac:dyDescent="0.25">
       <c r="A80" s="8" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C80" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D80" s="8"/>
       <c r="I80">
@@ -12909,10 +12895,10 @@
       </c>
       <c r="J80" s="8"/>
       <c r="K80" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AC80">
         <v>1</v>
@@ -12922,14 +12908,14 @@
       </c>
       <c r="AI80" s="8"/>
       <c r="AJ80" s="8" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="AO80" s="8"/>
       <c r="AT80">
         <v>99</v>
       </c>
       <c r="AV80" s="8" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AX80">
         <v>1</v>
@@ -12941,16 +12927,16 @@
       <c r="BN80" s="8"/>
       <c r="BP80" s="8"/>
       <c r="CE80" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="CF80" s="8" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="CG80" s="8" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="CL80" s="8" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="CP80">
         <v>6</v>
@@ -12961,19 +12947,19 @@
     </row>
     <row r="81" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A81" s="8" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C81" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I81">
         <v>1</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AC81">
         <v>1</v>
@@ -12982,7 +12968,7 @@
         <v>1</v>
       </c>
       <c r="AG81" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AJ81" s="8"/>
       <c r="AO81" s="8"/>
@@ -12998,7 +12984,7 @@
       <c r="CE81" s="8"/>
       <c r="CJ81" s="3"/>
       <c r="CL81" s="8" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="CP81">
         <v>99999</v>
@@ -13013,32 +12999,32 @@
     </row>
     <row r="82" spans="1:110" x14ac:dyDescent="0.25">
       <c r="A82" s="8" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C82" s="8" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="I82">
         <v>1</v>
       </c>
       <c r="K82" s="3" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="L82" s="3" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="AC82">
         <v>1</v>
       </c>
       <c r="AG82" s="8"/>
       <c r="AJ82" s="8" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AT82">
         <v>99</v>
       </c>
       <c r="AV82" s="8" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="AX82">
         <v>99999</v>
@@ -13051,7 +13037,7 @@
       </c>
       <c r="BT82"/>
       <c r="CE82" s="8" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="CJ82" s="3"/>
       <c r="CL82" s="8"/>
@@ -14726,34 +14712,34 @@
         <v>16</v>
       </c>
       <c r="E1" t="s">
+        <v>602</v>
+      </c>
+      <c r="F1" t="s">
         <v>603</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>604</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>605</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>606</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>607</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>608</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>609</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>610</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>611</v>
-      </c>
-      <c r="O1" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
@@ -14767,40 +14753,40 @@
         <v>87</v>
       </c>
       <c r="E2" t="s">
+        <v>612</v>
+      </c>
+      <c r="F2" t="s">
         <v>613</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>614</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>615</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>616</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>617</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>618</v>
-      </c>
-      <c r="K2" t="s">
-        <v>619</v>
       </c>
       <c r="L2" t="s">
         <v>63</v>
       </c>
       <c r="M2" t="s">
+        <v>619</v>
+      </c>
+      <c r="N2" t="s">
         <v>620</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>621</v>
       </c>
-      <c r="O2" t="s">
-        <v>622</v>
-      </c>
       <c r="P2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
@@ -14829,13 +14815,13 @@
         <v>124</v>
       </c>
       <c r="J3" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="K3" t="s">
         <v>125</v>
       </c>
       <c r="L3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="M3" t="s">
         <v>124</v>
@@ -14844,7 +14830,7 @@
         <v>124</v>
       </c>
       <c r="O3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="P3" t="s">
         <v>133</v>
@@ -14852,10 +14838,10 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="C4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -14870,32 +14856,32 @@
         <v>1</v>
       </c>
       <c r="P4" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C5" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J5" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="K5">
         <v>0.01</v>
       </c>
       <c r="P5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="C6" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -14904,18 +14890,18 @@
         <v>0.01</v>
       </c>
       <c r="P6" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C7" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="K7">
         <v>9999</v>
@@ -14924,40 +14910,40 @@
         <v>1</v>
       </c>
       <c r="P7" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>746</v>
+      </c>
+      <c r="C8" t="s">
         <v>747</v>
       </c>
-      <c r="C8" t="s">
-        <v>748</v>
-      </c>
       <c r="J8" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="C9" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="J9" t="s">
+        <v>751</v>
+      </c>
+      <c r="P9" t="s">
         <v>752</v>
-      </c>
-      <c r="P9" t="s">
-        <v>753</v>
       </c>
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
+        <v>762</v>
+      </c>
+      <c r="C10" s="8" t="s">
         <v>763</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>764</v>
       </c>
     </row>
   </sheetData>
@@ -14982,7 +14968,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -14993,10 +14979,10 @@
         <v>58</v>
       </c>
       <c r="C2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -15007,7 +14993,7 @@
         <v>2</v>
       </c>
       <c r="C3" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D3" t="s">
         <v>133</v>
@@ -15015,13 +15001,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B4" t="s">
+        <v>627</v>
+      </c>
+      <c r="D4" t="s">
         <v>628</v>
-      </c>
-      <c r="D4" t="s">
-        <v>629</v>
       </c>
     </row>
   </sheetData>
@@ -15053,22 +15039,22 @@
         <v>60</v>
       </c>
       <c r="D2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="E2" t="s">
         <v>82</v>
       </c>
       <c r="F2" t="s">
+        <v>630</v>
+      </c>
+      <c r="G2" t="s">
         <v>631</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>632</v>
       </c>
-      <c r="H2" t="s">
-        <v>633</v>
-      </c>
       <c r="I2" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -15102,19 +15088,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" s="8" t="s">
+        <v>736</v>
+      </c>
+      <c r="B4" s="8" t="s">
         <v>737</v>
       </c>
-      <c r="B4" s="8" t="s">
+      <c r="C4" t="s">
         <v>738</v>
-      </c>
-      <c r="C4" t="s">
-        <v>739</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="I4" s="8" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
     </row>
   </sheetData>
@@ -15141,34 +15127,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>633</v>
+      </c>
+      <c r="C1" t="s">
         <v>634</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>635</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>636</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>637</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>638</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>639</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>640</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>641</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>642</v>
-      </c>
-      <c r="L1" t="s">
-        <v>643</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -15176,34 +15162,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>643</v>
+      </c>
+      <c r="C2" t="s">
         <v>644</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>645</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>646</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>647</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>648</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>649</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>650</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>651</v>
       </c>
-      <c r="J2" t="s">
-        <v>652</v>
-      </c>
       <c r="K2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="L2" t="s">
         <v>106</v>
@@ -15220,7 +15206,7 @@
         <v>126</v>
       </c>
       <c r="D3" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -15249,10 +15235,10 @@
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -15266,10 +15252,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="B5" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -15283,13 +15269,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="B6" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="E6" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -15303,10 +15289,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="B7" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -15320,10 +15306,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B8" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -15337,10 +15323,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="B9" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -15354,10 +15340,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="B10" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -15374,10 +15360,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B11" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -15391,10 +15377,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B12" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -15411,10 +15397,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="B13" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -15428,13 +15414,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="B14" t="s">
+        <v>663</v>
+      </c>
+      <c r="E14" t="s">
         <v>664</v>
-      </c>
-      <c r="E14" t="s">
-        <v>665</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -15451,13 +15437,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="B15" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="E15" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -15471,18 +15457,18 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="B16" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B17" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -15496,10 +15482,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="I18">
         <v>2</v>
@@ -15513,10 +15499,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B19" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="I19">
         <v>2</v>
@@ -15530,10 +15516,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B20" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -15547,10 +15533,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="B21" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -15564,10 +15550,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>672</v>
+      </c>
+      <c r="B22" t="s">
         <v>673</v>
-      </c>
-      <c r="B22" t="s">
-        <v>674</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -15581,10 +15567,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="B23" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -15595,10 +15581,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B24" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="I24">
         <v>2</v>
@@ -15612,10 +15598,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B25" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -15629,10 +15615,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B26" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -15671,28 +15657,28 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="C2" t="s">
         <v>87</v>
       </c>
       <c r="D2" t="s">
+        <v>678</v>
+      </c>
+      <c r="E2" t="s">
         <v>679</v>
-      </c>
-      <c r="E2" t="s">
-        <v>680</v>
       </c>
       <c r="F2" t="s">
         <v>89</v>
       </c>
       <c r="G2" t="s">
+        <v>680</v>
+      </c>
+      <c r="H2" t="s">
+        <v>333</v>
+      </c>
+      <c r="I2" t="s">
         <v>681</v>
-      </c>
-      <c r="H2" t="s">
-        <v>334</v>
-      </c>
-      <c r="I2" t="s">
-        <v>682</v>
       </c>
       <c r="J2" t="s">
         <v>64</v>
@@ -15721,7 +15707,7 @@
         <v>126</v>
       </c>
       <c r="H3" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="I3" t="s">
         <v>126</v>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\学习专用\ark_-n\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A6DD850-D562-4C36-AA9C-DBE2B3301640}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250A4979-BC58-40E5-83A6-D89616B264B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -23,18 +23,6 @@
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -297,7 +285,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1509" uniqueCount="783">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="785">
   <si>
     <t>Id</t>
   </si>
@@ -2730,6 +2718,14 @@
   </si>
   <si>
     <t>前锋剑术,部署影哨</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>可无视buff抑制检测</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsCancelable</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -3268,7 +3264,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
@@ -3427,48 +3423,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BS613"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.58203125" customWidth="1"/>
-    <col min="4" max="4" width="8.58203125" customWidth="1"/>
-    <col min="5" max="5" width="5.33203125" customWidth="1"/>
-    <col min="6" max="6" width="19.58203125" customWidth="1"/>
-    <col min="7" max="7" width="8.25" customWidth="1"/>
+    <col min="1" max="1" width="22.54296875" customWidth="1"/>
+    <col min="4" max="4" width="8.54296875" customWidth="1"/>
+    <col min="5" max="5" width="5.36328125" customWidth="1"/>
+    <col min="6" max="6" width="19.54296875" customWidth="1"/>
+    <col min="7" max="7" width="8.26953125" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08203125" customWidth="1"/>
-    <col min="13" max="13" width="5.58203125" customWidth="1"/>
+    <col min="12" max="12" width="4.08984375" customWidth="1"/>
+    <col min="13" max="13" width="5.54296875" customWidth="1"/>
     <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.75" customWidth="1"/>
-    <col min="16" max="16" width="10.83203125" customWidth="1"/>
-    <col min="17" max="18" width="3.83203125" customWidth="1"/>
-    <col min="19" max="20" width="3.58203125" customWidth="1"/>
-    <col min="21" max="21" width="10.25" customWidth="1"/>
-    <col min="22" max="22" width="9.58203125" customWidth="1"/>
-    <col min="23" max="23" width="10.75" customWidth="1"/>
-    <col min="24" max="24" width="12.83203125" customWidth="1"/>
-    <col min="25" max="25" width="13.08203125" customWidth="1"/>
-    <col min="26" max="26" width="10.75" customWidth="1"/>
+    <col min="15" max="15" width="7.7265625" customWidth="1"/>
+    <col min="16" max="16" width="10.81640625" customWidth="1"/>
+    <col min="17" max="18" width="3.81640625" customWidth="1"/>
+    <col min="19" max="20" width="3.54296875" customWidth="1"/>
+    <col min="21" max="21" width="10.26953125" customWidth="1"/>
+    <col min="22" max="22" width="9.54296875" customWidth="1"/>
+    <col min="23" max="23" width="10.7265625" customWidth="1"/>
+    <col min="24" max="24" width="12.81640625" customWidth="1"/>
+    <col min="25" max="25" width="13.08984375" customWidth="1"/>
+    <col min="26" max="26" width="10.7265625" customWidth="1"/>
     <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08203125" customWidth="1"/>
-    <col min="31" max="31" width="9.75" customWidth="1"/>
-    <col min="32" max="32" width="7.83203125" customWidth="1"/>
-    <col min="33" max="33" width="15.83203125" customWidth="1"/>
-    <col min="34" max="34" width="13.83203125" customWidth="1"/>
-    <col min="35" max="35" width="34.5" customWidth="1"/>
-    <col min="36" max="37" width="9.83203125" customWidth="1"/>
-    <col min="43" max="43" width="12.5" customWidth="1"/>
-    <col min="50" max="50" width="8.5" customWidth="1"/>
-    <col min="52" max="52" width="17.75" customWidth="1"/>
-    <col min="53" max="53" width="7.83203125" customWidth="1"/>
-    <col min="56" max="56" width="24.25" customWidth="1"/>
-    <col min="57" max="57" width="13.25" customWidth="1"/>
-    <col min="58" max="58" width="16.08203125" customWidth="1"/>
+    <col min="30" max="30" width="17.08984375" customWidth="1"/>
+    <col min="31" max="31" width="9.7265625" customWidth="1"/>
+    <col min="32" max="32" width="7.81640625" customWidth="1"/>
+    <col min="33" max="33" width="15.81640625" customWidth="1"/>
+    <col min="34" max="34" width="13.81640625" customWidth="1"/>
+    <col min="35" max="35" width="34.453125" customWidth="1"/>
+    <col min="36" max="37" width="9.81640625" customWidth="1"/>
+    <col min="43" max="43" width="12.453125" customWidth="1"/>
+    <col min="50" max="50" width="8.453125" customWidth="1"/>
+    <col min="52" max="52" width="17.7265625" customWidth="1"/>
+    <col min="53" max="53" width="7.81640625" customWidth="1"/>
+    <col min="56" max="56" width="24.26953125" customWidth="1"/>
+    <col min="57" max="57" width="13.26953125" customWidth="1"/>
+    <col min="58" max="58" width="16.08984375" customWidth="1"/>
     <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.58203125" customWidth="1"/>
+    <col min="64" max="64" width="39.54296875" customWidth="1"/>
     <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.83203125" customWidth="1"/>
+    <col min="66" max="66" width="14.81640625" customWidth="1"/>
     <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1640625" customWidth="1"/>
+    <col min="71" max="71" width="19.1796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.25">
@@ -6012,2755 +6008,2755 @@
       <c r="AI50" s="8"/>
       <c r="BK50" s="8"/>
     </row>
-    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D51" s="6"/>
       <c r="E51" s="1"/>
       <c r="BO51" s="7"/>
       <c r="BR51" s="7"/>
     </row>
-    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D52" s="6"/>
       <c r="E52" s="1"/>
       <c r="BO52" s="7"/>
       <c r="BR52" s="7"/>
     </row>
-    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D53" s="6"/>
       <c r="E53" s="1"/>
       <c r="BO53" s="7"/>
       <c r="BR53" s="7"/>
     </row>
-    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D54" s="6"/>
       <c r="E54" s="1"/>
       <c r="BO54" s="7"/>
       <c r="BR54" s="7"/>
     </row>
-    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D55" s="6"/>
       <c r="E55" s="1"/>
       <c r="BO55" s="7"/>
       <c r="BR55" s="7"/>
     </row>
-    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D56" s="6"/>
       <c r="E56" s="1"/>
       <c r="BO56" s="7"/>
       <c r="BR56" s="7"/>
     </row>
-    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D57" s="6"/>
       <c r="E57" s="1"/>
       <c r="BO57" s="7"/>
       <c r="BR57" s="7"/>
     </row>
-    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D58" s="6"/>
       <c r="E58" s="1"/>
       <c r="BR58" s="7"/>
     </row>
-    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D59" s="6"/>
       <c r="E59" s="1"/>
       <c r="BR59" s="7"/>
     </row>
-    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D60" s="6"/>
       <c r="E60" s="1"/>
       <c r="BR60" s="7"/>
     </row>
-    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D61" s="6"/>
       <c r="E61" s="1"/>
       <c r="BO61" s="7"/>
       <c r="BR61" s="7"/>
     </row>
-    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D62" s="6"/>
       <c r="E62" s="1"/>
       <c r="BO62" s="7"/>
       <c r="BR62" s="7"/>
     </row>
-    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D63" s="6"/>
       <c r="E63" s="1"/>
       <c r="BO63" s="7"/>
       <c r="BR63" s="7"/>
     </row>
-    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D64" s="6"/>
       <c r="E64" s="1"/>
       <c r="BO64" s="7"/>
       <c r="BR64" s="7"/>
     </row>
-    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D65" s="6"/>
       <c r="E65" s="1"/>
       <c r="BO65" s="7"/>
       <c r="BR65" s="7"/>
     </row>
-    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D66" s="6"/>
       <c r="E66" s="1"/>
       <c r="BO66" s="7"/>
       <c r="BR66" s="7"/>
     </row>
-    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D67" s="6"/>
       <c r="E67" s="1"/>
       <c r="BO67" s="7"/>
       <c r="BR67" s="7"/>
     </row>
-    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D68" s="6"/>
       <c r="E68" s="1"/>
       <c r="BO68" s="7"/>
       <c r="BR68" s="7"/>
     </row>
-    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D69" s="6"/>
       <c r="E69" s="1"/>
       <c r="BO69" s="7"/>
       <c r="BR69" s="7"/>
     </row>
-    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D70" s="6"/>
       <c r="E70" s="1"/>
       <c r="BO70" s="7"/>
       <c r="BR70" s="7"/>
     </row>
-    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D71" s="6"/>
       <c r="E71" s="1"/>
       <c r="BO71" s="7"/>
       <c r="BR71" s="7"/>
     </row>
-    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D72" s="6"/>
       <c r="E72" s="1"/>
       <c r="BO72" s="7"/>
       <c r="BR72" s="7"/>
     </row>
-    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D73" s="6"/>
       <c r="E73" s="1"/>
       <c r="BO73" s="7"/>
       <c r="BR73" s="7"/>
     </row>
-    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D74" s="6"/>
       <c r="E74" s="1"/>
       <c r="BO74" s="7"/>
       <c r="BR74" s="7"/>
     </row>
-    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D75" s="6"/>
       <c r="E75" s="1"/>
       <c r="BO75" s="7"/>
       <c r="BR75" s="7"/>
     </row>
-    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D76" s="6"/>
       <c r="E76" s="1"/>
       <c r="BO76" s="7"/>
       <c r="BR76" s="7"/>
     </row>
-    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D77" s="6"/>
       <c r="E77" s="1"/>
       <c r="BO77" s="7"/>
       <c r="BR77" s="7"/>
     </row>
-    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D78" s="6"/>
       <c r="E78" s="1"/>
       <c r="BO78" s="7"/>
       <c r="BR78" s="7"/>
     </row>
-    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D79" s="6"/>
       <c r="E79" s="1"/>
       <c r="BO79" s="7"/>
       <c r="BR79" s="7"/>
     </row>
-    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D80" s="6"/>
       <c r="E80" s="1"/>
       <c r="BO80" s="7"/>
       <c r="BR80" s="7"/>
     </row>
-    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D81" s="6"/>
       <c r="E81" s="1"/>
       <c r="BO81" s="7"/>
       <c r="BR81" s="7"/>
     </row>
-    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D82" s="6"/>
       <c r="E82" s="1"/>
       <c r="BO82" s="7"/>
       <c r="BR82" s="7"/>
     </row>
-    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D83" s="6"/>
       <c r="E83" s="1"/>
       <c r="BO83" s="7"/>
       <c r="BR83" s="7"/>
     </row>
-    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D84" s="6"/>
       <c r="E84" s="1"/>
       <c r="BO84" s="7"/>
       <c r="BR84" s="7"/>
     </row>
-    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D85" s="6"/>
       <c r="E85" s="1"/>
       <c r="BO85" s="7"/>
       <c r="BR85" s="7"/>
     </row>
-    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D86" s="6"/>
       <c r="E86" s="1"/>
       <c r="BO86" s="7"/>
       <c r="BR86" s="7"/>
     </row>
-    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="1"/>
       <c r="BO87" s="7"/>
       <c r="BR87" s="7"/>
     </row>
-    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="1"/>
       <c r="BO88" s="7"/>
       <c r="BR88" s="7"/>
     </row>
-    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="1"/>
       <c r="BO89" s="7"/>
       <c r="BR89" s="7"/>
     </row>
-    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="1"/>
       <c r="BO90" s="7"/>
       <c r="BR90" s="7"/>
     </row>
-    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="1"/>
       <c r="BO91" s="7"/>
       <c r="BR91" s="7"/>
     </row>
-    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="1"/>
       <c r="BO92" s="7"/>
       <c r="BR92" s="7"/>
     </row>
-    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D93" s="6"/>
       <c r="E93" s="1"/>
       <c r="BO93" s="7"/>
       <c r="BR93" s="7"/>
     </row>
-    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D94" s="6"/>
       <c r="E94" s="1"/>
       <c r="BO94" s="7"/>
       <c r="BR94" s="7"/>
     </row>
-    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D95" s="6"/>
       <c r="E95" s="1"/>
       <c r="BO95" s="7"/>
       <c r="BR95" s="7"/>
     </row>
-    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D96" s="6"/>
       <c r="E96" s="1"/>
       <c r="BO96" s="7"/>
       <c r="BR96" s="7"/>
     </row>
-    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D97" s="6"/>
       <c r="E97" s="1"/>
       <c r="BO97" s="7"/>
       <c r="BR97" s="7"/>
     </row>
-    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D98" s="6"/>
       <c r="E98" s="1"/>
       <c r="BO98" s="7"/>
       <c r="BR98" s="7"/>
     </row>
-    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D99" s="6"/>
       <c r="E99" s="1"/>
       <c r="BO99" s="7"/>
       <c r="BR99" s="7"/>
     </row>
-    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D100" s="6"/>
       <c r="E100" s="1"/>
       <c r="BO100" s="7"/>
       <c r="BR100" s="7"/>
     </row>
-    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D101" s="6"/>
       <c r="E101" s="1"/>
       <c r="BO101" s="7"/>
       <c r="BR101" s="7"/>
     </row>
-    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D102" s="6"/>
       <c r="E102" s="1"/>
       <c r="BO102" s="7"/>
       <c r="BR102" s="7"/>
     </row>
-    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D103" s="6"/>
       <c r="E103" s="1"/>
       <c r="BO103" s="7"/>
       <c r="BR103" s="7"/>
     </row>
-    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D104" s="6"/>
       <c r="E104" s="1"/>
       <c r="BO104" s="7"/>
       <c r="BR104" s="7"/>
     </row>
-    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="1"/>
       <c r="BO105" s="7"/>
       <c r="BR105" s="7"/>
     </row>
-    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D106" s="6"/>
       <c r="E106" s="1"/>
       <c r="BO106" s="7"/>
       <c r="BR106" s="7"/>
     </row>
-    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="1"/>
       <c r="BO107" s="7"/>
       <c r="BR107" s="7"/>
     </row>
-    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="1"/>
       <c r="BO108" s="7"/>
       <c r="BR108" s="7"/>
     </row>
-    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="1"/>
       <c r="BO109" s="7"/>
       <c r="BR109" s="7"/>
     </row>
-    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="1"/>
       <c r="BO110" s="7"/>
       <c r="BR110" s="7"/>
     </row>
-    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="1"/>
       <c r="BO111" s="7"/>
       <c r="BR111" s="7"/>
     </row>
-    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="1"/>
       <c r="BO112" s="7"/>
       <c r="BR112" s="7"/>
     </row>
-    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="1"/>
       <c r="BO113" s="7"/>
       <c r="BR113" s="7"/>
     </row>
-    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="1"/>
       <c r="BO114" s="7"/>
       <c r="BR114" s="7"/>
     </row>
-    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="1"/>
       <c r="BO115" s="7"/>
       <c r="BR115" s="7"/>
     </row>
-    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
       <c r="E116" s="1"/>
       <c r="BO116" s="7"/>
       <c r="BR116" s="7"/>
     </row>
-    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
       <c r="E117" s="1"/>
       <c r="BO117" s="7"/>
       <c r="BR117" s="7"/>
     </row>
-    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D118" s="6"/>
       <c r="E118" s="1"/>
       <c r="BO118" s="7"/>
       <c r="BR118" s="7"/>
     </row>
-    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D119" s="6"/>
       <c r="E119" s="1"/>
       <c r="BO119" s="7"/>
       <c r="BR119" s="7"/>
     </row>
-    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D120" s="6"/>
       <c r="E120" s="1"/>
       <c r="BO120" s="7"/>
       <c r="BR120" s="7"/>
     </row>
-    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="1"/>
       <c r="BO121" s="7"/>
       <c r="BR121" s="7"/>
     </row>
-    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D122" s="6"/>
       <c r="E122" s="1"/>
       <c r="BO122" s="7"/>
       <c r="BR122" s="7"/>
     </row>
-    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D123" s="6"/>
       <c r="E123" s="1"/>
       <c r="BO123" s="7"/>
       <c r="BR123" s="7"/>
     </row>
-    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D124" s="6"/>
       <c r="E124" s="1"/>
       <c r="BO124" s="7"/>
       <c r="BR124" s="7"/>
     </row>
-    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D125" s="6"/>
       <c r="E125" s="1"/>
       <c r="BO125" s="7"/>
       <c r="BR125" s="7"/>
     </row>
-    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D126" s="6"/>
       <c r="E126" s="1"/>
       <c r="BO126" s="7"/>
       <c r="BR126" s="7"/>
     </row>
-    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
       <c r="E127" s="1"/>
       <c r="BO127" s="7"/>
       <c r="BR127" s="7"/>
     </row>
-    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
       <c r="E128" s="1"/>
       <c r="BO128" s="7"/>
       <c r="BR128" s="7"/>
     </row>
-    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D129" s="6"/>
       <c r="E129" s="1"/>
       <c r="BO129" s="7"/>
       <c r="BR129" s="7"/>
     </row>
-    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D130" s="6"/>
       <c r="E130" s="1"/>
       <c r="BO130" s="7"/>
       <c r="BR130" s="7"/>
     </row>
-    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D131" s="6"/>
       <c r="E131" s="1"/>
       <c r="BO131" s="7"/>
       <c r="BR131" s="7"/>
     </row>
-    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D132" s="6"/>
       <c r="E132" s="1"/>
       <c r="BO132" s="7"/>
       <c r="BR132" s="7"/>
     </row>
-    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D133" s="6"/>
       <c r="E133" s="1"/>
       <c r="BO133" s="7"/>
       <c r="BR133" s="7"/>
     </row>
-    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D134" s="6"/>
       <c r="E134" s="1"/>
       <c r="BO134" s="7"/>
       <c r="BR134" s="7"/>
     </row>
-    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D135" s="6"/>
       <c r="E135" s="1"/>
       <c r="BO135" s="7"/>
       <c r="BR135" s="7"/>
     </row>
-    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D136" s="6"/>
       <c r="E136" s="1"/>
       <c r="BO136" s="7"/>
       <c r="BR136" s="7"/>
     </row>
-    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D137" s="6"/>
       <c r="E137" s="1"/>
       <c r="BO137" s="7"/>
       <c r="BR137" s="7"/>
     </row>
-    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D138" s="6"/>
       <c r="E138" s="1"/>
       <c r="BO138" s="7"/>
       <c r="BR138" s="7"/>
     </row>
-    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D139" s="6"/>
       <c r="E139" s="1"/>
       <c r="BO139" s="7"/>
       <c r="BR139" s="7"/>
     </row>
-    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D140" s="6"/>
       <c r="E140" s="1"/>
       <c r="BO140" s="7"/>
       <c r="BR140" s="7"/>
     </row>
-    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D141" s="6"/>
       <c r="E141" s="1"/>
       <c r="BO141" s="7"/>
       <c r="BR141" s="7"/>
     </row>
-    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D142" s="6"/>
       <c r="E142" s="1"/>
       <c r="BO142" s="7"/>
       <c r="BR142" s="7"/>
     </row>
-    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D143" s="6"/>
       <c r="E143" s="1"/>
       <c r="BO143" s="7"/>
       <c r="BR143" s="7"/>
     </row>
-    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D144" s="6"/>
       <c r="E144" s="1"/>
       <c r="BO144" s="7"/>
       <c r="BR144" s="7"/>
     </row>
-    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D145" s="6"/>
       <c r="E145" s="1"/>
       <c r="BO145" s="7"/>
       <c r="BR145" s="7"/>
     </row>
-    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D146" s="6"/>
       <c r="E146" s="1"/>
       <c r="BO146" s="7"/>
       <c r="BR146" s="7"/>
     </row>
-    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D147" s="6"/>
       <c r="E147" s="1"/>
       <c r="BO147" s="7"/>
       <c r="BR147" s="7"/>
     </row>
-    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D148" s="6"/>
       <c r="E148" s="1"/>
       <c r="BO148" s="7"/>
       <c r="BR148" s="7"/>
     </row>
-    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D149" s="6"/>
       <c r="E149" s="1"/>
       <c r="BO149" s="7"/>
       <c r="BR149" s="7"/>
     </row>
-    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D150" s="6"/>
       <c r="E150" s="1"/>
       <c r="BO150" s="7"/>
       <c r="BR150" s="7"/>
     </row>
-    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D151" s="6"/>
       <c r="E151" s="1"/>
       <c r="BO151" s="7"/>
       <c r="BR151" s="7"/>
     </row>
-    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D152" s="6"/>
       <c r="E152" s="1"/>
       <c r="BO152" s="7"/>
       <c r="BR152" s="7"/>
     </row>
-    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D153" s="6"/>
       <c r="E153" s="1"/>
       <c r="BO153" s="7"/>
       <c r="BR153" s="7"/>
     </row>
-    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D154" s="6"/>
       <c r="E154" s="1"/>
       <c r="BO154" s="7"/>
       <c r="BR154" s="7"/>
     </row>
-    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D155" s="6"/>
       <c r="E155" s="1"/>
       <c r="BO155" s="7"/>
       <c r="BR155" s="7"/>
     </row>
-    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D156" s="6"/>
       <c r="E156" s="1"/>
       <c r="BO156" s="7"/>
       <c r="BR156" s="7"/>
     </row>
-    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D157" s="6"/>
       <c r="E157" s="1"/>
       <c r="BO157" s="7"/>
       <c r="BR157" s="7"/>
     </row>
-    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D158" s="6"/>
       <c r="E158" s="1"/>
       <c r="BO158" s="7"/>
       <c r="BR158" s="7"/>
     </row>
-    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D159" s="6"/>
       <c r="E159" s="1"/>
       <c r="BO159" s="7"/>
       <c r="BR159" s="7"/>
     </row>
-    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D160" s="6"/>
       <c r="E160" s="1"/>
       <c r="BO160" s="7"/>
       <c r="BR160" s="7"/>
     </row>
-    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D161" s="6"/>
       <c r="E161" s="1"/>
       <c r="BO161" s="7"/>
       <c r="BR161" s="7"/>
     </row>
-    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D162" s="6"/>
       <c r="E162" s="1"/>
       <c r="BO162" s="7"/>
       <c r="BR162" s="7"/>
     </row>
-    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D163" s="6"/>
       <c r="E163" s="1"/>
       <c r="BO163" s="7"/>
       <c r="BR163" s="7"/>
     </row>
-    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D164" s="6"/>
       <c r="E164" s="1"/>
       <c r="BO164" s="7"/>
       <c r="BR164" s="7"/>
     </row>
-    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D165" s="6"/>
       <c r="E165" s="1"/>
       <c r="BO165" s="7"/>
       <c r="BR165" s="7"/>
     </row>
-    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D166" s="6"/>
       <c r="E166" s="1"/>
       <c r="BO166" s="7"/>
       <c r="BR166" s="7"/>
     </row>
-    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D167" s="6"/>
       <c r="E167" s="1"/>
       <c r="BO167" s="7"/>
       <c r="BR167" s="7"/>
     </row>
-    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D168" s="6"/>
       <c r="E168" s="1"/>
       <c r="BO168" s="7"/>
       <c r="BR168" s="7"/>
     </row>
-    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D169" s="6"/>
       <c r="E169" s="1"/>
       <c r="BO169" s="7"/>
       <c r="BR169" s="7"/>
     </row>
-    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D170" s="6"/>
       <c r="E170" s="1"/>
       <c r="BO170" s="7"/>
       <c r="BR170" s="7"/>
     </row>
-    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D171" s="6"/>
       <c r="E171" s="1"/>
       <c r="BO171" s="7"/>
       <c r="BR171" s="7"/>
     </row>
-    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D172" s="6"/>
       <c r="E172" s="1"/>
       <c r="BO172" s="7"/>
       <c r="BR172" s="7"/>
     </row>
-    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D173" s="6"/>
       <c r="E173" s="1"/>
       <c r="BO173" s="7"/>
       <c r="BR173" s="7"/>
     </row>
-    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D174" s="6"/>
       <c r="E174" s="1"/>
       <c r="BO174" s="7"/>
       <c r="BR174" s="7"/>
     </row>
-    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D175" s="6"/>
       <c r="E175" s="1"/>
       <c r="BO175" s="7"/>
       <c r="BR175" s="7"/>
     </row>
-    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D176" s="6"/>
       <c r="E176" s="1"/>
       <c r="BO176" s="7"/>
       <c r="BR176" s="7"/>
     </row>
-    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D177" s="6"/>
       <c r="E177" s="1"/>
       <c r="BO177" s="7"/>
       <c r="BR177" s="7"/>
     </row>
-    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D178" s="6"/>
       <c r="E178" s="1"/>
       <c r="BO178" s="7"/>
       <c r="BR178" s="7"/>
     </row>
-    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D179" s="6"/>
       <c r="E179" s="1"/>
       <c r="BO179" s="7"/>
       <c r="BR179" s="7"/>
     </row>
-    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D180" s="6"/>
       <c r="E180" s="1"/>
       <c r="BO180" s="7"/>
       <c r="BR180" s="7"/>
     </row>
-    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D181" s="6"/>
       <c r="E181" s="1"/>
       <c r="BO181" s="7"/>
       <c r="BR181" s="7"/>
     </row>
-    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D182" s="6"/>
       <c r="E182" s="1"/>
       <c r="BO182" s="7"/>
       <c r="BR182" s="7"/>
     </row>
-    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D183" s="6"/>
       <c r="E183" s="1"/>
       <c r="BO183" s="7"/>
       <c r="BR183" s="7"/>
     </row>
-    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D184" s="6"/>
       <c r="E184" s="1"/>
       <c r="BO184" s="7"/>
       <c r="BR184" s="7"/>
     </row>
-    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D185" s="6"/>
       <c r="E185" s="1"/>
       <c r="BO185" s="7"/>
       <c r="BR185" s="7"/>
     </row>
-    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D186" s="6"/>
       <c r="E186" s="1"/>
       <c r="BO186" s="7"/>
       <c r="BR186" s="7"/>
     </row>
-    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D187" s="6"/>
       <c r="E187" s="1"/>
       <c r="BO187" s="7"/>
       <c r="BR187" s="7"/>
     </row>
-    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D188" s="6"/>
       <c r="E188" s="1"/>
       <c r="BO188" s="7"/>
       <c r="BR188" s="7"/>
     </row>
-    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D189" s="6"/>
       <c r="E189" s="1"/>
       <c r="BO189" s="7"/>
       <c r="BR189" s="7"/>
     </row>
-    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D190" s="6"/>
       <c r="E190" s="1"/>
       <c r="BO190" s="7"/>
       <c r="BR190" s="7"/>
     </row>
-    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D191" s="6"/>
       <c r="E191" s="1"/>
       <c r="BO191" s="7"/>
       <c r="BR191" s="7"/>
     </row>
-    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D192" s="6"/>
       <c r="E192" s="1"/>
       <c r="BO192" s="7"/>
       <c r="BR192" s="7"/>
     </row>
-    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D193" s="6"/>
       <c r="E193" s="1"/>
       <c r="BO193" s="7"/>
       <c r="BR193" s="7"/>
     </row>
-    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D194" s="6"/>
       <c r="E194" s="1"/>
       <c r="BO194" s="7"/>
       <c r="BR194" s="7"/>
     </row>
-    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D195" s="6"/>
       <c r="E195" s="1"/>
       <c r="BO195" s="7"/>
       <c r="BR195" s="7"/>
     </row>
-    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D196" s="6"/>
       <c r="E196" s="1"/>
       <c r="BO196" s="7"/>
       <c r="BR196" s="7"/>
     </row>
-    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D197" s="6"/>
       <c r="E197" s="1"/>
       <c r="BO197" s="7"/>
       <c r="BR197" s="7"/>
     </row>
-    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D198" s="6"/>
       <c r="E198" s="1"/>
       <c r="BO198" s="7"/>
       <c r="BR198" s="7"/>
     </row>
-    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D199" s="6"/>
       <c r="E199" s="1"/>
       <c r="BO199" s="7"/>
       <c r="BR199" s="7"/>
     </row>
-    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D200" s="6"/>
       <c r="E200" s="1"/>
       <c r="BO200" s="7"/>
       <c r="BR200" s="7"/>
     </row>
-    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D201" s="6"/>
       <c r="E201" s="1"/>
       <c r="BO201" s="7"/>
       <c r="BR201" s="7"/>
     </row>
-    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D202" s="6"/>
       <c r="E202" s="1"/>
       <c r="BO202" s="7"/>
       <c r="BR202" s="7"/>
     </row>
-    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D203" s="6"/>
       <c r="E203" s="1"/>
       <c r="BO203" s="7"/>
       <c r="BR203" s="7"/>
     </row>
-    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D204" s="6"/>
       <c r="E204" s="1"/>
       <c r="BO204" s="7"/>
       <c r="BR204" s="7"/>
     </row>
-    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D205" s="6"/>
       <c r="E205" s="1"/>
       <c r="BO205" s="7"/>
       <c r="BR205" s="7"/>
     </row>
-    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D206" s="6"/>
       <c r="E206" s="1"/>
       <c r="BO206" s="7"/>
       <c r="BR206" s="7"/>
     </row>
-    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D207" s="6"/>
       <c r="E207" s="1"/>
       <c r="BO207" s="7"/>
       <c r="BR207" s="7"/>
     </row>
-    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D208" s="6"/>
       <c r="E208" s="1"/>
       <c r="BO208" s="7"/>
       <c r="BR208" s="7"/>
     </row>
-    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D209" s="6"/>
       <c r="E209" s="1"/>
       <c r="BO209" s="7"/>
       <c r="BR209" s="7"/>
     </row>
-    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D210" s="6"/>
       <c r="E210" s="1"/>
       <c r="BO210" s="7"/>
       <c r="BR210" s="7"/>
     </row>
-    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D211" s="6"/>
       <c r="E211" s="1"/>
       <c r="BO211" s="7"/>
       <c r="BR211" s="7"/>
     </row>
-    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D212" s="6"/>
       <c r="E212" s="1"/>
       <c r="BO212" s="7"/>
       <c r="BR212" s="7"/>
     </row>
-    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D213" s="6"/>
       <c r="E213" s="1"/>
       <c r="BO213" s="7"/>
       <c r="BR213" s="7"/>
     </row>
-    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D214" s="6"/>
       <c r="E214" s="1"/>
       <c r="BO214" s="7"/>
       <c r="BR214" s="7"/>
     </row>
-    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D215" s="6"/>
       <c r="E215" s="1"/>
       <c r="BO215" s="7"/>
       <c r="BR215" s="7"/>
     </row>
-    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D216" s="6"/>
       <c r="E216" s="1"/>
       <c r="BO216" s="7"/>
       <c r="BR216" s="7"/>
     </row>
-    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D217" s="6"/>
       <c r="E217" s="1"/>
       <c r="BO217" s="7"/>
       <c r="BR217" s="7"/>
     </row>
-    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D218" s="6"/>
       <c r="E218" s="1"/>
       <c r="BO218" s="7"/>
       <c r="BR218" s="7"/>
     </row>
-    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D219" s="6"/>
       <c r="E219" s="1"/>
       <c r="BO219" s="7"/>
       <c r="BR219" s="7"/>
     </row>
-    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D220" s="6"/>
       <c r="E220" s="1"/>
       <c r="BO220" s="7"/>
       <c r="BR220" s="7"/>
     </row>
-    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D221" s="6"/>
       <c r="E221" s="1"/>
       <c r="BO221" s="7"/>
       <c r="BR221" s="7"/>
     </row>
-    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D222" s="6"/>
       <c r="E222" s="1"/>
       <c r="BO222" s="7"/>
       <c r="BR222" s="7"/>
     </row>
-    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D223" s="6"/>
       <c r="E223" s="1"/>
       <c r="BO223" s="7"/>
       <c r="BR223" s="7"/>
     </row>
-    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D224" s="6"/>
       <c r="E224" s="1"/>
       <c r="BO224" s="7"/>
       <c r="BR224" s="7"/>
     </row>
-    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D225" s="6"/>
       <c r="E225" s="1"/>
       <c r="BO225" s="7"/>
       <c r="BR225" s="7"/>
     </row>
-    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D226" s="6"/>
       <c r="E226" s="1"/>
       <c r="BO226" s="7"/>
       <c r="BR226" s="7"/>
     </row>
-    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D227" s="6"/>
       <c r="E227" s="1"/>
       <c r="BO227" s="7"/>
       <c r="BR227" s="7"/>
     </row>
-    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D228" s="6"/>
       <c r="E228" s="1"/>
       <c r="BO228" s="7"/>
       <c r="BR228" s="7"/>
     </row>
-    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D229" s="6"/>
       <c r="E229" s="1"/>
       <c r="BO229" s="7"/>
       <c r="BR229" s="7"/>
     </row>
-    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D230" s="6"/>
       <c r="E230" s="1"/>
       <c r="BO230" s="7"/>
       <c r="BR230" s="7"/>
     </row>
-    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D231" s="6"/>
       <c r="E231" s="1"/>
       <c r="BO231" s="7"/>
       <c r="BR231" s="7"/>
     </row>
-    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D232" s="6"/>
       <c r="E232" s="1"/>
       <c r="BO232" s="7"/>
       <c r="BR232" s="7"/>
     </row>
-    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D233" s="6"/>
       <c r="E233" s="1"/>
       <c r="BO233" s="7"/>
       <c r="BR233" s="7"/>
     </row>
-    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D234" s="6"/>
       <c r="E234" s="1"/>
       <c r="BO234" s="7"/>
       <c r="BR234" s="7"/>
     </row>
-    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D235" s="6"/>
       <c r="E235" s="1"/>
       <c r="BO235" s="7"/>
       <c r="BR235" s="7"/>
     </row>
-    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D236" s="6"/>
       <c r="E236" s="1"/>
       <c r="BO236" s="7"/>
       <c r="BR236" s="7"/>
     </row>
-    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D237" s="6"/>
       <c r="E237" s="1"/>
       <c r="BO237" s="7"/>
       <c r="BR237" s="7"/>
     </row>
-    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D238" s="6"/>
       <c r="E238" s="1"/>
       <c r="BO238" s="7"/>
       <c r="BR238" s="7"/>
     </row>
-    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D239" s="6"/>
       <c r="E239" s="1"/>
       <c r="BO239" s="7"/>
       <c r="BR239" s="7"/>
     </row>
-    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D240" s="6"/>
       <c r="E240" s="1"/>
       <c r="BO240" s="7"/>
       <c r="BR240" s="7"/>
     </row>
-    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D241" s="6"/>
       <c r="E241" s="1"/>
       <c r="BO241" s="7"/>
       <c r="BR241" s="7"/>
     </row>
-    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D242" s="6"/>
       <c r="E242" s="1"/>
       <c r="BO242" s="7"/>
       <c r="BR242" s="7"/>
     </row>
-    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D243" s="6"/>
       <c r="E243" s="1"/>
       <c r="BO243" s="7"/>
       <c r="BR243" s="7"/>
     </row>
-    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D244" s="6"/>
       <c r="E244" s="1"/>
       <c r="BO244" s="7"/>
       <c r="BR244" s="7"/>
     </row>
-    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D245" s="6"/>
       <c r="E245" s="1"/>
       <c r="BO245" s="7"/>
       <c r="BR245" s="7"/>
     </row>
-    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D246" s="6"/>
       <c r="E246" s="1"/>
       <c r="BO246" s="7"/>
       <c r="BR246" s="7"/>
     </row>
-    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D247" s="6"/>
       <c r="E247" s="1"/>
       <c r="BO247" s="7"/>
       <c r="BR247" s="7"/>
     </row>
-    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D248" s="6"/>
       <c r="E248" s="1"/>
       <c r="BO248" s="7"/>
       <c r="BR248" s="7"/>
     </row>
-    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D249" s="6"/>
       <c r="E249" s="1"/>
       <c r="BO249" s="7"/>
       <c r="BR249" s="7"/>
     </row>
-    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D250" s="6"/>
       <c r="E250" s="1"/>
       <c r="BO250" s="7"/>
       <c r="BR250" s="7"/>
     </row>
-    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D251" s="6"/>
       <c r="E251" s="1"/>
       <c r="BO251" s="7"/>
       <c r="BR251" s="7"/>
     </row>
-    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D252" s="6"/>
       <c r="E252" s="1"/>
       <c r="BO252" s="7"/>
       <c r="BR252" s="7"/>
     </row>
-    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D253" s="6"/>
       <c r="E253" s="1"/>
       <c r="BO253" s="7"/>
       <c r="BR253" s="7"/>
     </row>
-    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D254" s="6"/>
       <c r="E254" s="1"/>
       <c r="BO254" s="7"/>
       <c r="BR254" s="7"/>
     </row>
-    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D255" s="6"/>
       <c r="E255" s="1"/>
       <c r="BO255" s="7"/>
       <c r="BR255" s="7"/>
     </row>
-    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D256" s="6"/>
       <c r="E256" s="1"/>
       <c r="BO256" s="7"/>
       <c r="BR256" s="7"/>
     </row>
-    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D257" s="6"/>
       <c r="E257" s="1"/>
       <c r="BO257" s="7"/>
       <c r="BR257" s="7"/>
     </row>
-    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D258" s="6"/>
       <c r="E258" s="1"/>
       <c r="BR258" s="7"/>
     </row>
-    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D259" s="6"/>
       <c r="E259" s="1"/>
       <c r="BO259" s="7"/>
       <c r="BR259" s="7"/>
     </row>
-    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D260" s="6"/>
       <c r="E260" s="1"/>
       <c r="BO260" s="7"/>
       <c r="BR260" s="7"/>
     </row>
-    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D261" s="6"/>
       <c r="E261" s="1"/>
       <c r="BO261" s="7"/>
       <c r="BR261" s="7"/>
     </row>
-    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D262" s="6"/>
       <c r="E262" s="1"/>
       <c r="BO262" s="7"/>
       <c r="BR262" s="7"/>
     </row>
-    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D263" s="6"/>
       <c r="E263" s="1"/>
       <c r="BO263" s="7"/>
       <c r="BR263" s="7"/>
     </row>
-    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D264" s="6"/>
       <c r="E264" s="1"/>
       <c r="BO264" s="7"/>
       <c r="BR264" s="7"/>
     </row>
-    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D265" s="6"/>
       <c r="E265" s="1"/>
       <c r="BO265" s="7"/>
       <c r="BR265" s="7"/>
     </row>
-    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D266" s="6"/>
       <c r="E266" s="1"/>
       <c r="BO266" s="7"/>
       <c r="BR266" s="7"/>
     </row>
-    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D267" s="6"/>
       <c r="E267" s="1"/>
       <c r="BO267" s="7"/>
       <c r="BR267" s="7"/>
     </row>
-    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D268" s="6"/>
       <c r="E268" s="1"/>
       <c r="BO268" s="7"/>
       <c r="BR268" s="7"/>
     </row>
-    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D269" s="6"/>
       <c r="E269" s="1"/>
       <c r="BO269" s="7"/>
       <c r="BR269" s="7"/>
     </row>
-    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D270" s="6"/>
       <c r="E270" s="1"/>
       <c r="BO270" s="7"/>
       <c r="BR270" s="7"/>
     </row>
-    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D271" s="6"/>
       <c r="E271" s="1"/>
       <c r="BO271" s="7"/>
       <c r="BR271" s="7"/>
     </row>
-    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D272" s="6"/>
       <c r="E272" s="1"/>
       <c r="BO272" s="7"/>
       <c r="BR272" s="7"/>
     </row>
-    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D273" s="6"/>
       <c r="E273" s="1"/>
       <c r="BO273" s="7"/>
       <c r="BR273" s="7"/>
     </row>
-    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D274" s="6"/>
       <c r="E274" s="1"/>
       <c r="BO274" s="7"/>
       <c r="BR274" s="7"/>
     </row>
-    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D275" s="6"/>
       <c r="E275" s="1"/>
       <c r="BO275" s="7"/>
       <c r="BR275" s="7"/>
     </row>
-    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D276" s="6"/>
       <c r="E276" s="1"/>
       <c r="BO276" s="7"/>
       <c r="BR276" s="7"/>
     </row>
-    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D277" s="6"/>
       <c r="E277" s="1"/>
       <c r="BO277" s="7"/>
       <c r="BR277" s="7"/>
     </row>
-    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D278" s="6"/>
       <c r="E278" s="1"/>
       <c r="BO278" s="7"/>
       <c r="BR278" s="7"/>
     </row>
-    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D279" s="6"/>
       <c r="E279" s="1"/>
       <c r="BO279" s="7"/>
       <c r="BR279" s="7"/>
     </row>
-    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D280" s="6"/>
       <c r="E280" s="1"/>
       <c r="BO280" s="7"/>
       <c r="BR280" s="7"/>
     </row>
-    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D281" s="6"/>
       <c r="E281" s="1"/>
       <c r="BO281" s="7"/>
       <c r="BR281" s="7"/>
     </row>
-    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D282" s="6"/>
       <c r="E282" s="1"/>
       <c r="BO282" s="7"/>
       <c r="BR282" s="7"/>
     </row>
-    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D283" s="6"/>
       <c r="E283" s="1"/>
       <c r="BO283" s="7"/>
       <c r="BR283" s="7"/>
     </row>
-    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D284" s="6"/>
       <c r="E284" s="1"/>
       <c r="BO284" s="7"/>
       <c r="BR284" s="7"/>
     </row>
-    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D285" s="6"/>
       <c r="E285" s="1"/>
       <c r="BO285" s="7"/>
       <c r="BR285" s="7"/>
     </row>
-    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D286" s="6"/>
       <c r="E286" s="1"/>
       <c r="BO286" s="7"/>
       <c r="BR286" s="7"/>
     </row>
-    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D287" s="6"/>
       <c r="E287" s="1"/>
       <c r="BO287" s="7"/>
       <c r="BR287" s="7"/>
     </row>
-    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D288" s="6"/>
       <c r="E288" s="1"/>
       <c r="BO288" s="7"/>
       <c r="BR288" s="7"/>
     </row>
-    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D289" s="6"/>
       <c r="E289" s="1"/>
       <c r="BO289" s="7"/>
       <c r="BR289" s="7"/>
     </row>
-    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D290" s="6"/>
       <c r="E290" s="1"/>
       <c r="BO290" s="7"/>
       <c r="BR290" s="7"/>
     </row>
-    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D291" s="6"/>
       <c r="E291" s="1"/>
       <c r="BO291" s="7"/>
       <c r="BR291" s="7"/>
     </row>
-    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D292" s="6"/>
       <c r="E292" s="1"/>
       <c r="BO292" s="7"/>
       <c r="BR292" s="7"/>
     </row>
-    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D293" s="6"/>
       <c r="E293" s="1"/>
       <c r="BO293" s="7"/>
       <c r="BR293" s="7"/>
     </row>
-    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D294" s="6"/>
       <c r="E294" s="1"/>
       <c r="BO294" s="7"/>
       <c r="BR294" s="7"/>
     </row>
-    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D295" s="6"/>
       <c r="E295" s="1"/>
       <c r="BO295" s="7"/>
       <c r="BR295" s="7"/>
     </row>
-    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D296" s="6"/>
       <c r="E296" s="1"/>
       <c r="BO296" s="7"/>
       <c r="BR296" s="7"/>
     </row>
-    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D297" s="6"/>
       <c r="E297" s="1"/>
       <c r="BO297" s="7"/>
       <c r="BR297" s="7"/>
     </row>
-    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D298" s="6"/>
       <c r="E298" s="1"/>
       <c r="BO298" s="7"/>
       <c r="BR298" s="7"/>
     </row>
-    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D299" s="6"/>
       <c r="E299" s="1"/>
       <c r="BO299" s="7"/>
       <c r="BR299" s="7"/>
     </row>
-    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D300" s="6"/>
       <c r="E300" s="1"/>
       <c r="BO300" s="7"/>
       <c r="BR300" s="7"/>
     </row>
-    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D301" s="6"/>
       <c r="E301" s="1"/>
       <c r="BR301" s="7"/>
     </row>
-    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D302" s="6"/>
       <c r="E302" s="1"/>
       <c r="BO302" s="7"/>
       <c r="BR302" s="7"/>
     </row>
-    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D303" s="6"/>
       <c r="E303" s="1"/>
       <c r="BO303" s="7"/>
       <c r="BR303" s="7"/>
     </row>
-    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D304" s="6"/>
       <c r="E304" s="1"/>
       <c r="BO304" s="7"/>
       <c r="BR304" s="7"/>
     </row>
-    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D305" s="6"/>
       <c r="E305" s="1"/>
       <c r="BO305" s="7"/>
       <c r="BR305" s="7"/>
     </row>
-    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D306" s="6"/>
       <c r="E306" s="1"/>
       <c r="BO306" s="7"/>
       <c r="BR306" s="7"/>
     </row>
-    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D307" s="6"/>
       <c r="E307" s="1"/>
       <c r="BO307" s="7"/>
       <c r="BR307" s="7"/>
     </row>
-    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D308" s="6"/>
       <c r="E308" s="1"/>
       <c r="BO308" s="7"/>
       <c r="BR308" s="7"/>
     </row>
-    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D309" s="6"/>
       <c r="E309" s="1"/>
       <c r="BO309" s="7"/>
       <c r="BR309" s="7"/>
     </row>
-    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D310" s="6"/>
       <c r="E310" s="1"/>
       <c r="BO310" s="7"/>
       <c r="BR310" s="7"/>
     </row>
-    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D311" s="6"/>
       <c r="E311" s="1"/>
       <c r="BO311" s="7"/>
       <c r="BR311" s="7"/>
     </row>
-    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D312" s="6"/>
       <c r="E312" s="1"/>
       <c r="BO312" s="7"/>
       <c r="BR312" s="7"/>
     </row>
-    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D313" s="6"/>
       <c r="E313" s="1"/>
       <c r="BO313" s="7"/>
       <c r="BR313" s="7"/>
     </row>
-    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D314" s="6"/>
       <c r="E314" s="1"/>
       <c r="BO314" s="7"/>
       <c r="BR314" s="7"/>
     </row>
-    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D315" s="6"/>
       <c r="E315" s="1"/>
       <c r="BO315" s="7"/>
       <c r="BR315" s="7"/>
     </row>
-    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D316" s="6"/>
       <c r="E316" s="1"/>
       <c r="BO316" s="7"/>
       <c r="BR316" s="7"/>
     </row>
-    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D317" s="6"/>
       <c r="E317" s="1"/>
       <c r="BO317" s="7"/>
       <c r="BR317" s="7"/>
     </row>
-    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D318" s="6"/>
       <c r="E318" s="1"/>
       <c r="BO318" s="7"/>
       <c r="BR318" s="7"/>
     </row>
-    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D319" s="6"/>
       <c r="E319" s="1"/>
       <c r="BO319" s="7"/>
       <c r="BR319" s="7"/>
     </row>
-    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D320" s="6"/>
       <c r="E320" s="1"/>
       <c r="BO320" s="7"/>
       <c r="BR320" s="7"/>
     </row>
-    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D321" s="6"/>
       <c r="E321" s="1"/>
       <c r="BO321" s="7"/>
       <c r="BR321" s="7"/>
     </row>
-    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D322" s="6"/>
       <c r="E322" s="1"/>
       <c r="BO322" s="7"/>
       <c r="BR322" s="7"/>
     </row>
-    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D323" s="6"/>
       <c r="E323" s="1"/>
       <c r="BO323" s="7"/>
       <c r="BR323" s="7"/>
     </row>
-    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D324" s="6"/>
       <c r="E324" s="1"/>
       <c r="BO324" s="7"/>
       <c r="BR324" s="7"/>
     </row>
-    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D325" s="6"/>
       <c r="E325" s="1"/>
       <c r="BO325" s="7"/>
       <c r="BR325" s="7"/>
     </row>
-    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D326" s="6"/>
       <c r="E326" s="1"/>
       <c r="BO326" s="7"/>
       <c r="BR326" s="7"/>
     </row>
-    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D327" s="6"/>
       <c r="E327" s="1"/>
       <c r="BO327" s="7"/>
       <c r="BR327" s="7"/>
     </row>
-    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D328" s="6"/>
       <c r="E328" s="1"/>
       <c r="BO328" s="7"/>
       <c r="BR328" s="7"/>
     </row>
-    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D329" s="6"/>
       <c r="E329" s="1"/>
       <c r="BO329" s="7"/>
       <c r="BR329" s="7"/>
     </row>
-    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D330" s="6"/>
       <c r="E330" s="1"/>
       <c r="BO330" s="7"/>
       <c r="BR330" s="7"/>
     </row>
-    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D331" s="6"/>
       <c r="E331" s="1"/>
       <c r="BO331" s="7"/>
       <c r="BR331" s="7"/>
     </row>
-    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D332" s="6"/>
       <c r="E332" s="1"/>
       <c r="BO332" s="7"/>
       <c r="BR332" s="7"/>
     </row>
-    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D333" s="6"/>
       <c r="E333" s="1"/>
       <c r="BO333" s="7"/>
       <c r="BR333" s="7"/>
     </row>
-    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D334" s="6"/>
       <c r="E334" s="1"/>
       <c r="BO334" s="7"/>
       <c r="BR334" s="7"/>
     </row>
-    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D335" s="6"/>
       <c r="E335" s="1"/>
       <c r="BO335" s="7"/>
       <c r="BR335" s="7"/>
     </row>
-    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D336" s="6"/>
       <c r="E336" s="1"/>
       <c r="BO336" s="7"/>
       <c r="BR336" s="7"/>
     </row>
-    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D337" s="6"/>
       <c r="E337" s="1"/>
       <c r="BO337" s="7"/>
       <c r="BR337" s="7"/>
     </row>
-    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D338" s="6"/>
       <c r="E338" s="1"/>
       <c r="BO338" s="7"/>
       <c r="BR338" s="7"/>
     </row>
-    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D339" s="6"/>
       <c r="E339" s="1"/>
       <c r="BO339" s="7"/>
       <c r="BR339" s="7"/>
     </row>
-    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D340" s="6"/>
       <c r="E340" s="1"/>
       <c r="BO340" s="7"/>
       <c r="BR340" s="7"/>
     </row>
-    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D341" s="6"/>
       <c r="E341" s="1"/>
       <c r="BO341" s="7"/>
       <c r="BR341" s="7"/>
     </row>
-    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D342" s="6"/>
       <c r="E342" s="1"/>
       <c r="BO342" s="7"/>
       <c r="BR342" s="7"/>
     </row>
-    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D343" s="6"/>
       <c r="E343" s="1"/>
       <c r="BO343" s="7"/>
       <c r="BR343" s="7"/>
     </row>
-    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D344" s="6"/>
       <c r="E344" s="1"/>
       <c r="BO344" s="7"/>
       <c r="BR344" s="7"/>
     </row>
-    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D345" s="6"/>
       <c r="E345" s="1"/>
       <c r="BO345" s="7"/>
       <c r="BR345" s="7"/>
     </row>
-    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D346" s="6"/>
       <c r="E346" s="1"/>
       <c r="BO346" s="7"/>
       <c r="BR346" s="7"/>
     </row>
-    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D347" s="6"/>
       <c r="E347" s="1"/>
       <c r="BO347" s="7"/>
       <c r="BR347" s="7"/>
     </row>
-    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D348" s="6"/>
       <c r="E348" s="1"/>
       <c r="BO348" s="7"/>
       <c r="BR348" s="7"/>
     </row>
-    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D349" s="6"/>
       <c r="E349" s="1"/>
       <c r="BO349" s="7"/>
       <c r="BR349" s="7"/>
     </row>
-    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D350" s="6"/>
       <c r="E350" s="1"/>
       <c r="BO350" s="7"/>
       <c r="BR350" s="7"/>
     </row>
-    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D351" s="6"/>
       <c r="E351" s="1"/>
       <c r="BO351" s="7"/>
       <c r="BR351" s="7"/>
     </row>
-    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D352" s="6"/>
       <c r="E352" s="1"/>
       <c r="BO352" s="7"/>
       <c r="BR352" s="7"/>
     </row>
-    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D353" s="6"/>
       <c r="E353" s="1"/>
       <c r="BO353" s="7"/>
       <c r="BR353" s="7"/>
     </row>
-    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D354" s="6"/>
       <c r="E354" s="1"/>
       <c r="BO354" s="7"/>
       <c r="BR354" s="7"/>
     </row>
-    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D355" s="6"/>
       <c r="E355" s="1"/>
       <c r="BO355" s="7"/>
       <c r="BR355" s="7"/>
     </row>
-    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D356" s="6"/>
       <c r="E356" s="1"/>
       <c r="BO356" s="7"/>
       <c r="BR356" s="7"/>
     </row>
-    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D357" s="6"/>
       <c r="E357" s="1"/>
       <c r="BR357" s="7"/>
     </row>
-    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D358" s="6"/>
       <c r="E358" s="1"/>
       <c r="BR358" s="7"/>
     </row>
-    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D359" s="6"/>
       <c r="E359" s="1"/>
       <c r="BR359" s="7"/>
     </row>
-    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D360" s="6"/>
       <c r="E360" s="1"/>
       <c r="BO360" s="7"/>
       <c r="BR360" s="7"/>
     </row>
-    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D361" s="6"/>
       <c r="E361" s="1"/>
       <c r="BO361" s="7"/>
       <c r="BR361" s="7"/>
     </row>
-    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D362" s="6"/>
       <c r="E362" s="1"/>
       <c r="BO362" s="7"/>
       <c r="BR362" s="7"/>
     </row>
-    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D363" s="6"/>
       <c r="E363" s="1"/>
       <c r="BO363" s="7"/>
       <c r="BR363" s="7"/>
     </row>
-    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D364" s="6"/>
       <c r="E364" s="1"/>
       <c r="BO364" s="7"/>
       <c r="BR364" s="7"/>
     </row>
-    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D365" s="6"/>
       <c r="E365" s="1"/>
       <c r="BO365" s="7"/>
       <c r="BR365" s="7"/>
     </row>
-    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D366" s="6"/>
       <c r="E366" s="1"/>
       <c r="BO366" s="7"/>
       <c r="BR366" s="7"/>
     </row>
-    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D367" s="6"/>
       <c r="E367" s="1"/>
       <c r="BO367" s="7"/>
       <c r="BR367" s="7"/>
     </row>
-    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D368" s="6"/>
       <c r="E368" s="1"/>
       <c r="BO368" s="7"/>
       <c r="BR368" s="7"/>
     </row>
-    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D369" s="6"/>
       <c r="E369" s="1"/>
       <c r="BO369" s="7"/>
       <c r="BR369" s="7"/>
     </row>
-    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D370" s="6"/>
       <c r="E370" s="1"/>
       <c r="BO370" s="7"/>
       <c r="BR370" s="7"/>
     </row>
-    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D371" s="6"/>
       <c r="E371" s="1"/>
       <c r="BO371" s="7"/>
       <c r="BR371" s="7"/>
     </row>
-    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D372" s="6"/>
       <c r="E372" s="1"/>
       <c r="BO372" s="7"/>
       <c r="BR372" s="7"/>
     </row>
-    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D373" s="6"/>
       <c r="E373" s="1"/>
       <c r="BO373" s="7"/>
       <c r="BR373" s="7"/>
     </row>
-    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D374" s="6"/>
       <c r="E374" s="1"/>
       <c r="BO374" s="7"/>
       <c r="BR374" s="7"/>
     </row>
-    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D375" s="6"/>
       <c r="E375" s="1"/>
       <c r="BO375" s="7"/>
       <c r="BR375" s="7"/>
     </row>
-    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D376" s="6"/>
       <c r="E376" s="1"/>
       <c r="BO376" s="7"/>
       <c r="BR376" s="7"/>
     </row>
-    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D377" s="6"/>
       <c r="E377" s="1"/>
       <c r="BO377" s="7"/>
       <c r="BR377" s="7"/>
     </row>
-    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D378" s="6"/>
       <c r="E378" s="1"/>
       <c r="BO378" s="7"/>
       <c r="BR378" s="7"/>
     </row>
-    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D379" s="6"/>
       <c r="E379" s="1"/>
       <c r="BO379" s="7"/>
       <c r="BR379" s="7"/>
     </row>
-    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D380" s="6"/>
       <c r="E380" s="1"/>
       <c r="BO380" s="7"/>
       <c r="BR380" s="7"/>
     </row>
-    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D381" s="6"/>
       <c r="E381" s="1"/>
       <c r="BO381" s="7"/>
       <c r="BR381" s="7"/>
     </row>
-    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D382" s="6"/>
       <c r="E382" s="1"/>
       <c r="BO382" s="7"/>
       <c r="BR382" s="7"/>
     </row>
-    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D383" s="6"/>
       <c r="E383" s="1"/>
       <c r="BO383" s="7"/>
       <c r="BR383" s="7"/>
     </row>
-    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D384" s="6"/>
       <c r="E384" s="1"/>
       <c r="BO384" s="7"/>
       <c r="BR384" s="7"/>
     </row>
-    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D385" s="6"/>
       <c r="E385" s="1"/>
       <c r="BO385" s="7"/>
       <c r="BR385" s="7"/>
     </row>
-    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D386" s="6"/>
       <c r="E386" s="1"/>
       <c r="BO386" s="7"/>
       <c r="BR386" s="7"/>
     </row>
-    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D387" s="6"/>
       <c r="E387" s="1"/>
       <c r="BO387" s="7"/>
       <c r="BR387" s="7"/>
     </row>
-    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D388" s="6"/>
       <c r="E388" s="1"/>
       <c r="BO388" s="7"/>
       <c r="BR388" s="7"/>
     </row>
-    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D389" s="6"/>
       <c r="E389" s="1"/>
       <c r="BO389" s="7"/>
       <c r="BR389" s="7"/>
     </row>
-    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D390" s="6"/>
       <c r="E390" s="1"/>
       <c r="BO390" s="7"/>
       <c r="BR390" s="7"/>
     </row>
-    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D391" s="6"/>
       <c r="E391" s="1"/>
       <c r="BO391" s="7"/>
       <c r="BR391" s="7"/>
     </row>
-    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D392" s="6"/>
       <c r="E392" s="1"/>
       <c r="BO392" s="7"/>
       <c r="BR392" s="7"/>
     </row>
-    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D393" s="6"/>
       <c r="E393" s="1"/>
       <c r="BO393" s="7"/>
       <c r="BR393" s="7"/>
     </row>
-    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D394" s="6"/>
       <c r="E394" s="1"/>
       <c r="BR394" s="7"/>
     </row>
-    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D395" s="6"/>
       <c r="E395" s="1"/>
       <c r="BR395" s="7"/>
     </row>
-    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D396" s="6"/>
       <c r="E396" s="1"/>
       <c r="BO396" s="7"/>
       <c r="BR396" s="7"/>
     </row>
-    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D397" s="6"/>
       <c r="E397" s="1"/>
       <c r="BO397" s="7"/>
       <c r="BR397" s="7"/>
     </row>
-    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D398" s="6"/>
       <c r="E398" s="1"/>
       <c r="BO398" s="7"/>
       <c r="BR398" s="7"/>
     </row>
-    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D399" s="6"/>
       <c r="E399" s="1"/>
       <c r="BO399" s="7"/>
       <c r="BR399" s="7"/>
     </row>
-    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D400" s="6"/>
       <c r="E400" s="1"/>
       <c r="BO400" s="7"/>
       <c r="BR400" s="7"/>
     </row>
-    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D401" s="6"/>
       <c r="E401" s="1"/>
       <c r="BO401" s="7"/>
       <c r="BR401" s="7"/>
     </row>
-    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D402" s="6"/>
       <c r="E402" s="1"/>
       <c r="BO402" s="7"/>
       <c r="BR402" s="7"/>
     </row>
-    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D403" s="6"/>
       <c r="E403" s="1"/>
       <c r="BO403" s="7"/>
       <c r="BR403" s="7"/>
     </row>
-    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D404" s="6"/>
       <c r="E404" s="1"/>
       <c r="BO404" s="7"/>
       <c r="BR404" s="7"/>
     </row>
-    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D405" s="6"/>
       <c r="E405" s="1"/>
       <c r="BO405" s="7"/>
       <c r="BR405" s="7"/>
     </row>
-    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D406" s="6"/>
       <c r="E406" s="1"/>
       <c r="BO406" s="7"/>
       <c r="BR406" s="7"/>
     </row>
-    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D407" s="6"/>
       <c r="E407" s="1"/>
       <c r="BO407" s="7"/>
       <c r="BR407" s="7"/>
     </row>
-    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D408" s="6"/>
       <c r="E408" s="1"/>
       <c r="BO408" s="7"/>
       <c r="BR408" s="7"/>
     </row>
-    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D409" s="6"/>
       <c r="E409" s="1"/>
       <c r="BO409" s="7"/>
       <c r="BR409" s="7"/>
     </row>
-    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D410" s="6"/>
       <c r="E410" s="1"/>
       <c r="BO410" s="7"/>
       <c r="BR410" s="7"/>
     </row>
-    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D411" s="6"/>
       <c r="E411" s="1"/>
       <c r="BO411" s="7"/>
       <c r="BR411" s="7"/>
     </row>
-    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D412" s="6"/>
       <c r="E412" s="1"/>
       <c r="BO412" s="7"/>
       <c r="BR412" s="7"/>
     </row>
-    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D413" s="6"/>
       <c r="E413" s="1"/>
       <c r="BO413" s="7"/>
       <c r="BR413" s="7"/>
     </row>
-    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D414" s="6"/>
       <c r="E414" s="1"/>
       <c r="BO414" s="7"/>
       <c r="BR414" s="7"/>
     </row>
-    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D415" s="6"/>
       <c r="E415" s="1"/>
       <c r="BO415" s="7"/>
       <c r="BR415" s="7"/>
     </row>
-    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D416" s="6"/>
       <c r="E416" s="1"/>
       <c r="BO416" s="7"/>
       <c r="BR416" s="7"/>
     </row>
-    <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D417" s="6"/>
       <c r="E417" s="1"/>
       <c r="BO417" s="7"/>
       <c r="BR417" s="7"/>
     </row>
-    <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D418" s="6"/>
       <c r="E418" s="1"/>
       <c r="BO418" s="7"/>
       <c r="BR418" s="7"/>
     </row>
-    <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D419" s="6"/>
       <c r="E419" s="1"/>
       <c r="BR419" s="7"/>
     </row>
-    <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D420" s="6"/>
       <c r="E420" s="1"/>
       <c r="BR420" s="7"/>
     </row>
-    <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D421" s="6"/>
       <c r="E421" s="1"/>
       <c r="BO421" s="7"/>
       <c r="BR421" s="7"/>
     </row>
-    <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D422" s="6"/>
       <c r="E422" s="1"/>
       <c r="BO422" s="7"/>
       <c r="BR422" s="7"/>
     </row>
-    <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D423" s="6"/>
       <c r="E423" s="1"/>
       <c r="BR423" s="7"/>
     </row>
-    <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D424" s="6"/>
       <c r="E424" s="1"/>
       <c r="BR424" s="7"/>
     </row>
-    <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D425" s="6"/>
       <c r="E425" s="1"/>
       <c r="BO425" s="7"/>
       <c r="BR425" s="7"/>
     </row>
-    <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D426" s="6"/>
       <c r="E426" s="1"/>
       <c r="BO426" s="7"/>
       <c r="BR426" s="7"/>
     </row>
-    <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D427" s="6"/>
       <c r="E427" s="1"/>
       <c r="BO427" s="7"/>
       <c r="BR427" s="7"/>
     </row>
-    <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D428" s="6"/>
       <c r="E428" s="1"/>
       <c r="BO428" s="7"/>
       <c r="BR428" s="7"/>
     </row>
-    <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D429" s="6"/>
       <c r="E429" s="1"/>
       <c r="BO429" s="7"/>
       <c r="BR429" s="7"/>
     </row>
-    <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D430" s="6"/>
       <c r="E430" s="1"/>
       <c r="BO430" s="7"/>
       <c r="BR430" s="7"/>
     </row>
-    <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D431" s="6"/>
       <c r="E431" s="1"/>
       <c r="BO431" s="7"/>
       <c r="BR431" s="7"/>
     </row>
-    <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D432" s="6"/>
       <c r="E432" s="1"/>
       <c r="BO432" s="7"/>
       <c r="BR432" s="7"/>
     </row>
-    <row r="433" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D433" s="6"/>
       <c r="E433" s="1"/>
       <c r="BO433" s="7"/>
       <c r="BR433" s="7"/>
     </row>
-    <row r="434" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D434" s="6"/>
       <c r="E434" s="1"/>
       <c r="BO434" s="7"/>
       <c r="BR434" s="7"/>
     </row>
-    <row r="435" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D435" s="6"/>
       <c r="E435" s="1"/>
       <c r="BO435" s="7"/>
       <c r="BR435" s="7"/>
     </row>
-    <row r="436" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D436" s="6"/>
       <c r="E436" s="1"/>
       <c r="BO436" s="7"/>
       <c r="BR436" s="7"/>
     </row>
-    <row r="437" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D437" s="6"/>
       <c r="E437" s="1"/>
       <c r="BO437" s="7"/>
       <c r="BR437" s="7"/>
     </row>
-    <row r="438" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D438" s="6"/>
       <c r="E438" s="1"/>
       <c r="BO438" s="7"/>
       <c r="BR438" s="7"/>
     </row>
-    <row r="439" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D439" s="6"/>
       <c r="E439" s="1"/>
       <c r="BO439" s="7"/>
       <c r="BR439" s="7"/>
     </row>
-    <row r="440" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D440" s="6"/>
       <c r="E440" s="1"/>
       <c r="BO440" s="7"/>
       <c r="BR440" s="7"/>
     </row>
-    <row r="441" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D441" s="6"/>
       <c r="E441" s="1"/>
       <c r="BO441" s="7"/>
       <c r="BR441" s="7"/>
     </row>
-    <row r="442" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D442" s="6"/>
       <c r="E442" s="1"/>
     </row>
-    <row r="443" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D443" s="6"/>
       <c r="E443" s="1"/>
     </row>
-    <row r="444" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D444" s="6"/>
       <c r="E444" s="1"/>
     </row>
-    <row r="445" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D445" s="6"/>
       <c r="E445" s="1"/>
     </row>
-    <row r="446" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D446" s="6"/>
       <c r="E446" s="1"/>
     </row>
-    <row r="447" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D447" s="6"/>
       <c r="E447" s="1"/>
     </row>
-    <row r="448" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:70" x14ac:dyDescent="0.25">
       <c r="D448" s="6"/>
       <c r="E448" s="1"/>
     </row>
-    <row r="449" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D449" s="6"/>
       <c r="E449" s="1"/>
     </row>
-    <row r="450" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D450" s="6"/>
       <c r="E450" s="1"/>
     </row>
-    <row r="451" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D451" s="6"/>
       <c r="E451" s="1"/>
     </row>
-    <row r="452" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D452" s="6"/>
       <c r="E452" s="1"/>
     </row>
-    <row r="453" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D453" s="6"/>
       <c r="E453" s="1"/>
     </row>
-    <row r="454" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D454" s="6"/>
       <c r="E454" s="1"/>
     </row>
-    <row r="455" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D455" s="6"/>
       <c r="E455" s="1"/>
     </row>
-    <row r="456" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D456" s="6"/>
       <c r="E456" s="1"/>
     </row>
-    <row r="457" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D457" s="6"/>
       <c r="E457" s="1"/>
     </row>
-    <row r="458" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D458" s="6"/>
       <c r="E458" s="1"/>
     </row>
-    <row r="459" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D459" s="6"/>
       <c r="E459" s="1"/>
     </row>
-    <row r="460" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D460" s="6"/>
       <c r="E460" s="1"/>
     </row>
-    <row r="461" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D461" s="6"/>
       <c r="E461" s="1"/>
     </row>
-    <row r="462" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D462" s="6"/>
       <c r="E462" s="1"/>
     </row>
-    <row r="463" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D463" s="6"/>
       <c r="E463" s="1"/>
     </row>
-    <row r="464" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D464" s="6"/>
       <c r="E464" s="1"/>
     </row>
-    <row r="465" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D465" s="6"/>
       <c r="E465" s="1"/>
     </row>
-    <row r="466" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D466" s="6"/>
       <c r="E466" s="1"/>
     </row>
-    <row r="467" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D467" s="6"/>
       <c r="E467" s="1"/>
     </row>
-    <row r="468" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D468" s="6"/>
       <c r="E468" s="1"/>
     </row>
-    <row r="469" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D469" s="6"/>
       <c r="E469" s="1"/>
     </row>
-    <row r="470" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D470" s="6"/>
       <c r="E470" s="1"/>
     </row>
-    <row r="471" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D471" s="6"/>
       <c r="E471" s="1"/>
     </row>
-    <row r="472" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D472" s="6"/>
       <c r="E472" s="1"/>
     </row>
-    <row r="473" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D473" s="6"/>
       <c r="E473" s="1"/>
     </row>
-    <row r="474" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D474" s="6"/>
       <c r="E474" s="1"/>
     </row>
-    <row r="475" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D475" s="6"/>
       <c r="E475" s="1"/>
     </row>
-    <row r="476" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D476" s="6"/>
       <c r="E476" s="1"/>
     </row>
-    <row r="477" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D477" s="6"/>
       <c r="E477" s="1"/>
     </row>
-    <row r="478" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D478" s="6"/>
       <c r="E478" s="1"/>
     </row>
-    <row r="479" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D479" s="6"/>
       <c r="E479" s="1"/>
     </row>
-    <row r="480" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D480" s="6"/>
       <c r="E480" s="1"/>
     </row>
-    <row r="481" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D481" s="6"/>
       <c r="E481" s="1"/>
     </row>
-    <row r="482" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D482" s="6"/>
       <c r="E482" s="1"/>
     </row>
-    <row r="483" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D483" s="6"/>
       <c r="E483" s="1"/>
     </row>
-    <row r="484" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D484" s="6"/>
       <c r="E484" s="1"/>
     </row>
-    <row r="485" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D485" s="6"/>
       <c r="E485" s="1"/>
     </row>
-    <row r="486" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D486" s="6"/>
       <c r="E486" s="1"/>
     </row>
-    <row r="487" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D487" s="6"/>
       <c r="E487" s="1"/>
     </row>
-    <row r="488" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D488" s="6"/>
       <c r="E488" s="1"/>
     </row>
-    <row r="489" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D489" s="6"/>
       <c r="E489" s="1"/>
     </row>
-    <row r="490" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D490" s="6"/>
       <c r="E490" s="1"/>
     </row>
-    <row r="491" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D491" s="6"/>
       <c r="E491" s="1"/>
     </row>
-    <row r="492" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D492" s="6"/>
       <c r="E492" s="1"/>
     </row>
-    <row r="493" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D493" s="6"/>
       <c r="E493" s="1"/>
     </row>
-    <row r="494" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D494" s="6"/>
       <c r="E494" s="1"/>
     </row>
-    <row r="495" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D495" s="6"/>
       <c r="E495" s="1"/>
     </row>
-    <row r="496" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D496" s="6"/>
       <c r="E496" s="1"/>
     </row>
-    <row r="497" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D497" s="6"/>
       <c r="E497" s="1"/>
     </row>
-    <row r="498" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D498" s="6"/>
       <c r="E498" s="1"/>
     </row>
-    <row r="499" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="499" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D499" s="6"/>
       <c r="E499" s="1"/>
     </row>
-    <row r="500" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="500" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D500" s="6"/>
       <c r="E500" s="1"/>
     </row>
-    <row r="501" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="501" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D501" s="6"/>
       <c r="E501" s="1"/>
     </row>
-    <row r="502" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="502" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D502" s="6"/>
       <c r="E502" s="1"/>
     </row>
-    <row r="503" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="503" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D503" s="6"/>
       <c r="E503" s="1"/>
     </row>
-    <row r="504" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="504" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D504" s="6"/>
       <c r="E504" s="1"/>
     </row>
-    <row r="505" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="505" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D505" s="6"/>
       <c r="E505" s="1"/>
     </row>
-    <row r="506" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="506" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D506" s="6"/>
       <c r="E506" s="1"/>
     </row>
-    <row r="507" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="507" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D507" s="6"/>
       <c r="E507" s="1"/>
     </row>
-    <row r="508" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="508" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D508" s="6"/>
       <c r="E508" s="1"/>
     </row>
-    <row r="509" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="509" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D509" s="6"/>
       <c r="E509" s="1"/>
     </row>
-    <row r="510" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="510" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D510" s="6"/>
       <c r="E510" s="1"/>
     </row>
-    <row r="511" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="511" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D511" s="6"/>
       <c r="E511" s="1"/>
     </row>
-    <row r="512" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="512" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D512" s="6"/>
       <c r="E512" s="1"/>
     </row>
-    <row r="513" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="513" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D513" s="6"/>
       <c r="E513" s="1"/>
     </row>
-    <row r="514" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="514" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D514" s="6"/>
       <c r="E514" s="1"/>
     </row>
-    <row r="515" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="515" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D515" s="6"/>
       <c r="E515" s="1"/>
     </row>
-    <row r="516" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="516" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D516" s="6"/>
       <c r="E516" s="1"/>
     </row>
-    <row r="517" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="517" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D517" s="6"/>
       <c r="E517" s="1"/>
     </row>
-    <row r="518" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="518" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D518" s="6"/>
       <c r="E518" s="1"/>
     </row>
-    <row r="519" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="519" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D519" s="6"/>
       <c r="E519" s="1"/>
     </row>
-    <row r="520" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="520" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D520" s="6"/>
       <c r="E520" s="1"/>
     </row>
-    <row r="521" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="521" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D521" s="6"/>
       <c r="E521" s="1"/>
     </row>
-    <row r="589" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D589" s="6"/>
       <c r="E589" s="1"/>
     </row>
-    <row r="590" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D590" s="6"/>
       <c r="E590" s="1"/>
     </row>
-    <row r="591" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="591" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D591" s="6"/>
       <c r="E591" s="1"/>
     </row>
-    <row r="592" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="592" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D592" s="6"/>
       <c r="E592" s="1"/>
     </row>
-    <row r="593" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="593" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D593" s="6"/>
       <c r="E593" s="1"/>
     </row>
-    <row r="594" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="594" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D594" s="6"/>
       <c r="E594" s="1"/>
     </row>
-    <row r="595" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="595" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D595" s="6"/>
       <c r="E595" s="1"/>
     </row>
-    <row r="596" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="596" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D596" s="6"/>
       <c r="E596" s="1"/>
     </row>
-    <row r="597" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="597" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D597" s="6"/>
       <c r="E597" s="1"/>
     </row>
-    <row r="598" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="598" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D598" s="6"/>
       <c r="E598" s="1"/>
     </row>
-    <row r="599" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="599" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D599" s="6"/>
       <c r="E599" s="1"/>
     </row>
-    <row r="600" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="600" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D600" s="6"/>
       <c r="E600" s="1"/>
     </row>
-    <row r="601" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="601" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D601" s="6"/>
       <c r="E601" s="1"/>
     </row>
-    <row r="602" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="602" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D602" s="6"/>
       <c r="E602" s="1"/>
     </row>
-    <row r="603" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="603" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D603" s="6"/>
       <c r="E603" s="1"/>
     </row>
-    <row r="604" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="604" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D604" s="6"/>
       <c r="E604" s="1"/>
     </row>
-    <row r="605" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="605" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D605" s="6"/>
       <c r="E605" s="1"/>
     </row>
-    <row r="606" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="606" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D606" s="6"/>
       <c r="E606" s="1"/>
     </row>
-    <row r="607" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="607" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D607" s="6"/>
       <c r="E607" s="1"/>
     </row>
-    <row r="608" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="608" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D608" s="6"/>
       <c r="E608" s="1"/>
     </row>
-    <row r="609" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="609" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D609" s="6"/>
       <c r="E609" s="1"/>
     </row>
-    <row r="610" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="610" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D610" s="6"/>
       <c r="E610" s="1"/>
     </row>
-    <row r="611" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="611" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D611" s="6"/>
       <c r="E611" s="1"/>
     </row>
-    <row r="612" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="612" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D612" s="6"/>
       <c r="E612" s="1"/>
     </row>
-    <row r="613" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
+    <row r="613" spans="4:5" x14ac:dyDescent="0.25">
       <c r="D613" s="6"/>
       <c r="E613" s="1"/>
     </row>
@@ -8775,82 +8771,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DH905"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08203125" customWidth="1"/>
-    <col min="2" max="2" width="15.58203125" customWidth="1"/>
-    <col min="3" max="3" width="7.75" customWidth="1"/>
-    <col min="4" max="4" width="16.58203125" customWidth="1"/>
-    <col min="5" max="5" width="16.83203125" customWidth="1"/>
-    <col min="6" max="6" width="31.33203125" customWidth="1"/>
-    <col min="7" max="7" width="7.33203125" customWidth="1"/>
-    <col min="8" max="8" width="17.83203125" customWidth="1"/>
-    <col min="9" max="9" width="7.33203125" customWidth="1"/>
-    <col min="10" max="10" width="15.75" customWidth="1"/>
-    <col min="11" max="13" width="8.33203125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.75" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.08203125" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.58203125" style="3" customWidth="1"/>
-    <col min="17" max="17" width="21.5" style="3" customWidth="1"/>
-    <col min="18" max="18" width="19.83203125" style="3" customWidth="1"/>
-    <col min="19" max="19" width="16.58203125" style="3" customWidth="1"/>
-    <col min="20" max="20" width="12.75" style="3" customWidth="1"/>
-    <col min="21" max="23" width="8.33203125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="18.5" style="3" customWidth="1"/>
-    <col min="25" max="25" width="16.58203125" customWidth="1"/>
-    <col min="26" max="26" width="10.6640625" customWidth="1"/>
-    <col min="27" max="27" width="8.33203125" customWidth="1"/>
-    <col min="28" max="28" width="15.1640625" customWidth="1"/>
-    <col min="29" max="30" width="8.58203125" customWidth="1"/>
-    <col min="31" max="31" width="13.4140625" customWidth="1"/>
-    <col min="32" max="32" width="13.75" customWidth="1"/>
-    <col min="33" max="33" width="14.58203125" customWidth="1"/>
-    <col min="34" max="34" width="17.4140625" customWidth="1"/>
-    <col min="35" max="35" width="8.58203125" customWidth="1"/>
-    <col min="36" max="36" width="12.5" customWidth="1"/>
-    <col min="37" max="37" width="8.58203125" customWidth="1"/>
-    <col min="38" max="39" width="8.33203125" customWidth="1"/>
+    <col min="1" max="1" width="21.08984375" customWidth="1"/>
+    <col min="2" max="2" width="15.54296875" customWidth="1"/>
+    <col min="3" max="3" width="7.7265625" customWidth="1"/>
+    <col min="4" max="4" width="16.54296875" customWidth="1"/>
+    <col min="5" max="5" width="16.81640625" customWidth="1"/>
+    <col min="6" max="6" width="31.36328125" customWidth="1"/>
+    <col min="7" max="7" width="7.36328125" customWidth="1"/>
+    <col min="8" max="8" width="17.81640625" customWidth="1"/>
+    <col min="9" max="9" width="7.36328125" customWidth="1"/>
+    <col min="10" max="10" width="15.7265625" customWidth="1"/>
+    <col min="11" max="13" width="8.36328125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.7265625" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.08984375" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.54296875" style="3" customWidth="1"/>
+    <col min="17" max="17" width="21.453125" style="3" customWidth="1"/>
+    <col min="18" max="18" width="19.81640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="16.54296875" style="3" customWidth="1"/>
+    <col min="20" max="20" width="12.7265625" style="3" customWidth="1"/>
+    <col min="21" max="23" width="8.36328125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="18.453125" style="3" customWidth="1"/>
+    <col min="25" max="25" width="16.54296875" customWidth="1"/>
+    <col min="26" max="26" width="10.6328125" customWidth="1"/>
+    <col min="27" max="27" width="8.36328125" customWidth="1"/>
+    <col min="28" max="28" width="15.1796875" customWidth="1"/>
+    <col min="29" max="30" width="8.54296875" customWidth="1"/>
+    <col min="31" max="31" width="13.453125" customWidth="1"/>
+    <col min="32" max="32" width="13.7265625" customWidth="1"/>
+    <col min="33" max="33" width="14.54296875" customWidth="1"/>
+    <col min="34" max="34" width="17.453125" customWidth="1"/>
+    <col min="35" max="35" width="8.54296875" customWidth="1"/>
+    <col min="36" max="36" width="12.453125" customWidth="1"/>
+    <col min="37" max="37" width="8.54296875" customWidth="1"/>
+    <col min="38" max="39" width="8.36328125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.25" customWidth="1"/>
-    <col min="42" max="43" width="11.83203125" customWidth="1"/>
-    <col min="44" max="44" width="18.4140625" customWidth="1"/>
-    <col min="45" max="45" width="12.25" customWidth="1"/>
-    <col min="46" max="46" width="11.9140625" customWidth="1"/>
-    <col min="47" max="47" width="19.58203125" customWidth="1"/>
-    <col min="48" max="48" width="12.6640625" customWidth="1"/>
+    <col min="41" max="41" width="13.26953125" customWidth="1"/>
+    <col min="42" max="43" width="11.81640625" customWidth="1"/>
+    <col min="44" max="44" width="18.453125" customWidth="1"/>
+    <col min="45" max="45" width="12.26953125" customWidth="1"/>
+    <col min="46" max="46" width="11.90625" customWidth="1"/>
+    <col min="47" max="47" width="19.54296875" customWidth="1"/>
+    <col min="48" max="48" width="12.6328125" customWidth="1"/>
     <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.75" customWidth="1"/>
-    <col min="52" max="52" width="9.75" customWidth="1"/>
-    <col min="53" max="53" width="5.08203125" customWidth="1"/>
-    <col min="54" max="54" width="8.5" customWidth="1"/>
-    <col min="55" max="55" width="13.5" customWidth="1"/>
-    <col min="56" max="56" width="14.6640625" customWidth="1"/>
-    <col min="57" max="57" width="10.1640625" customWidth="1"/>
-    <col min="58" max="58" width="8.25" customWidth="1"/>
-    <col min="59" max="65" width="8.33203125" customWidth="1"/>
-    <col min="66" max="68" width="11.25" customWidth="1"/>
-    <col min="69" max="69" width="6.58203125" customWidth="1"/>
+    <col min="51" max="51" width="11.7265625" customWidth="1"/>
+    <col min="52" max="52" width="9.7265625" customWidth="1"/>
+    <col min="53" max="53" width="5.08984375" customWidth="1"/>
+    <col min="54" max="54" width="8.453125" customWidth="1"/>
+    <col min="55" max="55" width="13.453125" customWidth="1"/>
+    <col min="56" max="56" width="14.6328125" customWidth="1"/>
+    <col min="57" max="57" width="10.1796875" customWidth="1"/>
+    <col min="58" max="58" width="8.26953125" customWidth="1"/>
+    <col min="59" max="65" width="8.36328125" customWidth="1"/>
+    <col min="66" max="68" width="11.26953125" customWidth="1"/>
+    <col min="69" max="69" width="6.54296875" customWidth="1"/>
     <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.33203125" style="4" customWidth="1"/>
-    <col min="73" max="74" width="8.5" style="4" customWidth="1"/>
-    <col min="75" max="76" width="7.83203125" style="4" customWidth="1"/>
-    <col min="77" max="77" width="22.1640625" style="4" customWidth="1"/>
-    <col min="78" max="78" width="13.5" customWidth="1"/>
-    <col min="79" max="79" width="21.1640625" customWidth="1"/>
-    <col min="80" max="80" width="15.75" customWidth="1"/>
-    <col min="81" max="81" width="15.58203125" customWidth="1"/>
-    <col min="82" max="82" width="12.83203125" customWidth="1"/>
-    <col min="83" max="83" width="16.1640625" customWidth="1"/>
+    <col min="72" max="72" width="7.36328125" style="4" customWidth="1"/>
+    <col min="73" max="74" width="8.453125" style="4" customWidth="1"/>
+    <col min="75" max="76" width="7.81640625" style="4" customWidth="1"/>
+    <col min="77" max="77" width="22.1796875" style="4" customWidth="1"/>
+    <col min="78" max="78" width="13.453125" customWidth="1"/>
+    <col min="79" max="79" width="21.1796875" customWidth="1"/>
+    <col min="80" max="80" width="15.7265625" customWidth="1"/>
+    <col min="81" max="81" width="15.54296875" customWidth="1"/>
+    <col min="82" max="82" width="12.81640625" customWidth="1"/>
+    <col min="83" max="83" width="16.1796875" customWidth="1"/>
     <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.83203125" customWidth="1"/>
-    <col min="88" max="88" width="23.58203125" customWidth="1"/>
-    <col min="89" max="89" width="12.83203125" customWidth="1"/>
-    <col min="90" max="90" width="17.08203125" customWidth="1"/>
+    <col min="86" max="87" width="12.81640625" customWidth="1"/>
+    <col min="88" max="88" width="23.54296875" customWidth="1"/>
+    <col min="89" max="89" width="12.81640625" customWidth="1"/>
+    <col min="90" max="90" width="17.08984375" customWidth="1"/>
     <col min="97" max="97" width="14" customWidth="1"/>
     <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08203125" customWidth="1"/>
-    <col min="101" max="101" width="13.75" customWidth="1"/>
-    <col min="108" max="108" width="15.5" customWidth="1"/>
+    <col min="100" max="100" width="11.08984375" customWidth="1"/>
+    <col min="101" max="101" width="13.7265625" customWidth="1"/>
+    <col min="108" max="108" width="15.453125" customWidth="1"/>
     <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14691,20 +14687,21 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:Q10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="31.25" customWidth="1"/>
-    <col min="7" max="7" width="18.75" customWidth="1"/>
+    <col min="2" max="2" width="31.26953125" customWidth="1"/>
+    <col min="7" max="7" width="18.7265625" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.08203125" customWidth="1"/>
-    <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08984375" customWidth="1"/>
+    <col min="15" max="15" width="9.453125" customWidth="1"/>
+    <col min="16" max="16" width="22.1796875" customWidth="1"/>
+    <col min="17" max="17" width="12.81640625" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14741,8 +14738,11 @@
       <c r="O1" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P1" s="8" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -14785,11 +14785,14 @@
       <c r="O2" t="s">
         <v>621</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="8" t="s">
+        <v>784</v>
+      </c>
+      <c r="Q2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14833,10 +14836,13 @@
         <v>385</v>
       </c>
       <c r="P3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>471</v>
       </c>
@@ -14855,11 +14861,11 @@
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>486</v>
       </c>
@@ -14872,11 +14878,11 @@
       <c r="K5">
         <v>0.01</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>487</v>
       </c>
@@ -14889,11 +14895,11 @@
       <c r="K6">
         <v>0.01</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>622</v>
       </c>
@@ -14909,11 +14915,11 @@
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>746</v>
       </c>
@@ -14924,7 +14930,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>600</v>
       </c>
@@ -14934,11 +14940,11 @@
       <c r="J9" t="s">
         <v>751</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>762</v>
       </c>
@@ -14956,11 +14962,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.33203125" customWidth="1"/>
-    <col min="2" max="2" width="11.25" customWidth="1"/>
-    <col min="4" max="4" width="27.5" customWidth="1"/>
+    <col min="1" max="1" width="11.36328125" customWidth="1"/>
+    <col min="2" max="2" width="11.26953125" customWidth="1"/>
+    <col min="4" max="4" width="27.453125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -15020,11 +15026,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:I4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
-    <col min="3" max="3" width="27.25" customWidth="1"/>
-    <col min="4" max="4" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="3" max="3" width="27.26953125" customWidth="1"/>
+    <col min="4" max="4" width="10.81640625" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15113,13 +15119,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="1" max="1" width="15.26953125" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08203125" customWidth="1"/>
-    <col min="5" max="10" width="11.25" customWidth="1"/>
-    <col min="11" max="11" width="6.33203125" customWidth="1"/>
+    <col min="3" max="4" width="10.08984375" customWidth="1"/>
+    <col min="5" max="10" width="11.26953125" customWidth="1"/>
+    <col min="11" max="11" width="6.36328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -15641,15 +15647,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A2:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08203125" customWidth="1"/>
-    <col min="2" max="2" width="16.25" customWidth="1"/>
-    <col min="3" max="3" width="16.33203125" customWidth="1"/>
-    <col min="4" max="4" width="47.83203125" customWidth="1"/>
-    <col min="5" max="5" width="10.25" customWidth="1"/>
-    <col min="6" max="6" width="12.83203125" customWidth="1"/>
-    <col min="10" max="10" width="11.83203125" customWidth="1"/>
+    <col min="1" max="1" width="19.08984375" customWidth="1"/>
+    <col min="2" max="2" width="16.26953125" customWidth="1"/>
+    <col min="3" max="3" width="16.36328125" customWidth="1"/>
+    <col min="4" max="4" width="47.81640625" customWidth="1"/>
+    <col min="5" max="5" width="10.26953125" customWidth="1"/>
+    <col min="6" max="6" width="12.81640625" customWidth="1"/>
+    <col min="10" max="10" width="11.81640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\学习专用\ark_-n\Excel\Main\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250A4979-BC58-40E5-83A6-D89616B264B5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF8E5E8-89C9-4DB8-B42C-1700DAF6B943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -21,8 +21,21 @@
     <sheet name="BulletData" sheetId="4" r:id="rId6"/>
     <sheet name="EffectData" sheetId="9" r:id="rId7"/>
     <sheet name="ContractData" sheetId="11" r:id="rId8"/>
+    <sheet name="SpineData" sheetId="12" r:id="rId9"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -285,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1512" uniqueCount="785">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="801">
   <si>
     <t>Id</t>
   </si>
@@ -2721,11 +2734,75 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>可无视buff抑制检测</t>
+    <t>Id</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>IsCancelable</t>
+    <t>仅单面</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>相对路径</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面atlas</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面png</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>正面skel</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面atlas</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面png</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>背面skel</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>OnlyFront</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>UseAppHotfixResPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontAtlasPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontPngPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>FrontSkelPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackAtlasPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackPngPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>BackSkelPath</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>string?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -2898,12 +2975,15 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="19">
+  <cellXfs count="20">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2959,9 +3039,13 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="常规 2" xfId="1" xr:uid="{FE71D452-32E7-40DB-97FB-C755A1FE7CB7}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -3264,7 +3348,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A2:B21"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="9" customWidth="1"/>
   </cols>
@@ -3423,48 +3507,48 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:BS613"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="22.54296875" customWidth="1"/>
-    <col min="4" max="4" width="8.54296875" customWidth="1"/>
-    <col min="5" max="5" width="5.36328125" customWidth="1"/>
-    <col min="6" max="6" width="19.54296875" customWidth="1"/>
-    <col min="7" max="7" width="8.26953125" customWidth="1"/>
+    <col min="1" max="1" width="22.58203125" customWidth="1"/>
+    <col min="4" max="4" width="8.58203125" customWidth="1"/>
+    <col min="5" max="5" width="5.33203125" customWidth="1"/>
+    <col min="6" max="6" width="19.58203125" customWidth="1"/>
+    <col min="7" max="7" width="8.25" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="4.08984375" customWidth="1"/>
-    <col min="13" max="13" width="5.54296875" customWidth="1"/>
+    <col min="12" max="12" width="4.08203125" customWidth="1"/>
+    <col min="13" max="13" width="5.58203125" customWidth="1"/>
     <col min="14" max="14" width="4" customWidth="1"/>
-    <col min="15" max="15" width="7.7265625" customWidth="1"/>
-    <col min="16" max="16" width="10.81640625" customWidth="1"/>
-    <col min="17" max="18" width="3.81640625" customWidth="1"/>
-    <col min="19" max="20" width="3.54296875" customWidth="1"/>
-    <col min="21" max="21" width="10.26953125" customWidth="1"/>
-    <col min="22" max="22" width="9.54296875" customWidth="1"/>
-    <col min="23" max="23" width="10.7265625" customWidth="1"/>
-    <col min="24" max="24" width="12.81640625" customWidth="1"/>
-    <col min="25" max="25" width="13.08984375" customWidth="1"/>
-    <col min="26" max="26" width="10.7265625" customWidth="1"/>
+    <col min="15" max="15" width="7.75" customWidth="1"/>
+    <col min="16" max="16" width="10.83203125" customWidth="1"/>
+    <col min="17" max="18" width="3.83203125" customWidth="1"/>
+    <col min="19" max="20" width="3.58203125" customWidth="1"/>
+    <col min="21" max="21" width="10.25" customWidth="1"/>
+    <col min="22" max="22" width="9.58203125" customWidth="1"/>
+    <col min="23" max="23" width="10.75" customWidth="1"/>
+    <col min="24" max="24" width="12.83203125" customWidth="1"/>
+    <col min="25" max="25" width="13.08203125" customWidth="1"/>
+    <col min="26" max="26" width="10.75" customWidth="1"/>
     <col min="29" max="29" width="8" customWidth="1"/>
-    <col min="30" max="30" width="17.08984375" customWidth="1"/>
-    <col min="31" max="31" width="9.7265625" customWidth="1"/>
-    <col min="32" max="32" width="7.81640625" customWidth="1"/>
-    <col min="33" max="33" width="15.81640625" customWidth="1"/>
-    <col min="34" max="34" width="13.81640625" customWidth="1"/>
-    <col min="35" max="35" width="34.453125" customWidth="1"/>
-    <col min="36" max="37" width="9.81640625" customWidth="1"/>
-    <col min="43" max="43" width="12.453125" customWidth="1"/>
-    <col min="50" max="50" width="8.453125" customWidth="1"/>
-    <col min="52" max="52" width="17.7265625" customWidth="1"/>
-    <col min="53" max="53" width="7.81640625" customWidth="1"/>
-    <col min="56" max="56" width="24.26953125" customWidth="1"/>
-    <col min="57" max="57" width="13.26953125" customWidth="1"/>
-    <col min="58" max="58" width="16.08984375" customWidth="1"/>
+    <col min="30" max="30" width="17.08203125" customWidth="1"/>
+    <col min="31" max="31" width="9.75" customWidth="1"/>
+    <col min="32" max="32" width="7.83203125" customWidth="1"/>
+    <col min="33" max="33" width="15.83203125" customWidth="1"/>
+    <col min="34" max="34" width="13.83203125" customWidth="1"/>
+    <col min="35" max="35" width="34.5" customWidth="1"/>
+    <col min="36" max="37" width="9.83203125" customWidth="1"/>
+    <col min="43" max="43" width="12.5" customWidth="1"/>
+    <col min="50" max="50" width="8.5" customWidth="1"/>
+    <col min="52" max="52" width="17.75" customWidth="1"/>
+    <col min="53" max="53" width="7.83203125" customWidth="1"/>
+    <col min="56" max="56" width="24.25" customWidth="1"/>
+    <col min="57" max="57" width="13.25" customWidth="1"/>
+    <col min="58" max="58" width="16.08203125" customWidth="1"/>
     <col min="59" max="59" width="8" customWidth="1"/>
-    <col min="64" max="64" width="39.54296875" customWidth="1"/>
+    <col min="64" max="64" width="39.58203125" customWidth="1"/>
     <col min="65" max="65" width="14" customWidth="1"/>
-    <col min="66" max="66" width="14.81640625" customWidth="1"/>
+    <col min="66" max="66" width="14.83203125" customWidth="1"/>
     <col min="67" max="70" width="14" customWidth="1"/>
-    <col min="71" max="71" width="19.1796875" customWidth="1"/>
+    <col min="71" max="71" width="19.1640625" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:71" x14ac:dyDescent="0.25">
@@ -6008,2755 +6092,2755 @@
       <c r="AI50" s="8"/>
       <c r="BK50" s="8"/>
     </row>
-    <row r="51" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="51" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D51" s="6"/>
       <c r="E51" s="1"/>
       <c r="BO51" s="7"/>
       <c r="BR51" s="7"/>
     </row>
-    <row r="52" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="52" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D52" s="6"/>
       <c r="E52" s="1"/>
       <c r="BO52" s="7"/>
       <c r="BR52" s="7"/>
     </row>
-    <row r="53" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="53" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D53" s="6"/>
       <c r="E53" s="1"/>
       <c r="BO53" s="7"/>
       <c r="BR53" s="7"/>
     </row>
-    <row r="54" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="54" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D54" s="6"/>
       <c r="E54" s="1"/>
       <c r="BO54" s="7"/>
       <c r="BR54" s="7"/>
     </row>
-    <row r="55" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="55" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D55" s="6"/>
       <c r="E55" s="1"/>
       <c r="BO55" s="7"/>
       <c r="BR55" s="7"/>
     </row>
-    <row r="56" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="56" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D56" s="6"/>
       <c r="E56" s="1"/>
       <c r="BO56" s="7"/>
       <c r="BR56" s="7"/>
     </row>
-    <row r="57" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="57" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D57" s="6"/>
       <c r="E57" s="1"/>
       <c r="BO57" s="7"/>
       <c r="BR57" s="7"/>
     </row>
-    <row r="58" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="58" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D58" s="6"/>
       <c r="E58" s="1"/>
       <c r="BR58" s="7"/>
     </row>
-    <row r="59" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="59" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D59" s="6"/>
       <c r="E59" s="1"/>
       <c r="BR59" s="7"/>
     </row>
-    <row r="60" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="60" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D60" s="6"/>
       <c r="E60" s="1"/>
       <c r="BR60" s="7"/>
     </row>
-    <row r="61" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="61" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D61" s="6"/>
       <c r="E61" s="1"/>
       <c r="BO61" s="7"/>
       <c r="BR61" s="7"/>
     </row>
-    <row r="62" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="62" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D62" s="6"/>
       <c r="E62" s="1"/>
       <c r="BO62" s="7"/>
       <c r="BR62" s="7"/>
     </row>
-    <row r="63" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="63" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D63" s="6"/>
       <c r="E63" s="1"/>
       <c r="BO63" s="7"/>
       <c r="BR63" s="7"/>
     </row>
-    <row r="64" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="64" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D64" s="6"/>
       <c r="E64" s="1"/>
       <c r="BO64" s="7"/>
       <c r="BR64" s="7"/>
     </row>
-    <row r="65" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="65" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D65" s="6"/>
       <c r="E65" s="1"/>
       <c r="BO65" s="7"/>
       <c r="BR65" s="7"/>
     </row>
-    <row r="66" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="66" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D66" s="6"/>
       <c r="E66" s="1"/>
       <c r="BO66" s="7"/>
       <c r="BR66" s="7"/>
     </row>
-    <row r="67" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="67" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D67" s="6"/>
       <c r="E67" s="1"/>
       <c r="BO67" s="7"/>
       <c r="BR67" s="7"/>
     </row>
-    <row r="68" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="68" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D68" s="6"/>
       <c r="E68" s="1"/>
       <c r="BO68" s="7"/>
       <c r="BR68" s="7"/>
     </row>
-    <row r="69" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="69" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D69" s="6"/>
       <c r="E69" s="1"/>
       <c r="BO69" s="7"/>
       <c r="BR69" s="7"/>
     </row>
-    <row r="70" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="70" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D70" s="6"/>
       <c r="E70" s="1"/>
       <c r="BO70" s="7"/>
       <c r="BR70" s="7"/>
     </row>
-    <row r="71" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="71" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D71" s="6"/>
       <c r="E71" s="1"/>
       <c r="BO71" s="7"/>
       <c r="BR71" s="7"/>
     </row>
-    <row r="72" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="72" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D72" s="6"/>
       <c r="E72" s="1"/>
       <c r="BO72" s="7"/>
       <c r="BR72" s="7"/>
     </row>
-    <row r="73" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="73" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D73" s="6"/>
       <c r="E73" s="1"/>
       <c r="BO73" s="7"/>
       <c r="BR73" s="7"/>
     </row>
-    <row r="74" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="74" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D74" s="6"/>
       <c r="E74" s="1"/>
       <c r="BO74" s="7"/>
       <c r="BR74" s="7"/>
     </row>
-    <row r="75" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="75" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D75" s="6"/>
       <c r="E75" s="1"/>
       <c r="BO75" s="7"/>
       <c r="BR75" s="7"/>
     </row>
-    <row r="76" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="76" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D76" s="6"/>
       <c r="E76" s="1"/>
       <c r="BO76" s="7"/>
       <c r="BR76" s="7"/>
     </row>
-    <row r="77" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="77" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D77" s="6"/>
       <c r="E77" s="1"/>
       <c r="BO77" s="7"/>
       <c r="BR77" s="7"/>
     </row>
-    <row r="78" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="78" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D78" s="6"/>
       <c r="E78" s="1"/>
       <c r="BO78" s="7"/>
       <c r="BR78" s="7"/>
     </row>
-    <row r="79" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="79" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D79" s="6"/>
       <c r="E79" s="1"/>
       <c r="BO79" s="7"/>
       <c r="BR79" s="7"/>
     </row>
-    <row r="80" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="80" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D80" s="6"/>
       <c r="E80" s="1"/>
       <c r="BO80" s="7"/>
       <c r="BR80" s="7"/>
     </row>
-    <row r="81" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="81" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D81" s="6"/>
       <c r="E81" s="1"/>
       <c r="BO81" s="7"/>
       <c r="BR81" s="7"/>
     </row>
-    <row r="82" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="82" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D82" s="6"/>
       <c r="E82" s="1"/>
       <c r="BO82" s="7"/>
       <c r="BR82" s="7"/>
     </row>
-    <row r="83" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="83" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D83" s="6"/>
       <c r="E83" s="1"/>
       <c r="BO83" s="7"/>
       <c r="BR83" s="7"/>
     </row>
-    <row r="84" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="84" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D84" s="6"/>
       <c r="E84" s="1"/>
       <c r="BO84" s="7"/>
       <c r="BR84" s="7"/>
     </row>
-    <row r="85" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="85" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D85" s="6"/>
       <c r="E85" s="1"/>
       <c r="BO85" s="7"/>
       <c r="BR85" s="7"/>
     </row>
-    <row r="86" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="86" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D86" s="6"/>
       <c r="E86" s="1"/>
       <c r="BO86" s="7"/>
       <c r="BR86" s="7"/>
     </row>
-    <row r="87" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="87" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D87" s="6"/>
       <c r="E87" s="1"/>
       <c r="BO87" s="7"/>
       <c r="BR87" s="7"/>
     </row>
-    <row r="88" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="88" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D88" s="6"/>
       <c r="E88" s="1"/>
       <c r="BO88" s="7"/>
       <c r="BR88" s="7"/>
     </row>
-    <row r="89" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="89" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D89" s="6"/>
       <c r="E89" s="1"/>
       <c r="BO89" s="7"/>
       <c r="BR89" s="7"/>
     </row>
-    <row r="90" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="90" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D90" s="6"/>
       <c r="E90" s="1"/>
       <c r="BO90" s="7"/>
       <c r="BR90" s="7"/>
     </row>
-    <row r="91" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="91" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D91" s="6"/>
       <c r="E91" s="1"/>
       <c r="BO91" s="7"/>
       <c r="BR91" s="7"/>
     </row>
-    <row r="92" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="92" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D92" s="6"/>
       <c r="E92" s="1"/>
       <c r="BO92" s="7"/>
       <c r="BR92" s="7"/>
     </row>
-    <row r="93" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="93" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D93" s="6"/>
       <c r="E93" s="1"/>
       <c r="BO93" s="7"/>
       <c r="BR93" s="7"/>
     </row>
-    <row r="94" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="94" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D94" s="6"/>
       <c r="E94" s="1"/>
       <c r="BO94" s="7"/>
       <c r="BR94" s="7"/>
     </row>
-    <row r="95" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="95" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D95" s="6"/>
       <c r="E95" s="1"/>
       <c r="BO95" s="7"/>
       <c r="BR95" s="7"/>
     </row>
-    <row r="96" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="96" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D96" s="6"/>
       <c r="E96" s="1"/>
       <c r="BO96" s="7"/>
       <c r="BR96" s="7"/>
     </row>
-    <row r="97" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="97" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D97" s="6"/>
       <c r="E97" s="1"/>
       <c r="BO97" s="7"/>
       <c r="BR97" s="7"/>
     </row>
-    <row r="98" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="98" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D98" s="6"/>
       <c r="E98" s="1"/>
       <c r="BO98" s="7"/>
       <c r="BR98" s="7"/>
     </row>
-    <row r="99" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="99" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D99" s="6"/>
       <c r="E99" s="1"/>
       <c r="BO99" s="7"/>
       <c r="BR99" s="7"/>
     </row>
-    <row r="100" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="100" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D100" s="6"/>
       <c r="E100" s="1"/>
       <c r="BO100" s="7"/>
       <c r="BR100" s="7"/>
     </row>
-    <row r="101" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="101" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D101" s="6"/>
       <c r="E101" s="1"/>
       <c r="BO101" s="7"/>
       <c r="BR101" s="7"/>
     </row>
-    <row r="102" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="102" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D102" s="6"/>
       <c r="E102" s="1"/>
       <c r="BO102" s="7"/>
       <c r="BR102" s="7"/>
     </row>
-    <row r="103" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="103" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D103" s="6"/>
       <c r="E103" s="1"/>
       <c r="BO103" s="7"/>
       <c r="BR103" s="7"/>
     </row>
-    <row r="104" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="104" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D104" s="6"/>
       <c r="E104" s="1"/>
       <c r="BO104" s="7"/>
       <c r="BR104" s="7"/>
     </row>
-    <row r="105" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="105" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D105" s="6"/>
       <c r="E105" s="1"/>
       <c r="BO105" s="7"/>
       <c r="BR105" s="7"/>
     </row>
-    <row r="106" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="106" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D106" s="6"/>
       <c r="E106" s="1"/>
       <c r="BO106" s="7"/>
       <c r="BR106" s="7"/>
     </row>
-    <row r="107" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="107" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D107" s="6"/>
       <c r="E107" s="1"/>
       <c r="BO107" s="7"/>
       <c r="BR107" s="7"/>
     </row>
-    <row r="108" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="108" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D108" s="6"/>
       <c r="E108" s="1"/>
       <c r="BO108" s="7"/>
       <c r="BR108" s="7"/>
     </row>
-    <row r="109" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="109" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D109" s="6"/>
       <c r="E109" s="1"/>
       <c r="BO109" s="7"/>
       <c r="BR109" s="7"/>
     </row>
-    <row r="110" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="110" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D110" s="6"/>
       <c r="E110" s="1"/>
       <c r="BO110" s="7"/>
       <c r="BR110" s="7"/>
     </row>
-    <row r="111" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="111" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D111" s="6"/>
       <c r="E111" s="1"/>
       <c r="BO111" s="7"/>
       <c r="BR111" s="7"/>
     </row>
-    <row r="112" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="112" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D112" s="6"/>
       <c r="E112" s="1"/>
       <c r="BO112" s="7"/>
       <c r="BR112" s="7"/>
     </row>
-    <row r="113" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="113" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D113" s="6"/>
       <c r="E113" s="1"/>
       <c r="BO113" s="7"/>
       <c r="BR113" s="7"/>
     </row>
-    <row r="114" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="114" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D114" s="6"/>
       <c r="E114" s="1"/>
       <c r="BO114" s="7"/>
       <c r="BR114" s="7"/>
     </row>
-    <row r="115" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="115" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D115" s="6"/>
       <c r="E115" s="1"/>
       <c r="BO115" s="7"/>
       <c r="BR115" s="7"/>
     </row>
-    <row r="116" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="116" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D116" s="6"/>
       <c r="E116" s="1"/>
       <c r="BO116" s="7"/>
       <c r="BR116" s="7"/>
     </row>
-    <row r="117" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="117" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D117" s="6"/>
       <c r="E117" s="1"/>
       <c r="BO117" s="7"/>
       <c r="BR117" s="7"/>
     </row>
-    <row r="118" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="118" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D118" s="6"/>
       <c r="E118" s="1"/>
       <c r="BO118" s="7"/>
       <c r="BR118" s="7"/>
     </row>
-    <row r="119" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="119" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D119" s="6"/>
       <c r="E119" s="1"/>
       <c r="BO119" s="7"/>
       <c r="BR119" s="7"/>
     </row>
-    <row r="120" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="120" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D120" s="6"/>
       <c r="E120" s="1"/>
       <c r="BO120" s="7"/>
       <c r="BR120" s="7"/>
     </row>
-    <row r="121" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="121" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D121" s="6"/>
       <c r="E121" s="1"/>
       <c r="BO121" s="7"/>
       <c r="BR121" s="7"/>
     </row>
-    <row r="122" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="122" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D122" s="6"/>
       <c r="E122" s="1"/>
       <c r="BO122" s="7"/>
       <c r="BR122" s="7"/>
     </row>
-    <row r="123" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="123" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D123" s="6"/>
       <c r="E123" s="1"/>
       <c r="BO123" s="7"/>
       <c r="BR123" s="7"/>
     </row>
-    <row r="124" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="124" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D124" s="6"/>
       <c r="E124" s="1"/>
       <c r="BO124" s="7"/>
       <c r="BR124" s="7"/>
     </row>
-    <row r="125" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="125" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D125" s="6"/>
       <c r="E125" s="1"/>
       <c r="BO125" s="7"/>
       <c r="BR125" s="7"/>
     </row>
-    <row r="126" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="126" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D126" s="6"/>
       <c r="E126" s="1"/>
       <c r="BO126" s="7"/>
       <c r="BR126" s="7"/>
     </row>
-    <row r="127" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="127" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D127" s="6"/>
       <c r="E127" s="1"/>
       <c r="BO127" s="7"/>
       <c r="BR127" s="7"/>
     </row>
-    <row r="128" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="128" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D128" s="6"/>
       <c r="E128" s="1"/>
       <c r="BO128" s="7"/>
       <c r="BR128" s="7"/>
     </row>
-    <row r="129" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="129" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D129" s="6"/>
       <c r="E129" s="1"/>
       <c r="BO129" s="7"/>
       <c r="BR129" s="7"/>
     </row>
-    <row r="130" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="130" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D130" s="6"/>
       <c r="E130" s="1"/>
       <c r="BO130" s="7"/>
       <c r="BR130" s="7"/>
     </row>
-    <row r="131" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="131" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D131" s="6"/>
       <c r="E131" s="1"/>
       <c r="BO131" s="7"/>
       <c r="BR131" s="7"/>
     </row>
-    <row r="132" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="132" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D132" s="6"/>
       <c r="E132" s="1"/>
       <c r="BO132" s="7"/>
       <c r="BR132" s="7"/>
     </row>
-    <row r="133" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="133" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D133" s="6"/>
       <c r="E133" s="1"/>
       <c r="BO133" s="7"/>
       <c r="BR133" s="7"/>
     </row>
-    <row r="134" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="134" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D134" s="6"/>
       <c r="E134" s="1"/>
       <c r="BO134" s="7"/>
       <c r="BR134" s="7"/>
     </row>
-    <row r="135" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="135" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D135" s="6"/>
       <c r="E135" s="1"/>
       <c r="BO135" s="7"/>
       <c r="BR135" s="7"/>
     </row>
-    <row r="136" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="136" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D136" s="6"/>
       <c r="E136" s="1"/>
       <c r="BO136" s="7"/>
       <c r="BR136" s="7"/>
     </row>
-    <row r="137" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="137" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D137" s="6"/>
       <c r="E137" s="1"/>
       <c r="BO137" s="7"/>
       <c r="BR137" s="7"/>
     </row>
-    <row r="138" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="138" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D138" s="6"/>
       <c r="E138" s="1"/>
       <c r="BO138" s="7"/>
       <c r="BR138" s="7"/>
     </row>
-    <row r="139" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="139" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D139" s="6"/>
       <c r="E139" s="1"/>
       <c r="BO139" s="7"/>
       <c r="BR139" s="7"/>
     </row>
-    <row r="140" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="140" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D140" s="6"/>
       <c r="E140" s="1"/>
       <c r="BO140" s="7"/>
       <c r="BR140" s="7"/>
     </row>
-    <row r="141" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="141" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D141" s="6"/>
       <c r="E141" s="1"/>
       <c r="BO141" s="7"/>
       <c r="BR141" s="7"/>
     </row>
-    <row r="142" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="142" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D142" s="6"/>
       <c r="E142" s="1"/>
       <c r="BO142" s="7"/>
       <c r="BR142" s="7"/>
     </row>
-    <row r="143" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="143" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D143" s="6"/>
       <c r="E143" s="1"/>
       <c r="BO143" s="7"/>
       <c r="BR143" s="7"/>
     </row>
-    <row r="144" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="144" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D144" s="6"/>
       <c r="E144" s="1"/>
       <c r="BO144" s="7"/>
       <c r="BR144" s="7"/>
     </row>
-    <row r="145" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="145" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D145" s="6"/>
       <c r="E145" s="1"/>
       <c r="BO145" s="7"/>
       <c r="BR145" s="7"/>
     </row>
-    <row r="146" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="146" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D146" s="6"/>
       <c r="E146" s="1"/>
       <c r="BO146" s="7"/>
       <c r="BR146" s="7"/>
     </row>
-    <row r="147" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="147" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D147" s="6"/>
       <c r="E147" s="1"/>
       <c r="BO147" s="7"/>
       <c r="BR147" s="7"/>
     </row>
-    <row r="148" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="148" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D148" s="6"/>
       <c r="E148" s="1"/>
       <c r="BO148" s="7"/>
       <c r="BR148" s="7"/>
     </row>
-    <row r="149" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="149" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D149" s="6"/>
       <c r="E149" s="1"/>
       <c r="BO149" s="7"/>
       <c r="BR149" s="7"/>
     </row>
-    <row r="150" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="150" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D150" s="6"/>
       <c r="E150" s="1"/>
       <c r="BO150" s="7"/>
       <c r="BR150" s="7"/>
     </row>
-    <row r="151" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="151" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D151" s="6"/>
       <c r="E151" s="1"/>
       <c r="BO151" s="7"/>
       <c r="BR151" s="7"/>
     </row>
-    <row r="152" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="152" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D152" s="6"/>
       <c r="E152" s="1"/>
       <c r="BO152" s="7"/>
       <c r="BR152" s="7"/>
     </row>
-    <row r="153" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="153" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D153" s="6"/>
       <c r="E153" s="1"/>
       <c r="BO153" s="7"/>
       <c r="BR153" s="7"/>
     </row>
-    <row r="154" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="154" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D154" s="6"/>
       <c r="E154" s="1"/>
       <c r="BO154" s="7"/>
       <c r="BR154" s="7"/>
     </row>
-    <row r="155" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="155" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D155" s="6"/>
       <c r="E155" s="1"/>
       <c r="BO155" s="7"/>
       <c r="BR155" s="7"/>
     </row>
-    <row r="156" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="156" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D156" s="6"/>
       <c r="E156" s="1"/>
       <c r="BO156" s="7"/>
       <c r="BR156" s="7"/>
     </row>
-    <row r="157" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="157" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D157" s="6"/>
       <c r="E157" s="1"/>
       <c r="BO157" s="7"/>
       <c r="BR157" s="7"/>
     </row>
-    <row r="158" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="158" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D158" s="6"/>
       <c r="E158" s="1"/>
       <c r="BO158" s="7"/>
       <c r="BR158" s="7"/>
     </row>
-    <row r="159" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="159" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D159" s="6"/>
       <c r="E159" s="1"/>
       <c r="BO159" s="7"/>
       <c r="BR159" s="7"/>
     </row>
-    <row r="160" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="160" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D160" s="6"/>
       <c r="E160" s="1"/>
       <c r="BO160" s="7"/>
       <c r="BR160" s="7"/>
     </row>
-    <row r="161" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="161" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D161" s="6"/>
       <c r="E161" s="1"/>
       <c r="BO161" s="7"/>
       <c r="BR161" s="7"/>
     </row>
-    <row r="162" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="162" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D162" s="6"/>
       <c r="E162" s="1"/>
       <c r="BO162" s="7"/>
       <c r="BR162" s="7"/>
     </row>
-    <row r="163" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="163" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D163" s="6"/>
       <c r="E163" s="1"/>
       <c r="BO163" s="7"/>
       <c r="BR163" s="7"/>
     </row>
-    <row r="164" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="164" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D164" s="6"/>
       <c r="E164" s="1"/>
       <c r="BO164" s="7"/>
       <c r="BR164" s="7"/>
     </row>
-    <row r="165" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="165" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D165" s="6"/>
       <c r="E165" s="1"/>
       <c r="BO165" s="7"/>
       <c r="BR165" s="7"/>
     </row>
-    <row r="166" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="166" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D166" s="6"/>
       <c r="E166" s="1"/>
       <c r="BO166" s="7"/>
       <c r="BR166" s="7"/>
     </row>
-    <row r="167" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="167" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D167" s="6"/>
       <c r="E167" s="1"/>
       <c r="BO167" s="7"/>
       <c r="BR167" s="7"/>
     </row>
-    <row r="168" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="168" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D168" s="6"/>
       <c r="E168" s="1"/>
       <c r="BO168" s="7"/>
       <c r="BR168" s="7"/>
     </row>
-    <row r="169" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="169" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D169" s="6"/>
       <c r="E169" s="1"/>
       <c r="BO169" s="7"/>
       <c r="BR169" s="7"/>
     </row>
-    <row r="170" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="170" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D170" s="6"/>
       <c r="E170" s="1"/>
       <c r="BO170" s="7"/>
       <c r="BR170" s="7"/>
     </row>
-    <row r="171" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="171" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D171" s="6"/>
       <c r="E171" s="1"/>
       <c r="BO171" s="7"/>
       <c r="BR171" s="7"/>
     </row>
-    <row r="172" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="172" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D172" s="6"/>
       <c r="E172" s="1"/>
       <c r="BO172" s="7"/>
       <c r="BR172" s="7"/>
     </row>
-    <row r="173" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="173" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D173" s="6"/>
       <c r="E173" s="1"/>
       <c r="BO173" s="7"/>
       <c r="BR173" s="7"/>
     </row>
-    <row r="174" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="174" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D174" s="6"/>
       <c r="E174" s="1"/>
       <c r="BO174" s="7"/>
       <c r="BR174" s="7"/>
     </row>
-    <row r="175" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="175" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D175" s="6"/>
       <c r="E175" s="1"/>
       <c r="BO175" s="7"/>
       <c r="BR175" s="7"/>
     </row>
-    <row r="176" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="176" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D176" s="6"/>
       <c r="E176" s="1"/>
       <c r="BO176" s="7"/>
       <c r="BR176" s="7"/>
     </row>
-    <row r="177" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="177" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D177" s="6"/>
       <c r="E177" s="1"/>
       <c r="BO177" s="7"/>
       <c r="BR177" s="7"/>
     </row>
-    <row r="178" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="178" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D178" s="6"/>
       <c r="E178" s="1"/>
       <c r="BO178" s="7"/>
       <c r="BR178" s="7"/>
     </row>
-    <row r="179" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="179" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D179" s="6"/>
       <c r="E179" s="1"/>
       <c r="BO179" s="7"/>
       <c r="BR179" s="7"/>
     </row>
-    <row r="180" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="180" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D180" s="6"/>
       <c r="E180" s="1"/>
       <c r="BO180" s="7"/>
       <c r="BR180" s="7"/>
     </row>
-    <row r="181" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="181" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D181" s="6"/>
       <c r="E181" s="1"/>
       <c r="BO181" s="7"/>
       <c r="BR181" s="7"/>
     </row>
-    <row r="182" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="182" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D182" s="6"/>
       <c r="E182" s="1"/>
       <c r="BO182" s="7"/>
       <c r="BR182" s="7"/>
     </row>
-    <row r="183" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="183" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D183" s="6"/>
       <c r="E183" s="1"/>
       <c r="BO183" s="7"/>
       <c r="BR183" s="7"/>
     </row>
-    <row r="184" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="184" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D184" s="6"/>
       <c r="E184" s="1"/>
       <c r="BO184" s="7"/>
       <c r="BR184" s="7"/>
     </row>
-    <row r="185" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="185" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D185" s="6"/>
       <c r="E185" s="1"/>
       <c r="BO185" s="7"/>
       <c r="BR185" s="7"/>
     </row>
-    <row r="186" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="186" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D186" s="6"/>
       <c r="E186" s="1"/>
       <c r="BO186" s="7"/>
       <c r="BR186" s="7"/>
     </row>
-    <row r="187" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="187" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D187" s="6"/>
       <c r="E187" s="1"/>
       <c r="BO187" s="7"/>
       <c r="BR187" s="7"/>
     </row>
-    <row r="188" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="188" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D188" s="6"/>
       <c r="E188" s="1"/>
       <c r="BO188" s="7"/>
       <c r="BR188" s="7"/>
     </row>
-    <row r="189" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="189" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D189" s="6"/>
       <c r="E189" s="1"/>
       <c r="BO189" s="7"/>
       <c r="BR189" s="7"/>
     </row>
-    <row r="190" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="190" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D190" s="6"/>
       <c r="E190" s="1"/>
       <c r="BO190" s="7"/>
       <c r="BR190" s="7"/>
     </row>
-    <row r="191" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="191" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D191" s="6"/>
       <c r="E191" s="1"/>
       <c r="BO191" s="7"/>
       <c r="BR191" s="7"/>
     </row>
-    <row r="192" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="192" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D192" s="6"/>
       <c r="E192" s="1"/>
       <c r="BO192" s="7"/>
       <c r="BR192" s="7"/>
     </row>
-    <row r="193" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="193" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D193" s="6"/>
       <c r="E193" s="1"/>
       <c r="BO193" s="7"/>
       <c r="BR193" s="7"/>
     </row>
-    <row r="194" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="194" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D194" s="6"/>
       <c r="E194" s="1"/>
       <c r="BO194" s="7"/>
       <c r="BR194" s="7"/>
     </row>
-    <row r="195" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="195" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D195" s="6"/>
       <c r="E195" s="1"/>
       <c r="BO195" s="7"/>
       <c r="BR195" s="7"/>
     </row>
-    <row r="196" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="196" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D196" s="6"/>
       <c r="E196" s="1"/>
       <c r="BO196" s="7"/>
       <c r="BR196" s="7"/>
     </row>
-    <row r="197" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="197" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D197" s="6"/>
       <c r="E197" s="1"/>
       <c r="BO197" s="7"/>
       <c r="BR197" s="7"/>
     </row>
-    <row r="198" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="198" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D198" s="6"/>
       <c r="E198" s="1"/>
       <c r="BO198" s="7"/>
       <c r="BR198" s="7"/>
     </row>
-    <row r="199" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="199" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D199" s="6"/>
       <c r="E199" s="1"/>
       <c r="BO199" s="7"/>
       <c r="BR199" s="7"/>
     </row>
-    <row r="200" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="200" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D200" s="6"/>
       <c r="E200" s="1"/>
       <c r="BO200" s="7"/>
       <c r="BR200" s="7"/>
     </row>
-    <row r="201" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="201" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D201" s="6"/>
       <c r="E201" s="1"/>
       <c r="BO201" s="7"/>
       <c r="BR201" s="7"/>
     </row>
-    <row r="202" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="202" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D202" s="6"/>
       <c r="E202" s="1"/>
       <c r="BO202" s="7"/>
       <c r="BR202" s="7"/>
     </row>
-    <row r="203" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="203" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D203" s="6"/>
       <c r="E203" s="1"/>
       <c r="BO203" s="7"/>
       <c r="BR203" s="7"/>
     </row>
-    <row r="204" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="204" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D204" s="6"/>
       <c r="E204" s="1"/>
       <c r="BO204" s="7"/>
       <c r="BR204" s="7"/>
     </row>
-    <row r="205" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="205" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D205" s="6"/>
       <c r="E205" s="1"/>
       <c r="BO205" s="7"/>
       <c r="BR205" s="7"/>
     </row>
-    <row r="206" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="206" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D206" s="6"/>
       <c r="E206" s="1"/>
       <c r="BO206" s="7"/>
       <c r="BR206" s="7"/>
     </row>
-    <row r="207" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="207" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D207" s="6"/>
       <c r="E207" s="1"/>
       <c r="BO207" s="7"/>
       <c r="BR207" s="7"/>
     </row>
-    <row r="208" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="208" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D208" s="6"/>
       <c r="E208" s="1"/>
       <c r="BO208" s="7"/>
       <c r="BR208" s="7"/>
     </row>
-    <row r="209" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="209" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D209" s="6"/>
       <c r="E209" s="1"/>
       <c r="BO209" s="7"/>
       <c r="BR209" s="7"/>
     </row>
-    <row r="210" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="210" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D210" s="6"/>
       <c r="E210" s="1"/>
       <c r="BO210" s="7"/>
       <c r="BR210" s="7"/>
     </row>
-    <row r="211" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="211" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D211" s="6"/>
       <c r="E211" s="1"/>
       <c r="BO211" s="7"/>
       <c r="BR211" s="7"/>
     </row>
-    <row r="212" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="212" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D212" s="6"/>
       <c r="E212" s="1"/>
       <c r="BO212" s="7"/>
       <c r="BR212" s="7"/>
     </row>
-    <row r="213" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="213" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D213" s="6"/>
       <c r="E213" s="1"/>
       <c r="BO213" s="7"/>
       <c r="BR213" s="7"/>
     </row>
-    <row r="214" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="214" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D214" s="6"/>
       <c r="E214" s="1"/>
       <c r="BO214" s="7"/>
       <c r="BR214" s="7"/>
     </row>
-    <row r="215" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="215" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D215" s="6"/>
       <c r="E215" s="1"/>
       <c r="BO215" s="7"/>
       <c r="BR215" s="7"/>
     </row>
-    <row r="216" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="216" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D216" s="6"/>
       <c r="E216" s="1"/>
       <c r="BO216" s="7"/>
       <c r="BR216" s="7"/>
     </row>
-    <row r="217" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="217" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D217" s="6"/>
       <c r="E217" s="1"/>
       <c r="BO217" s="7"/>
       <c r="BR217" s="7"/>
     </row>
-    <row r="218" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="218" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D218" s="6"/>
       <c r="E218" s="1"/>
       <c r="BO218" s="7"/>
       <c r="BR218" s="7"/>
     </row>
-    <row r="219" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="219" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D219" s="6"/>
       <c r="E219" s="1"/>
       <c r="BO219" s="7"/>
       <c r="BR219" s="7"/>
     </row>
-    <row r="220" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="220" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D220" s="6"/>
       <c r="E220" s="1"/>
       <c r="BO220" s="7"/>
       <c r="BR220" s="7"/>
     </row>
-    <row r="221" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="221" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D221" s="6"/>
       <c r="E221" s="1"/>
       <c r="BO221" s="7"/>
       <c r="BR221" s="7"/>
     </row>
-    <row r="222" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="222" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D222" s="6"/>
       <c r="E222" s="1"/>
       <c r="BO222" s="7"/>
       <c r="BR222" s="7"/>
     </row>
-    <row r="223" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="223" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D223" s="6"/>
       <c r="E223" s="1"/>
       <c r="BO223" s="7"/>
       <c r="BR223" s="7"/>
     </row>
-    <row r="224" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="224" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D224" s="6"/>
       <c r="E224" s="1"/>
       <c r="BO224" s="7"/>
       <c r="BR224" s="7"/>
     </row>
-    <row r="225" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="225" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D225" s="6"/>
       <c r="E225" s="1"/>
       <c r="BO225" s="7"/>
       <c r="BR225" s="7"/>
     </row>
-    <row r="226" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="226" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D226" s="6"/>
       <c r="E226" s="1"/>
       <c r="BO226" s="7"/>
       <c r="BR226" s="7"/>
     </row>
-    <row r="227" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="227" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D227" s="6"/>
       <c r="E227" s="1"/>
       <c r="BO227" s="7"/>
       <c r="BR227" s="7"/>
     </row>
-    <row r="228" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="228" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D228" s="6"/>
       <c r="E228" s="1"/>
       <c r="BO228" s="7"/>
       <c r="BR228" s="7"/>
     </row>
-    <row r="229" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="229" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D229" s="6"/>
       <c r="E229" s="1"/>
       <c r="BO229" s="7"/>
       <c r="BR229" s="7"/>
     </row>
-    <row r="230" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="230" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D230" s="6"/>
       <c r="E230" s="1"/>
       <c r="BO230" s="7"/>
       <c r="BR230" s="7"/>
     </row>
-    <row r="231" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="231" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D231" s="6"/>
       <c r="E231" s="1"/>
       <c r="BO231" s="7"/>
       <c r="BR231" s="7"/>
     </row>
-    <row r="232" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="232" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D232" s="6"/>
       <c r="E232" s="1"/>
       <c r="BO232" s="7"/>
       <c r="BR232" s="7"/>
     </row>
-    <row r="233" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="233" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D233" s="6"/>
       <c r="E233" s="1"/>
       <c r="BO233" s="7"/>
       <c r="BR233" s="7"/>
     </row>
-    <row r="234" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="234" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D234" s="6"/>
       <c r="E234" s="1"/>
       <c r="BO234" s="7"/>
       <c r="BR234" s="7"/>
     </row>
-    <row r="235" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="235" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D235" s="6"/>
       <c r="E235" s="1"/>
       <c r="BO235" s="7"/>
       <c r="BR235" s="7"/>
     </row>
-    <row r="236" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="236" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D236" s="6"/>
       <c r="E236" s="1"/>
       <c r="BO236" s="7"/>
       <c r="BR236" s="7"/>
     </row>
-    <row r="237" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="237" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D237" s="6"/>
       <c r="E237" s="1"/>
       <c r="BO237" s="7"/>
       <c r="BR237" s="7"/>
     </row>
-    <row r="238" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="238" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D238" s="6"/>
       <c r="E238" s="1"/>
       <c r="BO238" s="7"/>
       <c r="BR238" s="7"/>
     </row>
-    <row r="239" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="239" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D239" s="6"/>
       <c r="E239" s="1"/>
       <c r="BO239" s="7"/>
       <c r="BR239" s="7"/>
     </row>
-    <row r="240" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="240" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D240" s="6"/>
       <c r="E240" s="1"/>
       <c r="BO240" s="7"/>
       <c r="BR240" s="7"/>
     </row>
-    <row r="241" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="241" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D241" s="6"/>
       <c r="E241" s="1"/>
       <c r="BO241" s="7"/>
       <c r="BR241" s="7"/>
     </row>
-    <row r="242" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="242" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D242" s="6"/>
       <c r="E242" s="1"/>
       <c r="BO242" s="7"/>
       <c r="BR242" s="7"/>
     </row>
-    <row r="243" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="243" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D243" s="6"/>
       <c r="E243" s="1"/>
       <c r="BO243" s="7"/>
       <c r="BR243" s="7"/>
     </row>
-    <row r="244" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="244" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D244" s="6"/>
       <c r="E244" s="1"/>
       <c r="BO244" s="7"/>
       <c r="BR244" s="7"/>
     </row>
-    <row r="245" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="245" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D245" s="6"/>
       <c r="E245" s="1"/>
       <c r="BO245" s="7"/>
       <c r="BR245" s="7"/>
     </row>
-    <row r="246" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="246" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D246" s="6"/>
       <c r="E246" s="1"/>
       <c r="BO246" s="7"/>
       <c r="BR246" s="7"/>
     </row>
-    <row r="247" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="247" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D247" s="6"/>
       <c r="E247" s="1"/>
       <c r="BO247" s="7"/>
       <c r="BR247" s="7"/>
     </row>
-    <row r="248" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="248" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D248" s="6"/>
       <c r="E248" s="1"/>
       <c r="BO248" s="7"/>
       <c r="BR248" s="7"/>
     </row>
-    <row r="249" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="249" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D249" s="6"/>
       <c r="E249" s="1"/>
       <c r="BO249" s="7"/>
       <c r="BR249" s="7"/>
     </row>
-    <row r="250" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="250" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D250" s="6"/>
       <c r="E250" s="1"/>
       <c r="BO250" s="7"/>
       <c r="BR250" s="7"/>
     </row>
-    <row r="251" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="251" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D251" s="6"/>
       <c r="E251" s="1"/>
       <c r="BO251" s="7"/>
       <c r="BR251" s="7"/>
     </row>
-    <row r="252" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="252" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D252" s="6"/>
       <c r="E252" s="1"/>
       <c r="BO252" s="7"/>
       <c r="BR252" s="7"/>
     </row>
-    <row r="253" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="253" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D253" s="6"/>
       <c r="E253" s="1"/>
       <c r="BO253" s="7"/>
       <c r="BR253" s="7"/>
     </row>
-    <row r="254" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="254" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D254" s="6"/>
       <c r="E254" s="1"/>
       <c r="BO254" s="7"/>
       <c r="BR254" s="7"/>
     </row>
-    <row r="255" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="255" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D255" s="6"/>
       <c r="E255" s="1"/>
       <c r="BO255" s="7"/>
       <c r="BR255" s="7"/>
     </row>
-    <row r="256" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="256" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D256" s="6"/>
       <c r="E256" s="1"/>
       <c r="BO256" s="7"/>
       <c r="BR256" s="7"/>
     </row>
-    <row r="257" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="257" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D257" s="6"/>
       <c r="E257" s="1"/>
       <c r="BO257" s="7"/>
       <c r="BR257" s="7"/>
     </row>
-    <row r="258" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="258" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D258" s="6"/>
       <c r="E258" s="1"/>
       <c r="BR258" s="7"/>
     </row>
-    <row r="259" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="259" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D259" s="6"/>
       <c r="E259" s="1"/>
       <c r="BO259" s="7"/>
       <c r="BR259" s="7"/>
     </row>
-    <row r="260" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="260" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D260" s="6"/>
       <c r="E260" s="1"/>
       <c r="BO260" s="7"/>
       <c r="BR260" s="7"/>
     </row>
-    <row r="261" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="261" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D261" s="6"/>
       <c r="E261" s="1"/>
       <c r="BO261" s="7"/>
       <c r="BR261" s="7"/>
     </row>
-    <row r="262" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="262" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D262" s="6"/>
       <c r="E262" s="1"/>
       <c r="BO262" s="7"/>
       <c r="BR262" s="7"/>
     </row>
-    <row r="263" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="263" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D263" s="6"/>
       <c r="E263" s="1"/>
       <c r="BO263" s="7"/>
       <c r="BR263" s="7"/>
     </row>
-    <row r="264" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="264" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D264" s="6"/>
       <c r="E264" s="1"/>
       <c r="BO264" s="7"/>
       <c r="BR264" s="7"/>
     </row>
-    <row r="265" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="265" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D265" s="6"/>
       <c r="E265" s="1"/>
       <c r="BO265" s="7"/>
       <c r="BR265" s="7"/>
     </row>
-    <row r="266" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="266" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D266" s="6"/>
       <c r="E266" s="1"/>
       <c r="BO266" s="7"/>
       <c r="BR266" s="7"/>
     </row>
-    <row r="267" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="267" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D267" s="6"/>
       <c r="E267" s="1"/>
       <c r="BO267" s="7"/>
       <c r="BR267" s="7"/>
     </row>
-    <row r="268" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="268" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D268" s="6"/>
       <c r="E268" s="1"/>
       <c r="BO268" s="7"/>
       <c r="BR268" s="7"/>
     </row>
-    <row r="269" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="269" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D269" s="6"/>
       <c r="E269" s="1"/>
       <c r="BO269" s="7"/>
       <c r="BR269" s="7"/>
     </row>
-    <row r="270" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="270" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D270" s="6"/>
       <c r="E270" s="1"/>
       <c r="BO270" s="7"/>
       <c r="BR270" s="7"/>
     </row>
-    <row r="271" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="271" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D271" s="6"/>
       <c r="E271" s="1"/>
       <c r="BO271" s="7"/>
       <c r="BR271" s="7"/>
     </row>
-    <row r="272" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="272" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D272" s="6"/>
       <c r="E272" s="1"/>
       <c r="BO272" s="7"/>
       <c r="BR272" s="7"/>
     </row>
-    <row r="273" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="273" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D273" s="6"/>
       <c r="E273" s="1"/>
       <c r="BO273" s="7"/>
       <c r="BR273" s="7"/>
     </row>
-    <row r="274" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="274" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D274" s="6"/>
       <c r="E274" s="1"/>
       <c r="BO274" s="7"/>
       <c r="BR274" s="7"/>
     </row>
-    <row r="275" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="275" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D275" s="6"/>
       <c r="E275" s="1"/>
       <c r="BO275" s="7"/>
       <c r="BR275" s="7"/>
     </row>
-    <row r="276" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="276" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D276" s="6"/>
       <c r="E276" s="1"/>
       <c r="BO276" s="7"/>
       <c r="BR276" s="7"/>
     </row>
-    <row r="277" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="277" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D277" s="6"/>
       <c r="E277" s="1"/>
       <c r="BO277" s="7"/>
       <c r="BR277" s="7"/>
     </row>
-    <row r="278" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="278" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D278" s="6"/>
       <c r="E278" s="1"/>
       <c r="BO278" s="7"/>
       <c r="BR278" s="7"/>
     </row>
-    <row r="279" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="279" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D279" s="6"/>
       <c r="E279" s="1"/>
       <c r="BO279" s="7"/>
       <c r="BR279" s="7"/>
     </row>
-    <row r="280" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="280" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D280" s="6"/>
       <c r="E280" s="1"/>
       <c r="BO280" s="7"/>
       <c r="BR280" s="7"/>
     </row>
-    <row r="281" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="281" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D281" s="6"/>
       <c r="E281" s="1"/>
       <c r="BO281" s="7"/>
       <c r="BR281" s="7"/>
     </row>
-    <row r="282" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="282" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D282" s="6"/>
       <c r="E282" s="1"/>
       <c r="BO282" s="7"/>
       <c r="BR282" s="7"/>
     </row>
-    <row r="283" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="283" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D283" s="6"/>
       <c r="E283" s="1"/>
       <c r="BO283" s="7"/>
       <c r="BR283" s="7"/>
     </row>
-    <row r="284" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="284" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D284" s="6"/>
       <c r="E284" s="1"/>
       <c r="BO284" s="7"/>
       <c r="BR284" s="7"/>
     </row>
-    <row r="285" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="285" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D285" s="6"/>
       <c r="E285" s="1"/>
       <c r="BO285" s="7"/>
       <c r="BR285" s="7"/>
     </row>
-    <row r="286" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="286" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D286" s="6"/>
       <c r="E286" s="1"/>
       <c r="BO286" s="7"/>
       <c r="BR286" s="7"/>
     </row>
-    <row r="287" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="287" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D287" s="6"/>
       <c r="E287" s="1"/>
       <c r="BO287" s="7"/>
       <c r="BR287" s="7"/>
     </row>
-    <row r="288" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="288" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D288" s="6"/>
       <c r="E288" s="1"/>
       <c r="BO288" s="7"/>
       <c r="BR288" s="7"/>
     </row>
-    <row r="289" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="289" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D289" s="6"/>
       <c r="E289" s="1"/>
       <c r="BO289" s="7"/>
       <c r="BR289" s="7"/>
     </row>
-    <row r="290" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="290" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D290" s="6"/>
       <c r="E290" s="1"/>
       <c r="BO290" s="7"/>
       <c r="BR290" s="7"/>
     </row>
-    <row r="291" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="291" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D291" s="6"/>
       <c r="E291" s="1"/>
       <c r="BO291" s="7"/>
       <c r="BR291" s="7"/>
     </row>
-    <row r="292" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="292" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D292" s="6"/>
       <c r="E292" s="1"/>
       <c r="BO292" s="7"/>
       <c r="BR292" s="7"/>
     </row>
-    <row r="293" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="293" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D293" s="6"/>
       <c r="E293" s="1"/>
       <c r="BO293" s="7"/>
       <c r="BR293" s="7"/>
     </row>
-    <row r="294" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="294" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D294" s="6"/>
       <c r="E294" s="1"/>
       <c r="BO294" s="7"/>
       <c r="BR294" s="7"/>
     </row>
-    <row r="295" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="295" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D295" s="6"/>
       <c r="E295" s="1"/>
       <c r="BO295" s="7"/>
       <c r="BR295" s="7"/>
     </row>
-    <row r="296" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="296" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D296" s="6"/>
       <c r="E296" s="1"/>
       <c r="BO296" s="7"/>
       <c r="BR296" s="7"/>
     </row>
-    <row r="297" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="297" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D297" s="6"/>
       <c r="E297" s="1"/>
       <c r="BO297" s="7"/>
       <c r="BR297" s="7"/>
     </row>
-    <row r="298" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="298" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D298" s="6"/>
       <c r="E298" s="1"/>
       <c r="BO298" s="7"/>
       <c r="BR298" s="7"/>
     </row>
-    <row r="299" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="299" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D299" s="6"/>
       <c r="E299" s="1"/>
       <c r="BO299" s="7"/>
       <c r="BR299" s="7"/>
     </row>
-    <row r="300" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="300" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D300" s="6"/>
       <c r="E300" s="1"/>
       <c r="BO300" s="7"/>
       <c r="BR300" s="7"/>
     </row>
-    <row r="301" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="301" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D301" s="6"/>
       <c r="E301" s="1"/>
       <c r="BR301" s="7"/>
     </row>
-    <row r="302" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="302" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D302" s="6"/>
       <c r="E302" s="1"/>
       <c r="BO302" s="7"/>
       <c r="BR302" s="7"/>
     </row>
-    <row r="303" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="303" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D303" s="6"/>
       <c r="E303" s="1"/>
       <c r="BO303" s="7"/>
       <c r="BR303" s="7"/>
     </row>
-    <row r="304" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="304" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D304" s="6"/>
       <c r="E304" s="1"/>
       <c r="BO304" s="7"/>
       <c r="BR304" s="7"/>
     </row>
-    <row r="305" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="305" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D305" s="6"/>
       <c r="E305" s="1"/>
       <c r="BO305" s="7"/>
       <c r="BR305" s="7"/>
     </row>
-    <row r="306" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="306" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D306" s="6"/>
       <c r="E306" s="1"/>
       <c r="BO306" s="7"/>
       <c r="BR306" s="7"/>
     </row>
-    <row r="307" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="307" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D307" s="6"/>
       <c r="E307" s="1"/>
       <c r="BO307" s="7"/>
       <c r="BR307" s="7"/>
     </row>
-    <row r="308" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="308" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D308" s="6"/>
       <c r="E308" s="1"/>
       <c r="BO308" s="7"/>
       <c r="BR308" s="7"/>
     </row>
-    <row r="309" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="309" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D309" s="6"/>
       <c r="E309" s="1"/>
       <c r="BO309" s="7"/>
       <c r="BR309" s="7"/>
     </row>
-    <row r="310" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="310" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D310" s="6"/>
       <c r="E310" s="1"/>
       <c r="BO310" s="7"/>
       <c r="BR310" s="7"/>
     </row>
-    <row r="311" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="311" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D311" s="6"/>
       <c r="E311" s="1"/>
       <c r="BO311" s="7"/>
       <c r="BR311" s="7"/>
     </row>
-    <row r="312" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="312" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D312" s="6"/>
       <c r="E312" s="1"/>
       <c r="BO312" s="7"/>
       <c r="BR312" s="7"/>
     </row>
-    <row r="313" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="313" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D313" s="6"/>
       <c r="E313" s="1"/>
       <c r="BO313" s="7"/>
       <c r="BR313" s="7"/>
     </row>
-    <row r="314" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="314" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D314" s="6"/>
       <c r="E314" s="1"/>
       <c r="BO314" s="7"/>
       <c r="BR314" s="7"/>
     </row>
-    <row r="315" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="315" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D315" s="6"/>
       <c r="E315" s="1"/>
       <c r="BO315" s="7"/>
       <c r="BR315" s="7"/>
     </row>
-    <row r="316" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="316" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D316" s="6"/>
       <c r="E316" s="1"/>
       <c r="BO316" s="7"/>
       <c r="BR316" s="7"/>
     </row>
-    <row r="317" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="317" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D317" s="6"/>
       <c r="E317" s="1"/>
       <c r="BO317" s="7"/>
       <c r="BR317" s="7"/>
     </row>
-    <row r="318" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="318" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D318" s="6"/>
       <c r="E318" s="1"/>
       <c r="BO318" s="7"/>
       <c r="BR318" s="7"/>
     </row>
-    <row r="319" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="319" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D319" s="6"/>
       <c r="E319" s="1"/>
       <c r="BO319" s="7"/>
       <c r="BR319" s="7"/>
     </row>
-    <row r="320" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="320" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D320" s="6"/>
       <c r="E320" s="1"/>
       <c r="BO320" s="7"/>
       <c r="BR320" s="7"/>
     </row>
-    <row r="321" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="321" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D321" s="6"/>
       <c r="E321" s="1"/>
       <c r="BO321" s="7"/>
       <c r="BR321" s="7"/>
     </row>
-    <row r="322" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="322" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D322" s="6"/>
       <c r="E322" s="1"/>
       <c r="BO322" s="7"/>
       <c r="BR322" s="7"/>
     </row>
-    <row r="323" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="323" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D323" s="6"/>
       <c r="E323" s="1"/>
       <c r="BO323" s="7"/>
       <c r="BR323" s="7"/>
     </row>
-    <row r="324" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="324" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D324" s="6"/>
       <c r="E324" s="1"/>
       <c r="BO324" s="7"/>
       <c r="BR324" s="7"/>
     </row>
-    <row r="325" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="325" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D325" s="6"/>
       <c r="E325" s="1"/>
       <c r="BO325" s="7"/>
       <c r="BR325" s="7"/>
     </row>
-    <row r="326" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="326" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D326" s="6"/>
       <c r="E326" s="1"/>
       <c r="BO326" s="7"/>
       <c r="BR326" s="7"/>
     </row>
-    <row r="327" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="327" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D327" s="6"/>
       <c r="E327" s="1"/>
       <c r="BO327" s="7"/>
       <c r="BR327" s="7"/>
     </row>
-    <row r="328" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="328" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D328" s="6"/>
       <c r="E328" s="1"/>
       <c r="BO328" s="7"/>
       <c r="BR328" s="7"/>
     </row>
-    <row r="329" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="329" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D329" s="6"/>
       <c r="E329" s="1"/>
       <c r="BO329" s="7"/>
       <c r="BR329" s="7"/>
     </row>
-    <row r="330" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="330" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D330" s="6"/>
       <c r="E330" s="1"/>
       <c r="BO330" s="7"/>
       <c r="BR330" s="7"/>
     </row>
-    <row r="331" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="331" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D331" s="6"/>
       <c r="E331" s="1"/>
       <c r="BO331" s="7"/>
       <c r="BR331" s="7"/>
     </row>
-    <row r="332" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="332" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D332" s="6"/>
       <c r="E332" s="1"/>
       <c r="BO332" s="7"/>
       <c r="BR332" s="7"/>
     </row>
-    <row r="333" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="333" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D333" s="6"/>
       <c r="E333" s="1"/>
       <c r="BO333" s="7"/>
       <c r="BR333" s="7"/>
     </row>
-    <row r="334" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="334" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D334" s="6"/>
       <c r="E334" s="1"/>
       <c r="BO334" s="7"/>
       <c r="BR334" s="7"/>
     </row>
-    <row r="335" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="335" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D335" s="6"/>
       <c r="E335" s="1"/>
       <c r="BO335" s="7"/>
       <c r="BR335" s="7"/>
     </row>
-    <row r="336" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="336" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D336" s="6"/>
       <c r="E336" s="1"/>
       <c r="BO336" s="7"/>
       <c r="BR336" s="7"/>
     </row>
-    <row r="337" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="337" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D337" s="6"/>
       <c r="E337" s="1"/>
       <c r="BO337" s="7"/>
       <c r="BR337" s="7"/>
     </row>
-    <row r="338" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="338" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D338" s="6"/>
       <c r="E338" s="1"/>
       <c r="BO338" s="7"/>
       <c r="BR338" s="7"/>
     </row>
-    <row r="339" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="339" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D339" s="6"/>
       <c r="E339" s="1"/>
       <c r="BO339" s="7"/>
       <c r="BR339" s="7"/>
     </row>
-    <row r="340" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="340" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D340" s="6"/>
       <c r="E340" s="1"/>
       <c r="BO340" s="7"/>
       <c r="BR340" s="7"/>
     </row>
-    <row r="341" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="341" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D341" s="6"/>
       <c r="E341" s="1"/>
       <c r="BO341" s="7"/>
       <c r="BR341" s="7"/>
     </row>
-    <row r="342" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="342" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D342" s="6"/>
       <c r="E342" s="1"/>
       <c r="BO342" s="7"/>
       <c r="BR342" s="7"/>
     </row>
-    <row r="343" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="343" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D343" s="6"/>
       <c r="E343" s="1"/>
       <c r="BO343" s="7"/>
       <c r="BR343" s="7"/>
     </row>
-    <row r="344" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="344" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D344" s="6"/>
       <c r="E344" s="1"/>
       <c r="BO344" s="7"/>
       <c r="BR344" s="7"/>
     </row>
-    <row r="345" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="345" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D345" s="6"/>
       <c r="E345" s="1"/>
       <c r="BO345" s="7"/>
       <c r="BR345" s="7"/>
     </row>
-    <row r="346" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="346" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D346" s="6"/>
       <c r="E346" s="1"/>
       <c r="BO346" s="7"/>
       <c r="BR346" s="7"/>
     </row>
-    <row r="347" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="347" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D347" s="6"/>
       <c r="E347" s="1"/>
       <c r="BO347" s="7"/>
       <c r="BR347" s="7"/>
     </row>
-    <row r="348" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="348" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D348" s="6"/>
       <c r="E348" s="1"/>
       <c r="BO348" s="7"/>
       <c r="BR348" s="7"/>
     </row>
-    <row r="349" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="349" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D349" s="6"/>
       <c r="E349" s="1"/>
       <c r="BO349" s="7"/>
       <c r="BR349" s="7"/>
     </row>
-    <row r="350" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="350" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D350" s="6"/>
       <c r="E350" s="1"/>
       <c r="BO350" s="7"/>
       <c r="BR350" s="7"/>
     </row>
-    <row r="351" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="351" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D351" s="6"/>
       <c r="E351" s="1"/>
       <c r="BO351" s="7"/>
       <c r="BR351" s="7"/>
     </row>
-    <row r="352" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="352" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D352" s="6"/>
       <c r="E352" s="1"/>
       <c r="BO352" s="7"/>
       <c r="BR352" s="7"/>
     </row>
-    <row r="353" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="353" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D353" s="6"/>
       <c r="E353" s="1"/>
       <c r="BO353" s="7"/>
       <c r="BR353" s="7"/>
     </row>
-    <row r="354" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="354" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D354" s="6"/>
       <c r="E354" s="1"/>
       <c r="BO354" s="7"/>
       <c r="BR354" s="7"/>
     </row>
-    <row r="355" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="355" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D355" s="6"/>
       <c r="E355" s="1"/>
       <c r="BO355" s="7"/>
       <c r="BR355" s="7"/>
     </row>
-    <row r="356" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="356" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D356" s="6"/>
       <c r="E356" s="1"/>
       <c r="BO356" s="7"/>
       <c r="BR356" s="7"/>
     </row>
-    <row r="357" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="357" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D357" s="6"/>
       <c r="E357" s="1"/>
       <c r="BR357" s="7"/>
     </row>
-    <row r="358" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="358" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D358" s="6"/>
       <c r="E358" s="1"/>
       <c r="BR358" s="7"/>
     </row>
-    <row r="359" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="359" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D359" s="6"/>
       <c r="E359" s="1"/>
       <c r="BR359" s="7"/>
     </row>
-    <row r="360" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="360" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D360" s="6"/>
       <c r="E360" s="1"/>
       <c r="BO360" s="7"/>
       <c r="BR360" s="7"/>
     </row>
-    <row r="361" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="361" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D361" s="6"/>
       <c r="E361" s="1"/>
       <c r="BO361" s="7"/>
       <c r="BR361" s="7"/>
     </row>
-    <row r="362" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="362" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D362" s="6"/>
       <c r="E362" s="1"/>
       <c r="BO362" s="7"/>
       <c r="BR362" s="7"/>
     </row>
-    <row r="363" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="363" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D363" s="6"/>
       <c r="E363" s="1"/>
       <c r="BO363" s="7"/>
       <c r="BR363" s="7"/>
     </row>
-    <row r="364" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="364" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D364" s="6"/>
       <c r="E364" s="1"/>
       <c r="BO364" s="7"/>
       <c r="BR364" s="7"/>
     </row>
-    <row r="365" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="365" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D365" s="6"/>
       <c r="E365" s="1"/>
       <c r="BO365" s="7"/>
       <c r="BR365" s="7"/>
     </row>
-    <row r="366" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="366" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D366" s="6"/>
       <c r="E366" s="1"/>
       <c r="BO366" s="7"/>
       <c r="BR366" s="7"/>
     </row>
-    <row r="367" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="367" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D367" s="6"/>
       <c r="E367" s="1"/>
       <c r="BO367" s="7"/>
       <c r="BR367" s="7"/>
     </row>
-    <row r="368" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="368" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D368" s="6"/>
       <c r="E368" s="1"/>
       <c r="BO368" s="7"/>
       <c r="BR368" s="7"/>
     </row>
-    <row r="369" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="369" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D369" s="6"/>
       <c r="E369" s="1"/>
       <c r="BO369" s="7"/>
       <c r="BR369" s="7"/>
     </row>
-    <row r="370" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="370" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D370" s="6"/>
       <c r="E370" s="1"/>
       <c r="BO370" s="7"/>
       <c r="BR370" s="7"/>
     </row>
-    <row r="371" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="371" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D371" s="6"/>
       <c r="E371" s="1"/>
       <c r="BO371" s="7"/>
       <c r="BR371" s="7"/>
     </row>
-    <row r="372" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="372" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D372" s="6"/>
       <c r="E372" s="1"/>
       <c r="BO372" s="7"/>
       <c r="BR372" s="7"/>
     </row>
-    <row r="373" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="373" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D373" s="6"/>
       <c r="E373" s="1"/>
       <c r="BO373" s="7"/>
       <c r="BR373" s="7"/>
     </row>
-    <row r="374" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="374" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D374" s="6"/>
       <c r="E374" s="1"/>
       <c r="BO374" s="7"/>
       <c r="BR374" s="7"/>
     </row>
-    <row r="375" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="375" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D375" s="6"/>
       <c r="E375" s="1"/>
       <c r="BO375" s="7"/>
       <c r="BR375" s="7"/>
     </row>
-    <row r="376" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="376" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D376" s="6"/>
       <c r="E376" s="1"/>
       <c r="BO376" s="7"/>
       <c r="BR376" s="7"/>
     </row>
-    <row r="377" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="377" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D377" s="6"/>
       <c r="E377" s="1"/>
       <c r="BO377" s="7"/>
       <c r="BR377" s="7"/>
     </row>
-    <row r="378" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="378" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D378" s="6"/>
       <c r="E378" s="1"/>
       <c r="BO378" s="7"/>
       <c r="BR378" s="7"/>
     </row>
-    <row r="379" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="379" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D379" s="6"/>
       <c r="E379" s="1"/>
       <c r="BO379" s="7"/>
       <c r="BR379" s="7"/>
     </row>
-    <row r="380" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="380" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D380" s="6"/>
       <c r="E380" s="1"/>
       <c r="BO380" s="7"/>
       <c r="BR380" s="7"/>
     </row>
-    <row r="381" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="381" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D381" s="6"/>
       <c r="E381" s="1"/>
       <c r="BO381" s="7"/>
       <c r="BR381" s="7"/>
     </row>
-    <row r="382" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="382" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D382" s="6"/>
       <c r="E382" s="1"/>
       <c r="BO382" s="7"/>
       <c r="BR382" s="7"/>
     </row>
-    <row r="383" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="383" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D383" s="6"/>
       <c r="E383" s="1"/>
       <c r="BO383" s="7"/>
       <c r="BR383" s="7"/>
     </row>
-    <row r="384" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="384" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D384" s="6"/>
       <c r="E384" s="1"/>
       <c r="BO384" s="7"/>
       <c r="BR384" s="7"/>
     </row>
-    <row r="385" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="385" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D385" s="6"/>
       <c r="E385" s="1"/>
       <c r="BO385" s="7"/>
       <c r="BR385" s="7"/>
     </row>
-    <row r="386" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="386" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D386" s="6"/>
       <c r="E386" s="1"/>
       <c r="BO386" s="7"/>
       <c r="BR386" s="7"/>
     </row>
-    <row r="387" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="387" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D387" s="6"/>
       <c r="E387" s="1"/>
       <c r="BO387" s="7"/>
       <c r="BR387" s="7"/>
     </row>
-    <row r="388" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="388" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D388" s="6"/>
       <c r="E388" s="1"/>
       <c r="BO388" s="7"/>
       <c r="BR388" s="7"/>
     </row>
-    <row r="389" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="389" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D389" s="6"/>
       <c r="E389" s="1"/>
       <c r="BO389" s="7"/>
       <c r="BR389" s="7"/>
     </row>
-    <row r="390" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="390" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D390" s="6"/>
       <c r="E390" s="1"/>
       <c r="BO390" s="7"/>
       <c r="BR390" s="7"/>
     </row>
-    <row r="391" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="391" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D391" s="6"/>
       <c r="E391" s="1"/>
       <c r="BO391" s="7"/>
       <c r="BR391" s="7"/>
     </row>
-    <row r="392" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="392" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D392" s="6"/>
       <c r="E392" s="1"/>
       <c r="BO392" s="7"/>
       <c r="BR392" s="7"/>
     </row>
-    <row r="393" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="393" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D393" s="6"/>
       <c r="E393" s="1"/>
       <c r="BO393" s="7"/>
       <c r="BR393" s="7"/>
     </row>
-    <row r="394" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="394" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D394" s="6"/>
       <c r="E394" s="1"/>
       <c r="BR394" s="7"/>
     </row>
-    <row r="395" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="395" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D395" s="6"/>
       <c r="E395" s="1"/>
       <c r="BR395" s="7"/>
     </row>
-    <row r="396" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="396" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D396" s="6"/>
       <c r="E396" s="1"/>
       <c r="BO396" s="7"/>
       <c r="BR396" s="7"/>
     </row>
-    <row r="397" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="397" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D397" s="6"/>
       <c r="E397" s="1"/>
       <c r="BO397" s="7"/>
       <c r="BR397" s="7"/>
     </row>
-    <row r="398" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="398" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D398" s="6"/>
       <c r="E398" s="1"/>
       <c r="BO398" s="7"/>
       <c r="BR398" s="7"/>
     </row>
-    <row r="399" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="399" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D399" s="6"/>
       <c r="E399" s="1"/>
       <c r="BO399" s="7"/>
       <c r="BR399" s="7"/>
     </row>
-    <row r="400" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="400" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D400" s="6"/>
       <c r="E400" s="1"/>
       <c r="BO400" s="7"/>
       <c r="BR400" s="7"/>
     </row>
-    <row r="401" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="401" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D401" s="6"/>
       <c r="E401" s="1"/>
       <c r="BO401" s="7"/>
       <c r="BR401" s="7"/>
     </row>
-    <row r="402" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="402" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D402" s="6"/>
       <c r="E402" s="1"/>
       <c r="BO402" s="7"/>
       <c r="BR402" s="7"/>
     </row>
-    <row r="403" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="403" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D403" s="6"/>
       <c r="E403" s="1"/>
       <c r="BO403" s="7"/>
       <c r="BR403" s="7"/>
     </row>
-    <row r="404" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="404" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D404" s="6"/>
       <c r="E404" s="1"/>
       <c r="BO404" s="7"/>
       <c r="BR404" s="7"/>
     </row>
-    <row r="405" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="405" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D405" s="6"/>
       <c r="E405" s="1"/>
       <c r="BO405" s="7"/>
       <c r="BR405" s="7"/>
     </row>
-    <row r="406" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="406" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D406" s="6"/>
       <c r="E406" s="1"/>
       <c r="BO406" s="7"/>
       <c r="BR406" s="7"/>
     </row>
-    <row r="407" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="407" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D407" s="6"/>
       <c r="E407" s="1"/>
       <c r="BO407" s="7"/>
       <c r="BR407" s="7"/>
     </row>
-    <row r="408" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="408" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D408" s="6"/>
       <c r="E408" s="1"/>
       <c r="BO408" s="7"/>
       <c r="BR408" s="7"/>
     </row>
-    <row r="409" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="409" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D409" s="6"/>
       <c r="E409" s="1"/>
       <c r="BO409" s="7"/>
       <c r="BR409" s="7"/>
     </row>
-    <row r="410" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="410" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D410" s="6"/>
       <c r="E410" s="1"/>
       <c r="BO410" s="7"/>
       <c r="BR410" s="7"/>
     </row>
-    <row r="411" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="411" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D411" s="6"/>
       <c r="E411" s="1"/>
       <c r="BO411" s="7"/>
       <c r="BR411" s="7"/>
     </row>
-    <row r="412" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="412" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D412" s="6"/>
       <c r="E412" s="1"/>
       <c r="BO412" s="7"/>
       <c r="BR412" s="7"/>
     </row>
-    <row r="413" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="413" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D413" s="6"/>
       <c r="E413" s="1"/>
       <c r="BO413" s="7"/>
       <c r="BR413" s="7"/>
     </row>
-    <row r="414" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="414" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D414" s="6"/>
       <c r="E414" s="1"/>
       <c r="BO414" s="7"/>
       <c r="BR414" s="7"/>
     </row>
-    <row r="415" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="415" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D415" s="6"/>
       <c r="E415" s="1"/>
       <c r="BO415" s="7"/>
       <c r="BR415" s="7"/>
     </row>
-    <row r="416" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="416" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D416" s="6"/>
       <c r="E416" s="1"/>
       <c r="BO416" s="7"/>
       <c r="BR416" s="7"/>
     </row>
-    <row r="417" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="417" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D417" s="6"/>
       <c r="E417" s="1"/>
       <c r="BO417" s="7"/>
       <c r="BR417" s="7"/>
     </row>
-    <row r="418" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="418" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D418" s="6"/>
       <c r="E418" s="1"/>
       <c r="BO418" s="7"/>
       <c r="BR418" s="7"/>
     </row>
-    <row r="419" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="419" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D419" s="6"/>
       <c r="E419" s="1"/>
       <c r="BR419" s="7"/>
     </row>
-    <row r="420" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="420" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D420" s="6"/>
       <c r="E420" s="1"/>
       <c r="BR420" s="7"/>
     </row>
-    <row r="421" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="421" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D421" s="6"/>
       <c r="E421" s="1"/>
       <c r="BO421" s="7"/>
       <c r="BR421" s="7"/>
     </row>
-    <row r="422" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="422" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D422" s="6"/>
       <c r="E422" s="1"/>
       <c r="BO422" s="7"/>
       <c r="BR422" s="7"/>
     </row>
-    <row r="423" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="423" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D423" s="6"/>
       <c r="E423" s="1"/>
       <c r="BR423" s="7"/>
     </row>
-    <row r="424" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="424" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D424" s="6"/>
       <c r="E424" s="1"/>
       <c r="BR424" s="7"/>
     </row>
-    <row r="425" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="425" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D425" s="6"/>
       <c r="E425" s="1"/>
       <c r="BO425" s="7"/>
       <c r="BR425" s="7"/>
     </row>
-    <row r="426" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="426" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D426" s="6"/>
       <c r="E426" s="1"/>
       <c r="BO426" s="7"/>
       <c r="BR426" s="7"/>
     </row>
-    <row r="427" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="427" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D427" s="6"/>
       <c r="E427" s="1"/>
       <c r="BO427" s="7"/>
       <c r="BR427" s="7"/>
     </row>
-    <row r="428" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="428" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D428" s="6"/>
       <c r="E428" s="1"/>
       <c r="BO428" s="7"/>
       <c r="BR428" s="7"/>
     </row>
-    <row r="429" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="429" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D429" s="6"/>
       <c r="E429" s="1"/>
       <c r="BO429" s="7"/>
       <c r="BR429" s="7"/>
     </row>
-    <row r="430" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="430" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D430" s="6"/>
       <c r="E430" s="1"/>
       <c r="BO430" s="7"/>
       <c r="BR430" s="7"/>
     </row>
-    <row r="431" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="431" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D431" s="6"/>
       <c r="E431" s="1"/>
       <c r="BO431" s="7"/>
       <c r="BR431" s="7"/>
     </row>
-    <row r="432" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="432" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D432" s="6"/>
       <c r="E432" s="1"/>
       <c r="BO432" s="7"/>
       <c r="BR432" s="7"/>
     </row>
-    <row r="433" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="433" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D433" s="6"/>
       <c r="E433" s="1"/>
       <c r="BO433" s="7"/>
       <c r="BR433" s="7"/>
     </row>
-    <row r="434" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="434" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D434" s="6"/>
       <c r="E434" s="1"/>
       <c r="BO434" s="7"/>
       <c r="BR434" s="7"/>
     </row>
-    <row r="435" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="435" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D435" s="6"/>
       <c r="E435" s="1"/>
       <c r="BO435" s="7"/>
       <c r="BR435" s="7"/>
     </row>
-    <row r="436" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="436" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D436" s="6"/>
       <c r="E436" s="1"/>
       <c r="BO436" s="7"/>
       <c r="BR436" s="7"/>
     </row>
-    <row r="437" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="437" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D437" s="6"/>
       <c r="E437" s="1"/>
       <c r="BO437" s="7"/>
       <c r="BR437" s="7"/>
     </row>
-    <row r="438" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="438" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D438" s="6"/>
       <c r="E438" s="1"/>
       <c r="BO438" s="7"/>
       <c r="BR438" s="7"/>
     </row>
-    <row r="439" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="439" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D439" s="6"/>
       <c r="E439" s="1"/>
       <c r="BO439" s="7"/>
       <c r="BR439" s="7"/>
     </row>
-    <row r="440" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="440" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D440" s="6"/>
       <c r="E440" s="1"/>
       <c r="BO440" s="7"/>
       <c r="BR440" s="7"/>
     </row>
-    <row r="441" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="441" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D441" s="6"/>
       <c r="E441" s="1"/>
       <c r="BO441" s="7"/>
       <c r="BR441" s="7"/>
     </row>
-    <row r="442" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="442" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D442" s="6"/>
       <c r="E442" s="1"/>
     </row>
-    <row r="443" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="443" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D443" s="6"/>
       <c r="E443" s="1"/>
     </row>
-    <row r="444" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="444" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D444" s="6"/>
       <c r="E444" s="1"/>
     </row>
-    <row r="445" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="445" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D445" s="6"/>
       <c r="E445" s="1"/>
     </row>
-    <row r="446" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="446" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D446" s="6"/>
       <c r="E446" s="1"/>
     </row>
-    <row r="447" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="447" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D447" s="6"/>
       <c r="E447" s="1"/>
     </row>
-    <row r="448" spans="4:70" x14ac:dyDescent="0.25">
+    <row r="448" spans="4:70" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D448" s="6"/>
       <c r="E448" s="1"/>
     </row>
-    <row r="449" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="449" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D449" s="6"/>
       <c r="E449" s="1"/>
     </row>
-    <row r="450" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="450" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D450" s="6"/>
       <c r="E450" s="1"/>
     </row>
-    <row r="451" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="451" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D451" s="6"/>
       <c r="E451" s="1"/>
     </row>
-    <row r="452" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="452" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D452" s="6"/>
       <c r="E452" s="1"/>
     </row>
-    <row r="453" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="453" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D453" s="6"/>
       <c r="E453" s="1"/>
     </row>
-    <row r="454" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="454" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D454" s="6"/>
       <c r="E454" s="1"/>
     </row>
-    <row r="455" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="455" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D455" s="6"/>
       <c r="E455" s="1"/>
     </row>
-    <row r="456" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="456" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D456" s="6"/>
       <c r="E456" s="1"/>
     </row>
-    <row r="457" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="457" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D457" s="6"/>
       <c r="E457" s="1"/>
     </row>
-    <row r="458" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="458" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D458" s="6"/>
       <c r="E458" s="1"/>
     </row>
-    <row r="459" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="459" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D459" s="6"/>
       <c r="E459" s="1"/>
     </row>
-    <row r="460" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="460" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D460" s="6"/>
       <c r="E460" s="1"/>
     </row>
-    <row r="461" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="461" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D461" s="6"/>
       <c r="E461" s="1"/>
     </row>
-    <row r="462" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="462" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D462" s="6"/>
       <c r="E462" s="1"/>
     </row>
-    <row r="463" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="463" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D463" s="6"/>
       <c r="E463" s="1"/>
     </row>
-    <row r="464" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="464" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D464" s="6"/>
       <c r="E464" s="1"/>
     </row>
-    <row r="465" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="465" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D465" s="6"/>
       <c r="E465" s="1"/>
     </row>
-    <row r="466" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="466" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D466" s="6"/>
       <c r="E466" s="1"/>
     </row>
-    <row r="467" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="467" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D467" s="6"/>
       <c r="E467" s="1"/>
     </row>
-    <row r="468" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="468" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D468" s="6"/>
       <c r="E468" s="1"/>
     </row>
-    <row r="469" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="469" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D469" s="6"/>
       <c r="E469" s="1"/>
     </row>
-    <row r="470" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="470" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D470" s="6"/>
       <c r="E470" s="1"/>
     </row>
-    <row r="471" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="471" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D471" s="6"/>
       <c r="E471" s="1"/>
     </row>
-    <row r="472" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="472" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D472" s="6"/>
       <c r="E472" s="1"/>
     </row>
-    <row r="473" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="473" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D473" s="6"/>
       <c r="E473" s="1"/>
     </row>
-    <row r="474" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="474" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D474" s="6"/>
       <c r="E474" s="1"/>
     </row>
-    <row r="475" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="475" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D475" s="6"/>
       <c r="E475" s="1"/>
     </row>
-    <row r="476" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="476" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D476" s="6"/>
       <c r="E476" s="1"/>
     </row>
-    <row r="477" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="477" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D477" s="6"/>
       <c r="E477" s="1"/>
     </row>
-    <row r="478" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="478" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D478" s="6"/>
       <c r="E478" s="1"/>
     </row>
-    <row r="479" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="479" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D479" s="6"/>
       <c r="E479" s="1"/>
     </row>
-    <row r="480" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="480" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D480" s="6"/>
       <c r="E480" s="1"/>
     </row>
-    <row r="481" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="481" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D481" s="6"/>
       <c r="E481" s="1"/>
     </row>
-    <row r="482" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="482" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D482" s="6"/>
       <c r="E482" s="1"/>
     </row>
-    <row r="483" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="483" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D483" s="6"/>
       <c r="E483" s="1"/>
     </row>
-    <row r="484" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="484" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D484" s="6"/>
       <c r="E484" s="1"/>
     </row>
-    <row r="485" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="485" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D485" s="6"/>
       <c r="E485" s="1"/>
     </row>
-    <row r="486" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="486" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D486" s="6"/>
       <c r="E486" s="1"/>
     </row>
-    <row r="487" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="487" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D487" s="6"/>
       <c r="E487" s="1"/>
     </row>
-    <row r="488" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="488" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D488" s="6"/>
       <c r="E488" s="1"/>
     </row>
-    <row r="489" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="489" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D489" s="6"/>
       <c r="E489" s="1"/>
     </row>
-    <row r="490" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="490" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D490" s="6"/>
       <c r="E490" s="1"/>
     </row>
-    <row r="491" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="491" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D491" s="6"/>
       <c r="E491" s="1"/>
     </row>
-    <row r="492" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="492" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D492" s="6"/>
       <c r="E492" s="1"/>
     </row>
-    <row r="493" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="493" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D493" s="6"/>
       <c r="E493" s="1"/>
     </row>
-    <row r="494" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="494" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D494" s="6"/>
       <c r="E494" s="1"/>
     </row>
-    <row r="495" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="495" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D495" s="6"/>
       <c r="E495" s="1"/>
     </row>
-    <row r="496" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="496" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D496" s="6"/>
       <c r="E496" s="1"/>
     </row>
-    <row r="497" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="497" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D497" s="6"/>
       <c r="E497" s="1"/>
     </row>
-    <row r="498" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="498" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D498" s="6"/>
       <c r="E498" s="1"/>
     </row>
-    <row r="499" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="499" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D499" s="6"/>
       <c r="E499" s="1"/>
     </row>
-    <row r="500" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="500" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D500" s="6"/>
       <c r="E500" s="1"/>
     </row>
-    <row r="501" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="501" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D501" s="6"/>
       <c r="E501" s="1"/>
     </row>
-    <row r="502" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="502" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D502" s="6"/>
       <c r="E502" s="1"/>
     </row>
-    <row r="503" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="503" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D503" s="6"/>
       <c r="E503" s="1"/>
     </row>
-    <row r="504" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="504" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D504" s="6"/>
       <c r="E504" s="1"/>
     </row>
-    <row r="505" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="505" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D505" s="6"/>
       <c r="E505" s="1"/>
     </row>
-    <row r="506" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="506" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D506" s="6"/>
       <c r="E506" s="1"/>
     </row>
-    <row r="507" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="507" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D507" s="6"/>
       <c r="E507" s="1"/>
     </row>
-    <row r="508" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="508" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D508" s="6"/>
       <c r="E508" s="1"/>
     </row>
-    <row r="509" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="509" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D509" s="6"/>
       <c r="E509" s="1"/>
     </row>
-    <row r="510" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="510" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D510" s="6"/>
       <c r="E510" s="1"/>
     </row>
-    <row r="511" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="511" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D511" s="6"/>
       <c r="E511" s="1"/>
     </row>
-    <row r="512" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="512" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D512" s="6"/>
       <c r="E512" s="1"/>
     </row>
-    <row r="513" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="513" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D513" s="6"/>
       <c r="E513" s="1"/>
     </row>
-    <row r="514" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="514" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D514" s="6"/>
       <c r="E514" s="1"/>
     </row>
-    <row r="515" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="515" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D515" s="6"/>
       <c r="E515" s="1"/>
     </row>
-    <row r="516" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="516" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D516" s="6"/>
       <c r="E516" s="1"/>
     </row>
-    <row r="517" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="517" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D517" s="6"/>
       <c r="E517" s="1"/>
     </row>
-    <row r="518" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="518" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D518" s="6"/>
       <c r="E518" s="1"/>
     </row>
-    <row r="519" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="519" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D519" s="6"/>
       <c r="E519" s="1"/>
     </row>
-    <row r="520" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="520" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D520" s="6"/>
       <c r="E520" s="1"/>
     </row>
-    <row r="521" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="521" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D521" s="6"/>
       <c r="E521" s="1"/>
     </row>
-    <row r="589" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="589" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D589" s="6"/>
       <c r="E589" s="1"/>
     </row>
-    <row r="590" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="590" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D590" s="6"/>
       <c r="E590" s="1"/>
     </row>
-    <row r="591" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="591" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D591" s="6"/>
       <c r="E591" s="1"/>
     </row>
-    <row r="592" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="592" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D592" s="6"/>
       <c r="E592" s="1"/>
     </row>
-    <row r="593" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="593" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D593" s="6"/>
       <c r="E593" s="1"/>
     </row>
-    <row r="594" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="594" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D594" s="6"/>
       <c r="E594" s="1"/>
     </row>
-    <row r="595" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="595" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D595" s="6"/>
       <c r="E595" s="1"/>
     </row>
-    <row r="596" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="596" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D596" s="6"/>
       <c r="E596" s="1"/>
     </row>
-    <row r="597" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="597" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D597" s="6"/>
       <c r="E597" s="1"/>
     </row>
-    <row r="598" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="598" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D598" s="6"/>
       <c r="E598" s="1"/>
     </row>
-    <row r="599" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="599" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D599" s="6"/>
       <c r="E599" s="1"/>
     </row>
-    <row r="600" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="600" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D600" s="6"/>
       <c r="E600" s="1"/>
     </row>
-    <row r="601" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="601" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D601" s="6"/>
       <c r="E601" s="1"/>
     </row>
-    <row r="602" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="602" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D602" s="6"/>
       <c r="E602" s="1"/>
     </row>
-    <row r="603" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="603" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D603" s="6"/>
       <c r="E603" s="1"/>
     </row>
-    <row r="604" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="604" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D604" s="6"/>
       <c r="E604" s="1"/>
     </row>
-    <row r="605" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="605" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D605" s="6"/>
       <c r="E605" s="1"/>
     </row>
-    <row r="606" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="606" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D606" s="6"/>
       <c r="E606" s="1"/>
     </row>
-    <row r="607" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="607" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D607" s="6"/>
       <c r="E607" s="1"/>
     </row>
-    <row r="608" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="608" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D608" s="6"/>
       <c r="E608" s="1"/>
     </row>
-    <row r="609" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="609" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D609" s="6"/>
       <c r="E609" s="1"/>
     </row>
-    <row r="610" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="610" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D610" s="6"/>
       <c r="E610" s="1"/>
     </row>
-    <row r="611" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="611" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D611" s="6"/>
       <c r="E611" s="1"/>
     </row>
-    <row r="612" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="612" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D612" s="6"/>
       <c r="E612" s="1"/>
     </row>
-    <row r="613" spans="4:5" x14ac:dyDescent="0.25">
+    <row r="613" spans="4:5" ht="14.5" x14ac:dyDescent="0.25">
       <c r="D613" s="6"/>
       <c r="E613" s="1"/>
     </row>
@@ -8771,82 +8855,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:DH905"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="21.08984375" customWidth="1"/>
-    <col min="2" max="2" width="15.54296875" customWidth="1"/>
-    <col min="3" max="3" width="7.7265625" customWidth="1"/>
-    <col min="4" max="4" width="16.54296875" customWidth="1"/>
-    <col min="5" max="5" width="16.81640625" customWidth="1"/>
-    <col min="6" max="6" width="31.36328125" customWidth="1"/>
-    <col min="7" max="7" width="7.36328125" customWidth="1"/>
-    <col min="8" max="8" width="17.81640625" customWidth="1"/>
-    <col min="9" max="9" width="7.36328125" customWidth="1"/>
-    <col min="10" max="10" width="15.7265625" customWidth="1"/>
-    <col min="11" max="13" width="8.36328125" style="3" customWidth="1"/>
-    <col min="14" max="14" width="11.7265625" style="3" customWidth="1"/>
-    <col min="15" max="15" width="13.08984375" style="3" customWidth="1"/>
-    <col min="16" max="16" width="11.54296875" style="3" customWidth="1"/>
-    <col min="17" max="17" width="21.453125" style="3" customWidth="1"/>
-    <col min="18" max="18" width="19.81640625" style="3" customWidth="1"/>
-    <col min="19" max="19" width="16.54296875" style="3" customWidth="1"/>
-    <col min="20" max="20" width="12.7265625" style="3" customWidth="1"/>
-    <col min="21" max="23" width="8.36328125" style="3" customWidth="1"/>
-    <col min="24" max="24" width="18.453125" style="3" customWidth="1"/>
-    <col min="25" max="25" width="16.54296875" customWidth="1"/>
-    <col min="26" max="26" width="10.6328125" customWidth="1"/>
-    <col min="27" max="27" width="8.36328125" customWidth="1"/>
-    <col min="28" max="28" width="15.1796875" customWidth="1"/>
-    <col min="29" max="30" width="8.54296875" customWidth="1"/>
-    <col min="31" max="31" width="13.453125" customWidth="1"/>
-    <col min="32" max="32" width="13.7265625" customWidth="1"/>
-    <col min="33" max="33" width="14.54296875" customWidth="1"/>
-    <col min="34" max="34" width="17.453125" customWidth="1"/>
-    <col min="35" max="35" width="8.54296875" customWidth="1"/>
-    <col min="36" max="36" width="12.453125" customWidth="1"/>
-    <col min="37" max="37" width="8.54296875" customWidth="1"/>
-    <col min="38" max="39" width="8.36328125" customWidth="1"/>
+    <col min="1" max="1" width="21.08203125" customWidth="1"/>
+    <col min="2" max="2" width="15.58203125" customWidth="1"/>
+    <col min="3" max="3" width="7.75" customWidth="1"/>
+    <col min="4" max="4" width="16.58203125" customWidth="1"/>
+    <col min="5" max="5" width="16.83203125" customWidth="1"/>
+    <col min="6" max="6" width="31.33203125" customWidth="1"/>
+    <col min="7" max="7" width="7.33203125" customWidth="1"/>
+    <col min="8" max="8" width="17.83203125" customWidth="1"/>
+    <col min="9" max="9" width="7.33203125" customWidth="1"/>
+    <col min="10" max="10" width="15.75" customWidth="1"/>
+    <col min="11" max="13" width="8.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="11.75" style="3" customWidth="1"/>
+    <col min="15" max="15" width="13.08203125" style="3" customWidth="1"/>
+    <col min="16" max="16" width="11.58203125" style="3" customWidth="1"/>
+    <col min="17" max="17" width="21.5" style="3" customWidth="1"/>
+    <col min="18" max="18" width="19.83203125" style="3" customWidth="1"/>
+    <col min="19" max="19" width="16.58203125" style="3" customWidth="1"/>
+    <col min="20" max="20" width="12.75" style="3" customWidth="1"/>
+    <col min="21" max="23" width="8.33203125" style="3" customWidth="1"/>
+    <col min="24" max="24" width="18.5" style="3" customWidth="1"/>
+    <col min="25" max="25" width="16.58203125" customWidth="1"/>
+    <col min="26" max="26" width="10.6640625" customWidth="1"/>
+    <col min="27" max="27" width="8.33203125" customWidth="1"/>
+    <col min="28" max="28" width="15.1640625" customWidth="1"/>
+    <col min="29" max="30" width="8.58203125" customWidth="1"/>
+    <col min="31" max="31" width="13.4140625" customWidth="1"/>
+    <col min="32" max="32" width="13.75" customWidth="1"/>
+    <col min="33" max="33" width="14.58203125" customWidth="1"/>
+    <col min="34" max="34" width="17.4140625" customWidth="1"/>
+    <col min="35" max="35" width="8.58203125" customWidth="1"/>
+    <col min="36" max="36" width="12.5" customWidth="1"/>
+    <col min="37" max="37" width="8.58203125" customWidth="1"/>
+    <col min="38" max="39" width="8.33203125" customWidth="1"/>
     <col min="40" max="40" width="15" customWidth="1"/>
-    <col min="41" max="41" width="13.26953125" customWidth="1"/>
-    <col min="42" max="43" width="11.81640625" customWidth="1"/>
-    <col min="44" max="44" width="18.453125" customWidth="1"/>
-    <col min="45" max="45" width="12.26953125" customWidth="1"/>
-    <col min="46" max="46" width="11.90625" customWidth="1"/>
-    <col min="47" max="47" width="19.54296875" customWidth="1"/>
-    <col min="48" max="48" width="12.6328125" customWidth="1"/>
+    <col min="41" max="41" width="13.25" customWidth="1"/>
+    <col min="42" max="43" width="11.83203125" customWidth="1"/>
+    <col min="44" max="44" width="18.4140625" customWidth="1"/>
+    <col min="45" max="45" width="12.25" customWidth="1"/>
+    <col min="46" max="46" width="11.9140625" customWidth="1"/>
+    <col min="47" max="47" width="19.58203125" customWidth="1"/>
+    <col min="48" max="48" width="12.6640625" customWidth="1"/>
     <col min="50" max="50" width="7" customWidth="1"/>
-    <col min="51" max="51" width="11.7265625" customWidth="1"/>
-    <col min="52" max="52" width="9.7265625" customWidth="1"/>
-    <col min="53" max="53" width="5.08984375" customWidth="1"/>
-    <col min="54" max="54" width="8.453125" customWidth="1"/>
-    <col min="55" max="55" width="13.453125" customWidth="1"/>
-    <col min="56" max="56" width="14.6328125" customWidth="1"/>
-    <col min="57" max="57" width="10.1796875" customWidth="1"/>
-    <col min="58" max="58" width="8.26953125" customWidth="1"/>
-    <col min="59" max="65" width="8.36328125" customWidth="1"/>
-    <col min="66" max="68" width="11.26953125" customWidth="1"/>
-    <col min="69" max="69" width="6.54296875" customWidth="1"/>
+    <col min="51" max="51" width="11.75" customWidth="1"/>
+    <col min="52" max="52" width="9.75" customWidth="1"/>
+    <col min="53" max="53" width="5.08203125" customWidth="1"/>
+    <col min="54" max="54" width="8.5" customWidth="1"/>
+    <col min="55" max="55" width="13.5" customWidth="1"/>
+    <col min="56" max="56" width="14.6640625" customWidth="1"/>
+    <col min="57" max="57" width="10.1640625" customWidth="1"/>
+    <col min="58" max="58" width="8.25" customWidth="1"/>
+    <col min="59" max="65" width="8.33203125" customWidth="1"/>
+    <col min="66" max="68" width="11.25" customWidth="1"/>
+    <col min="69" max="69" width="6.58203125" customWidth="1"/>
     <col min="70" max="71" width="8" customWidth="1"/>
-    <col min="72" max="72" width="7.36328125" style="4" customWidth="1"/>
-    <col min="73" max="74" width="8.453125" style="4" customWidth="1"/>
-    <col min="75" max="76" width="7.81640625" style="4" customWidth="1"/>
-    <col min="77" max="77" width="22.1796875" style="4" customWidth="1"/>
-    <col min="78" max="78" width="13.453125" customWidth="1"/>
-    <col min="79" max="79" width="21.1796875" customWidth="1"/>
-    <col min="80" max="80" width="15.7265625" customWidth="1"/>
-    <col min="81" max="81" width="15.54296875" customWidth="1"/>
-    <col min="82" max="82" width="12.81640625" customWidth="1"/>
-    <col min="83" max="83" width="16.1796875" customWidth="1"/>
+    <col min="72" max="72" width="7.33203125" style="4" customWidth="1"/>
+    <col min="73" max="74" width="8.5" style="4" customWidth="1"/>
+    <col min="75" max="76" width="7.83203125" style="4" customWidth="1"/>
+    <col min="77" max="77" width="22.1640625" style="4" customWidth="1"/>
+    <col min="78" max="78" width="13.5" customWidth="1"/>
+    <col min="79" max="79" width="21.1640625" customWidth="1"/>
+    <col min="80" max="80" width="15.75" customWidth="1"/>
+    <col min="81" max="81" width="15.58203125" customWidth="1"/>
+    <col min="82" max="82" width="12.83203125" customWidth="1"/>
+    <col min="83" max="83" width="16.1640625" customWidth="1"/>
     <col min="85" max="85" width="16" customWidth="1"/>
-    <col min="86" max="87" width="12.81640625" customWidth="1"/>
-    <col min="88" max="88" width="23.54296875" customWidth="1"/>
-    <col min="89" max="89" width="12.81640625" customWidth="1"/>
-    <col min="90" max="90" width="17.08984375" customWidth="1"/>
+    <col min="86" max="87" width="12.83203125" customWidth="1"/>
+    <col min="88" max="88" width="23.58203125" customWidth="1"/>
+    <col min="89" max="89" width="12.83203125" customWidth="1"/>
+    <col min="90" max="90" width="17.08203125" customWidth="1"/>
     <col min="97" max="97" width="14" customWidth="1"/>
     <col min="98" max="98" width="8" customWidth="1"/>
-    <col min="100" max="100" width="11.08984375" customWidth="1"/>
-    <col min="101" max="101" width="13.7265625" customWidth="1"/>
-    <col min="108" max="108" width="15.453125" customWidth="1"/>
+    <col min="100" max="100" width="11.08203125" customWidth="1"/>
+    <col min="101" max="101" width="13.75" customWidth="1"/>
+    <col min="108" max="108" width="15.5" customWidth="1"/>
     <col min="112" max="112" width="9" hidden="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -14687,21 +14771,20 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:Q10"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:P10"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
-    <col min="2" max="2" width="31.26953125" customWidth="1"/>
-    <col min="7" max="7" width="18.7265625" customWidth="1"/>
+    <col min="2" max="2" width="31.25" customWidth="1"/>
+    <col min="7" max="7" width="18.75" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
-    <col min="14" max="14" width="16.08984375" customWidth="1"/>
-    <col min="15" max="15" width="9.453125" customWidth="1"/>
-    <col min="16" max="16" width="22.1796875" customWidth="1"/>
-    <col min="17" max="17" width="12.81640625" customWidth="1"/>
-    <col min="20" max="20" width="9" customWidth="1"/>
+    <col min="14" max="14" width="16.08203125" customWidth="1"/>
+    <col min="15" max="15" width="9.5" customWidth="1"/>
+    <col min="16" max="16" width="12.83203125" customWidth="1"/>
+    <col min="19" max="19" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14738,11 +14821,8 @@
       <c r="O1" t="s">
         <v>611</v>
       </c>
-      <c r="P1" s="8" t="s">
-        <v>783</v>
-      </c>
-    </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -14785,14 +14865,11 @@
       <c r="O2" t="s">
         <v>621</v>
       </c>
-      <c r="P2" s="8" t="s">
-        <v>784</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="P2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14836,13 +14913,10 @@
         <v>385</v>
       </c>
       <c r="P3" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>471</v>
       </c>
@@ -14861,11 +14935,11 @@
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="P4" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>486</v>
       </c>
@@ -14878,11 +14952,11 @@
       <c r="K5">
         <v>0.01</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="P5" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>487</v>
       </c>
@@ -14895,11 +14969,11 @@
       <c r="K6">
         <v>0.01</v>
       </c>
-      <c r="Q6" t="s">
+      <c r="P6" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>622</v>
       </c>
@@ -14915,11 +14989,11 @@
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="Q7" t="s">
+      <c r="P7" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>746</v>
       </c>
@@ -14930,7 +15004,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>600</v>
       </c>
@@ -14940,11 +15014,11 @@
       <c r="J9" t="s">
         <v>751</v>
       </c>
-      <c r="Q9" t="s">
+      <c r="P9" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>762</v>
       </c>
@@ -14962,11 +15036,11 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:D4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.36328125" customWidth="1"/>
-    <col min="2" max="2" width="11.26953125" customWidth="1"/>
-    <col min="4" max="4" width="27.453125" customWidth="1"/>
+    <col min="1" max="1" width="11.33203125" customWidth="1"/>
+    <col min="2" max="2" width="11.25" customWidth="1"/>
+    <col min="4" max="4" width="27.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -15026,11 +15100,11 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="A2:I4"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
-    <col min="3" max="3" width="27.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.81640625" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
+    <col min="3" max="3" width="27.25" customWidth="1"/>
+    <col min="4" max="4" width="10.83203125" customWidth="1"/>
     <col min="9" max="9" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -15119,13 +15193,13 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.26953125" customWidth="1"/>
+    <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="2" max="2" width="28" customWidth="1"/>
-    <col min="3" max="4" width="10.08984375" customWidth="1"/>
-    <col min="5" max="10" width="11.26953125" customWidth="1"/>
-    <col min="11" max="11" width="6.36328125" customWidth="1"/>
+    <col min="3" max="4" width="10.08203125" customWidth="1"/>
+    <col min="5" max="10" width="11.25" customWidth="1"/>
+    <col min="11" max="11" width="6.33203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
@@ -15647,15 +15721,15 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
   <dimension ref="A2:J3"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.08984375" customWidth="1"/>
-    <col min="2" max="2" width="16.26953125" customWidth="1"/>
-    <col min="3" max="3" width="16.36328125" customWidth="1"/>
-    <col min="4" max="4" width="47.81640625" customWidth="1"/>
-    <col min="5" max="5" width="10.26953125" customWidth="1"/>
-    <col min="6" max="6" width="12.81640625" customWidth="1"/>
-    <col min="10" max="10" width="11.81640625" customWidth="1"/>
+    <col min="1" max="1" width="19.08203125" customWidth="1"/>
+    <col min="2" max="2" width="16.25" customWidth="1"/>
+    <col min="3" max="3" width="16.33203125" customWidth="1"/>
+    <col min="4" max="4" width="47.83203125" customWidth="1"/>
+    <col min="5" max="5" width="10.25" customWidth="1"/>
+    <col min="6" max="6" width="12.83203125" customWidth="1"/>
+    <col min="10" max="10" width="11.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -15720,6 +15794,116 @@
       </c>
       <c r="J3" t="s">
         <v>126</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="8" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B967DC26-0945-406F-B64D-075568096CAC}">
+  <dimension ref="A1:I3"/>
+  <sheetFormatPr defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="8.6640625" style="19"/>
+    <col min="2" max="2" width="13.83203125" style="19" customWidth="1"/>
+    <col min="3" max="3" width="20.58203125" style="19" customWidth="1"/>
+    <col min="4" max="4" width="15.83203125" style="19" customWidth="1"/>
+    <col min="5" max="5" width="13.1640625" style="19" customWidth="1"/>
+    <col min="6" max="6" width="14.25" style="19" customWidth="1"/>
+    <col min="7" max="7" width="15" style="19" customWidth="1"/>
+    <col min="8" max="8" width="14.6640625" style="19" customWidth="1"/>
+    <col min="9" max="9" width="14.25" style="19" customWidth="1"/>
+    <col min="10" max="16384" width="8.6640625" style="19"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="B1" s="19" t="s">
+        <v>784</v>
+      </c>
+      <c r="C1" s="19" t="s">
+        <v>785</v>
+      </c>
+      <c r="D1" s="19" t="s">
+        <v>786</v>
+      </c>
+      <c r="E1" s="19" t="s">
+        <v>787</v>
+      </c>
+      <c r="F1" s="19" t="s">
+        <v>788</v>
+      </c>
+      <c r="G1" s="19" t="s">
+        <v>789</v>
+      </c>
+      <c r="H1" s="19" t="s">
+        <v>790</v>
+      </c>
+      <c r="I1" s="19" t="s">
+        <v>791</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A2" s="19" t="s">
+        <v>783</v>
+      </c>
+      <c r="B2" s="19" t="s">
+        <v>792</v>
+      </c>
+      <c r="C2" s="19" t="s">
+        <v>793</v>
+      </c>
+      <c r="D2" s="19" t="s">
+        <v>794</v>
+      </c>
+      <c r="E2" s="19" t="s">
+        <v>795</v>
+      </c>
+      <c r="F2" s="19" t="s">
+        <v>796</v>
+      </c>
+      <c r="G2" s="19" t="s">
+        <v>797</v>
+      </c>
+      <c r="H2" s="19" t="s">
+        <v>798</v>
+      </c>
+      <c r="I2" s="19" t="s">
+        <v>799</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="B3" s="19" t="s">
+        <v>766</v>
+      </c>
+      <c r="C3" s="19" t="s">
+        <v>766</v>
+      </c>
+      <c r="D3" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>774</v>
+      </c>
+      <c r="G3" s="19" t="s">
+        <v>800</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>800</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>800</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6EF8E5E8-89C9-4DB8-B42C-1700DAF6B943}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4796F4D-E8C5-4629-8350-4138DFAF4D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1536" uniqueCount="801">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="803">
   <si>
     <t>Id</t>
   </si>
@@ -2803,6 +2803,14 @@
   </si>
   <si>
     <t>string?</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>可无视buff抑制检测</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>IsCancelable</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -14771,7 +14779,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:P10"/>
+  <dimension ref="A1:Q10"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13" customWidth="1"/>
@@ -14780,11 +14788,12 @@
     <col min="8" max="8" width="15" customWidth="1"/>
     <col min="14" max="14" width="16.08203125" customWidth="1"/>
     <col min="15" max="15" width="9.5" customWidth="1"/>
-    <col min="16" max="16" width="12.83203125" customWidth="1"/>
-    <col min="19" max="19" width="9" customWidth="1"/>
+    <col min="16" max="16" width="22.1640625" customWidth="1"/>
+    <col min="17" max="17" width="12.83203125" customWidth="1"/>
+    <col min="20" max="20" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -14821,8 +14830,11 @@
       <c r="O1" t="s">
         <v>611</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P1" s="8" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -14865,11 +14877,14 @@
       <c r="O2" t="s">
         <v>621</v>
       </c>
-      <c r="P2" t="s">
+      <c r="P2" s="8" t="s">
+        <v>802</v>
+      </c>
+      <c r="Q2" t="s">
         <v>391</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14913,10 +14928,13 @@
         <v>385</v>
       </c>
       <c r="P3" t="s">
+        <v>124</v>
+      </c>
+      <c r="Q3" t="s">
         <v>133</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>471</v>
       </c>
@@ -14935,11 +14953,11 @@
       <c r="N4">
         <v>1</v>
       </c>
-      <c r="P4" t="s">
+      <c r="Q4" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>486</v>
       </c>
@@ -14952,11 +14970,11 @@
       <c r="K5">
         <v>0.01</v>
       </c>
-      <c r="P5" t="s">
+      <c r="Q5" t="s">
         <v>748</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>487</v>
       </c>
@@ -14969,11 +14987,11 @@
       <c r="K6">
         <v>0.01</v>
       </c>
-      <c r="P6" t="s">
+      <c r="Q6" t="s">
         <v>750</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>622</v>
       </c>
@@ -14989,11 +15007,11 @@
       <c r="N7">
         <v>1</v>
       </c>
-      <c r="P7" t="s">
+      <c r="Q7" t="s">
         <v>745</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>746</v>
       </c>
@@ -15004,7 +15022,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>600</v>
       </c>
@@ -15014,11 +15032,11 @@
       <c r="J9" t="s">
         <v>751</v>
       </c>
-      <c r="P9" t="s">
+      <c r="Q9" t="s">
         <v>752</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
         <v>762</v>
       </c>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4796F4D-E8C5-4629-8350-4138DFAF4D48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A716117-06C3-4284-94B8-945E3F8F01FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3338" yWindow="1421" windowWidth="17953" windowHeight="10398" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -2806,12 +2806,10 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>可无视buff抑制检测</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>IsCancelable</t>
-    <phoneticPr fontId="8" type="noConversion"/>
+    <t>不可被抵挡</t>
+  </si>
+  <si>
+    <t>NotCancelable</t>
   </si>
 </sst>
 </file>
@@ -14786,6 +14784,7 @@
     <col min="2" max="2" width="31.25" customWidth="1"/>
     <col min="7" max="7" width="18.75" customWidth="1"/>
     <col min="8" max="8" width="15" customWidth="1"/>
+    <col min="13" max="13" width="12.4140625" customWidth="1"/>
     <col min="14" max="14" width="16.08203125" customWidth="1"/>
     <col min="15" max="15" width="9.5" customWidth="1"/>
     <col min="16" max="16" width="22.1640625" customWidth="1"/>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A716117-06C3-4284-94B8-945E3F8F01FC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8047748C-3A5B-460C-A440-BF1BF5FA2ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3338" yWindow="1421" windowWidth="17953" windowHeight="10398" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -298,7 +298,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="803">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1539" uniqueCount="802">
   <si>
     <t>Id</t>
   </si>
@@ -2799,10 +2799,6 @@
   </si>
   <si>
     <t>BackSkelPath</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>string?</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
@@ -14830,7 +14826,7 @@
         <v>611</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -14877,7 +14873,7 @@
         <v>621</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="Q2" t="s">
         <v>391</v>
@@ -15827,12 +15823,12 @@
     <col min="1" max="1" width="8.6640625" style="19"/>
     <col min="2" max="2" width="13.83203125" style="19" customWidth="1"/>
     <col min="3" max="3" width="20.58203125" style="19" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" style="19" customWidth="1"/>
-    <col min="5" max="5" width="13.1640625" style="19" customWidth="1"/>
-    <col min="6" max="6" width="14.25" style="19" customWidth="1"/>
-    <col min="7" max="7" width="15" style="19" customWidth="1"/>
-    <col min="8" max="8" width="14.6640625" style="19" customWidth="1"/>
-    <col min="9" max="9" width="14.25" style="19" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" style="19" customWidth="1"/>
+    <col min="5" max="5" width="37.58203125" style="19" customWidth="1"/>
+    <col min="6" max="6" width="39.5" style="19" customWidth="1"/>
+    <col min="7" max="7" width="38.58203125" style="19" customWidth="1"/>
+    <col min="8" max="8" width="32.25" style="19" customWidth="1"/>
+    <col min="9" max="9" width="39.9140625" style="19" customWidth="1"/>
     <col min="10" max="16384" width="8.6640625" style="19"/>
   </cols>
   <sheetData>
@@ -15914,13 +15910,13 @@
         <v>774</v>
       </c>
       <c r="G3" s="19" t="s">
-        <v>800</v>
+        <v>774</v>
       </c>
       <c r="H3" s="19" t="s">
-        <v>800</v>
+        <v>774</v>
       </c>
       <c r="I3" s="19" t="s">
-        <v>800</v>
+        <v>774</v>
       </c>
     </row>
   </sheetData>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8047748C-3A5B-460C-A440-BF1BF5FA2ACF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54200EA9-FFF4-4196-82FE-EFC755846D80}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="2" activeTab="8" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="5984" yWindow="337" windowWidth="17954" windowHeight="10398" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -2718,10 +2718,6 @@
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>{"UnitId":"先锋型斯卡蒂","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"先锋型斯卡蒂"}</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
     <t>攻击</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
@@ -2806,6 +2802,10 @@
   </si>
   <si>
     <t>NotCancelable</t>
+  </si>
+  <si>
+    <t>{"UnitId":"影哨","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"先锋型斯卡蒂"}</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -5858,7 +5858,7 @@
         <v>688</v>
       </c>
       <c r="AI22" s="8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="AK22">
         <v>0</v>
@@ -11925,7 +11925,7 @@
         <v>428</v>
       </c>
       <c r="BY53" s="4" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="BZ53" t="s">
         <v>508</v>
@@ -12685,7 +12685,7 @@
         <v>730</v>
       </c>
       <c r="BM69" s="8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="CS69" s="8" t="s">
         <v>735</v>
@@ -12848,7 +12848,7 @@
       <c r="BT73"/>
       <c r="CJ73" s="3"/>
       <c r="CS73" s="8" t="s">
-        <v>779</v>
+        <v>801</v>
       </c>
     </row>
     <row r="74" spans="1:109" x14ac:dyDescent="0.25">
@@ -14826,7 +14826,7 @@
         <v>611</v>
       </c>
       <c r="P1" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -14873,7 +14873,7 @@
         <v>621</v>
       </c>
       <c r="P2" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="Q2" t="s">
         <v>391</v>
@@ -15834,60 +15834,60 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
+        <v>782</v>
+      </c>
+      <c r="B1" s="19" t="s">
         <v>783</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="C1" s="19" t="s">
         <v>784</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="D1" s="19" t="s">
         <v>785</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>786</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>787</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="G1" s="19" t="s">
         <v>788</v>
       </c>
-      <c r="G1" s="19" t="s">
+      <c r="H1" s="19" t="s">
         <v>789</v>
       </c>
-      <c r="H1" s="19" t="s">
+      <c r="I1" s="19" t="s">
         <v>790</v>
-      </c>
-      <c r="I1" s="19" t="s">
-        <v>791</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" s="19" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="B2" s="19" t="s">
+        <v>791</v>
+      </c>
+      <c r="C2" s="19" t="s">
         <v>792</v>
       </c>
-      <c r="C2" s="19" t="s">
+      <c r="D2" s="19" t="s">
         <v>793</v>
       </c>
-      <c r="D2" s="19" t="s">
+      <c r="E2" s="19" t="s">
         <v>794</v>
       </c>
-      <c r="E2" s="19" t="s">
+      <c r="F2" s="19" t="s">
         <v>795</v>
       </c>
-      <c r="F2" s="19" t="s">
+      <c r="G2" s="19" t="s">
         <v>796</v>
       </c>
-      <c r="G2" s="19" t="s">
+      <c r="H2" s="19" t="s">
         <v>797</v>
       </c>
-      <c r="H2" s="19" t="s">
+      <c r="I2" s="19" t="s">
         <v>798</v>
-      </c>
-      <c r="I2" s="19" t="s">
-        <v>799</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A63BD737-BD9E-4836-9005-A5B6F9651630}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687988EB-7D50-4605-BBCF-BA8AE8AE01DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2236,9 +2236,6 @@
     <t>撤退</t>
   </si>
   <si>
-    <t>{"UnitId":"影哨","TargetPos":"useSelfPos","SetMod":"Add","UseMod":"UserDirection","UserName":"先锋型斯卡蒂"}</t>
-  </si>
-  <si>
     <t>#显示影哨范围</t>
   </si>
   <si>
@@ -2632,6 +2629,10 @@
   </si>
   <si>
     <t>入场</t>
+    <phoneticPr fontId="14" type="noConversion"/>
+  </si>
+  <si>
+    <t>{"召唤物ID":"影哨","召唤位置":"使用自身位置","部署模式":"追加","召唤物方向":"使用指定单位方向","指定单位名称":"先锋型斯卡蒂"}</t>
     <phoneticPr fontId="14" type="noConversion"/>
   </si>
 </sst>
@@ -8865,10 +8866,10 @@
         <v>269</v>
       </c>
       <c r="AR1" s="17" t="s">
+        <v>769</v>
+      </c>
+      <c r="AS1" s="17" t="s">
         <v>770</v>
-      </c>
-      <c r="AS1" s="17" t="s">
-        <v>771</v>
       </c>
       <c r="AT1" t="s">
         <v>270</v>
@@ -9200,10 +9201,10 @@
         <v>371</v>
       </c>
       <c r="AR2" s="17" t="s">
+        <v>771</v>
+      </c>
+      <c r="AS2" s="17" t="s">
         <v>772</v>
-      </c>
-      <c r="AS2" s="17" t="s">
-        <v>773</v>
       </c>
       <c r="AT2" t="s">
         <v>372</v>
@@ -9538,10 +9539,10 @@
         <v>2</v>
       </c>
       <c r="AR3" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AS3" s="17" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="AT3" t="s">
         <v>444</v>
@@ -12497,8 +12498,8 @@
       </c>
       <c r="BV72"/>
       <c r="CL72" s="2"/>
-      <c r="CU72" t="s">
-        <v>645</v>
+      <c r="CU72" s="17" t="s">
+        <v>775</v>
       </c>
     </row>
     <row r="73" spans="1:111" x14ac:dyDescent="0.25">
@@ -12514,10 +12515,10 @@
     </row>
     <row r="77" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
+        <v>645</v>
+      </c>
+      <c r="C77" t="s">
         <v>646</v>
-      </c>
-      <c r="C77" t="s">
-        <v>647</v>
       </c>
       <c r="I77">
         <v>1</v>
@@ -12545,7 +12546,7 @@
     </row>
     <row r="78" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C78" t="s">
         <v>480</v>
@@ -12590,7 +12591,7 @@
     </row>
     <row r="79" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C79" t="s">
         <v>480</v>
@@ -12602,7 +12603,7 @@
         <v>458</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AC79">
         <v>1</v>
@@ -12632,13 +12633,13 @@
         <v>557</v>
       </c>
       <c r="CH79" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="CI79" t="s">
         <v>145</v>
       </c>
       <c r="CN79" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="CR79">
         <v>6</v>
@@ -12649,7 +12650,7 @@
     </row>
     <row r="80" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C80" t="s">
         <v>480</v>
@@ -12681,7 +12682,7 @@
       <c r="BV80"/>
       <c r="CL80" s="2"/>
       <c r="CN80" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="CR80">
         <v>99999</v>
@@ -12695,7 +12696,7 @@
     </row>
     <row r="81" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C81" t="s">
         <v>480</v>
@@ -12707,7 +12708,7 @@
         <v>458</v>
       </c>
       <c r="L81" s="2" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="AC81">
         <v>1</v>
@@ -12719,7 +12720,7 @@
         <v>99</v>
       </c>
       <c r="AX81" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AZ81">
         <v>99999</v>
@@ -14318,37 +14319,37 @@
         <v>22</v>
       </c>
       <c r="E1" t="s">
+        <v>656</v>
+      </c>
+      <c r="F1" t="s">
         <v>657</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>658</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>659</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>660</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>661</v>
       </c>
-      <c r="J1" t="s">
+      <c r="L1" t="s">
         <v>662</v>
       </c>
-      <c r="L1" t="s">
+      <c r="M1" t="s">
         <v>663</v>
       </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>664</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>665</v>
       </c>
-      <c r="O1" t="s">
+      <c r="P1" t="s">
         <v>666</v>
-      </c>
-      <c r="P1" t="s">
-        <v>667</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -14362,40 +14363,40 @@
         <v>94</v>
       </c>
       <c r="E2" t="s">
+        <v>667</v>
+      </c>
+      <c r="F2" t="s">
         <v>668</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>669</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>670</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>671</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>672</v>
       </c>
-      <c r="J2" t="s">
+      <c r="K2" t="s">
         <v>673</v>
-      </c>
-      <c r="K2" t="s">
-        <v>674</v>
       </c>
       <c r="L2" t="s">
         <v>70</v>
       </c>
       <c r="M2" t="s">
+        <v>674</v>
+      </c>
+      <c r="N2" t="s">
         <v>675</v>
       </c>
-      <c r="N2" t="s">
+      <c r="O2" t="s">
         <v>676</v>
       </c>
-      <c r="O2" t="s">
+      <c r="P2" t="s">
         <v>677</v>
-      </c>
-      <c r="P2" t="s">
-        <v>678</v>
       </c>
       <c r="Q2" t="s">
         <v>423</v>
@@ -14456,7 +14457,7 @@
         <v>488</v>
       </c>
       <c r="C4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -14471,7 +14472,7 @@
         <v>1</v>
       </c>
       <c r="Q4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
@@ -14479,16 +14480,16 @@
         <v>502</v>
       </c>
       <c r="C5" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J5" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="K5">
         <v>0.01</v>
       </c>
       <c r="Q5" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
@@ -14496,7 +14497,7 @@
         <v>503</v>
       </c>
       <c r="C6" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="G6">
         <v>1</v>
@@ -14505,18 +14506,18 @@
         <v>0.01</v>
       </c>
       <c r="Q6" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C7" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J7" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="K7">
         <v>9999</v>
@@ -14525,18 +14526,18 @@
         <v>1</v>
       </c>
       <c r="Q7" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>684</v>
+      </c>
+      <c r="C8" t="s">
         <v>685</v>
       </c>
-      <c r="C8" t="s">
+      <c r="J8" t="s">
         <v>686</v>
-      </c>
-      <c r="J8" t="s">
-        <v>687</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
@@ -14544,21 +14545,21 @@
         <v>626</v>
       </c>
       <c r="C9" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="J9" t="s">
+        <v>687</v>
+      </c>
+      <c r="Q9" t="s">
         <v>688</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>689</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C10" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
     </row>
   </sheetData>
@@ -14583,7 +14584,7 @@
         <v>0</v>
       </c>
       <c r="C1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -14594,7 +14595,7 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D2" t="s">
         <v>423</v>
@@ -14619,10 +14620,10 @@
         <v>609</v>
       </c>
       <c r="B4" t="s">
+        <v>692</v>
+      </c>
+      <c r="D4" t="s">
         <v>693</v>
-      </c>
-      <c r="D4" t="s">
-        <v>694</v>
       </c>
     </row>
   </sheetData>
@@ -14654,19 +14655,19 @@
         <v>67</v>
       </c>
       <c r="D2" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="E2" t="s">
         <v>89</v>
       </c>
       <c r="F2" t="s">
+        <v>695</v>
+      </c>
+      <c r="G2" t="s">
         <v>696</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>697</v>
-      </c>
-      <c r="H2" t="s">
-        <v>698</v>
       </c>
       <c r="I2" t="s">
         <v>423</v>
@@ -14703,19 +14704,19 @@
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B4" t="s">
+        <v>698</v>
+      </c>
+      <c r="C4" t="s">
         <v>699</v>
-      </c>
-      <c r="C4" t="s">
-        <v>700</v>
       </c>
       <c r="E4">
         <v>10</v>
       </c>
       <c r="I4" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
     </row>
   </sheetData>
@@ -14742,34 +14743,34 @@
         <v>0</v>
       </c>
       <c r="B1" t="s">
+        <v>701</v>
+      </c>
+      <c r="C1" t="s">
         <v>702</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>703</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>704</v>
       </c>
-      <c r="E1" t="s">
+      <c r="F1" t="s">
         <v>705</v>
       </c>
-      <c r="F1" t="s">
+      <c r="H1" t="s">
         <v>706</v>
       </c>
-      <c r="H1" t="s">
+      <c r="I1" t="s">
         <v>707</v>
       </c>
-      <c r="I1" t="s">
+      <c r="J1" t="s">
         <v>708</v>
       </c>
-      <c r="J1" t="s">
+      <c r="K1" t="s">
         <v>709</v>
       </c>
-      <c r="K1" t="s">
+      <c r="L1" t="s">
         <v>710</v>
-      </c>
-      <c r="L1" t="s">
-        <v>711</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -14777,34 +14778,34 @@
         <v>0</v>
       </c>
       <c r="B2" t="s">
+        <v>711</v>
+      </c>
+      <c r="C2" t="s">
         <v>712</v>
       </c>
-      <c r="C2" t="s">
+      <c r="D2" t="s">
         <v>713</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>714</v>
       </c>
-      <c r="E2" t="s">
+      <c r="F2" t="s">
         <v>715</v>
       </c>
-      <c r="F2" t="s">
+      <c r="G2" t="s">
         <v>716</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>717</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" t="s">
         <v>718</v>
       </c>
-      <c r="I2" t="s">
+      <c r="J2" t="s">
         <v>719</v>
       </c>
-      <c r="J2" t="s">
-        <v>720</v>
-      </c>
       <c r="K2" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="L2" t="s">
         <v>114</v>
@@ -14821,7 +14822,7 @@
         <v>135</v>
       </c>
       <c r="D3" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="E3" t="s">
         <v>2</v>
@@ -14853,7 +14854,7 @@
         <v>562</v>
       </c>
       <c r="B4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="I4">
         <v>2</v>
@@ -14870,7 +14871,7 @@
         <v>577</v>
       </c>
       <c r="B5" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="I5">
         <v>2</v>
@@ -14884,13 +14885,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
+        <v>723</v>
+      </c>
+      <c r="B6" t="s">
         <v>724</v>
       </c>
-      <c r="B6" t="s">
+      <c r="E6" t="s">
         <v>725</v>
-      </c>
-      <c r="E6" t="s">
-        <v>726</v>
       </c>
       <c r="F6">
         <v>1</v>
@@ -14907,7 +14908,7 @@
         <v>586</v>
       </c>
       <c r="B7" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="I7">
         <v>2</v>
@@ -14924,7 +14925,7 @@
         <v>585</v>
       </c>
       <c r="B8" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="I8">
         <v>2</v>
@@ -14941,7 +14942,7 @@
         <v>492</v>
       </c>
       <c r="B9" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I9">
         <v>2</v>
@@ -14958,7 +14959,7 @@
         <v>491</v>
       </c>
       <c r="B10" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="H10">
         <v>2</v>
@@ -14978,7 +14979,7 @@
         <v>509</v>
       </c>
       <c r="B11" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I11">
         <v>2</v>
@@ -14995,7 +14996,7 @@
         <v>508</v>
       </c>
       <c r="B12" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="H12">
         <v>2</v>
@@ -15015,7 +15016,7 @@
         <v>518</v>
       </c>
       <c r="B13" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="I13">
         <v>2</v>
@@ -15032,10 +15033,10 @@
         <v>517</v>
       </c>
       <c r="B14" t="s">
+        <v>733</v>
+      </c>
+      <c r="E14" t="s">
         <v>734</v>
-      </c>
-      <c r="E14" t="s">
-        <v>735</v>
       </c>
       <c r="H14">
         <v>2</v>
@@ -15052,13 +15053,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B15" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="E15" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -15072,10 +15073,10 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="B16" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
@@ -15083,7 +15084,7 @@
         <v>527</v>
       </c>
       <c r="B17" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="I17">
         <v>2</v>
@@ -15100,7 +15101,7 @@
         <v>526</v>
       </c>
       <c r="B18" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="I18">
         <v>2</v>
@@ -15117,7 +15118,7 @@
         <v>547</v>
       </c>
       <c r="B19" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="I19">
         <v>2</v>
@@ -15134,7 +15135,7 @@
         <v>546</v>
       </c>
       <c r="B20" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="I20">
         <v>2</v>
@@ -15151,7 +15152,7 @@
         <v>560</v>
       </c>
       <c r="B21" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="I21">
         <v>2</v>
@@ -15165,10 +15166,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>742</v>
+      </c>
+      <c r="B22" t="s">
         <v>743</v>
-      </c>
-      <c r="B22" t="s">
-        <v>744</v>
       </c>
       <c r="I22">
         <v>2</v>
@@ -15185,7 +15186,7 @@
         <v>559</v>
       </c>
       <c r="B23" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="I23">
         <v>2</v>
@@ -15199,7 +15200,7 @@
         <v>590</v>
       </c>
       <c r="B24" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="I24">
         <v>2</v>
@@ -15216,7 +15217,7 @@
         <v>589</v>
       </c>
       <c r="B25" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="I25">
         <v>2</v>
@@ -15233,7 +15234,7 @@
         <v>604</v>
       </c>
       <c r="B26" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="I26">
         <v>2</v>
@@ -15278,22 +15279,22 @@
         <v>94</v>
       </c>
       <c r="D2" t="s">
+        <v>748</v>
+      </c>
+      <c r="E2" t="s">
         <v>749</v>
-      </c>
-      <c r="E2" t="s">
-        <v>750</v>
       </c>
       <c r="F2" t="s">
         <v>96</v>
       </c>
       <c r="G2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="H2" t="s">
         <v>363</v>
       </c>
       <c r="I2" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="J2" t="s">
         <v>71</v>
@@ -15322,7 +15323,7 @@
         <v>135</v>
       </c>
       <c r="H3" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="I3" t="s">
         <v>135</v>
@@ -15359,28 +15360,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
+        <v>753</v>
+      </c>
+      <c r="C1" s="1" t="s">
         <v>754</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="D1" s="1" t="s">
         <v>755</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="E1" s="1" t="s">
         <v>756</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="F1" s="1" t="s">
         <v>757</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="G1" s="1" t="s">
         <v>758</v>
       </c>
-      <c r="G1" s="1" t="s">
+      <c r="H1" s="1" t="s">
         <v>759</v>
       </c>
-      <c r="H1" s="1" t="s">
+      <c r="I1" s="1" t="s">
         <v>760</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>761</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -15388,28 +15389,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
+        <v>761</v>
+      </c>
+      <c r="C2" s="1" t="s">
         <v>762</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="D2" s="1" t="s">
         <v>763</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="E2" s="1" t="s">
         <v>764</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
         <v>765</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="G2" s="1" t="s">
         <v>766</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
         <v>767</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="I2" s="1" t="s">
         <v>768</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>769</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{687988EB-7D50-4605-BBCF-BA8AE8AE01DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2938780C-5B6E-4CA8-A71B-CE9B846204F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" firstSheet="1" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="CardData" sheetId="10" r:id="rId1"/>
@@ -299,7 +299,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1521" uniqueCount="776">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1524" uniqueCount="776">
   <si>
     <t>Id</t>
   </si>
@@ -14635,16 +14635,21 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A2:I4"/>
+  <dimension ref="A1:J4"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.25" customWidth="1"/>
     <col min="3" max="3" width="27.25" customWidth="1"/>
     <col min="4" max="4" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="9" customWidth="1"/>
+    <col min="10" max="10" width="9" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="I1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -14670,10 +14675,13 @@
         <v>697</v>
       </c>
       <c r="I2" t="s">
+        <v>412</v>
+      </c>
+      <c r="J2" t="s">
         <v>423</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>2</v>
       </c>
@@ -14699,10 +14707,13 @@
         <v>135</v>
       </c>
       <c r="I3" t="s">
+        <v>452</v>
+      </c>
+      <c r="J3" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>649</v>
       </c>
@@ -14715,7 +14726,7 @@
       <c r="E4">
         <v>10</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>700</v>
       </c>
     </row>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityWork\zhou-master\Excel\Main\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{768B5736-E19F-4702-B1BF-2A25AC909983}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9E9AEF3-7467-4DDE-8FB0-2916E31B76C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-103" yWindow="-103" windowWidth="24144" windowHeight="14447" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -47,6 +47,30 @@
   </authors>
   <commentList>
     <comment ref="AK1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0100-000001000000}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>PC:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+0:干员 1:敌人 2:仅技能条 3:技能+血条</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AM1" authorId="0" shapeId="0" xr:uid="{9C884131-3168-4C84-B962-AAA5F32D544D}">
       <text>
         <r>
           <rPr>
@@ -299,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1599" uniqueCount="811">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1630" uniqueCount="817">
   <si>
     <t>Id</t>
   </si>
@@ -436,9 +460,6 @@
     <t>可选技能</t>
   </si>
   <si>
-    <t>血条类型</t>
-  </si>
-  <si>
     <t>高度</t>
   </si>
   <si>
@@ -2732,13 +2753,41 @@
   </si>
   <si>
     <t>BackSkelPath</t>
+  </si>
+  <si>
+    <t>血条</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>技力条</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>SpBarType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>string</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:蓝</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>小型:绿</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>无</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -2787,6 +2836,21 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -2813,7 +2877,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2827,6 +2891,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -3286,7 +3353,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BT24"/>
+  <dimension ref="A1:BU24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" style="3" customWidth="1"/>
@@ -3318,31 +3385,31 @@
     <col min="35" max="35" width="15.83203125" style="3" customWidth="1"/>
     <col min="36" max="36" width="13.83203125" style="3" customWidth="1"/>
     <col min="37" max="37" width="34.5" style="3" customWidth="1"/>
-    <col min="38" max="39" width="9.83203125" style="3" customWidth="1"/>
-    <col min="40" max="43" width="9" style="3" customWidth="1"/>
-    <col min="44" max="44" width="12.5" style="3" customWidth="1"/>
-    <col min="45" max="50" width="9" style="3" customWidth="1"/>
-    <col min="51" max="51" width="8.5" style="3" customWidth="1"/>
-    <col min="52" max="52" width="9" style="3" customWidth="1"/>
-    <col min="53" max="53" width="17.75" style="3" customWidth="1"/>
-    <col min="54" max="54" width="7.83203125" style="3" customWidth="1"/>
-    <col min="55" max="56" width="9" style="3" customWidth="1"/>
-    <col min="57" max="57" width="24.25" style="3" customWidth="1"/>
-    <col min="58" max="58" width="13.25" style="3" customWidth="1"/>
-    <col min="59" max="59" width="16.08203125" style="3" customWidth="1"/>
-    <col min="60" max="60" width="8" style="3" customWidth="1"/>
-    <col min="61" max="62" width="9" style="3" customWidth="1"/>
-    <col min="63" max="63" width="27" style="3" customWidth="1"/>
-    <col min="64" max="64" width="9" style="3" customWidth="1"/>
-    <col min="65" max="65" width="39.58203125" style="3" customWidth="1"/>
-    <col min="66" max="66" width="14" style="3" customWidth="1"/>
-    <col min="67" max="67" width="14.83203125" style="3" customWidth="1"/>
-    <col min="68" max="71" width="14" style="3" customWidth="1"/>
-    <col min="72" max="72" width="19.1640625" style="3" customWidth="1"/>
-    <col min="73" max="16384" width="9" style="4"/>
+    <col min="38" max="40" width="9.83203125" style="3" customWidth="1"/>
+    <col min="41" max="44" width="9" style="3" customWidth="1"/>
+    <col min="45" max="45" width="12.5" style="3" customWidth="1"/>
+    <col min="46" max="51" width="9" style="3" customWidth="1"/>
+    <col min="52" max="52" width="8.5" style="3" customWidth="1"/>
+    <col min="53" max="53" width="9" style="3" customWidth="1"/>
+    <col min="54" max="54" width="17.75" style="3" customWidth="1"/>
+    <col min="55" max="55" width="7.83203125" style="3" customWidth="1"/>
+    <col min="56" max="57" width="9" style="3" customWidth="1"/>
+    <col min="58" max="58" width="24.25" style="3" customWidth="1"/>
+    <col min="59" max="59" width="13.25" style="3" customWidth="1"/>
+    <col min="60" max="60" width="16.08203125" style="3" customWidth="1"/>
+    <col min="61" max="61" width="8" style="3" customWidth="1"/>
+    <col min="62" max="63" width="9" style="3" customWidth="1"/>
+    <col min="64" max="64" width="27" style="3" customWidth="1"/>
+    <col min="65" max="65" width="9" style="3" customWidth="1"/>
+    <col min="66" max="66" width="39.58203125" style="3" customWidth="1"/>
+    <col min="67" max="67" width="14" style="3" customWidth="1"/>
+    <col min="68" max="68" width="14.83203125" style="3" customWidth="1"/>
+    <col min="69" max="72" width="14" style="3" customWidth="1"/>
+    <col min="73" max="73" width="19.1640625" style="3" customWidth="1"/>
+    <col min="74" max="16384" width="9" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:73" x14ac:dyDescent="0.25">
       <c r="D1" s="3" t="s">
         <v>21</v>
       </c>
@@ -3418,399 +3485,405 @@
       <c r="AL1" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="AM1" s="3" t="s">
+      <c r="AM1" s="5" t="s">
+        <v>810</v>
+      </c>
+      <c r="AN1" s="5" t="s">
+        <v>811</v>
+      </c>
+      <c r="AO1" s="3" t="s">
         <v>45</v>
       </c>
-      <c r="AN1" s="3" t="s">
+      <c r="AP1" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="AO1" s="3" t="s">
+      <c r="AQ1" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="AP1" s="3" t="s">
+      <c r="AR1" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="AQ1" s="3" t="s">
+      <c r="AS1" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="AR1" s="3" t="s">
+      <c r="AU1" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="AT1" s="3" t="s">
+      <c r="AV1" s="3" t="s">
         <v>51</v>
       </c>
-      <c r="AU1" s="3" t="s">
+      <c r="AW1" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="AV1" s="3" t="s">
+      <c r="AX1" s="3" t="s">
         <v>53</v>
       </c>
-      <c r="AW1" s="3" t="s">
+      <c r="AY1" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="AX1" s="3" t="s">
+      <c r="AZ1" s="3" t="s">
         <v>55</v>
       </c>
-      <c r="AY1" s="3" t="s">
+      <c r="BA1" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="AZ1" s="3" t="s">
+      <c r="BB1" s="3" t="s">
         <v>57</v>
       </c>
-      <c r="BA1" s="3" t="s">
+      <c r="BC1" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="BB1" s="3" t="s">
+      <c r="BF1" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="BE1" s="3" t="s">
+      <c r="BG1" s="3" t="s">
         <v>60</v>
       </c>
-      <c r="BF1" s="3" t="s">
+      <c r="BH1" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="BG1" s="3" t="s">
+      <c r="BI1" s="3" t="s">
         <v>62</v>
       </c>
-      <c r="BH1" s="3" t="s">
+      <c r="BJ1" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="BI1" s="3" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="2" spans="1:72" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C2" s="3" t="s">
         <v>65</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F2" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="G2" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="H2" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="I2" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="I2" s="3" t="s">
+      <c r="J2" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J2" s="3" t="s">
+      <c r="K2" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="K2" s="3" t="s">
+      <c r="L2" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="L2" s="3" t="s">
+      <c r="M2" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="M2" s="3" t="s">
+      <c r="N2" s="3" t="s">
         <v>74</v>
       </c>
-      <c r="N2" s="3" t="s">
+      <c r="O2" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="O2" s="3" t="s">
+      <c r="P2" s="3" t="s">
         <v>76</v>
       </c>
-      <c r="P2" s="3" t="s">
+      <c r="Q2" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="R2" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="R2" s="3" t="s">
+      <c r="S2" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="S2" s="3" t="s">
+      <c r="T2" s="3" t="s">
         <v>80</v>
       </c>
-      <c r="T2" s="3" t="s">
+      <c r="U2" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="U2" s="3" t="s">
+      <c r="V2" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="V2" s="3" t="s">
+      <c r="W2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="W2" s="3" t="s">
+      <c r="X2" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="X2" s="3" t="s">
+      <c r="Y2" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="Y2" s="3" t="s">
+      <c r="Z2" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="Z2" s="3" t="s">
+      <c r="AA2" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="AA2" s="3" t="s">
+      <c r="AB2" s="3" t="s">
         <v>88</v>
       </c>
-      <c r="AB2" s="3" t="s">
+      <c r="AC2" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="AC2" s="3" t="s">
+      <c r="AD2" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="AD2" s="4" t="s">
+      <c r="AE2" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="AE2" s="3" t="s">
+      <c r="AF2" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="AF2" s="3" t="s">
+      <c r="AG2" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="AG2" s="3" t="s">
+      <c r="AH2" s="3" t="s">
         <v>94</v>
       </c>
-      <c r="AH2" s="3" t="s">
+      <c r="AI2" s="3" t="s">
         <v>95</v>
       </c>
-      <c r="AI2" s="3" t="s">
+      <c r="AJ2" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="AJ2" s="3" t="s">
+      <c r="AK2" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="AK2" s="3" t="s">
+      <c r="AL2" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="AL2" s="3" t="s">
+      <c r="AM2" s="1" t="s">
         <v>99</v>
       </c>
-      <c r="AM2" s="3" t="s">
+      <c r="AN2" s="5" t="s">
+        <v>812</v>
+      </c>
+      <c r="AO2" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="AN2" s="3" t="s">
+      <c r="AP2" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="AO2" s="3" t="s">
+      <c r="AQ2" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="AP2" s="3" t="s">
+      <c r="AR2" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="AQ2" s="3" t="s">
+      <c r="AS2" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="AR2" s="3" t="s">
+      <c r="AT2" s="3" t="s">
         <v>105</v>
       </c>
-      <c r="AS2" s="3" t="s">
+      <c r="AU2" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="AT2" s="3" t="s">
+      <c r="AV2" s="3" t="s">
         <v>107</v>
       </c>
-      <c r="AU2" s="3" t="s">
+      <c r="AW2" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="AV2" s="3" t="s">
+      <c r="AX2" s="3" t="s">
         <v>109</v>
       </c>
-      <c r="AW2" s="3" t="s">
+      <c r="AY2" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="AX2" s="3" t="s">
+      <c r="AZ2" s="3" t="s">
         <v>111</v>
       </c>
-      <c r="AY2" s="3" t="s">
+      <c r="BA2" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="AZ2" s="3" t="s">
+      <c r="BB2" s="3" t="s">
         <v>113</v>
       </c>
-      <c r="BA2" s="3" t="s">
+      <c r="BC2" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="BB2" s="3" t="s">
+      <c r="BD2" s="3" t="s">
         <v>115</v>
       </c>
-      <c r="BC2" s="3" t="s">
+      <c r="BE2" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="BD2" s="3" t="s">
+      <c r="BF2" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="BE2" s="3" t="s">
+      <c r="BG2" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="BF2" s="3" t="s">
+      <c r="BH2" s="3" t="s">
         <v>119</v>
       </c>
-      <c r="BG2" s="3" t="s">
+      <c r="BI2" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="BH2" s="3" t="s">
+      <c r="BJ2" s="3" t="s">
         <v>121</v>
       </c>
-      <c r="BI2" s="3" t="s">
+      <c r="BK2" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="BJ2" s="3" t="s">
+      <c r="BL2" s="3" t="s">
         <v>123</v>
       </c>
-      <c r="BK2" s="3" t="s">
+      <c r="BM2" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="BL2" s="3" t="s">
+      <c r="BN2" s="3" t="s">
         <v>125</v>
       </c>
-      <c r="BM2" s="3" t="s">
+      <c r="BO2" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="BN2" s="3" t="s">
+      <c r="BP2" s="3" t="s">
         <v>127</v>
       </c>
-      <c r="BO2" s="3" t="s">
+      <c r="BQ2" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="BP2" s="3" t="s">
+      <c r="BR2" s="3" t="s">
         <v>129</v>
       </c>
-      <c r="BQ2" s="3" t="s">
+      <c r="BS2" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="BR2" s="3" t="s">
+      <c r="BT2" s="3" t="s">
         <v>131</v>
       </c>
-      <c r="BS2" s="3" t="s">
+      <c r="BU2" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="BT2" s="3" t="s">
+    </row>
+    <row r="3" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="3" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="3" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="3" t="s">
+      <c r="F3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="G3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="G3" s="3" t="s">
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="3" t="s">
+      <c r="J3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="T3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="U3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="V3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="W3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="X3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="Y3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="Z3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AA3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AB3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AC3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AF3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AG3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AJ3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="AL3" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="K3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="M3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="N3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="O3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="W3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="X3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="Y3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="Z3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AA3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AB3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AC3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AD3" s="3" t="s">
+      <c r="AM3" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="AN3" s="5" t="s">
+        <v>813</v>
+      </c>
+      <c r="AO3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AE3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AF3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AG3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AH3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AI3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AJ3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="3" t="s">
+      <c r="AP3" s="3" t="s">
         <v>137</v>
-      </c>
-      <c r="AL3" s="3" t="s">
-        <v>137</v>
-      </c>
-      <c r="AM3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="AO3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AP3" s="3" t="s">
-        <v>136</v>
       </c>
       <c r="AQ3" s="3" t="s">
         <v>135</v>
@@ -3818,103 +3891,106 @@
       <c r="AR3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="AT3" s="3" t="s">
-        <v>135</v>
+      <c r="AS3" s="3" t="s">
+        <v>133</v>
       </c>
       <c r="AU3" s="3" t="s">
         <v>134</v>
       </c>
       <c r="AV3" s="3" t="s">
-        <v>136</v>
+        <v>133</v>
       </c>
       <c r="AW3" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="AX3" s="3" t="s">
+      <c r="BA3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="BC3" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="BD3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BF3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="AY3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="AZ3" s="3" t="s">
+      <c r="BK3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BL3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BM3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="BO3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BP3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BQ3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BS3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BT3" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="BU3" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="BA3" s="3" t="s">
-        <v>134</v>
-      </c>
-      <c r="BB3" s="3" t="s">
-        <v>135</v>
-      </c>
-      <c r="BC3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="BD3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BE3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BF3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="BI3" s="3" t="s">
-        <v>136</v>
-      </c>
-      <c r="BJ3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BK3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BL3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="3" t="s">
-        <v>143</v>
-      </c>
-      <c r="BN3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BO3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BP3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BQ3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BR3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BS3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BT3" s="3" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="5" spans="1:72" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>144</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="E5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="F5" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="E5" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="G5" s="3">
         <v>1</v>
@@ -3968,87 +4044,97 @@
         <v>5</v>
       </c>
       <c r="AJ5" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="AK5" s="3" t="s">
         <v>147</v>
       </c>
-      <c r="AK5" s="3" t="s">
+      <c r="AM5" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN5" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP5" s="3" t="s">
         <v>148</v>
       </c>
-      <c r="AO5" s="3" t="s">
+      <c r="AQ5" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR5" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY5" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD5" s="3" t="s">
         <v>149</v>
       </c>
-      <c r="AP5" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ5" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX5" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC5" s="3" t="s">
+      <c r="BE5" s="3" t="s">
         <v>150</v>
       </c>
-      <c r="BD5" s="3" t="s">
+      <c r="BF5" s="3" t="s">
         <v>151</v>
       </c>
-      <c r="BE5" s="3" t="s">
+      <c r="BG5" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="BF5" s="3" t="s">
+      <c r="BH5" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BI5" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="BG5" s="3" t="s">
-        <v>145</v>
-      </c>
-      <c r="BH5" s="3" t="s">
+      <c r="BJ5" s="3">
+        <v>2</v>
+      </c>
+      <c r="BK5" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="BI5" s="3">
-        <v>2</v>
-      </c>
-      <c r="BJ5" s="3" t="s">
+      <c r="BL5" s="3" t="s">
         <v>155</v>
       </c>
-      <c r="BK5" s="3" t="s">
+      <c r="BM5" s="3" t="s">
         <v>156</v>
       </c>
-      <c r="BL5" s="3" t="s">
+      <c r="BN5" s="3" t="s">
         <v>157</v>
       </c>
-      <c r="BM5" s="3" t="s">
+      <c r="BO5" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="BN5" s="3" t="s">
+      <c r="BP5" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO5" s="3" t="s">
+      <c r="BR5" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ5" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR5" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT5" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS5" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU5" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AM6" s="5"/>
+      <c r="AN6" s="5"/>
+    </row>
+    <row r="7" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="F7" s="3" t="s">
         <v>162</v>
-      </c>
-      <c r="E7" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="F7" s="3" t="s">
-        <v>163</v>
       </c>
       <c r="G7" s="3">
         <v>1</v>
@@ -4102,90 +4188,96 @@
         <v>7</v>
       </c>
       <c r="AJ7" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK7" s="3" t="s">
+        <v>163</v>
+      </c>
+      <c r="AL7" s="3" t="s">
         <v>164</v>
       </c>
-      <c r="AL7" s="3" t="s">
+      <c r="AM7" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN7" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP7" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ7" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR7" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY7" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD7" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE7" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF7" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="AO7" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP7" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ7" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX7" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC7" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD7" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE7" s="3" t="s">
+      <c r="BG7" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="BF7" s="3" t="s">
+      <c r="BH7" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="BI7" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ7" s="3">
+        <v>3</v>
+      </c>
+      <c r="BK7" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL7" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="BG7" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="BH7" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI7" s="3">
-        <v>3</v>
-      </c>
-      <c r="BJ7" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK7" s="3" t="s">
+      <c r="BM7" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN7" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="BL7" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM7" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="BN7" s="3" t="s">
+      <c r="BO7" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP7" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO7" s="3" t="s">
+      <c r="BR7" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ7" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR7" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT7" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS7" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU7" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>8</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="3" t="s">
         <v>170</v>
-      </c>
-      <c r="E8" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="F8" s="3" t="s">
-        <v>171</v>
       </c>
       <c r="G8" s="3">
         <v>1</v>
@@ -4239,90 +4331,96 @@
         <v>8</v>
       </c>
       <c r="AJ8" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK8" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="AL8" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="AL8" s="3" t="s">
+      <c r="AM8" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN8" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP8" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ8" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR8" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY8" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD8" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE8" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF8" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="AO8" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP8" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ8" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX8" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC8" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD8" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE8" s="3" t="s">
+      <c r="BG8" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="BF8" s="3" t="s">
+      <c r="BH8" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="BI8" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ8" s="3">
+        <v>3</v>
+      </c>
+      <c r="BK8" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL8" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="BG8" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="BH8" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI8" s="3">
-        <v>3</v>
-      </c>
-      <c r="BJ8" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK8" s="3" t="s">
+      <c r="BM8" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN8" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="BL8" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM8" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="BN8" s="3" t="s">
+      <c r="BO8" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP8" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO8" s="3" t="s">
+      <c r="BR8" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ8" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR8" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT8" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS8" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU8" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="F9" s="3" t="s">
         <v>178</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="F9" s="3" t="s">
-        <v>179</v>
       </c>
       <c r="G9" s="3">
         <v>1</v>
@@ -4376,90 +4474,100 @@
         <v>9</v>
       </c>
       <c r="AJ9" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK9" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="AL9" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="AL9" s="3" t="s">
+      <c r="AM9" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN9" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP9" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AR9" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY9" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD9" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE9" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="AO9" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP9" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ9" s="3">
-        <v>1</v>
-      </c>
-      <c r="AX9" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC9" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD9" s="3" t="s">
+      <c r="BF9" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="BE9" s="3" t="s">
+      <c r="BG9" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="BF9" s="3" t="s">
+      <c r="BH9" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="BI9" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ9" s="3">
+        <v>3</v>
+      </c>
+      <c r="BK9" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL9" s="3" t="s">
         <v>184</v>
       </c>
-      <c r="BG9" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="BH9" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI9" s="3">
-        <v>3</v>
-      </c>
-      <c r="BJ9" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK9" s="3" t="s">
+      <c r="BM9" s="3" t="s">
         <v>185</v>
       </c>
-      <c r="BL9" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="BM9" s="3" t="s">
-        <v>177</v>
-      </c>
       <c r="BN9" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="BO9" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP9" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO9" s="3" t="s">
+      <c r="BR9" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ9" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR9" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT9" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="11" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS9" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU9" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AM10" s="5"/>
+      <c r="AN10" s="5"/>
+    </row>
+    <row r="11" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="F11" s="3" t="s">
         <v>187</v>
-      </c>
-      <c r="E11" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="F11" s="3" t="s">
-        <v>188</v>
       </c>
       <c r="G11" s="3">
         <v>1</v>
@@ -4513,90 +4621,96 @@
         <v>11</v>
       </c>
       <c r="AJ11" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK11" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="AL11" s="3" t="s">
         <v>189</v>
       </c>
-      <c r="AL11" s="3" t="s">
+      <c r="AM11" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN11" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP11" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ11" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR11" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY11" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD11" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE11" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF11" s="3" t="s">
         <v>190</v>
       </c>
-      <c r="AO11" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP11" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ11" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX11" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC11" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD11" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE11" s="3" t="s">
+      <c r="BG11" s="3" t="s">
         <v>191</v>
       </c>
-      <c r="BF11" s="3" t="s">
+      <c r="BH11" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="BI11" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ11" s="3">
+        <v>4</v>
+      </c>
+      <c r="BK11" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL11" s="3" t="s">
         <v>192</v>
       </c>
-      <c r="BG11" s="3" t="s">
-        <v>187</v>
-      </c>
-      <c r="BH11" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI11" s="3">
-        <v>4</v>
-      </c>
-      <c r="BJ11" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK11" s="3" t="s">
+      <c r="BM11" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN11" s="3" t="s">
         <v>193</v>
       </c>
-      <c r="BL11" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM11" s="3" t="s">
-        <v>194</v>
-      </c>
-      <c r="BN11" s="3" t="s">
+      <c r="BO11" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP11" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO11" s="3" t="s">
+      <c r="BR11" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ11" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR11" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT11" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="12" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS11" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU11" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A12" s="3" t="s">
         <v>12</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D12" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="F12" s="3" t="s">
         <v>195</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="F12" s="3" t="s">
-        <v>196</v>
       </c>
       <c r="G12" s="3">
         <v>1</v>
@@ -4650,90 +4764,96 @@
         <v>12</v>
       </c>
       <c r="AJ12" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK12" s="3" t="s">
+        <v>196</v>
+      </c>
+      <c r="AL12" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="AL12" s="3" t="s">
+      <c r="AM12" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN12" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP12" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ12" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR12" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY12" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD12" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE12" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF12" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="AO12" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP12" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ12" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX12" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC12" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD12" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE12" s="3" t="s">
+      <c r="BG12" s="3" t="s">
         <v>199</v>
       </c>
-      <c r="BF12" s="3" t="s">
+      <c r="BH12" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="BI12" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ12" s="3">
+        <v>4</v>
+      </c>
+      <c r="BK12" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL12" s="3" t="s">
         <v>200</v>
       </c>
-      <c r="BG12" s="3" t="s">
-        <v>195</v>
-      </c>
-      <c r="BH12" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI12" s="3">
-        <v>4</v>
-      </c>
-      <c r="BJ12" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK12" s="3" t="s">
+      <c r="BM12" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN12" s="3" t="s">
         <v>201</v>
       </c>
-      <c r="BL12" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM12" s="3" t="s">
-        <v>202</v>
-      </c>
-      <c r="BN12" s="3" t="s">
+      <c r="BO12" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP12" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO12" s="3" t="s">
+      <c r="BR12" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ12" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR12" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT12" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="13" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS12" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU12" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A13" s="3" t="s">
         <v>13</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="F13" s="3" t="s">
         <v>203</v>
-      </c>
-      <c r="E13" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="F13" s="3" t="s">
-        <v>204</v>
       </c>
       <c r="G13" s="3">
         <v>1</v>
@@ -4787,90 +4907,96 @@
         <v>13</v>
       </c>
       <c r="AJ13" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK13" s="3" t="s">
+        <v>204</v>
+      </c>
+      <c r="AL13" s="3" t="s">
         <v>205</v>
       </c>
-      <c r="AL13" s="3" t="s">
+      <c r="AM13" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN13" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP13" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AR13" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY13" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD13" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE13" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="BF13" s="3" t="s">
         <v>206</v>
       </c>
-      <c r="AO13" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ13" s="3">
-        <v>1</v>
-      </c>
-      <c r="AX13" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC13" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD13" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="BE13" s="3" t="s">
+      <c r="BG13" s="3" t="s">
         <v>207</v>
       </c>
-      <c r="BF13" s="3" t="s">
+      <c r="BH13" s="3" t="s">
+        <v>202</v>
+      </c>
+      <c r="BI13" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ13" s="3">
+        <v>4</v>
+      </c>
+      <c r="BK13" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL13" s="3" t="s">
         <v>208</v>
       </c>
-      <c r="BG13" s="3" t="s">
-        <v>203</v>
-      </c>
-      <c r="BH13" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI13" s="3">
-        <v>4</v>
-      </c>
-      <c r="BJ13" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK13" s="3" t="s">
+      <c r="BM13" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="BN13" s="3" t="s">
         <v>209</v>
       </c>
-      <c r="BL13" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="BM13" s="3" t="s">
-        <v>210</v>
-      </c>
-      <c r="BN13" s="3" t="s">
+      <c r="BO13" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP13" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO13" s="3" t="s">
+      <c r="BR13" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ13" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR13" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT13" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="14" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS13" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU13" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A14" s="3" t="s">
         <v>14</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D14" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="F14" s="3" t="s">
         <v>211</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>212</v>
       </c>
       <c r="G14" s="3">
         <v>1</v>
@@ -4924,90 +5050,100 @@
         <v>14</v>
       </c>
       <c r="AJ14" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK14" s="3" t="s">
+        <v>212</v>
+      </c>
+      <c r="AL14" s="3" t="s">
         <v>213</v>
       </c>
-      <c r="AL14" s="3" t="s">
+      <c r="AM14" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN14" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP14" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ14" s="3">
+        <v>1</v>
+      </c>
+      <c r="AR14" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY14" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD14" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE14" s="3" t="s">
         <v>214</v>
       </c>
-      <c r="AO14" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP14" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ14" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX14" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC14" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD14" s="3" t="s">
+      <c r="BF14" s="3" t="s">
         <v>215</v>
       </c>
-      <c r="BE14" s="3" t="s">
+      <c r="BG14" s="3" t="s">
         <v>216</v>
       </c>
-      <c r="BF14" s="3" t="s">
+      <c r="BH14" s="3" t="s">
+        <v>210</v>
+      </c>
+      <c r="BI14" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ14" s="3">
+        <v>4</v>
+      </c>
+      <c r="BK14" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL14" s="3" t="s">
         <v>217</v>
       </c>
-      <c r="BG14" s="3" t="s">
-        <v>211</v>
-      </c>
-      <c r="BH14" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI14" s="3">
-        <v>4</v>
-      </c>
-      <c r="BJ14" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK14" s="3" t="s">
+      <c r="BM14" s="3" t="s">
         <v>218</v>
       </c>
-      <c r="BL14" s="3" t="s">
+      <c r="BN14" s="3" t="s">
         <v>219</v>
       </c>
-      <c r="BM14" s="3" t="s">
-        <v>220</v>
-      </c>
-      <c r="BN14" s="3" t="s">
+      <c r="BO14" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP14" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO14" s="3" t="s">
+      <c r="BR14" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR14" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT14" s="3">
+      <c r="BS14" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU14" s="3">
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="16" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AM15" s="5"/>
+      <c r="AN15" s="5"/>
+    </row>
+    <row r="16" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A16" s="3" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D16" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>221</v>
-      </c>
-      <c r="E16" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>222</v>
       </c>
       <c r="G16" s="3">
         <v>1</v>
@@ -5061,90 +5197,96 @@
         <v>16</v>
       </c>
       <c r="AJ16" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK16" s="3" t="s">
+        <v>222</v>
+      </c>
+      <c r="AL16" s="3" t="s">
         <v>223</v>
       </c>
-      <c r="AL16" s="3" t="s">
+      <c r="AM16" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN16" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP16" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ16" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR16" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY16" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD16" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE16" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF16" s="3" t="s">
         <v>224</v>
       </c>
-      <c r="AO16" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP16" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ16" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX16" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC16" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD16" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE16" s="3" t="s">
+      <c r="BG16" s="3" t="s">
         <v>225</v>
       </c>
-      <c r="BF16" s="3" t="s">
+      <c r="BH16" s="3" t="s">
+        <v>220</v>
+      </c>
+      <c r="BI16" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ16" s="3">
+        <v>5</v>
+      </c>
+      <c r="BK16" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL16" s="3" t="s">
         <v>226</v>
       </c>
-      <c r="BG16" s="3" t="s">
-        <v>221</v>
-      </c>
-      <c r="BH16" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI16" s="3">
-        <v>5</v>
-      </c>
-      <c r="BJ16" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK16" s="3" t="s">
+      <c r="BM16" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN16" s="3" t="s">
         <v>227</v>
       </c>
-      <c r="BL16" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM16" s="3" t="s">
-        <v>228</v>
-      </c>
-      <c r="BN16" s="3" t="s">
+      <c r="BO16" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP16" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO16" s="3" t="s">
+      <c r="BR16" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ16" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR16" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT16" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="17" spans="1:72" x14ac:dyDescent="0.25">
+      <c r="BS16" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU16" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A17" s="3" t="s">
         <v>17</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D17" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="F17" s="3" t="s">
         <v>229</v>
-      </c>
-      <c r="E17" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="F17" s="3" t="s">
-        <v>230</v>
       </c>
       <c r="G17" s="3">
         <v>1</v>
@@ -5198,93 +5340,103 @@
         <v>17</v>
       </c>
       <c r="AJ17" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK17" s="3" t="s">
+        <v>230</v>
+      </c>
+      <c r="AL17" s="3" t="s">
         <v>231</v>
       </c>
-      <c r="AL17" s="3" t="s">
+      <c r="AM17" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN17" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP17" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ17" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR17" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY17" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD17" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE17" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF17" s="3" t="s">
         <v>232</v>
       </c>
-      <c r="AO17" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP17" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ17" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX17" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC17" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD17" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE17" s="3" t="s">
+      <c r="BG17" s="3" t="s">
         <v>233</v>
       </c>
-      <c r="BF17" s="3" t="s">
+      <c r="BH17" s="3" t="s">
+        <v>228</v>
+      </c>
+      <c r="BI17" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ17" s="3">
+        <v>5</v>
+      </c>
+      <c r="BK17" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL17" s="3" t="s">
         <v>234</v>
       </c>
-      <c r="BG17" s="3" t="s">
-        <v>229</v>
-      </c>
-      <c r="BH17" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI17" s="3">
-        <v>5</v>
-      </c>
-      <c r="BJ17" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK17" s="3" t="s">
+      <c r="BM17" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN17" s="3" t="s">
         <v>235</v>
       </c>
-      <c r="BL17" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM17" s="3" t="s">
+      <c r="BO17" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP17" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="BR17" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BS17" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BT17" s="3" t="s">
         <v>236</v>
       </c>
-      <c r="BN17" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BO17" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="BQ17" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR17" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BS17" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="BT17" s="3">
+      <c r="BU17" s="3">
         <v>1.05</v>
       </c>
     </row>
-    <row r="19" spans="1:72" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AM18" s="5"/>
+      <c r="AN18" s="5"/>
+    </row>
+    <row r="19" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A19" s="3" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D19" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="F19" s="3" t="s">
         <v>238</v>
-      </c>
-      <c r="E19" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="F19" s="3" t="s">
-        <v>239</v>
       </c>
       <c r="G19" s="3">
         <v>1</v>
@@ -5341,93 +5493,99 @@
         <v>19</v>
       </c>
       <c r="AJ19" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK19" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="AL19" s="3" t="s">
         <v>240</v>
       </c>
-      <c r="AL19" s="3" t="s">
+      <c r="AM19" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN19" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP19" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ19" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR19" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AY19" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD19" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE19" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="BF19" s="3" t="s">
         <v>241</v>
       </c>
-      <c r="AO19" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP19" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ19" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AX19" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC19" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD19" s="3" t="s">
-        <v>151</v>
-      </c>
-      <c r="BE19" s="3" t="s">
+      <c r="BG19" s="3" t="s">
         <v>242</v>
       </c>
-      <c r="BF19" s="3" t="s">
+      <c r="BH19" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="BI19" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ19" s="3">
+        <v>6</v>
+      </c>
+      <c r="BK19" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL19" s="3" t="s">
         <v>243</v>
       </c>
-      <c r="BG19" s="3" t="s">
-        <v>238</v>
-      </c>
-      <c r="BH19" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI19" s="3">
-        <v>6</v>
-      </c>
-      <c r="BJ19" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK19" s="3" t="s">
+      <c r="BM19" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="BN19" s="3" t="s">
         <v>244</v>
       </c>
-      <c r="BL19" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BM19" s="3" t="s">
-        <v>245</v>
-      </c>
-      <c r="BN19" s="3" t="s">
+      <c r="BO19" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP19" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO19" s="3" t="s">
+      <c r="BR19" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ19" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR19" s="3" t="s">
-        <v>161</v>
-      </c>
       <c r="BS19" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="BT19" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="20" spans="1:72" x14ac:dyDescent="0.25">
+        <v>160</v>
+      </c>
+      <c r="BT19" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="BU19" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:73" x14ac:dyDescent="0.25">
       <c r="A20" s="3" t="s">
         <v>20</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D20" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="E20" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="F20" s="3" t="s">
         <v>246</v>
-      </c>
-      <c r="E20" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="F20" s="3" t="s">
-        <v>247</v>
       </c>
       <c r="G20" s="3">
         <v>1</v>
@@ -5478,84 +5636,94 @@
         <v>20</v>
       </c>
       <c r="AJ20" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK20" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="AL20" s="3" t="s">
         <v>248</v>
       </c>
-      <c r="AL20" s="3" t="s">
+      <c r="AM20" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN20" s="5" t="s">
+        <v>815</v>
+      </c>
+      <c r="AP20" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AR20" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY20" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD20" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BE20" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="BF20" s="3" t="s">
         <v>249</v>
       </c>
-      <c r="AO20" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP20" s="3">
-        <v>1</v>
-      </c>
-      <c r="AQ20" s="3">
-        <v>1</v>
-      </c>
-      <c r="AX20" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC20" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD20" s="3" t="s">
-        <v>182</v>
-      </c>
-      <c r="BE20" s="3" t="s">
+      <c r="BG20" s="3" t="s">
         <v>250</v>
       </c>
-      <c r="BF20" s="3" t="s">
+      <c r="BH20" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="BI20" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ20" s="3">
+        <v>6</v>
+      </c>
+      <c r="BK20" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BL20" s="3" t="s">
         <v>251</v>
       </c>
-      <c r="BG20" s="3" t="s">
-        <v>246</v>
-      </c>
-      <c r="BH20" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI20" s="3">
-        <v>6</v>
-      </c>
-      <c r="BJ20" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BK20" s="3" t="s">
+      <c r="BM20" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="BN20" s="3" t="s">
         <v>252</v>
       </c>
-      <c r="BL20" s="3" t="s">
-        <v>186</v>
-      </c>
-      <c r="BM20" s="3" t="s">
+      <c r="BO20" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP20" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="BR20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BS20" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU20" s="3">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="21" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AM21" s="5"/>
+      <c r="AN21" s="5"/>
+    </row>
+    <row r="22" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A22" s="3" t="s">
         <v>253</v>
       </c>
-      <c r="BN20" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BO20" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="BQ20" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR20" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT20" s="3">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="22" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A22" s="3" t="s">
+      <c r="B22" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F22" s="3" t="s">
         <v>254</v>
-      </c>
-      <c r="B22" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F22" s="3" t="s">
-        <v>255</v>
       </c>
       <c r="G22" s="3">
         <v>1</v>
@@ -5597,87 +5765,94 @@
         <v>1</v>
       </c>
       <c r="AI22" s="3" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AJ22" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK22" s="3" t="s">
+        <v>255</v>
+      </c>
+      <c r="AM22" s="5" t="s">
+        <v>814</v>
+      </c>
+      <c r="AN22" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="AP22" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="AQ22" s="3">
+        <v>2</v>
+      </c>
+      <c r="AR22" s="3">
+        <v>0.5</v>
+      </c>
+      <c r="AS22" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY22" s="3">
+        <v>0.25</v>
+      </c>
+      <c r="BD22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="BF22" s="3" t="s">
         <v>256</v>
       </c>
-      <c r="AM22" s="3">
-        <v>0</v>
-      </c>
-      <c r="AO22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP22" s="3">
-        <v>2</v>
-      </c>
-      <c r="AQ22" s="3">
-        <v>0.5</v>
-      </c>
-      <c r="AR22" s="3">
-        <v>1</v>
-      </c>
-      <c r="AX22" s="3">
-        <v>0.25</v>
-      </c>
-      <c r="BC22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="BE22" s="3" t="s">
+      <c r="BG22" s="3" t="s">
         <v>257</v>
       </c>
-      <c r="BF22" s="3" t="s">
+      <c r="BH22" s="3" t="s">
         <v>258</v>
       </c>
-      <c r="BG22" s="3" t="s">
+      <c r="BI22" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ22" s="3">
+        <v>6</v>
+      </c>
+      <c r="BK22" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="BO22" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP22" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="BR22" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BS22" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BT22" s="3" t="s">
+        <v>236</v>
+      </c>
+      <c r="BU22" s="3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="AM23" s="5"/>
+      <c r="AN23" s="5"/>
+    </row>
+    <row r="24" spans="1:73" x14ac:dyDescent="0.25">
+      <c r="A24" s="3" t="s">
         <v>259</v>
       </c>
-      <c r="BH22" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="BI22" s="3">
-        <v>6</v>
-      </c>
-      <c r="BJ22" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BN22" s="3" t="s">
-        <v>159</v>
-      </c>
-      <c r="BO22" s="3" t="s">
-        <v>160</v>
-      </c>
-      <c r="BQ22" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR22" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BS22" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="BT22" s="3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="24" spans="1:72" x14ac:dyDescent="0.25">
-      <c r="A24" s="3" t="s">
+      <c r="B24" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>260</v>
       </c>
-      <c r="B24" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="D24" s="3" t="s">
+      <c r="E24" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="F24" s="3" t="s">
         <v>261</v>
-      </c>
-      <c r="E24" s="3" t="s">
-        <v>261</v>
-      </c>
-      <c r="F24" s="3" t="s">
-        <v>262</v>
       </c>
       <c r="G24" s="3">
         <v>0.01</v>
@@ -5725,72 +5900,75 @@
         <v>-1</v>
       </c>
       <c r="AI24" s="3" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AJ24" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="AK24" s="3" t="s">
-        <v>263</v>
-      </c>
-      <c r="AM24" s="3">
-        <v>3</v>
-      </c>
-      <c r="AN24" s="3">
+        <v>262</v>
+      </c>
+      <c r="AM24" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="AN24" s="5" t="s">
+        <v>816</v>
+      </c>
+      <c r="AO24" s="3">
         <v>-0.5</v>
       </c>
-      <c r="AO24" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="AP24" s="3">
-        <v>0</v>
+      <c r="AP24" s="3" t="s">
+        <v>148</v>
       </c>
       <c r="AQ24" s="3">
         <v>0</v>
       </c>
       <c r="AR24" s="3">
-        <v>1</v>
-      </c>
-      <c r="AX24" s="3">
         <v>0</v>
       </c>
-      <c r="BA24" s="3">
-        <v>1</v>
-      </c>
-      <c r="BC24" s="3" t="s">
+      <c r="AS24" s="3">
+        <v>1</v>
+      </c>
+      <c r="AY24" s="3">
+        <v>0</v>
+      </c>
+      <c r="BB24" s="3">
+        <v>1</v>
+      </c>
+      <c r="BD24" s="3" t="s">
+        <v>263</v>
+      </c>
+      <c r="BF24" s="3" t="s">
         <v>264</v>
       </c>
-      <c r="BE24" s="3" t="s">
+      <c r="BG24" s="3" t="s">
         <v>265</v>
       </c>
-      <c r="BF24" s="3" t="s">
-        <v>266</v>
-      </c>
-      <c r="BG24" s="3" t="s">
-        <v>261</v>
-      </c>
       <c r="BH24" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="BI24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="BJ24" s="3">
+        <v>6</v>
+      </c>
+      <c r="BK24" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="BI24" s="3">
-        <v>6</v>
-      </c>
-      <c r="BJ24" s="3" t="s">
-        <v>155</v>
-      </c>
-      <c r="BN24" s="3" t="s">
+      <c r="BO24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="BP24" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="BO24" s="3" t="s">
+      <c r="BR24" s="3" t="s">
         <v>160</v>
       </c>
-      <c r="BQ24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BR24" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="BT24" s="3">
+      <c r="BS24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="BU24" s="3">
         <v>1</v>
       </c>
     </row>
@@ -5891,334 +6069,334 @@
   <sheetData>
     <row r="1" spans="1:113" x14ac:dyDescent="0.25">
       <c r="B1" s="2" t="s">
+        <v>266</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>267</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>270</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>271</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>272</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>273</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>274</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>275</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>276</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>277</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>278</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>279</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="Q1" s="2" t="s">
         <v>280</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="R1" s="2" t="s">
         <v>281</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="S1" s="2" t="s">
         <v>282</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="T1" s="2" t="s">
         <v>283</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="U1" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="V1" s="2" t="s">
         <v>284</v>
       </c>
-      <c r="U1" s="2" t="s">
-        <v>284</v>
-      </c>
-      <c r="V1" s="2" t="s">
+      <c r="W1" s="2" t="s">
         <v>285</v>
       </c>
-      <c r="W1" s="2" t="s">
+      <c r="X1" s="2" t="s">
         <v>286</v>
       </c>
-      <c r="X1" s="2" t="s">
+      <c r="Y1" s="2" t="s">
         <v>287</v>
       </c>
-      <c r="Y1" s="2" t="s">
+      <c r="Z1" s="2" t="s">
         <v>288</v>
       </c>
-      <c r="Z1" s="2" t="s">
+      <c r="AA1" s="2" t="s">
         <v>289</v>
       </c>
-      <c r="AA1" s="2" t="s">
+      <c r="AB1" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="AB1" s="2" t="s">
+      <c r="AC1" s="2" t="s">
         <v>291</v>
       </c>
-      <c r="AC1" s="2" t="s">
+      <c r="AD1" s="2" t="s">
         <v>292</v>
       </c>
-      <c r="AD1" s="2" t="s">
+      <c r="AE1" s="2" t="s">
         <v>293</v>
       </c>
-      <c r="AE1" s="2" t="s">
+      <c r="AF1" s="2" t="s">
         <v>294</v>
       </c>
-      <c r="AF1" s="2" t="s">
+      <c r="AG1" s="2" t="s">
         <v>295</v>
       </c>
-      <c r="AG1" s="2" t="s">
+      <c r="AH1" s="2" t="s">
         <v>296</v>
       </c>
-      <c r="AH1" s="2" t="s">
+      <c r="AI1" s="2" t="s">
         <v>297</v>
       </c>
-      <c r="AI1" s="2" t="s">
+      <c r="AJ1" s="2" t="s">
         <v>298</v>
       </c>
-      <c r="AJ1" s="2" t="s">
+      <c r="AK1" s="2" t="s">
         <v>299</v>
       </c>
-      <c r="AK1" s="2" t="s">
+      <c r="AL1" s="2" t="s">
         <v>300</v>
       </c>
-      <c r="AL1" s="2" t="s">
+      <c r="AM1" s="2" t="s">
         <v>301</v>
       </c>
-      <c r="AM1" s="2" t="s">
+      <c r="AN1" s="2" t="s">
         <v>302</v>
       </c>
-      <c r="AN1" s="2" t="s">
+      <c r="AO1" s="2" t="s">
         <v>303</v>
       </c>
-      <c r="AO1" s="2" t="s">
+      <c r="AP1" s="2" t="s">
         <v>304</v>
       </c>
-      <c r="AP1" s="2" t="s">
+      <c r="AQ1" s="2" t="s">
         <v>305</v>
       </c>
-      <c r="AQ1" s="2" t="s">
+      <c r="AR1" s="2" t="s">
         <v>306</v>
       </c>
-      <c r="AR1" s="2" t="s">
+      <c r="AS1" s="2" t="s">
         <v>307</v>
       </c>
-      <c r="AS1" s="2" t="s">
+      <c r="AT1" s="2" t="s">
         <v>308</v>
       </c>
-      <c r="AT1" s="2" t="s">
+      <c r="AU1" s="2" t="s">
         <v>309</v>
       </c>
-      <c r="AU1" s="2" t="s">
+      <c r="AV1" s="2" t="s">
         <v>310</v>
       </c>
-      <c r="AV1" s="2" t="s">
+      <c r="AW1" s="2" t="s">
         <v>311</v>
       </c>
-      <c r="AW1" s="2" t="s">
+      <c r="AX1" s="2" t="s">
         <v>312</v>
       </c>
-      <c r="AX1" s="2" t="s">
+      <c r="AY1" s="2" t="s">
         <v>313</v>
       </c>
-      <c r="AY1" s="2" t="s">
+      <c r="AZ1" s="2" t="s">
         <v>314</v>
       </c>
-      <c r="AZ1" s="2" t="s">
+      <c r="BA1" s="2" t="s">
         <v>315</v>
       </c>
-      <c r="BA1" s="2" t="s">
+      <c r="BB1" s="2" t="s">
         <v>316</v>
       </c>
-      <c r="BB1" s="2" t="s">
+      <c r="BC1" s="2" t="s">
         <v>317</v>
       </c>
-      <c r="BC1" s="2" t="s">
+      <c r="BD1" s="2" t="s">
         <v>318</v>
       </c>
-      <c r="BD1" s="2" t="s">
+      <c r="BE1" s="2" t="s">
         <v>319</v>
       </c>
-      <c r="BE1" s="2" t="s">
+      <c r="BF1" s="2" t="s">
         <v>320</v>
       </c>
-      <c r="BF1" s="2" t="s">
+      <c r="BG1" s="2" t="s">
         <v>321</v>
       </c>
-      <c r="BG1" s="2" t="s">
+      <c r="BH1" s="2" t="s">
         <v>322</v>
       </c>
-      <c r="BH1" s="2" t="s">
+      <c r="BJ1" s="2" t="s">
+        <v>322</v>
+      </c>
+      <c r="BK1" s="2" t="s">
         <v>323</v>
       </c>
-      <c r="BJ1" s="2" t="s">
-        <v>323</v>
-      </c>
-      <c r="BK1" s="2" t="s">
+      <c r="BL1" s="2" t="s">
         <v>324</v>
       </c>
-      <c r="BL1" s="2" t="s">
+      <c r="BM1" s="2" t="s">
         <v>325</v>
       </c>
-      <c r="BM1" s="2" t="s">
+      <c r="BN1" s="2" t="s">
         <v>326</v>
       </c>
-      <c r="BN1" s="2" t="s">
+      <c r="BO1" s="2" t="s">
         <v>327</v>
       </c>
-      <c r="BO1" s="2" t="s">
+      <c r="BP1" s="2" t="s">
         <v>328</v>
       </c>
-      <c r="BP1" s="2" t="s">
+      <c r="BQ1" s="2" t="s">
         <v>329</v>
       </c>
-      <c r="BQ1" s="2" t="s">
+      <c r="BR1" s="2" t="s">
         <v>330</v>
       </c>
-      <c r="BR1" s="2" t="s">
+      <c r="BS1" s="2" t="s">
         <v>331</v>
       </c>
-      <c r="BS1" s="2" t="s">
+      <c r="BT1" s="2" t="s">
         <v>332</v>
       </c>
-      <c r="BT1" s="2" t="s">
+      <c r="BU1" s="2" t="s">
         <v>333</v>
       </c>
-      <c r="BU1" s="2" t="s">
+      <c r="BV1" s="2" t="s">
         <v>334</v>
       </c>
-      <c r="BV1" s="2" t="s">
+      <c r="BW1" s="2" t="s">
         <v>335</v>
       </c>
-      <c r="BW1" s="2" t="s">
+      <c r="BX1" s="2" t="s">
         <v>336</v>
       </c>
-      <c r="BX1" s="2" t="s">
+      <c r="BY1" s="2" t="s">
         <v>337</v>
       </c>
-      <c r="BY1" s="2" t="s">
+      <c r="BZ1" s="2" t="s">
         <v>338</v>
       </c>
-      <c r="BZ1" s="2" t="s">
+      <c r="CA1" s="2" t="s">
         <v>339</v>
       </c>
-      <c r="CA1" s="2" t="s">
+      <c r="CB1" s="2" t="s">
         <v>340</v>
       </c>
-      <c r="CB1" s="2" t="s">
+      <c r="CC1" s="2" t="s">
         <v>341</v>
       </c>
-      <c r="CC1" s="2" t="s">
+      <c r="CD1" s="2" t="s">
         <v>342</v>
       </c>
-      <c r="CD1" s="2" t="s">
+      <c r="CE1" s="2" t="s">
         <v>343</v>
       </c>
-      <c r="CE1" s="2" t="s">
+      <c r="CF1" s="2" t="s">
         <v>344</v>
       </c>
-      <c r="CF1" s="2" t="s">
+      <c r="CG1" s="2" t="s">
         <v>345</v>
       </c>
-      <c r="CG1" s="2" t="s">
+      <c r="CH1" s="2" t="s">
         <v>346</v>
       </c>
-      <c r="CH1" s="2" t="s">
+      <c r="CI1" s="2" t="s">
         <v>347</v>
       </c>
-      <c r="CI1" s="2" t="s">
+      <c r="CJ1" s="2" t="s">
         <v>348</v>
       </c>
-      <c r="CJ1" s="2" t="s">
+      <c r="CK1" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="CK1" s="2" t="s">
+      <c r="CL1" s="2" t="s">
         <v>350</v>
       </c>
-      <c r="CL1" s="2" t="s">
+      <c r="CM1" s="2" t="s">
         <v>351</v>
       </c>
-      <c r="CM1" s="2" t="s">
+      <c r="CN1" s="2" t="s">
         <v>352</v>
       </c>
-      <c r="CN1" s="2" t="s">
+      <c r="CO1" s="2" t="s">
         <v>353</v>
       </c>
-      <c r="CO1" s="2" t="s">
+      <c r="CP1" s="2" t="s">
         <v>354</v>
       </c>
-      <c r="CP1" s="2" t="s">
+      <c r="CQ1" s="2" t="s">
         <v>355</v>
       </c>
-      <c r="CQ1" s="2" t="s">
+      <c r="CR1" s="2" t="s">
+        <v>332</v>
+      </c>
+      <c r="CS1" s="2" t="s">
         <v>356</v>
       </c>
-      <c r="CR1" s="2" t="s">
-        <v>333</v>
-      </c>
-      <c r="CS1" s="2" t="s">
+      <c r="CT1" s="2" t="s">
         <v>357</v>
       </c>
-      <c r="CT1" s="2" t="s">
+      <c r="CU1" s="2" t="s">
         <v>358</v>
       </c>
-      <c r="CU1" s="2" t="s">
+      <c r="CV1" s="2" t="s">
         <v>359</v>
       </c>
-      <c r="CV1" s="2" t="s">
+      <c r="CW1" s="2" t="s">
         <v>360</v>
       </c>
-      <c r="CW1" s="2" t="s">
+      <c r="CX1" s="2" t="s">
         <v>361</v>
       </c>
-      <c r="CX1" s="2" t="s">
+      <c r="CY1" s="2" t="s">
         <v>362</v>
       </c>
-      <c r="CY1" s="2" t="s">
+      <c r="CZ1" s="2" t="s">
+        <v>361</v>
+      </c>
+      <c r="DA1" s="2" t="s">
         <v>363</v>
       </c>
-      <c r="CZ1" s="2" t="s">
-        <v>362</v>
-      </c>
-      <c r="DA1" s="2" t="s">
+      <c r="DB1" s="2" t="s">
         <v>364</v>
       </c>
-      <c r="DB1" s="2" t="s">
+      <c r="DC1" s="2" t="s">
         <v>365</v>
       </c>
-      <c r="DC1" s="2" t="s">
+      <c r="DD1" s="2" t="s">
         <v>366</v>
       </c>
-      <c r="DD1" s="2" t="s">
+      <c r="DE1" s="2" t="s">
         <v>367</v>
       </c>
-      <c r="DE1" s="2" t="s">
+      <c r="DF1" s="2" t="s">
         <v>368</v>
       </c>
-      <c r="DF1" s="2" t="s">
+      <c r="DG1" s="2" t="s">
         <v>369</v>
       </c>
-      <c r="DG1" s="2" t="s">
+      <c r="DH1" s="2" t="s">
         <v>370</v>
       </c>
-      <c r="DH1" s="2" t="s">
+      <c r="DI1" s="2" t="s">
         <v>371</v>
-      </c>
-      <c r="DI1" s="2" t="s">
-        <v>372</v>
       </c>
     </row>
     <row r="2" spans="1:113" x14ac:dyDescent="0.25">
@@ -6226,337 +6404,337 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>372</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>373</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>374</v>
       </c>
-      <c r="G2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>375</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>376</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>377</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>378</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>379</v>
       </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>380</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>381</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>382</v>
       </c>
-      <c r="P2" s="2" t="s">
+      <c r="Q2" s="2" t="s">
         <v>383</v>
       </c>
-      <c r="Q2" s="2" t="s">
+      <c r="R2" s="2" t="s">
         <v>384</v>
       </c>
-      <c r="R2" s="2" t="s">
+      <c r="S2" s="2" t="s">
         <v>385</v>
       </c>
-      <c r="S2" s="2" t="s">
+      <c r="T2" s="2" t="s">
         <v>386</v>
       </c>
-      <c r="T2" s="2" t="s">
+      <c r="U2" s="2" t="s">
         <v>387</v>
       </c>
-      <c r="U2" s="2" t="s">
+      <c r="V2" s="2" t="s">
         <v>388</v>
       </c>
-      <c r="V2" s="2" t="s">
+      <c r="W2" s="2" t="s">
         <v>389</v>
       </c>
-      <c r="W2" s="2" t="s">
+      <c r="X2" s="2" t="s">
         <v>390</v>
       </c>
-      <c r="X2" s="2" t="s">
+      <c r="Y2" s="2" t="s">
         <v>391</v>
       </c>
-      <c r="Y2" s="2" t="s">
+      <c r="Z2" s="2" t="s">
         <v>392</v>
       </c>
-      <c r="Z2" s="2" t="s">
+      <c r="AA2" s="2" t="s">
         <v>393</v>
       </c>
-      <c r="AA2" s="2" t="s">
+      <c r="AB2" s="2" t="s">
         <v>394</v>
       </c>
-      <c r="AB2" s="2" t="s">
+      <c r="AC2" s="2" t="s">
         <v>395</v>
       </c>
-      <c r="AC2" s="2" t="s">
+      <c r="AD2" s="2" t="s">
         <v>396</v>
       </c>
-      <c r="AD2" s="2" t="s">
+      <c r="AE2" s="2" t="s">
         <v>397</v>
       </c>
-      <c r="AE2" s="2" t="s">
+      <c r="AF2" s="2" t="s">
         <v>398</v>
       </c>
-      <c r="AF2" s="2" t="s">
+      <c r="AG2" s="2" t="s">
         <v>399</v>
       </c>
-      <c r="AG2" s="2" t="s">
+      <c r="AH2" s="2" t="s">
         <v>400</v>
       </c>
-      <c r="AH2" s="2" t="s">
+      <c r="AI2" s="2" t="s">
         <v>401</v>
       </c>
-      <c r="AI2" s="2" t="s">
+      <c r="AJ2" s="2" t="s">
         <v>402</v>
       </c>
-      <c r="AJ2" s="2" t="s">
+      <c r="AK2" s="2" t="s">
         <v>403</v>
       </c>
-      <c r="AK2" s="2" t="s">
+      <c r="AL2" s="2" t="s">
         <v>404</v>
       </c>
-      <c r="AL2" s="2" t="s">
+      <c r="AM2" s="2" t="s">
         <v>405</v>
       </c>
-      <c r="AM2" s="2" t="s">
+      <c r="AN2" s="2" t="s">
         <v>406</v>
       </c>
-      <c r="AN2" s="2" t="s">
+      <c r="AO2" s="2" t="s">
         <v>407</v>
       </c>
-      <c r="AO2" s="2" t="s">
+      <c r="AP2" s="2" t="s">
         <v>408</v>
       </c>
-      <c r="AP2" s="2" t="s">
+      <c r="AQ2" s="2" t="s">
         <v>409</v>
       </c>
-      <c r="AQ2" s="2" t="s">
+      <c r="AR2" s="2" t="s">
         <v>410</v>
       </c>
-      <c r="AR2" s="2" t="s">
+      <c r="AS2" s="2" t="s">
         <v>411</v>
       </c>
-      <c r="AS2" s="2" t="s">
+      <c r="AT2" s="2" t="s">
         <v>412</v>
       </c>
-      <c r="AT2" s="2" t="s">
+      <c r="AU2" s="2" t="s">
         <v>413</v>
       </c>
-      <c r="AU2" s="2" t="s">
+      <c r="AV2" s="2" t="s">
         <v>414</v>
       </c>
-      <c r="AV2" s="2" t="s">
+      <c r="AW2" s="2" t="s">
         <v>415</v>
       </c>
-      <c r="AW2" s="2" t="s">
+      <c r="AX2" s="2" t="s">
         <v>416</v>
       </c>
-      <c r="AX2" s="2" t="s">
+      <c r="AY2" s="2" t="s">
         <v>417</v>
       </c>
-      <c r="AY2" s="2" t="s">
+      <c r="AZ2" s="2" t="s">
         <v>418</v>
       </c>
-      <c r="AZ2" s="2" t="s">
+      <c r="BA2" s="2" t="s">
         <v>419</v>
       </c>
-      <c r="BA2" s="2" t="s">
+      <c r="BB2" s="2" t="s">
         <v>420</v>
       </c>
-      <c r="BB2" s="2" t="s">
+      <c r="BC2" s="2" t="s">
         <v>421</v>
       </c>
-      <c r="BC2" s="2" t="s">
+      <c r="BD2" s="2" t="s">
         <v>422</v>
       </c>
-      <c r="BD2" s="2" t="s">
+      <c r="BE2" s="2" t="s">
         <v>423</v>
       </c>
-      <c r="BE2" s="2" t="s">
+      <c r="BF2" s="2" t="s">
         <v>424</v>
       </c>
-      <c r="BF2" s="2" t="s">
+      <c r="BG2" s="2" t="s">
         <v>425</v>
       </c>
-      <c r="BG2" s="2" t="s">
+      <c r="BH2" s="2" t="s">
         <v>426</v>
       </c>
-      <c r="BH2" s="2" t="s">
+      <c r="BI2" s="2" t="s">
         <v>427</v>
       </c>
-      <c r="BI2" s="2" t="s">
+      <c r="BJ2" s="2" t="s">
         <v>428</v>
       </c>
-      <c r="BJ2" s="2" t="s">
+      <c r="BK2" s="2" t="s">
         <v>429</v>
       </c>
-      <c r="BK2" s="2" t="s">
+      <c r="BL2" s="2" t="s">
         <v>430</v>
       </c>
-      <c r="BL2" s="2" t="s">
+      <c r="BM2" s="2" t="s">
         <v>431</v>
       </c>
-      <c r="BM2" s="2" t="s">
+      <c r="BN2" s="2" t="s">
         <v>432</v>
       </c>
-      <c r="BN2" s="2" t="s">
+      <c r="BO2" s="2" t="s">
+        <v>97</v>
+      </c>
+      <c r="BP2" s="2" t="s">
         <v>433</v>
       </c>
-      <c r="BO2" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="BP2" s="2" t="s">
+      <c r="BQ2" s="2" t="s">
         <v>434</v>
       </c>
-      <c r="BQ2" s="2" t="s">
+      <c r="BR2" s="2" t="s">
         <v>435</v>
       </c>
-      <c r="BR2" s="2" t="s">
+      <c r="BS2" s="2" t="s">
         <v>436</v>
       </c>
-      <c r="BS2" s="2" t="s">
+      <c r="BT2" s="2" t="s">
         <v>437</v>
       </c>
-      <c r="BT2" s="2" t="s">
+      <c r="BU2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="BV2" s="2" t="s">
         <v>438</v>
       </c>
-      <c r="BU2" s="2" t="s">
-        <v>113</v>
-      </c>
-      <c r="BV2" s="2" t="s">
+      <c r="BW2" s="2" t="s">
         <v>439</v>
       </c>
-      <c r="BW2" s="2" t="s">
+      <c r="BX2" s="2" t="s">
         <v>440</v>
       </c>
-      <c r="BX2" s="2" t="s">
+      <c r="BY2" s="2" t="s">
         <v>441</v>
       </c>
-      <c r="BY2" s="2" t="s">
+      <c r="BZ2" s="2" t="s">
         <v>442</v>
       </c>
-      <c r="BZ2" s="2" t="s">
+      <c r="CA2" s="2" t="s">
         <v>443</v>
       </c>
-      <c r="CA2" s="2" t="s">
+      <c r="CB2" s="2" t="s">
         <v>444</v>
       </c>
-      <c r="CB2" s="2" t="s">
+      <c r="CC2" s="2" t="s">
         <v>445</v>
       </c>
-      <c r="CC2" s="2" t="s">
+      <c r="CD2" s="2" t="s">
         <v>446</v>
       </c>
-      <c r="CD2" s="2" t="s">
+      <c r="CE2" s="2" t="s">
         <v>447</v>
       </c>
-      <c r="CE2" s="2" t="s">
+      <c r="CF2" s="2" t="s">
         <v>448</v>
       </c>
-      <c r="CF2" s="2" t="s">
+      <c r="CG2" s="2" t="s">
         <v>449</v>
       </c>
-      <c r="CG2" s="2" t="s">
+      <c r="CH2" s="2" t="s">
         <v>450</v>
       </c>
-      <c r="CH2" s="2" t="s">
+      <c r="CI2" s="2" t="s">
         <v>451</v>
       </c>
-      <c r="CI2" s="2" t="s">
+      <c r="CJ2" s="2" t="s">
         <v>452</v>
       </c>
-      <c r="CJ2" s="2" t="s">
+      <c r="CK2" s="2" t="s">
         <v>453</v>
       </c>
-      <c r="CK2" s="2" t="s">
+      <c r="CL2" s="2" t="s">
         <v>454</v>
       </c>
-      <c r="CL2" s="2" t="s">
+      <c r="CM2" s="2" t="s">
         <v>455</v>
       </c>
-      <c r="CM2" s="2" t="s">
+      <c r="CN2" s="2" t="s">
         <v>456</v>
       </c>
-      <c r="CN2" s="2" t="s">
+      <c r="CO2" s="2" t="s">
         <v>457</v>
       </c>
-      <c r="CO2" s="2" t="s">
+      <c r="CP2" s="2" t="s">
         <v>458</v>
       </c>
-      <c r="CP2" s="2" t="s">
+      <c r="CQ2" s="2" t="s">
         <v>459</v>
       </c>
-      <c r="CQ2" s="2" t="s">
+      <c r="CR2" s="2" t="s">
         <v>460</v>
       </c>
-      <c r="CR2" s="2" t="s">
+      <c r="CS2" s="2" t="s">
         <v>461</v>
       </c>
-      <c r="CS2" s="2" t="s">
+      <c r="CT2" s="2" t="s">
         <v>462</v>
       </c>
-      <c r="CT2" s="2" t="s">
+      <c r="CU2" s="2" t="s">
         <v>463</v>
       </c>
-      <c r="CU2" s="2" t="s">
+      <c r="CV2" s="2" t="s">
         <v>464</v>
       </c>
-      <c r="CV2" s="2" t="s">
+      <c r="CW2" s="2" t="s">
         <v>465</v>
       </c>
-      <c r="CW2" s="2" t="s">
+      <c r="CX2" s="2" t="s">
         <v>466</v>
       </c>
-      <c r="CX2" s="2" t="s">
+      <c r="CY2" s="2" t="s">
         <v>467</v>
       </c>
-      <c r="CY2" s="2" t="s">
+      <c r="CZ2" s="2" t="s">
         <v>468</v>
       </c>
-      <c r="CZ2" s="2" t="s">
+      <c r="DA2" s="2" t="s">
         <v>469</v>
       </c>
-      <c r="DA2" s="2" t="s">
+      <c r="DB2" s="2" t="s">
         <v>470</v>
       </c>
-      <c r="DB2" s="2" t="s">
+      <c r="DC2" s="2" t="s">
         <v>471</v>
       </c>
-      <c r="DC2" s="2" t="s">
+      <c r="DD2" s="2" t="s">
         <v>472</v>
       </c>
-      <c r="DD2" s="2" t="s">
+      <c r="DE2" s="2" t="s">
         <v>473</v>
       </c>
-      <c r="DE2" s="2" t="s">
+      <c r="DF2" s="2" t="s">
         <v>474</v>
       </c>
-      <c r="DF2" s="2" t="s">
+      <c r="DG2" s="2" t="s">
         <v>475</v>
       </c>
-      <c r="DG2" s="2" t="s">
+      <c r="DH2" s="2" t="s">
         <v>476</v>
       </c>
-      <c r="DH2" s="2" t="s">
+      <c r="DI2" s="2" t="s">
         <v>477</v>
-      </c>
-      <c r="DI2" s="2" t="s">
-        <v>478</v>
       </c>
     </row>
     <row r="3" spans="1:113" x14ac:dyDescent="0.25">
@@ -6576,344 +6754,344 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="I3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>478</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>479</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>480</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="T3" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="J3" s="2" t="s">
-        <v>479</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>480</v>
-      </c>
-      <c r="L3" s="2" t="s">
+      <c r="U3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AE3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AF3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AG3" s="2" t="s">
         <v>481</v>
       </c>
-      <c r="M3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>482</v>
-      </c>
       <c r="AH3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AI3" s="2" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="AJ3" s="2" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="AP3" s="2" t="s">
+        <v>483</v>
+      </c>
+      <c r="AQ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="AU3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AV3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AX3" s="2" t="s">
+        <v>485</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BA3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BM3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BN3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="BO3" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AL3" s="2" t="s">
+      <c r="BP3" s="2" t="s">
         <v>136</v>
       </c>
-      <c r="AM3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="AN3" s="2" t="s">
+      <c r="BQ3" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>487</v>
+      </c>
+      <c r="BS3" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AO3" s="2" t="s">
-        <v>483</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>484</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="AU3" s="2" t="s">
+      <c r="BT3" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="AV3" s="2" t="s">
+      <c r="BU3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="BX3" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="AW3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AX3" s="2" t="s">
-        <v>486</v>
-      </c>
-      <c r="AY3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BA3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BB3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>485</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BK3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BO3" s="2" t="s">
+      <c r="BY3" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="BZ3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="CA3" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="CB3" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="BP3" s="2" t="s">
+      <c r="CC3" s="2" t="s">
+        <v>489</v>
+      </c>
+      <c r="CD3" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="BQ3" s="2" t="s">
-        <v>487</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>488</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BW3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="BX3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="BY3" s="2" t="s">
+      <c r="CE3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="CF3" s="2" t="s">
+        <v>137</v>
+      </c>
+      <c r="CG3" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="CH3" s="2" t="s">
+        <v>491</v>
+      </c>
+      <c r="CI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="CK3" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="CL3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CM3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CN3" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="CO3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CP3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CQ3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CR3" s="2" t="s">
         <v>489</v>
       </c>
-      <c r="BZ3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="CA3" s="2" t="s">
-        <v>489</v>
-      </c>
-      <c r="CB3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="CC3" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="CD3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="CE3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="CF3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="CG3" s="2" t="s">
-        <v>491</v>
-      </c>
-      <c r="CH3" s="2" t="s">
-        <v>492</v>
-      </c>
-      <c r="CI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="2" t="s">
+      <c r="CS3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="CT3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="CU3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="CV3" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="CK3" s="2" t="s">
+      <c r="CW3" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="CX3" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="CY3" s="2" t="s">
         <v>493</v>
       </c>
-      <c r="CL3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="CM3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="CN3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="CO3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="CP3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="CQ3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="CR3" s="2" t="s">
-        <v>490</v>
-      </c>
-      <c r="CS3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="CT3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="CU3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="CV3" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="CW3" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="CX3" s="2" t="s">
-        <v>495</v>
-      </c>
-      <c r="CY3" s="2" t="s">
-        <v>494</v>
-      </c>
       <c r="CZ3" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="DA3" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="DB3" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="DC3" s="2" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="DD3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="DE3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="DF3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="DG3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="DH3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="DI3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="4" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
     </row>
     <row r="5" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>497</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="K5" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="K5" s="2" t="s">
+      <c r="L5" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="L5" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="AC5" s="2">
         <v>1</v>
@@ -6927,16 +7105,16 @@
     </row>
     <row r="6" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="K6" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="L6" s="2" t="s">
         <v>499</v>
-      </c>
-      <c r="L6" s="2" t="s">
-        <v>500</v>
       </c>
       <c r="AC6" s="2">
         <v>1</v>
@@ -6950,25 +7128,25 @@
     </row>
     <row r="8" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D8" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="E8" s="2" t="s">
         <v>502</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="F8" s="2" t="s">
         <v>503</v>
       </c>
-      <c r="F8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>504</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="K8" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="K8" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="W8" s="2">
         <v>1</v>
@@ -6995,36 +7173,36 @@
         <v>1</v>
       </c>
       <c r="BY8" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="CX8" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="CX8" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="9" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
+        <v>507</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D9" s="2" t="s">
         <v>508</v>
       </c>
-      <c r="C9" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D9" s="2" t="s">
+      <c r="E9" s="2" t="s">
         <v>509</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="F9" s="2" t="s">
         <v>510</v>
-      </c>
-      <c r="F9" s="2" t="s">
-        <v>511</v>
       </c>
       <c r="G9" s="2">
         <v>3</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="K9" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="W9" s="2">
         <v>1</v>
@@ -7051,173 +7229,173 @@
         <v>1</v>
       </c>
       <c r="BY9" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="CX9" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="CX9" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="11" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="C11" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC11" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO11" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="AC11" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO11" s="2" t="s">
+      <c r="AT11" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="AT11" s="2" t="s">
+      <c r="AX11" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="AX11" s="2" t="s">
+      <c r="AZ11" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD11" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB11" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG11" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="AZ11" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD11" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB11" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG11" s="2" t="s">
+      <c r="CY11" s="2" t="s">
         <v>516</v>
-      </c>
-      <c r="CY11" s="2" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="13" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="C13" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC13" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO13" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="AC13" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO13" s="2" t="s">
+      <c r="AT13" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="AT13" s="2" t="s">
+      <c r="AX13" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="AX13" s="2" t="s">
+      <c r="AZ13" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD13" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB13" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG13" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="AZ13" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD13" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB13" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG13" s="2" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="15" spans="1:113" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
       <c r="C15" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC15" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO15" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="AC15" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO15" s="2" t="s">
+      <c r="AT15" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="AT15" s="2" t="s">
+      <c r="AX15" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="AX15" s="2" t="s">
+      <c r="AZ15" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD15" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB15" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG15" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="AZ15" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD15" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB15" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG15" s="2" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="17" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
       <c r="C17" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC17" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO17" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="AC17" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO17" s="2" t="s">
+      <c r="AT17" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="AT17" s="2" t="s">
+      <c r="AX17" s="2" t="s">
         <v>514</v>
       </c>
-      <c r="AX17" s="2" t="s">
+      <c r="AZ17" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD17" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB17" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG17" s="2" t="s">
         <v>515</v>
-      </c>
-      <c r="AZ17" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD17" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB17" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG17" s="2" t="s">
-        <v>516</v>
       </c>
     </row>
     <row r="18" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="C18" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D18" s="2" t="s">
         <v>521</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="E18" s="2" t="s">
         <v>522</v>
       </c>
-      <c r="E18" s="2" t="s">
+      <c r="F18" s="2" t="s">
         <v>523</v>
       </c>
-      <c r="F18" s="2" t="s">
+      <c r="J18" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="K18" s="2" t="s">
         <v>524</v>
       </c>
-      <c r="J18" s="2" t="s">
-        <v>505</v>
-      </c>
-      <c r="K18" s="2" t="s">
+      <c r="AC18" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD18" s="2">
+        <v>1</v>
+      </c>
+      <c r="BP18" s="2" t="s">
         <v>525</v>
-      </c>
-      <c r="AC18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD18" s="2">
-        <v>1</v>
-      </c>
-      <c r="BP18" s="2" t="s">
-        <v>526</v>
       </c>
       <c r="BT18" s="2">
         <v>10</v>
@@ -7232,10 +7410,10 @@
         <v>1</v>
       </c>
       <c r="BY18" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CN18" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="CO18" s="2">
         <v>0.35</v>
@@ -7246,19 +7424,19 @@
     </row>
     <row r="19" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C19" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="K19" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="AC19" s="2">
         <v>1</v>
       </c>
       <c r="AG19" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BD19" s="2">
         <v>1</v>
@@ -7267,36 +7445,36 @@
         <v>6</v>
       </c>
       <c r="CX19" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="21" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
+        <v>528</v>
+      </c>
+      <c r="C21" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L21" s="2" t="s">
         <v>529</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>530</v>
-      </c>
       <c r="AC21" s="2">
         <v>1</v>
       </c>
       <c r="AG21" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="AH21" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD21" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN21" s="2" t="s">
         <v>528</v>
-      </c>
-      <c r="AH21" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD21" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN21" s="2" t="s">
-        <v>529</v>
       </c>
       <c r="CO21" s="2">
         <v>0.19</v>
@@ -7307,66 +7485,66 @@
     </row>
     <row r="22" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="C22" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC22" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO22" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT22" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX22" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ22" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD22" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB22" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG22" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="CW22" s="2" t="s">
         <v>531</v>
       </c>
-      <c r="C22" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="AC22" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO22" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="AT22" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="AX22" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="AZ22" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD22" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB22" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG22" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="CW22" s="2" t="s">
+      <c r="CY22" s="2" t="s">
         <v>532</v>
-      </c>
-      <c r="CY22" s="2" t="s">
-        <v>533</v>
       </c>
     </row>
     <row r="23" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
+        <v>533</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>534</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="D23" s="2" t="s">
         <v>535</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="E23" s="2" t="s">
         <v>536</v>
       </c>
-      <c r="E23" s="2" t="s">
+      <c r="F23" s="2" t="s">
         <v>537</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>538</v>
       </c>
       <c r="G23" s="2">
         <v>3</v>
       </c>
       <c r="J23" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K23" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC23" s="2">
         <v>1</v>
@@ -7378,7 +7556,7 @@
         <v>8</v>
       </c>
       <c r="BO23" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="BT23" s="2">
         <v>15</v>
@@ -7393,24 +7571,24 @@
         <v>1</v>
       </c>
       <c r="BY23" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CX23" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="24" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="C24" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="K24" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="L24" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AC24" s="2">
         <v>1</v>
@@ -7422,7 +7600,7 @@
         <v>3</v>
       </c>
       <c r="CN24" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="CO24" s="2">
         <v>0.8</v>
@@ -7433,37 +7611,37 @@
     </row>
     <row r="26" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="K26" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L26" s="2" t="s">
         <v>544</v>
       </c>
-      <c r="C26" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L26" s="2" t="s">
+      <c r="AC26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF26" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG26" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="AH26" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD26" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN26" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="CO26" s="2" t="s">
         <v>545</v>
-      </c>
-      <c r="AC26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF26" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG26" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="AH26" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD26" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN26" s="2" t="s">
-        <v>544</v>
-      </c>
-      <c r="CO26" s="2" t="s">
-        <v>546</v>
       </c>
       <c r="CR26" s="2">
         <v>99999</v>
@@ -7474,66 +7652,66 @@
     </row>
     <row r="27" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
+        <v>546</v>
+      </c>
+      <c r="C27" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC27" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO27" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT27" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX27" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ27" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD27" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB27" s="2" t="s">
         <v>547</v>
       </c>
-      <c r="C27" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="AC27" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO27" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="AT27" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="AX27" s="2" t="s">
+      <c r="CG27" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="AZ27" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD27" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB27" s="2" t="s">
+      <c r="CW27" s="2" t="s">
         <v>548</v>
       </c>
-      <c r="CG27" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="CW27" s="2" t="s">
+      <c r="CY27" s="2" t="s">
         <v>549</v>
-      </c>
-      <c r="CY27" s="2" t="s">
-        <v>550</v>
       </c>
     </row>
     <row r="28" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
+        <v>550</v>
+      </c>
+      <c r="C28" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D28" s="2" t="s">
         <v>551</v>
       </c>
-      <c r="C28" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D28" s="2" t="s">
+      <c r="E28" s="2" t="s">
         <v>552</v>
       </c>
-      <c r="E28" s="2" t="s">
+      <c r="F28" s="2" t="s">
         <v>553</v>
-      </c>
-      <c r="F28" s="2" t="s">
-        <v>554</v>
       </c>
       <c r="G28" s="2">
         <v>3</v>
       </c>
       <c r="J28" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K28" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC28" s="2">
         <v>1</v>
@@ -7542,7 +7720,7 @@
         <v>1</v>
       </c>
       <c r="BP28" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="BT28" s="2">
         <v>15</v>
@@ -7557,10 +7735,10 @@
         <v>1</v>
       </c>
       <c r="BY28" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CN28" s="2" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="CO28" s="2">
         <v>0.7</v>
@@ -7571,89 +7749,89 @@
     </row>
     <row r="29" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="C29" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="K29" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="K29" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="L29" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="BN29" s="2">
         <v>11</v>
       </c>
       <c r="CX29" s="2" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
     </row>
     <row r="31" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="C31" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC31" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO31" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT31" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX31" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ31" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD31" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB31" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG31" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="CJ31" s="2" t="s">
         <v>556</v>
       </c>
-      <c r="C31" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="AC31" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO31" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="AT31" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="AX31" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="AZ31" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD31" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB31" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG31" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="CJ31" s="2" t="s">
+      <c r="CW31" s="2" t="s">
         <v>557</v>
       </c>
-      <c r="CW31" s="2" t="s">
+      <c r="CY31" s="2" t="s">
         <v>558</v>
-      </c>
-      <c r="CY31" s="2" t="s">
-        <v>559</v>
       </c>
     </row>
     <row r="32" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
+        <v>559</v>
+      </c>
+      <c r="C32" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D32" s="2" t="s">
         <v>560</v>
       </c>
-      <c r="C32" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D32" s="2" t="s">
+      <c r="E32" s="2" t="s">
         <v>561</v>
       </c>
-      <c r="E32" s="2" t="s">
+      <c r="F32" s="2" t="s">
         <v>562</v>
-      </c>
-      <c r="F32" s="2" t="s">
-        <v>563</v>
       </c>
       <c r="G32" s="2">
         <v>3</v>
       </c>
       <c r="J32" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K32" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC32" s="2">
         <v>1</v>
@@ -7674,16 +7852,16 @@
         <v>1</v>
       </c>
       <c r="BY32" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CJ32" s="2" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="CN32" s="2" t="s">
+        <v>563</v>
+      </c>
+      <c r="CO32" s="2" t="s">
         <v>564</v>
-      </c>
-      <c r="CO32" s="2" t="s">
-        <v>565</v>
       </c>
       <c r="CR32" s="2">
         <v>30</v>
@@ -7691,69 +7869,69 @@
     </row>
     <row r="34" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC34" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO34" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT34" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX34" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ34" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD34" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB34" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG34" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="CW34" s="2" t="s">
         <v>566</v>
       </c>
-      <c r="C34" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="AC34" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO34" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="AT34" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="AX34" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="AZ34" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD34" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB34" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG34" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="CW34" s="2" t="s">
+      <c r="CY34" s="2" t="s">
         <v>567</v>
-      </c>
-      <c r="CY34" s="2" t="s">
-        <v>568</v>
       </c>
     </row>
     <row r="35" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
+        <v>568</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="K35" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="AC35" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF35" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH35" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI35" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="CN35" s="2" t="s">
         <v>569</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="K35" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L35" s="2" t="s">
-        <v>530</v>
-      </c>
-      <c r="AC35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH35" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI35" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="CN35" s="2" t="s">
-        <v>570</v>
       </c>
       <c r="CO35" s="2">
         <v>-1</v>
@@ -7761,28 +7939,28 @@
     </row>
     <row r="36" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
+        <v>570</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D36" s="2" t="s">
         <v>571</v>
       </c>
-      <c r="C36" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D36" s="2" t="s">
+      <c r="E36" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E36" s="2" t="s">
+      <c r="F36" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="F36" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="G36" s="2">
         <v>3</v>
       </c>
       <c r="J36" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="K36" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="K36" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="W36" s="2">
         <v>1</v>
@@ -7809,36 +7987,36 @@
         <v>1</v>
       </c>
       <c r="BY36" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="CX36" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="CX36" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="37" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
+        <v>574</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D37" s="2" t="s">
         <v>575</v>
       </c>
-      <c r="C37" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D37" s="2" t="s">
+      <c r="E37" s="2" t="s">
         <v>576</v>
       </c>
-      <c r="E37" s="2" t="s">
+      <c r="F37" s="2" t="s">
         <v>577</v>
-      </c>
-      <c r="F37" s="2" t="s">
-        <v>578</v>
       </c>
       <c r="G37" s="2">
         <v>3</v>
       </c>
       <c r="J37" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K37" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC37" s="2">
         <v>1</v>
@@ -7850,7 +8028,7 @@
         <v>9</v>
       </c>
       <c r="BO37" s="2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="BT37" s="2">
         <v>10</v>
@@ -7865,24 +8043,24 @@
         <v>1</v>
       </c>
       <c r="BY37" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CX37" s="2" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
     </row>
     <row r="38" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="K38" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L38" s="2" t="s">
         <v>580</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>576</v>
-      </c>
-      <c r="K38" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L38" s="2" t="s">
-        <v>581</v>
       </c>
       <c r="AC38" s="2">
         <v>1</v>
@@ -7896,22 +8074,22 @@
     </row>
     <row r="39" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="C39" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K39" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L39" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AC39" s="2">
         <v>1</v>
       </c>
       <c r="AI39" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AV39" s="2">
         <v>99</v>
@@ -7920,10 +8098,10 @@
         <v>99</v>
       </c>
       <c r="CN39" s="2" t="s">
+        <v>582</v>
+      </c>
+      <c r="CO39" s="2" t="s">
         <v>583</v>
-      </c>
-      <c r="CO39" s="2" t="s">
-        <v>584</v>
       </c>
       <c r="CR39" s="2">
         <v>10</v>
@@ -7934,58 +8112,58 @@
     </row>
     <row r="41" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
+        <v>584</v>
+      </c>
+      <c r="C41" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="K41" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="AC41" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO41" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT41" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX41" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ41" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD41" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB41" s="2" t="s">
         <v>585</v>
       </c>
-      <c r="C41" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="K41" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="AC41" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO41" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="AT41" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="AX41" s="2" t="s">
+      <c r="CG41" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="AZ41" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD41" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB41" s="2" t="s">
+      <c r="CW41" s="2" t="s">
         <v>586</v>
       </c>
-      <c r="CG41" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="CW41" s="2" t="s">
+      <c r="CY41" s="2" t="s">
         <v>587</v>
-      </c>
-      <c r="CY41" s="2" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="42" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="C42" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="K42" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L42" s="2" t="s">
         <v>589</v>
       </c>
-      <c r="C42" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="K42" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L42" s="2" t="s">
-        <v>590</v>
-      </c>
       <c r="X42" s="2">
         <v>1</v>
       </c>
@@ -7993,7 +8171,7 @@
         <v>1</v>
       </c>
       <c r="AG42" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="BD42" s="2">
         <v>1</v>
@@ -8004,16 +8182,16 @@
     </row>
     <row r="43" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="C43" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="K43" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="K43" s="2" t="s">
-        <v>499</v>
-      </c>
       <c r="L43" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AC43" s="2">
         <v>1</v>
@@ -8027,28 +8205,28 @@
     </row>
     <row r="44" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
+        <v>591</v>
+      </c>
+      <c r="C44" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D44" s="2" t="s">
         <v>592</v>
       </c>
-      <c r="C44" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D44" s="2" t="s">
+      <c r="E44" s="2" t="s">
         <v>593</v>
       </c>
-      <c r="E44" s="2" t="s">
+      <c r="F44" s="2" t="s">
         <v>594</v>
-      </c>
-      <c r="F44" s="2" t="s">
-        <v>595</v>
       </c>
       <c r="G44" s="2">
         <v>3</v>
       </c>
       <c r="J44" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K44" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="X44" s="2">
         <v>1</v>
@@ -8063,13 +8241,13 @@
         <v>2</v>
       </c>
       <c r="AO44" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AT44" s="2" t="s">
+        <v>595</v>
+      </c>
+      <c r="AX44" s="2" t="s">
         <v>596</v>
-      </c>
-      <c r="AX44" s="2" t="s">
-        <v>597</v>
       </c>
       <c r="AZ44" s="2">
         <v>1.7</v>
@@ -8084,7 +8262,7 @@
         <v>0.8</v>
       </c>
       <c r="BO44" s="2" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="BS44" s="2">
         <v>2.1669999999999998</v>
@@ -8102,95 +8280,95 @@
         <v>1</v>
       </c>
       <c r="BY44" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CB44" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="CC44" s="2">
         <v>0.5</v>
       </c>
       <c r="CG44" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="CN44" s="2" t="s">
         <v>598</v>
-      </c>
-      <c r="CN44" s="2" t="s">
-        <v>599</v>
       </c>
       <c r="CR44" s="2">
         <v>3</v>
       </c>
       <c r="CW44" s="2" t="s">
+        <v>599</v>
+      </c>
+      <c r="CY44" s="2" t="s">
         <v>600</v>
-      </c>
-      <c r="CY44" s="2" t="s">
-        <v>601</v>
       </c>
     </row>
     <row r="46" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
+        <v>601</v>
+      </c>
+      <c r="C46" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC46" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO46" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT46" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX46" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ46" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD46" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB46" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG46" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="CW46" s="2" t="s">
         <v>602</v>
-      </c>
-      <c r="C46" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="AC46" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO46" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="AT46" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="AX46" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="AZ46" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD46" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB46" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG46" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="CW46" s="2" t="s">
-        <v>603</v>
       </c>
     </row>
     <row r="47" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="C47" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="K47" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L47" s="2" t="s">
         <v>604</v>
       </c>
-      <c r="C47" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="K47" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L47" s="2" t="s">
-        <v>605</v>
-      </c>
       <c r="AC47" s="2">
         <v>1</v>
       </c>
       <c r="AI47" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="BD47" s="2">
         <v>99</v>
       </c>
       <c r="BO47" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="CN47" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="CO47" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="CN47" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="CO47" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="CR47" s="2">
         <v>99999</v>
@@ -8201,37 +8379,37 @@
     </row>
     <row r="48" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
+        <v>605</v>
+      </c>
+      <c r="C48" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="K48" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L48" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="AC48" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF48" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="2" t="s">
+        <v>607</v>
+      </c>
+      <c r="AI48" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BD48" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN48" s="2" t="s">
+        <v>603</v>
+      </c>
+      <c r="CO48" s="2" t="s">
         <v>606</v>
-      </c>
-      <c r="C48" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="K48" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L48" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="AC48" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF48" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG48" s="2" t="s">
-        <v>608</v>
-      </c>
-      <c r="AI48" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD48" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN48" s="2" t="s">
-        <v>604</v>
-      </c>
-      <c r="CO48" s="2" t="s">
-        <v>607</v>
       </c>
       <c r="CR48" s="2">
         <v>99999</v>
@@ -8242,54 +8420,54 @@
     </row>
     <row r="49" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
+        <v>608</v>
+      </c>
+      <c r="C49" s="2" t="s">
         <v>609</v>
       </c>
-      <c r="C49" s="2" t="s">
+      <c r="K49" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L49" s="2" t="s">
+        <v>580</v>
+      </c>
+      <c r="AC49" s="2">
+        <v>2</v>
+      </c>
+      <c r="AH49" s="2">
+        <v>1</v>
+      </c>
+      <c r="AT49" s="2" t="s">
         <v>610</v>
       </c>
-      <c r="K49" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L49" s="2" t="s">
-        <v>581</v>
-      </c>
-      <c r="AC49" s="2">
-        <v>2</v>
-      </c>
-      <c r="AH49" s="2">
-        <v>1</v>
-      </c>
-      <c r="AT49" s="2" t="s">
+      <c r="CU49" s="2" t="s">
         <v>611</v>
-      </c>
-      <c r="CU49" s="2" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="50" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="C50" s="2" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D50" s="2" t="s">
+        <v>571</v>
+      </c>
+      <c r="E50" s="2" t="s">
         <v>572</v>
       </c>
-      <c r="E50" s="2" t="s">
+      <c r="F50" s="2" t="s">
         <v>573</v>
-      </c>
-      <c r="F50" s="2" t="s">
-        <v>574</v>
       </c>
       <c r="G50" s="2">
         <v>3</v>
       </c>
       <c r="J50" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="K50" s="2" t="s">
         <v>505</v>
-      </c>
-      <c r="K50" s="2" t="s">
-        <v>506</v>
       </c>
       <c r="W50" s="2">
         <v>1</v>
@@ -8316,48 +8494,48 @@
         <v>1</v>
       </c>
       <c r="BY50" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="CX50" s="2" t="s">
         <v>506</v>
-      </c>
-      <c r="CX50" s="2" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="51" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
+        <v>613</v>
+      </c>
+      <c r="C51" s="2" t="s">
+        <v>497</v>
+      </c>
+      <c r="D51" s="2" t="s">
         <v>614</v>
       </c>
-      <c r="C51" s="2" t="s">
-        <v>498</v>
-      </c>
-      <c r="D51" s="2" t="s">
+      <c r="E51" s="2" t="s">
         <v>615</v>
       </c>
-      <c r="E51" s="2" t="s">
+      <c r="F51" s="2" t="s">
         <v>616</v>
-      </c>
-      <c r="F51" s="2" t="s">
-        <v>617</v>
       </c>
       <c r="G51" s="2">
         <v>3</v>
       </c>
       <c r="J51" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="K51" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="K51" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="AC51" s="2">
         <v>2</v>
       </c>
       <c r="AO51" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AT51" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AX51" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AZ51" s="2">
         <v>3.4</v>
@@ -8384,54 +8562,54 @@
         <v>3</v>
       </c>
       <c r="BY51" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CB51" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="CG51" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="CW51" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
     </row>
     <row r="52" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
+        <v>618</v>
+      </c>
+      <c r="C52" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D52" s="2" t="s">
         <v>619</v>
       </c>
-      <c r="C52" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D52" s="2" t="s">
+      <c r="E52" s="2" t="s">
         <v>620</v>
       </c>
-      <c r="E52" s="2" t="s">
+      <c r="F52" s="2" t="s">
         <v>621</v>
-      </c>
-      <c r="F52" s="2" t="s">
-        <v>622</v>
       </c>
       <c r="G52" s="2">
         <v>3</v>
       </c>
       <c r="J52" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K52" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC52" s="2">
         <v>2</v>
       </c>
       <c r="AO52" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT52" s="2" t="s">
         <v>513</v>
       </c>
-      <c r="AT52" s="2" t="s">
+      <c r="AX52" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="AX52" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="AZ52" s="2">
         <v>3.8</v>
@@ -8440,7 +8618,7 @@
         <v>1</v>
       </c>
       <c r="BO52" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="BT52" s="2">
         <v>25</v>
@@ -8458,19 +8636,19 @@
         <v>1</v>
       </c>
       <c r="BY52" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CA52" s="2" t="s">
+        <v>623</v>
+      </c>
+      <c r="CB52" s="2" t="s">
         <v>624</v>
       </c>
-      <c r="CB52" s="2" t="s">
-        <v>625</v>
-      </c>
       <c r="CG52" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="CN52" s="2" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="CR52" s="2">
         <v>1.5</v>
@@ -8479,24 +8657,24 @@
         <v>0.4</v>
       </c>
       <c r="CW52" s="2" t="s">
+        <v>625</v>
+      </c>
+      <c r="CX52" s="2" t="s">
         <v>626</v>
-      </c>
-      <c r="CX52" s="2" t="s">
-        <v>627</v>
       </c>
     </row>
     <row r="53" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C53" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K53" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L53" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AC53" s="2">
         <v>1</v>
@@ -8505,7 +8683,7 @@
         <v>1</v>
       </c>
       <c r="CN53" s="2" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="CO53" s="2">
         <v>1</v>
@@ -8519,60 +8697,60 @@
     </row>
     <row r="55" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
+        <v>628</v>
+      </c>
+      <c r="C55" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC55" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO55" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT55" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX55" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ55" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD55" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB55" s="2" t="s">
+        <v>73</v>
+      </c>
+      <c r="CG55" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="CX55" s="2" t="s">
         <v>629</v>
       </c>
-      <c r="C55" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="AC55" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO55" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="AT55" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="AX55" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="AZ55" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD55" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB55" s="2" t="s">
-        <v>74</v>
-      </c>
-      <c r="CG55" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="CX55" s="2" t="s">
+      <c r="CY55" s="2" t="s">
         <v>630</v>
-      </c>
-      <c r="CY55" s="2" t="s">
-        <v>631</v>
       </c>
     </row>
     <row r="56" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C56" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I56" s="2">
         <v>1</v>
       </c>
       <c r="K56" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AC56" s="2">
         <v>1</v>
       </c>
       <c r="AI56" s="2" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AV56" s="2">
         <v>99</v>
@@ -8598,34 +8776,34 @@
     </row>
     <row r="57" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
+        <v>632</v>
+      </c>
+      <c r="C57" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D57" s="2" t="s">
         <v>633</v>
       </c>
-      <c r="C57" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D57" s="2" t="s">
+      <c r="E57" s="2" t="s">
         <v>634</v>
       </c>
-      <c r="E57" s="2" t="s">
+      <c r="F57" s="2" t="s">
         <v>635</v>
-      </c>
-      <c r="F57" s="2" t="s">
-        <v>636</v>
       </c>
       <c r="G57" s="2">
         <v>3</v>
       </c>
       <c r="J57" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K57" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC57" s="2">
         <v>1</v>
       </c>
       <c r="AT57" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="BD57" s="2">
         <v>1</v>
@@ -8649,22 +8827,22 @@
         <v>1</v>
       </c>
       <c r="BY57" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CB57" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="CC57" s="2">
         <v>0</v>
       </c>
       <c r="CE57" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="CG57" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="CN57" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="CG57" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="CN57" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="CP57" s="2">
         <v>-1</v>
@@ -8678,34 +8856,34 @@
     </row>
     <row r="58" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C58" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="D58" s="2" t="s">
         <v>640</v>
       </c>
-      <c r="C58" s="2" t="s">
-        <v>535</v>
-      </c>
-      <c r="D58" s="2" t="s">
+      <c r="E58" s="2" t="s">
         <v>641</v>
       </c>
-      <c r="E58" s="2" t="s">
+      <c r="F58" s="2" t="s">
         <v>642</v>
-      </c>
-      <c r="F58" s="2" t="s">
-        <v>643</v>
       </c>
       <c r="G58" s="2">
         <v>3</v>
       </c>
       <c r="J58" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K58" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC58" s="2">
         <v>1</v>
       </c>
       <c r="AT58" s="2" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="BD58" s="2">
         <v>1</v>
@@ -8714,7 +8892,7 @@
         <v>16</v>
       </c>
       <c r="BO58" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="BS58" s="2">
         <v>0.01</v>
@@ -8732,22 +8910,22 @@
         <v>1</v>
       </c>
       <c r="BY58" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CB58" s="2" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="CC58" s="2">
         <v>0</v>
       </c>
       <c r="CE58" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="CG58" s="2" t="s">
+        <v>597</v>
+      </c>
+      <c r="CN58" s="2" t="s">
         <v>638</v>
-      </c>
-      <c r="CG58" s="2" t="s">
-        <v>598</v>
-      </c>
-      <c r="CN58" s="2" t="s">
-        <v>639</v>
       </c>
       <c r="CP58" s="2">
         <v>-1</v>
@@ -8759,21 +8937,21 @@
         <v>1</v>
       </c>
       <c r="DC58" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
     </row>
     <row r="59" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C59" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="J59" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K59" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AB59" s="2">
         <v>1</v>
@@ -8782,10 +8960,10 @@
         <v>1</v>
       </c>
       <c r="AO59" s="2" t="s">
+        <v>645</v>
+      </c>
+      <c r="AT59" s="2" t="s">
         <v>646</v>
-      </c>
-      <c r="AT59" s="2" t="s">
-        <v>647</v>
       </c>
       <c r="AY59" s="2">
         <v>1</v>
@@ -8802,92 +8980,92 @@
     </row>
     <row r="61" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
+        <v>647</v>
+      </c>
+      <c r="C61" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="AC61" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO61" s="2" t="s">
+        <v>512</v>
+      </c>
+      <c r="AT61" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX61" s="2" t="s">
+        <v>514</v>
+      </c>
+      <c r="AZ61" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD61" s="2">
+        <v>1</v>
+      </c>
+      <c r="CB61" s="2" t="s">
         <v>648</v>
       </c>
-      <c r="C61" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="AC61" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO61" s="2" t="s">
-        <v>513</v>
-      </c>
-      <c r="AT61" s="2" t="s">
-        <v>514</v>
-      </c>
-      <c r="AX61" s="2" t="s">
+      <c r="CG61" s="2" t="s">
         <v>515</v>
       </c>
-      <c r="AZ61" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD61" s="2">
-        <v>1</v>
-      </c>
-      <c r="CB61" s="2" t="s">
+      <c r="CJ61" s="2" t="s">
         <v>649</v>
-      </c>
-      <c r="CG61" s="2" t="s">
-        <v>516</v>
-      </c>
-      <c r="CJ61" s="2" t="s">
-        <v>650</v>
       </c>
     </row>
     <row r="62" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="C62" s="2" t="s">
         <v>650</v>
       </c>
-      <c r="C62" s="2" t="s">
+      <c r="K62" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L62" s="2" t="s">
+        <v>544</v>
+      </c>
+      <c r="AC62" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF62" s="2">
+        <v>1</v>
+      </c>
+      <c r="AH62" s="2">
+        <v>1</v>
+      </c>
+      <c r="AI62" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BD62" s="2">
+        <v>1</v>
+      </c>
+      <c r="CU62" s="2" t="s">
         <v>651</v>
-      </c>
-      <c r="K62" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L62" s="2" t="s">
-        <v>545</v>
-      </c>
-      <c r="AC62" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF62" s="2">
-        <v>1</v>
-      </c>
-      <c r="AH62" s="2">
-        <v>1</v>
-      </c>
-      <c r="AI62" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="BD62" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU62" s="2" t="s">
-        <v>652</v>
       </c>
     </row>
     <row r="63" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="C63" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="D63" s="2" t="s">
         <v>653</v>
       </c>
-      <c r="C63" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="D63" s="2" t="s">
+      <c r="E63" s="2" t="s">
         <v>654</v>
       </c>
-      <c r="E63" s="2" t="s">
+      <c r="F63" s="2" t="s">
         <v>655</v>
       </c>
-      <c r="F63" s="2" t="s">
-        <v>656</v>
-      </c>
       <c r="J63" s="2" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K63" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AC63" s="2">
         <v>1</v>
@@ -8908,13 +9086,13 @@
         <v>1</v>
       </c>
       <c r="BY63" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CN63" s="2" t="s">
+        <v>656</v>
+      </c>
+      <c r="CO63" s="2" t="s">
         <v>657</v>
-      </c>
-      <c r="CO63" s="2" t="s">
-        <v>658</v>
       </c>
       <c r="CR63" s="2">
         <v>35</v>
@@ -8922,34 +9100,34 @@
     </row>
     <row r="64" spans="1:108" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
+        <v>658</v>
+      </c>
+      <c r="C64" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D64" s="2" t="s">
         <v>659</v>
       </c>
-      <c r="C64" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D64" s="2" t="s">
+      <c r="E64" s="2" t="s">
         <v>660</v>
       </c>
-      <c r="E64" s="2" t="s">
+      <c r="F64" s="2" t="s">
         <v>661</v>
       </c>
-      <c r="F64" s="2" t="s">
-        <v>662</v>
-      </c>
       <c r="J64" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="K64" s="2" t="s">
         <v>505</v>
       </c>
-      <c r="K64" s="2" t="s">
-        <v>506</v>
-      </c>
       <c r="AC64" s="2">
         <v>2</v>
       </c>
       <c r="AT64" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX64" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="AX64" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="AZ64" s="2">
         <v>2</v>
@@ -8976,39 +9154,39 @@
         <v>3</v>
       </c>
       <c r="BY64" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CB64" s="2" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="CG64" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="CJ64" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="65" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
+        <v>662</v>
+      </c>
+      <c r="C65" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="D65" s="2" t="s">
         <v>663</v>
       </c>
-      <c r="C65" s="2" t="s">
-        <v>512</v>
-      </c>
-      <c r="D65" s="2" t="s">
+      <c r="E65" s="2" t="s">
         <v>664</v>
       </c>
-      <c r="E65" s="2" t="s">
+      <c r="F65" s="2" t="s">
         <v>665</v>
       </c>
-      <c r="F65" s="2" t="s">
-        <v>666</v>
-      </c>
       <c r="J65" s="2" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="K65" s="2" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="AB65" s="2">
         <v>1</v>
@@ -9017,10 +9195,10 @@
         <v>2</v>
       </c>
       <c r="AT65" s="2" t="s">
+        <v>513</v>
+      </c>
+      <c r="AX65" s="2" t="s">
         <v>514</v>
-      </c>
-      <c r="AX65" s="2" t="s">
-        <v>515</v>
       </c>
       <c r="AZ65" s="2">
         <v>1</v>
@@ -9035,7 +9213,7 @@
         <v>0.1</v>
       </c>
       <c r="BO65" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="BT65" s="2">
         <v>20</v>
@@ -9053,30 +9231,30 @@
         <v>1</v>
       </c>
       <c r="BY65" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="CB65" s="2" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="CG65" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="CJ65" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="66" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="K66" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L66" s="2" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="AC66" s="2">
         <v>1</v>
@@ -9085,10 +9263,10 @@
         <v>1</v>
       </c>
       <c r="CN66" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="CO66" s="2" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="CR66" s="2">
         <v>20</v>
@@ -9096,42 +9274,42 @@
     </row>
     <row r="68" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="C68" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="AT68" s="2" t="s">
         <v>670</v>
       </c>
-      <c r="C68" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="AT68" s="2" t="s">
+      <c r="BO68" s="2" t="s">
         <v>671</v>
       </c>
-      <c r="BO68" s="2" t="s">
+      <c r="CU68" s="2" t="s">
         <v>672</v>
-      </c>
-      <c r="CU68" s="2" t="s">
-        <v>673</v>
       </c>
     </row>
     <row r="69" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C69" s="2" t="s">
+        <v>511</v>
+      </c>
+      <c r="K69" s="2" t="s">
+        <v>505</v>
+      </c>
+      <c r="AC69" s="2">
+        <v>2</v>
+      </c>
+      <c r="AO69" s="2" t="s">
         <v>512</v>
       </c>
-      <c r="K69" s="2" t="s">
-        <v>506</v>
-      </c>
-      <c r="AC69" s="2">
-        <v>2</v>
-      </c>
-      <c r="AO69" s="2" t="s">
-        <v>513</v>
-      </c>
       <c r="AT69" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AX69" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AZ69" s="2">
         <v>1</v>
@@ -9146,42 +9324,42 @@
         <v>0.3</v>
       </c>
       <c r="CB69" s="2" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="CG69" s="2" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="CL69" s="2" t="s">
+        <v>674</v>
+      </c>
+      <c r="CY69" s="2" t="s">
         <v>675</v>
-      </c>
-      <c r="CY69" s="2" t="s">
-        <v>676</v>
       </c>
     </row>
     <row r="70" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="C70" s="2" t="s">
         <v>677</v>
       </c>
-      <c r="C70" s="2" t="s">
+      <c r="K70" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L70" s="2" t="s">
         <v>678</v>
       </c>
-      <c r="K70" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L70" s="2" t="s">
-        <v>679</v>
-      </c>
       <c r="AC70" s="2">
         <v>2</v>
       </c>
       <c r="AO70" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AT70" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="AX70" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AZ70" s="2">
         <v>2</v>
@@ -9196,45 +9374,45 @@
         <v>0.1</v>
       </c>
       <c r="CG70" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="CY70" s="2" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
     </row>
     <row r="71" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
+        <v>679</v>
+      </c>
+      <c r="C71" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="I71" s="2">
+        <v>1</v>
+      </c>
+      <c r="K71" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L71" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="AC71" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF71" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG71" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="BD71" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN71" s="2" t="s">
         <v>680</v>
       </c>
-      <c r="C71" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I71" s="2">
-        <v>1</v>
-      </c>
-      <c r="K71" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L71" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="AC71" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF71" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG71" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="BD71" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN71" s="2" t="s">
+      <c r="CO71" s="2" t="s">
         <v>681</v>
-      </c>
-      <c r="CO71" s="2" t="s">
-        <v>682</v>
       </c>
       <c r="CR71" s="2">
         <v>99999</v>
@@ -9242,48 +9420,48 @@
     </row>
     <row r="72" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
+        <v>682</v>
+      </c>
+      <c r="C72" s="2" t="s">
         <v>683</v>
       </c>
-      <c r="C72" s="2" t="s">
+      <c r="K72" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L72" s="2" t="s">
         <v>684</v>
       </c>
-      <c r="K72" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L72" s="2" t="s">
+      <c r="AC72" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD72" s="2">
+        <v>1</v>
+      </c>
+      <c r="CU72" s="2" t="s">
         <v>685</v>
-      </c>
-      <c r="AC72" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD72" s="2">
-        <v>1</v>
-      </c>
-      <c r="CU72" s="2" t="s">
-        <v>686</v>
       </c>
     </row>
     <row r="77" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
+        <v>686</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>687</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>688</v>
-      </c>
       <c r="I77" s="2">
         <v>1</v>
       </c>
       <c r="K77" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AC77" s="2">
         <v>1</v>
       </c>
       <c r="AG77" s="2" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="AT77" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="BD77" s="2">
         <v>1</v>
@@ -9294,25 +9472,25 @@
     </row>
     <row r="78" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C78" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I78" s="2">
         <v>1</v>
       </c>
       <c r="K78" s="2" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AC78" s="2">
         <v>2</v>
       </c>
       <c r="AO78" s="2" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="AT78" s="2" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="BD78" s="2">
         <v>99</v>
@@ -9321,13 +9499,13 @@
         <v>0.01</v>
       </c>
       <c r="CN78" s="2" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="CR78" s="2">
         <v>0.02</v>
       </c>
       <c r="CU78" s="2" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="DD78" s="2">
         <v>1</v>
@@ -9338,19 +9516,19 @@
     </row>
     <row r="79" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C79" s="2" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="I79" s="2">
         <v>1</v>
       </c>
       <c r="K79" s="2" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="L79" s="2" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="AC79" s="2">
         <v>1</v>
@@ -9359,13 +9537,13 @@
         <v>1</v>
       </c>
       <c r="AJ79" s="2" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="AV79" s="2">
         <v>99</v>
       </c>
       <c r="AX79" s="2" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="AZ79" s="2">
         <v>1</v>
@@ -9377,16 +9555,16 @@
         <v>0.02</v>
       </c>
       <c r="CG79" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="CH79" s="2" t="s">
+        <v>690</v>
+      </c>
+      <c r="CI79" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="CN79" s="2" t="s">
         <v>691</v>
-      </c>
-      <c r="CI79" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="CN79" s="2" t="s">
-        <v>692</v>
       </c>
       <c r="CR79" s="2">
         <v>6</v>
@@ -9397,37 +9575,37 @@
     </row>
     <row r="80" spans="1:111" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
+        <v>692</v>
+      </c>
+      <c r="C80" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="I80" s="2">
+        <v>1</v>
+      </c>
+      <c r="K80" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L80" s="2" t="s">
+        <v>604</v>
+      </c>
+      <c r="AC80" s="2">
+        <v>1</v>
+      </c>
+      <c r="AF80" s="2">
+        <v>1</v>
+      </c>
+      <c r="AG80" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="AV80" s="2">
+        <v>1</v>
+      </c>
+      <c r="BD80" s="2">
+        <v>1</v>
+      </c>
+      <c r="CN80" s="2" t="s">
         <v>693</v>
-      </c>
-      <c r="C80" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I80" s="2">
-        <v>1</v>
-      </c>
-      <c r="K80" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L80" s="2" t="s">
-        <v>605</v>
-      </c>
-      <c r="AC80" s="2">
-        <v>1</v>
-      </c>
-      <c r="AF80" s="2">
-        <v>1</v>
-      </c>
-      <c r="AG80" s="2" t="s">
-        <v>528</v>
-      </c>
-      <c r="AV80" s="2">
-        <v>1</v>
-      </c>
-      <c r="BD80" s="2">
-        <v>1</v>
-      </c>
-      <c r="CN80" s="2" t="s">
-        <v>694</v>
       </c>
       <c r="CR80" s="2">
         <v>99999</v>
@@ -9441,31 +9619,31 @@
     </row>
     <row r="81" spans="1:112" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="C81" s="2" t="s">
+        <v>520</v>
+      </c>
+      <c r="I81" s="2">
+        <v>1</v>
+      </c>
+      <c r="K81" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="L81" s="2" t="s">
         <v>695</v>
       </c>
-      <c r="C81" s="2" t="s">
-        <v>521</v>
-      </c>
-      <c r="I81" s="2">
-        <v>1</v>
-      </c>
-      <c r="K81" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="L81" s="2" t="s">
-        <v>696</v>
-      </c>
       <c r="AC81" s="2">
         <v>1</v>
       </c>
       <c r="AJ81" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="AV81" s="2">
         <v>99</v>
       </c>
       <c r="AX81" s="2" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="AZ81" s="2">
         <v>99999</v>
@@ -9477,7 +9655,7 @@
         <v>1</v>
       </c>
       <c r="CG81" s="2" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="DD81" s="2">
         <v>1</v>
@@ -9573,37 +9751,37 @@
         <v>21</v>
       </c>
       <c r="E1" s="2" t="s">
+        <v>697</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>698</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>699</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>700</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>701</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>702</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>703</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="M1" s="2" t="s">
         <v>704</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="N1" s="2" t="s">
         <v>705</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="O1" s="2" t="s">
         <v>706</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="P1" s="2" t="s">
         <v>707</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>708</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.25">
@@ -9611,49 +9789,49 @@
         <v>0</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E2" s="2" t="s">
+        <v>708</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>709</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>710</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>711</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>712</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>713</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>714</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="M2" s="2" t="s">
         <v>715</v>
       </c>
-      <c r="L2" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M2" s="2" t="s">
+      <c r="N2" s="2" t="s">
         <v>716</v>
       </c>
-      <c r="N2" s="2" t="s">
+      <c r="O2" s="2" t="s">
         <v>717</v>
       </c>
-      <c r="O2" s="2" t="s">
+      <c r="P2" s="2" t="s">
         <v>718</v>
       </c>
-      <c r="P2" s="2" t="s">
-        <v>719</v>
-      </c>
       <c r="Q2" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.25">
@@ -9667,51 +9845,51 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>493</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>494</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>135</v>
-      </c>
       <c r="L3" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="M3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="N3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="O3" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="P3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="Q3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="E4" s="2">
         <v>2</v>
@@ -9726,32 +9904,32 @@
         <v>1</v>
       </c>
       <c r="Q4" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="K5" s="2">
         <v>0.01</v>
       </c>
       <c r="Q5" s="2" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="G6" s="2">
         <v>1</v>
@@ -9760,18 +9938,18 @@
         <v>0.01</v>
       </c>
       <c r="Q6" s="2" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="K7" s="2">
         <v>9999</v>
@@ -9780,40 +9958,40 @@
         <v>1</v>
       </c>
       <c r="Q7" s="2" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
+        <v>725</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>726</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="J8" s="2" t="s">
         <v>727</v>
-      </c>
-      <c r="J8" s="2" t="s">
-        <v>728</v>
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="J9" s="2" t="s">
+        <v>728</v>
+      </c>
+      <c r="Q9" s="2" t="s">
         <v>729</v>
-      </c>
-      <c r="Q9" s="2" t="s">
-        <v>730</v>
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
     </row>
   </sheetData>
@@ -9839,7 +10017,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -9847,13 +10025,13 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
@@ -9864,21 +10042,21 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>733</v>
+      </c>
+      <c r="D4" s="2" t="s">
         <v>734</v>
-      </c>
-      <c r="D4" s="2" t="s">
-        <v>735</v>
       </c>
     </row>
   </sheetData>
@@ -9902,7 +10080,7 @@
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.25">
       <c r="I1" s="2" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.25">
@@ -9910,31 +10088,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D2" s="2" t="s">
+        <v>735</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="F2" s="2" t="s">
         <v>736</v>
       </c>
-      <c r="E2" s="2" t="s">
-        <v>89</v>
-      </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>737</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>738</v>
       </c>
-      <c r="H2" s="2" t="s">
-        <v>739</v>
-      </c>
       <c r="I2" s="2" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -9951,39 +10129,39 @@
         <v>2</v>
       </c>
       <c r="E3" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="F3" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="F3" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="G3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="J3" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B4" s="2" t="s">
+        <v>739</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>740</v>
-      </c>
-      <c r="C4" s="2" t="s">
-        <v>741</v>
       </c>
       <c r="E4" s="2">
         <v>10</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
     </row>
   </sheetData>
@@ -10011,34 +10189,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>742</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>743</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>744</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>745</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>746</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>747</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>748</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="J1" s="2" t="s">
         <v>749</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="K1" s="2" t="s">
         <v>750</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>751</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>752</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
@@ -10046,37 +10224,37 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>752</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>753</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>754</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>755</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>756</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>757</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>758</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>759</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>760</v>
       </c>
-      <c r="J2" s="2" t="s">
-        <v>761</v>
-      </c>
       <c r="K2" s="2" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
@@ -10087,42 +10265,42 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="E3" s="2" t="s">
         <v>2</v>
       </c>
       <c r="F3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="G3" s="2" t="s">
+        <v>133</v>
+      </c>
+      <c r="H3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>135</v>
+      </c>
+      <c r="K3" s="2" t="s">
         <v>134</v>
       </c>
-      <c r="G3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>134</v>
-      </c>
-      <c r="H3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="I3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>136</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="I4" s="2">
         <v>2</v>
@@ -10136,10 +10314,10 @@
     </row>
     <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="I5" s="2">
         <v>2</v>
@@ -10153,13 +10331,13 @@
     </row>
     <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
+        <v>764</v>
+      </c>
+      <c r="B6" s="2" t="s">
         <v>765</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>766</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>767</v>
       </c>
       <c r="F6" s="2">
         <v>1</v>
@@ -10173,10 +10351,10 @@
     </row>
     <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="I7" s="2">
         <v>2</v>
@@ -10190,10 +10368,10 @@
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="I8" s="2">
         <v>2</v>
@@ -10207,10 +10385,10 @@
     </row>
     <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="I9" s="2">
         <v>2</v>
@@ -10224,10 +10402,10 @@
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B10" s="2" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="H10" s="2">
         <v>2</v>
@@ -10244,10 +10422,10 @@
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="I11" s="2">
         <v>2</v>
@@ -10261,10 +10439,10 @@
     </row>
     <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="H12" s="2">
         <v>2</v>
@@ -10281,10 +10459,10 @@
     </row>
     <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="I13" s="2">
         <v>2</v>
@@ -10298,13 +10476,13 @@
     </row>
     <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B14" s="2" t="s">
+        <v>774</v>
+      </c>
+      <c r="E14" s="2" t="s">
         <v>775</v>
-      </c>
-      <c r="E14" s="2" t="s">
-        <v>776</v>
       </c>
       <c r="H14" s="2">
         <v>2</v>
@@ -10321,13 +10499,13 @@
     </row>
     <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="B15" s="2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="F15" s="2">
         <v>1</v>
@@ -10341,18 +10519,18 @@
     </row>
     <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="I17" s="2">
         <v>2</v>
@@ -10366,10 +10544,10 @@
     </row>
     <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="I18" s="2">
         <v>2</v>
@@ -10383,10 +10561,10 @@
     </row>
     <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="I19" s="2">
         <v>2</v>
@@ -10400,10 +10578,10 @@
     </row>
     <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="I20" s="2">
         <v>2</v>
@@ -10417,10 +10595,10 @@
     </row>
     <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="I21" s="2">
         <v>2</v>
@@ -10434,10 +10612,10 @@
     </row>
     <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
+        <v>783</v>
+      </c>
+      <c r="B22" s="2" t="s">
         <v>784</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>785</v>
       </c>
       <c r="I22" s="2">
         <v>2</v>
@@ -10451,10 +10629,10 @@
     </row>
     <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B23" s="2" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="I23" s="2">
         <v>2</v>
@@ -10465,10 +10643,10 @@
     </row>
     <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="I24" s="2">
         <v>2</v>
@@ -10482,10 +10660,10 @@
     </row>
     <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="B25" s="2" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="I25" s="2">
         <v>2</v>
@@ -10499,10 +10677,10 @@
     </row>
     <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="I26" s="2">
         <v>2</v>
@@ -10544,31 +10722,31 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="D2" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>790</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="F2" s="1" t="s">
+        <v>97</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>791</v>
       </c>
-      <c r="F2" s="1" t="s">
-        <v>98</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="H2" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="I2" s="1" t="s">
         <v>792</v>
       </c>
-      <c r="H2" s="1" t="s">
-        <v>402</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>793</v>
-      </c>
       <c r="J2" s="1" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.25">
@@ -10585,22 +10763,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>136</v>
       </c>
-      <c r="F3" s="1" t="s">
-        <v>137</v>
-      </c>
       <c r="G3" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
   </sheetData>
@@ -10630,28 +10808,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="2" t="s">
+        <v>794</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>795</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="D1" s="2" t="s">
         <v>796</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="2" t="s">
         <v>797</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" s="2" t="s">
         <v>798</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>799</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>800</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>801</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>802</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.25">
@@ -10659,28 +10837,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="2" t="s">
+        <v>802</v>
+      </c>
+      <c r="C2" s="2" t="s">
         <v>803</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="D2" s="2" t="s">
         <v>804</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>805</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="F2" s="2" t="s">
         <v>806</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="G2" s="2" t="s">
         <v>807</v>
       </c>
-      <c r="G2" s="2" t="s">
+      <c r="H2" s="2" t="s">
         <v>808</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>809</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>810</v>
       </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.25">
@@ -10688,10 +10866,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>2</v>

--- a/Excel/Main/先锋.xlsx
+++ b/Excel/Main/先锋.xlsx
@@ -323,7 +323,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="818" uniqueCount="818">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="820" uniqueCount="820">
   <si>
     <t>Id</t>
   </si>
@@ -718,6 +718,9 @@
     <t>Ablititys</t>
   </si>
   <si>
+    <t>StartAnimation</t>
+  </si>
+  <si>
     <t>DefaultAnimation</t>
   </si>
   <si>
@@ -734,6 +737,9 @@
   </si>
   <si>
     <t>ForwardAnimation</t>
+  </si>
+  <si>
+    <t>DieAnimation</t>
   </si>
   <si>
     <t>MaxAnimationScale</t>
@@ -3303,7 +3309,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:BV24"/>
+  <dimension ref="A1:BX24"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.05" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.58203125" customWidth="1" style="2"/>
@@ -3373,13 +3379,15 @@
     <col min="65" max="65" width="27" customWidth="1" style="2"/>
     <col min="66" max="66" width="9" customWidth="1" style="2"/>
     <col min="67" max="67" width="39.58203125" customWidth="1" style="2"/>
-    <col min="68" max="68" width="14" customWidth="1" style="2"/>
-    <col min="69" max="69" width="14.83203125" customWidth="1" style="2"/>
-    <col min="70" max="70" width="14" customWidth="1" style="2"/>
+    <col min="68" max="68" width="9" customWidth="1" style="2"/>
+    <col min="69" max="69" width="14" customWidth="1" style="2"/>
+    <col min="70" max="70" width="14.83203125" customWidth="1" style="2"/>
     <col min="71" max="71" width="14" customWidth="1" style="2"/>
     <col min="72" max="72" width="14" customWidth="1" style="2"/>
     <col min="73" max="73" width="14" customWidth="1" style="2"/>
-    <col min="74" max="74" width="19.1640625" customWidth="1" style="2"/>
+    <col min="74" max="74" width="14" customWidth="1" style="2"/>
+    <col min="75" max="75" width="9" customWidth="1" style="2"/>
+    <col min="76" max="76" width="19.1640625" customWidth="1" style="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3551,6 +3559,8 @@
       <c r="BT1" s="2"/>
       <c r="BU1" s="2"/>
       <c r="BV1" s="2"/>
+      <c r="BW1" s="2"/>
+      <c r="BX1" s="2"/>
     </row>
     <row r="2">
       <c r="A2" s="2" t="s">
@@ -3771,6 +3781,12 @@
       <c r="BV2" s="2" t="s">
         <v>137</v>
       </c>
+      <c r="BW2" s="2" t="s">
+        <v>138</v>
+      </c>
+      <c r="BX2" s="2" t="s">
+        <v>139</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="s">
@@ -3780,7 +3796,7 @@
         <v>2</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D3" s="2"/>
       <c r="E3" s="2"/>
@@ -3788,206 +3804,212 @@
         <v>2</v>
       </c>
       <c r="G3" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H3" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="I3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="N3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="O3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="P3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="Q3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="R3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="S3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="T3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="U3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="V3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="W3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="X3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="Y3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="Z3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AA3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AC3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="AD3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AE3" s="2" t="s">
         <v>140</v>
       </c>
-      <c r="I3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="J3" s="2" t="s">
+      <c r="AF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AG3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AH3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AI3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AJ3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AK3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AL3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AM3" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="AN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AO3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="AP3" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="AQ3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="AR3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AS3" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="L3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="M3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="N3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="O3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="P3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="Q3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="R3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="S3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="T3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="U3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="V3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="W3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="X3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="Y3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="Z3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AA3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AB3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AC3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AD3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AE3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="AF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AG3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AH3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AI3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AJ3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AK3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AL3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="AM3" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="AN3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AO3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="AP3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="AQ3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="AR3" s="2" t="s">
-        <v>141</v>
-      </c>
-      <c r="AS3" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="AT3" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AU3" s="2"/>
       <c r="AV3" s="2" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AW3" s="2" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AX3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="AY3" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="AZ3" s="2" t="s">
         <v>141</v>
       </c>
-      <c r="AY3" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="AZ3" s="2" t="s">
-        <v>139</v>
-      </c>
       <c r="BA3" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="BB3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BC3" s="2" t="s">
+        <v>140</v>
+      </c>
+      <c r="BD3" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="BE3" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="BF3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BG3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BH3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BI3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BJ3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="BK3" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="BL3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BM3" s="2" t="s">
         <v>145</v>
       </c>
-      <c r="BB3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="BC3" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="BD3" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="BE3" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="BF3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BG3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BH3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BI3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BJ3" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="BK3" s="2" t="s">
+      <c r="BN3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="BO3" s="2" t="s">
+        <v>150</v>
+      </c>
+      <c r="BP3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BQ3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BR3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BS3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BT3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BU3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BV3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BW3" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="BX3" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="BL3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BM3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BN3" s="2" t="s">
-        <v>2</v>
-      </c>
-      <c r="BO3" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="BP3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BQ3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BR3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BS3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BT3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BU3" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="BV3" s="2" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4">
@@ -4065,23 +4087,25 @@
       <c r="BT4" s="2"/>
       <c r="BU4" s="2"/>
       <c r="BV4" s="2"/>
+      <c r="BW4" s="2"/>
+      <c r="BX4" s="2"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="s">
         <v>5</v>
       </c>
       <c r="B5" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G5" s="2">
         <v>1</v>
@@ -4148,21 +4172,21 @@
         <v>5</v>
       </c>
       <c r="AK5" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL5" s="2" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="AM5" s="2"/>
       <c r="AN5" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO5" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP5" s="2"/>
       <c r="AQ5" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR5" s="2">
         <v>2</v>
@@ -4184,53 +4208,55 @@
       <c r="BC5" s="2"/>
       <c r="BD5" s="2"/>
       <c r="BE5" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF5" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG5" s="2" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="BH5" s="2" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="BI5" s="2" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="BJ5" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK5" s="2">
         <v>2</v>
       </c>
       <c r="BL5" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM5" s="2" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="BN5" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BO5" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="BP5" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="BP5" s="2"/>
       <c r="BQ5" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR5" s="2"/>
-      <c r="BS5" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR5" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS5" s="2"/>
       <c r="BT5" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU5" s="2"/>
-      <c r="BV5" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU5" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV5" s="2"/>
+      <c r="BW5" s="2"/>
+      <c r="BX5" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4309,23 +4335,25 @@
       <c r="BT6" s="2"/>
       <c r="BU6" s="2"/>
       <c r="BV6" s="2"/>
+      <c r="BW6" s="2"/>
+      <c r="BX6" s="2"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="s">
         <v>7</v>
       </c>
       <c r="B7" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="G7" s="2">
         <v>1</v>
@@ -4392,23 +4420,23 @@
         <v>7</v>
       </c>
       <c r="AK7" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL7" s="2" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="AM7" s="2" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="AN7" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO7" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP7" s="2"/>
       <c r="AQ7" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR7" s="2">
         <v>2</v>
@@ -4430,53 +4458,55 @@
       <c r="BC7" s="2"/>
       <c r="BD7" s="2"/>
       <c r="BE7" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF7" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG7" s="2" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="BH7" s="2" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="BI7" s="2" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="BJ7" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK7" s="2">
         <v>3</v>
       </c>
       <c r="BL7" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM7" s="2" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="BN7" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BO7" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="BP7" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>178</v>
+      </c>
+      <c r="BP7" s="2"/>
       <c r="BQ7" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR7" s="2"/>
-      <c r="BS7" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS7" s="2"/>
       <c r="BT7" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU7" s="2"/>
-      <c r="BV7" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV7" s="2"/>
+      <c r="BW7" s="2"/>
+      <c r="BX7" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4485,17 +4515,17 @@
         <v>8</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G8" s="2">
         <v>1</v>
@@ -4562,23 +4592,23 @@
         <v>8</v>
       </c>
       <c r="AK8" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL8" s="2" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="AM8" s="2" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AN8" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO8" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP8" s="2"/>
       <c r="AQ8" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR8" s="2">
         <v>2</v>
@@ -4600,53 +4630,55 @@
       <c r="BC8" s="2"/>
       <c r="BD8" s="2"/>
       <c r="BE8" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF8" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG8" s="2" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="BH8" s="2" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="BI8" s="2" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="BJ8" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK8" s="2">
         <v>3</v>
       </c>
       <c r="BL8" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM8" s="2" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="BN8" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BO8" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="BP8" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="BP8" s="2"/>
       <c r="BQ8" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR8" s="2"/>
-      <c r="BS8" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR8" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS8" s="2"/>
       <c r="BT8" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU8" s="2"/>
-      <c r="BV8" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU8" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV8" s="2"/>
+      <c r="BW8" s="2"/>
+      <c r="BX8" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4655,17 +4687,17 @@
         <v>9</v>
       </c>
       <c r="B9" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C9" s="2"/>
       <c r="D9" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="G9" s="2">
         <v>1</v>
@@ -4732,23 +4764,23 @@
         <v>9</v>
       </c>
       <c r="AK9" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL9" s="2" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AM9" s="2" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AN9" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO9" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP9" s="2"/>
       <c r="AQ9" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR9" s="2">
         <v>1</v>
@@ -4770,53 +4802,55 @@
       <c r="BC9" s="2"/>
       <c r="BD9" s="2"/>
       <c r="BE9" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF9" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BG9" s="2" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="BH9" s="2" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="BI9" s="2" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="BJ9" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK9" s="2">
         <v>3</v>
       </c>
       <c r="BL9" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM9" s="2" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="BN9" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="BO9" s="2" t="s">
-        <v>184</v>
-      </c>
-      <c r="BP9" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>186</v>
+      </c>
+      <c r="BP9" s="2"/>
       <c r="BQ9" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR9" s="2"/>
-      <c r="BS9" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR9" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS9" s="2"/>
       <c r="BT9" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU9" s="2"/>
-      <c r="BV9" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU9" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV9" s="2"/>
+      <c r="BW9" s="2"/>
+      <c r="BX9" s="2">
         <v>1</v>
       </c>
     </row>
@@ -4895,23 +4929,25 @@
       <c r="BT10" s="2"/>
       <c r="BU10" s="2"/>
       <c r="BV10" s="2"/>
+      <c r="BW10" s="2"/>
+      <c r="BX10" s="2"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="s">
         <v>11</v>
       </c>
       <c r="B11" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="G11" s="2">
         <v>1</v>
@@ -4978,23 +5014,23 @@
         <v>11</v>
       </c>
       <c r="AK11" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL11" s="2" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AM11" s="2" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AN11" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO11" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP11" s="2"/>
       <c r="AQ11" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR11" s="2">
         <v>2</v>
@@ -5016,53 +5052,55 @@
       <c r="BC11" s="2"/>
       <c r="BD11" s="2"/>
       <c r="BE11" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF11" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG11" s="2" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="BH11" s="2" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="BI11" s="2" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="BJ11" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK11" s="2">
         <v>4</v>
       </c>
       <c r="BL11" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM11" s="2" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="BN11" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BO11" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="BP11" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>203</v>
+      </c>
+      <c r="BP11" s="2"/>
       <c r="BQ11" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR11" s="2"/>
-      <c r="BS11" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR11" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS11" s="2"/>
       <c r="BT11" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU11" s="2"/>
-      <c r="BV11" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU11" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV11" s="2"/>
+      <c r="BW11" s="2"/>
+      <c r="BX11" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5071,17 +5109,17 @@
         <v>12</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="G12" s="2">
         <v>1</v>
@@ -5148,23 +5186,23 @@
         <v>12</v>
       </c>
       <c r="AK12" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL12" s="2" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="AM12" s="2" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="AN12" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO12" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP12" s="2"/>
       <c r="AQ12" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR12" s="2">
         <v>2</v>
@@ -5186,53 +5224,55 @@
       <c r="BC12" s="2"/>
       <c r="BD12" s="2"/>
       <c r="BE12" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF12" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG12" s="2" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="BH12" s="2" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="BI12" s="2" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="BJ12" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK12" s="2">
         <v>4</v>
       </c>
       <c r="BL12" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM12" s="2" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="BN12" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BO12" s="2" t="s">
-        <v>209</v>
-      </c>
-      <c r="BP12" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>211</v>
+      </c>
+      <c r="BP12" s="2"/>
       <c r="BQ12" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR12" s="2"/>
-      <c r="BS12" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR12" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS12" s="2"/>
       <c r="BT12" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU12" s="2"/>
-      <c r="BV12" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU12" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV12" s="2"/>
+      <c r="BW12" s="2"/>
+      <c r="BX12" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5241,17 +5281,17 @@
         <v>13</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="G13" s="2">
         <v>1</v>
@@ -5318,23 +5358,23 @@
         <v>13</v>
       </c>
       <c r="AK13" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL13" s="2" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AM13" s="2" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="AN13" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO13" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP13" s="2"/>
       <c r="AQ13" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR13" s="2">
         <v>1</v>
@@ -5356,53 +5396,55 @@
       <c r="BC13" s="2"/>
       <c r="BD13" s="2"/>
       <c r="BE13" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF13" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BG13" s="2" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="BH13" s="2" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="BI13" s="2" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="BJ13" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK13" s="2">
         <v>4</v>
       </c>
       <c r="BL13" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM13" s="2" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="BN13" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="BO13" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="BP13" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>219</v>
+      </c>
+      <c r="BP13" s="2"/>
       <c r="BQ13" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR13" s="2"/>
-      <c r="BS13" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR13" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS13" s="2"/>
       <c r="BT13" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU13" s="2"/>
-      <c r="BV13" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV13" s="2"/>
+      <c r="BW13" s="2"/>
+      <c r="BX13" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5411,17 +5453,17 @@
         <v>14</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="G14" s="2">
         <v>1</v>
@@ -5488,23 +5530,23 @@
         <v>14</v>
       </c>
       <c r="AK14" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL14" s="2" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AM14" s="2" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AN14" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO14" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP14" s="2"/>
       <c r="AQ14" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR14" s="2">
         <v>1</v>
@@ -5526,53 +5568,55 @@
       <c r="BC14" s="2"/>
       <c r="BD14" s="2"/>
       <c r="BE14" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF14" s="2" t="s">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="BG14" s="2" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="BH14" s="2" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="BI14" s="2" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="BJ14" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK14" s="2">
         <v>4</v>
       </c>
       <c r="BL14" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM14" s="2" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="BN14" s="2" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="BO14" s="2" t="s">
-        <v>227</v>
-      </c>
-      <c r="BP14" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>229</v>
+      </c>
+      <c r="BP14" s="2"/>
       <c r="BQ14" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR14" s="2"/>
-      <c r="BS14" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR14" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS14" s="2"/>
       <c r="BT14" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU14" s="2"/>
-      <c r="BV14" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU14" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV14" s="2"/>
+      <c r="BW14" s="2"/>
+      <c r="BX14" s="2">
         <v>1.1</v>
       </c>
     </row>
@@ -5651,23 +5695,25 @@
       <c r="BT15" s="2"/>
       <c r="BU15" s="2"/>
       <c r="BV15" s="2"/>
+      <c r="BW15" s="2"/>
+      <c r="BX15" s="2"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="s">
         <v>16</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="G16" s="2">
         <v>1</v>
@@ -5734,23 +5780,23 @@
         <v>16</v>
       </c>
       <c r="AK16" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL16" s="2" t="s">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="AM16" s="2" t="s">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AN16" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO16" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP16" s="2"/>
       <c r="AQ16" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR16" s="2">
         <v>2</v>
@@ -5772,53 +5818,55 @@
       <c r="BC16" s="2"/>
       <c r="BD16" s="2"/>
       <c r="BE16" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF16" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG16" s="2" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="BH16" s="2" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="BI16" s="2" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="BJ16" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK16" s="2">
         <v>5</v>
       </c>
       <c r="BL16" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM16" s="2" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="BN16" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BO16" s="2" t="s">
-        <v>235</v>
-      </c>
-      <c r="BP16" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>237</v>
+      </c>
+      <c r="BP16" s="2"/>
       <c r="BQ16" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR16" s="2"/>
-      <c r="BS16" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR16" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS16" s="2"/>
       <c r="BT16" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU16" s="2"/>
-      <c r="BV16" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU16" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV16" s="2"/>
+      <c r="BW16" s="2"/>
+      <c r="BX16" s="2">
         <v>1</v>
       </c>
     </row>
@@ -5827,17 +5875,17 @@
         <v>17</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="G17" s="2">
         <v>1</v>
@@ -5904,23 +5952,23 @@
         <v>17</v>
       </c>
       <c r="AK17" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL17" s="2" t="s">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="AM17" s="2" t="s">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AN17" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO17" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP17" s="2"/>
       <c r="AQ17" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR17" s="2">
         <v>2</v>
@@ -5942,55 +5990,57 @@
       <c r="BC17" s="2"/>
       <c r="BD17" s="2"/>
       <c r="BE17" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF17" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG17" s="2" t="s">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="BH17" s="2" t="s">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="BI17" s="2" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="BJ17" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK17" s="2">
         <v>5</v>
       </c>
       <c r="BL17" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM17" s="2" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="BN17" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BO17" s="2" t="s">
-        <v>243</v>
-      </c>
-      <c r="BP17" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>245</v>
+      </c>
+      <c r="BP17" s="2"/>
       <c r="BQ17" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR17" s="2"/>
-      <c r="BS17" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR17" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS17" s="2"/>
       <c r="BT17" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BU17" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="BV17" s="2">
+        <v>170</v>
+      </c>
+      <c r="BV17" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="BW17" s="2"/>
+      <c r="BX17" s="2">
         <v>1.05</v>
       </c>
     </row>
@@ -6069,23 +6119,25 @@
       <c r="BT18" s="2"/>
       <c r="BU18" s="2"/>
       <c r="BV18" s="2"/>
+      <c r="BW18" s="2"/>
+      <c r="BX18" s="2"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="s">
         <v>19</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="E19" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -6154,23 +6206,23 @@
         <v>19</v>
       </c>
       <c r="AK19" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL19" s="2" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM19" s="2" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN19" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO19" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP19" s="2"/>
       <c r="AQ19" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR19" s="2">
         <v>2</v>
@@ -6192,55 +6244,57 @@
       <c r="BC19" s="2"/>
       <c r="BD19" s="2"/>
       <c r="BE19" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF19" s="2" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="BG19" s="2" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="BH19" s="2" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="BI19" s="2" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="BJ19" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK19" s="2">
         <v>6</v>
       </c>
       <c r="BL19" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM19" s="2" t="s">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="BN19" s="2" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="BO19" s="2" t="s">
-        <v>252</v>
-      </c>
-      <c r="BP19" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>254</v>
+      </c>
+      <c r="BP19" s="2"/>
       <c r="BQ19" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR19" s="2"/>
-      <c r="BS19" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR19" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS19" s="2"/>
       <c r="BT19" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BU19" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="BV19" s="2">
+        <v>170</v>
+      </c>
+      <c r="BV19" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="BW19" s="2"/>
+      <c r="BX19" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6249,17 +6303,17 @@
         <v>20</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="G20" s="2">
         <v>1</v>
@@ -6324,23 +6378,23 @@
         <v>20</v>
       </c>
       <c r="AK20" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL20" s="2" t="s">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="AM20" s="2" t="s">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="AN20" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO20" s="2" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="AP20" s="2"/>
       <c r="AQ20" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR20" s="2">
         <v>1</v>
@@ -6362,53 +6416,55 @@
       <c r="BC20" s="2"/>
       <c r="BD20" s="2"/>
       <c r="BE20" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF20" s="2" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="BG20" s="2" t="s">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="BH20" s="2" t="s">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="BI20" s="2" t="s">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="BJ20" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK20" s="2">
         <v>6</v>
       </c>
       <c r="BL20" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM20" s="2" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="BN20" s="2" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="BO20" s="2" t="s">
-        <v>260</v>
-      </c>
-      <c r="BP20" s="2" t="s">
-        <v>166</v>
-      </c>
+        <v>262</v>
+      </c>
+      <c r="BP20" s="2"/>
       <c r="BQ20" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR20" s="2"/>
-      <c r="BS20" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR20" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS20" s="2"/>
       <c r="BT20" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU20" s="2"/>
-      <c r="BV20" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU20" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV20" s="2"/>
+      <c r="BW20" s="2"/>
+      <c r="BX20" s="2">
         <v>2</v>
       </c>
     </row>
@@ -6487,19 +6543,21 @@
       <c r="BT21" s="2"/>
       <c r="BU21" s="2"/>
       <c r="BV21" s="2"/>
+      <c r="BW21" s="2"/>
+      <c r="BX21" s="2"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="B22" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" s="2"/>
       <c r="E22" s="2"/>
       <c r="F22" s="2" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="G22" s="2">
         <v>1</v>
@@ -6557,24 +6615,24 @@
       <c r="AH22" s="2"/>
       <c r="AI22" s="2"/>
       <c r="AJ22" s="2" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AK22" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL22" s="2" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AM22" s="2"/>
       <c r="AN22" s="2" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="AO22" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AP22" s="2"/>
       <c r="AQ22" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR22" s="2">
         <v>2</v>
@@ -6598,47 +6656,49 @@
       <c r="BC22" s="2"/>
       <c r="BD22" s="2"/>
       <c r="BE22" s="2" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BF22" s="2"/>
       <c r="BG22" s="2" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="BH22" s="2" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="BI22" s="2" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="BJ22" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK22" s="2">
         <v>6</v>
       </c>
       <c r="BL22" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM22" s="2"/>
       <c r="BN22" s="2"/>
       <c r="BO22" s="2"/>
-      <c r="BP22" s="2" t="s">
-        <v>166</v>
-      </c>
+      <c r="BP22" s="2"/>
       <c r="BQ22" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR22" s="2"/>
-      <c r="BS22" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR22" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS22" s="2"/>
       <c r="BT22" s="2" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="BU22" s="2" t="s">
-        <v>244</v>
-      </c>
-      <c r="BV22" s="2">
+        <v>170</v>
+      </c>
+      <c r="BV22" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="BW22" s="2"/>
+      <c r="BX22" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6717,23 +6777,25 @@
       <c r="BT23" s="2"/>
       <c r="BU23" s="2"/>
       <c r="BV23" s="2"/>
+      <c r="BW23" s="2"/>
+      <c r="BX23" s="2"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="B24" s="2" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="E24" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="G24" s="2">
         <v>0.01</v>
@@ -6795,26 +6857,26 @@
       </c>
       <c r="AI24" s="2"/>
       <c r="AJ24" s="2" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AK24" s="2" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="AL24" s="2" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AM24" s="2"/>
       <c r="AN24" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AO24" s="2" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AP24" s="2">
         <v>-0.5</v>
       </c>
       <c r="AQ24" s="2" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="AR24" s="2">
         <v>0</v>
@@ -6840,45 +6902,47 @@
       </c>
       <c r="BD24" s="2"/>
       <c r="BE24" s="2" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="BF24" s="2"/>
       <c r="BG24" s="2" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="BH24" s="2" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="BI24" s="2" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="BJ24" s="2" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="BK24" s="2">
         <v>6</v>
       </c>
       <c r="BL24" s="2" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="BM24" s="2"/>
       <c r="BN24" s="2"/>
       <c r="BO24" s="2"/>
-      <c r="BP24" s="2" t="s">
-        <v>166</v>
-      </c>
+      <c r="BP24" s="2"/>
       <c r="BQ24" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="BR24" s="2"/>
-      <c r="BS24" s="2" t="s">
         <v>168</v>
       </c>
+      <c r="BR24" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="BS24" s="2"/>
       <c r="BT24" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="BU24" s="2"/>
-      <c r="BV24" s="2">
+        <v>170</v>
+      </c>
+      <c r="BU24" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="BV24" s="2"/>
+      <c r="BW24" s="2"/>
+      <c r="BX24" s="2">
         <v>1</v>
       </c>
     </row>
@@ -6980,334 +7044,334 @@
   <sheetData>
     <row r="1">
       <c r="B1" s="3" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="Q1" s="3" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="R1" s="3" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="S1" s="3" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="T1" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="U1" s="3" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="V1" s="3" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
       <c r="W1" s="3" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="X1" s="3" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="Y1" s="3" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="Z1" s="3" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AA1" s="3" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="AB1" s="3" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="AC1" s="3" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="AD1" s="3" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="AE1" s="3" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AF1" s="3" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG1" s="3" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="AH1" s="3" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="AI1" s="3" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="AJ1" s="3" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AK1" s="3" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AL1" s="3" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="AM1" s="3" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="AN1" s="3" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="AO1" s="3" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="AP1" s="3" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="AQ1" s="3" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AR1" s="3" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AS1" s="3" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="AT1" s="3" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="AU1" s="3" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="AV1" s="3" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="AW1" s="3" t="s">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AX1" s="3" t="s">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="AY1" s="3" t="s">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="AZ1" s="3" t="s">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="BA1" s="3" t="s">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="BB1" s="3" t="s">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="BC1" s="3" t="s">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="BD1" s="3" t="s">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="BE1" s="3" t="s">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="BF1" s="3" t="s">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="BG1" s="3" t="s">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="BH1" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="BJ1" s="3" t="s">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="BK1" s="3" t="s">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="BL1" s="3" t="s">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="BM1" s="3" t="s">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="BN1" s="3" t="s">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="BO1" s="3" t="s">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="BP1" s="3" t="s">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="BQ1" s="3" t="s">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="BR1" s="3" t="s">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="BS1" s="3" t="s">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="BT1" s="3" t="s">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="BU1" s="3" t="s">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="BV1" s="3" t="s">
+        <v>345</v>
+      </c>
+      <c r="BW1" s="3" t="s">
+        <v>346</v>
+      </c>
+      <c r="BX1" s="3" t="s">
+        <v>347</v>
+      </c>
+      <c r="BY1" s="3" t="s">
+        <v>348</v>
+      </c>
+      <c r="BZ1" s="3" t="s">
+        <v>349</v>
+      </c>
+      <c r="CA1" s="3" t="s">
+        <v>350</v>
+      </c>
+      <c r="CB1" s="3" t="s">
+        <v>351</v>
+      </c>
+      <c r="CC1" s="3" t="s">
+        <v>352</v>
+      </c>
+      <c r="CD1" s="3" t="s">
+        <v>353</v>
+      </c>
+      <c r="CE1" s="3" t="s">
+        <v>354</v>
+      </c>
+      <c r="CF1" s="3" t="s">
+        <v>355</v>
+      </c>
+      <c r="CG1" s="3" t="s">
+        <v>356</v>
+      </c>
+      <c r="CH1" s="3" t="s">
+        <v>357</v>
+      </c>
+      <c r="CI1" s="3" t="s">
+        <v>358</v>
+      </c>
+      <c r="CJ1" s="3" t="s">
+        <v>359</v>
+      </c>
+      <c r="CK1" s="3" t="s">
+        <v>360</v>
+      </c>
+      <c r="CL1" s="3" t="s">
+        <v>361</v>
+      </c>
+      <c r="CM1" s="3" t="s">
+        <v>362</v>
+      </c>
+      <c r="CN1" s="3" t="s">
+        <v>363</v>
+      </c>
+      <c r="CO1" s="3" t="s">
+        <v>364</v>
+      </c>
+      <c r="CP1" s="3" t="s">
+        <v>365</v>
+      </c>
+      <c r="CQ1" s="3" t="s">
+        <v>366</v>
+      </c>
+      <c r="CR1" s="3" t="s">
         <v>343</v>
       </c>
-      <c r="BW1" s="3" t="s">
-        <v>344</v>
-      </c>
-      <c r="BX1" s="3" t="s">
-        <v>345</v>
-      </c>
-      <c r="BY1" s="3" t="s">
-        <v>346</v>
-      </c>
-      <c r="BZ1" s="3" t="s">
-        <v>347</v>
-      </c>
-      <c r="CA1" s="3" t="s">
-        <v>348</v>
-      </c>
-      <c r="CB1" s="3" t="s">
-        <v>349</v>
-      </c>
-      <c r="CC1" s="3" t="s">
-        <v>350</v>
-      </c>
-      <c r="CD1" s="3" t="s">
-        <v>351</v>
-      </c>
-      <c r="CE1" s="3" t="s">
-        <v>352</v>
-      </c>
-      <c r="CF1" s="3" t="s">
-        <v>353</v>
-      </c>
-      <c r="CG1" s="3" t="s">
-        <v>354</v>
-      </c>
-      <c r="CH1" s="3" t="s">
-        <v>355</v>
-      </c>
-      <c r="CI1" s="3" t="s">
-        <v>356</v>
-      </c>
-      <c r="CJ1" s="3" t="s">
-        <v>357</v>
-      </c>
-      <c r="CK1" s="3" t="s">
-        <v>358</v>
-      </c>
-      <c r="CL1" s="3" t="s">
-        <v>359</v>
-      </c>
-      <c r="CM1" s="3" t="s">
-        <v>360</v>
-      </c>
-      <c r="CN1" s="3" t="s">
-        <v>361</v>
-      </c>
-      <c r="CO1" s="3" t="s">
-        <v>362</v>
-      </c>
-      <c r="CP1" s="3" t="s">
-        <v>363</v>
-      </c>
-      <c r="CQ1" s="3" t="s">
-        <v>364</v>
-      </c>
-      <c r="CR1" s="3" t="s">
-        <v>341</v>
-      </c>
       <c r="CS1" s="3" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="CT1" s="3" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="CU1" s="3" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="CV1" s="3" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="CW1" s="3" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="CX1" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="CY1" s="3" t="s">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="CZ1" s="3" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="DA1" s="3" t="s">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="DB1" s="3" t="s">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="DC1" s="3" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="DD1" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="DE1" s="3" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="DF1" s="3" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="DG1" s="3" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="DH1" s="3" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="DI1" s="3" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="2">
@@ -7321,331 +7385,331 @@
         <v>99</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="G2" s="3" t="s">
         <v>73</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="L2" s="3" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="R2" s="3" t="s">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="S2" s="3" t="s">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="T2" s="3" t="s">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="U2" s="3" t="s">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="V2" s="3" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="W2" s="3" t="s">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="X2" s="3" t="s">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="Y2" s="3" t="s">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="Z2" s="3" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="AA2" s="3" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="AB2" s="3" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="AC2" s="3" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="AD2" s="3" t="s">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AE2" s="3" t="s">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AF2" s="3" t="s">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="AG2" s="3" t="s">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="AH2" s="3" t="s">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AI2" s="3" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AJ2" s="3" t="s">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="AK2" s="3" t="s">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AL2" s="3" t="s">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="AM2" s="3" t="s">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="AN2" s="3" t="s">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AO2" s="3" t="s">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AP2" s="3" t="s">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AQ2" s="3" t="s">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="AR2" s="3" t="s">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="AS2" s="3" t="s">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AT2" s="3" t="s">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AU2" s="3" t="s">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AV2" s="3" t="s">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AW2" s="3" t="s">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="AX2" s="3" t="s">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="AY2" s="3" t="s">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="AZ2" s="3" t="s">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="BA2" s="3" t="s">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="BB2" s="3" t="s">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="BC2" s="3" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="BD2" s="3" t="s">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="BE2" s="3" t="s">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="BF2" s="3" t="s">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="BG2" s="3" t="s">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="BH2" s="3" t="s">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="BI2" s="3" t="s">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="BJ2" s="3" t="s">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="BK2" s="3" t="s">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="BL2" s="3" t="s">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="BM2" s="3" t="s">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="BN2" s="3" t="s">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="BO2" s="3" t="s">
         <v>101</v>
       </c>
       <c r="BP2" s="3" t="s">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="BQ2" s="3" t="s">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="BR2" s="3" t="s">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="BS2" s="3" t="s">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="BT2" s="3" t="s">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="BU2" s="3" t="s">
         <v>117</v>
       </c>
       <c r="BV2" s="3" t="s">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="BW2" s="3" t="s">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="BX2" s="3" t="s">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="BY2" s="3" t="s">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="BZ2" s="3" t="s">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="CA2" s="3" t="s">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="CB2" s="3" t="s">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="CC2" s="3" t="s">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="CD2" s="3" t="s">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="CE2" s="3" t="s">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="CF2" s="3" t="s">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="CG2" s="3" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="CH2" s="3" t="s">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="CI2" s="3" t="s">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="CJ2" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="CK2" s="3" t="s">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="CL2" s="3" t="s">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="CM2" s="3" t="s">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="CN2" s="3" t="s">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="CO2" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="CP2" s="3" t="s">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="CQ2" s="3" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="CR2" s="3" t="s">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="CS2" s="3" t="s">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="CT2" s="3" t="s">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="CU2" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="CV2" s="3" t="s">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="CW2" s="3" t="s">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="CX2" s="3" t="s">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="CY2" s="3" t="s">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="CZ2" s="3" t="s">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="DA2" s="3" t="s">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="DB2" s="3" t="s">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="DC2" s="3" t="s">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="DD2" s="3" t="s">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="DE2" s="3" t="s">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="DF2" s="3" t="s">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="DG2" s="3" t="s">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="DH2" s="3" t="s">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="DI2" s="3" t="s">
-        <v>486</v>
+        <v>488</v>
       </c>
     </row>
     <row r="3">
@@ -7665,344 +7729,344 @@
         <v>2</v>
       </c>
       <c r="G3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>489</v>
+      </c>
+      <c r="K3" s="3" t="s">
+        <v>490</v>
+      </c>
+      <c r="L3" s="3" t="s">
+        <v>491</v>
+      </c>
+      <c r="M3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="N3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="O3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="P3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="Q3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="R3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="S3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="T3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="H3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>487</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>488</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>489</v>
-      </c>
-      <c r="M3" s="3" t="s">
+      <c r="U3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="N3" s="3" t="s">
+      <c r="V3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="O3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="Q3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="R3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="S3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="T3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="U3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="V3" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="W3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="X3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Y3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Z3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AA3" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="AB3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AC3" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="AD3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AE3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AF3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AG3" s="3" t="s">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="AH3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="AI3" s="3" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AJ3" s="3" t="s">
         <v>3</v>
       </c>
       <c r="AK3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AL3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AM3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="AN3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AO3" s="3" t="s">
+        <v>493</v>
+      </c>
+      <c r="AP3" s="3" t="s">
+        <v>494</v>
+      </c>
+      <c r="AQ3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AR3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AS3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="AT3" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="AU3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AV3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AL3" s="3" t="s">
+      <c r="AW3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AX3" s="3" t="s">
+        <v>496</v>
+      </c>
+      <c r="AY3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="AZ3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AM3" s="3" t="s">
+      <c r="BA3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="BB3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BC3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="AN3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AO3" s="3" t="s">
-        <v>491</v>
-      </c>
-      <c r="AP3" s="3" t="s">
-        <v>492</v>
-      </c>
-      <c r="AQ3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AR3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AS3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="AT3" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="AU3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AV3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="AW3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AX3" s="3" t="s">
-        <v>494</v>
-      </c>
-      <c r="AY3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="AZ3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BA3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BB3" s="3" t="s">
+      <c r="BD3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BE3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BF3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="BC3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BD3" s="3" t="s">
+      <c r="BG3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="BH3" s="3" t="s">
+        <v>495</v>
+      </c>
+      <c r="BI3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="BJ3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="BE3" s="3" t="s">
+      <c r="BK3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="BF3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BG3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BH3" s="3" t="s">
-        <v>493</v>
-      </c>
-      <c r="BI3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="BJ3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BK3" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="BL3" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BM3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BN3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="BO3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BP3" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="BQ3" s="3" t="s">
+        <v>497</v>
+      </c>
+      <c r="BR3" s="3" t="s">
+        <v>498</v>
+      </c>
+      <c r="BS3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="BN3" s="3" t="s">
+      <c r="BT3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="BO3" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="BP3" s="3" t="s">
-        <v>142</v>
-      </c>
-      <c r="BQ3" s="3" t="s">
-        <v>495</v>
-      </c>
-      <c r="BR3" s="3" t="s">
-        <v>496</v>
-      </c>
-      <c r="BS3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="BT3" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="BU3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="BV3" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BW3" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="BX3" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="BY3" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="BZ3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="CA3" s="3" t="s">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="CB3" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="CC3" s="3" t="s">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="CD3" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="CE3" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="CF3" s="3" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="CG3" s="3" t="s">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="CH3" s="3" t="s">
+        <v>502</v>
+      </c>
+      <c r="CI3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="CJ3" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="CK3" s="3" t="s">
+        <v>503</v>
+      </c>
+      <c r="CL3" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="CM3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="CN3" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="CO3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CP3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CQ3" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="CR3" s="3" t="s">
         <v>500</v>
       </c>
-      <c r="CI3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="CJ3" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="CK3" s="3" t="s">
-        <v>501</v>
-      </c>
-      <c r="CL3" s="3" t="s">
-        <v>148</v>
-      </c>
-      <c r="CM3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="CN3" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="CO3" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="CP3" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="CQ3" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="CR3" s="3" t="s">
-        <v>498</v>
-      </c>
       <c r="CS3" s="3" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="CT3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="CU3" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="CV3" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="CW3" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="CX3" s="3" t="s">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="CY3" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="CZ3" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="DA3" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="DB3" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="DC3" s="3" t="s">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="DD3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="DE3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="DF3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="DG3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="DH3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="DI3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K5" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AC5" s="3">
         <v>1</v>
@@ -8016,16 +8080,16 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
+        <v>511</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>508</v>
+      </c>
+      <c r="K6" s="3" t="s">
         <v>509</v>
       </c>
-      <c r="C6" s="3" t="s">
-        <v>506</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>507</v>
-      </c>
       <c r="L6" s="3" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="AC6" s="3">
         <v>1</v>
@@ -8039,25 +8103,25 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K8" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="W8" s="3">
         <v>1</v>
@@ -8084,36 +8148,36 @@
         <v>1</v>
       </c>
       <c r="BY8" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CX8" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="G9" s="3">
         <v>3</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K9" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="W9" s="3">
         <v>1</v>
@@ -8140,30 +8204,30 @@
         <v>1</v>
       </c>
       <c r="BY9" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CX9" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC11" s="3">
         <v>2</v>
       </c>
       <c r="AO11" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT11" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX11" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ11" s="3">
         <v>1</v>
@@ -8175,30 +8239,30 @@
         <v>77</v>
       </c>
       <c r="CG11" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CY11" s="3" t="s">
-        <v>525</v>
+        <v>527</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC13" s="3">
         <v>2</v>
       </c>
       <c r="AO13" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT13" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX13" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ13" s="3">
         <v>1</v>
@@ -8210,27 +8274,27 @@
         <v>77</v>
       </c>
       <c r="CG13" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC15" s="3">
         <v>2</v>
       </c>
       <c r="AO15" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT15" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX15" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ15" s="3">
         <v>1</v>
@@ -8242,27 +8306,27 @@
         <v>77</v>
       </c>
       <c r="CG15" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC17" s="3">
         <v>2</v>
       </c>
       <c r="AO17" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT17" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX17" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ17" s="3">
         <v>1</v>
@@ -8274,30 +8338,30 @@
         <v>77</v>
       </c>
       <c r="CG17" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="J18" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K18" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC18" s="3">
         <v>1</v>
@@ -8306,7 +8370,7 @@
         <v>1</v>
       </c>
       <c r="BP18" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="BT18" s="3">
         <v>10</v>
@@ -8321,10 +8385,10 @@
         <v>1</v>
       </c>
       <c r="BY18" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CN18" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="CO18" s="3">
         <v>0.35</v>
@@ -8335,19 +8399,19 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K19" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="AC19" s="3">
         <v>1</v>
       </c>
       <c r="AG19" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="BD19" s="3">
         <v>1</v>
@@ -8356,28 +8420,28 @@
         <v>6</v>
       </c>
       <c r="CX19" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K21" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L21" s="3" t="s">
+        <v>540</v>
+      </c>
+      <c r="AC21" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG21" s="3" t="s">
         <v>538</v>
       </c>
-      <c r="AC21" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG21" s="3" t="s">
-        <v>536</v>
-      </c>
       <c r="AH21" s="3">
         <v>1</v>
       </c>
@@ -8385,7 +8449,7 @@
         <v>1</v>
       </c>
       <c r="CN21" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="CO21" s="3">
         <v>0.19</v>
@@ -8396,22 +8460,22 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC22" s="3">
         <v>2</v>
       </c>
       <c r="AO22" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT22" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX22" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ22" s="3">
         <v>1</v>
@@ -8423,39 +8487,39 @@
         <v>77</v>
       </c>
       <c r="CG22" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CW22" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="CY22" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="G23" s="3">
         <v>3</v>
       </c>
       <c r="J23" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K23" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC23" s="3">
         <v>1</v>
@@ -8467,7 +8531,7 @@
         <v>8</v>
       </c>
       <c r="BO23" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="BT23" s="3">
         <v>15</v>
@@ -8482,24 +8546,24 @@
         <v>1</v>
       </c>
       <c r="BY23" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CX23" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K24" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L24" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AC24" s="3">
         <v>1</v>
@@ -8511,7 +8575,7 @@
         <v>3</v>
       </c>
       <c r="CN24" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="CO24" s="3">
         <v>0.8</v>
@@ -8522,16 +8586,16 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K26" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L26" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AC26" s="3">
         <v>1</v>
@@ -8540,7 +8604,7 @@
         <v>1</v>
       </c>
       <c r="AG26" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AH26" s="3">
         <v>1</v>
@@ -8549,10 +8613,10 @@
         <v>1</v>
       </c>
       <c r="CN26" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="CO26" s="3" t="s">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="CR26" s="3">
         <v>99999</v>
@@ -8563,22 +8627,22 @@
     </row>
     <row r="27">
       <c r="A27" s="3" t="s">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC27" s="3">
         <v>2</v>
       </c>
       <c r="AO27" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT27" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX27" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ27" s="3">
         <v>1</v>
@@ -8587,42 +8651,42 @@
         <v>1</v>
       </c>
       <c r="CB27" s="3" t="s">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="CG27" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CW27" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="CY27" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="3" t="s">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="G28" s="3">
         <v>3</v>
       </c>
       <c r="J28" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K28" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC28" s="3">
         <v>1</v>
@@ -8631,7 +8695,7 @@
         <v>1</v>
       </c>
       <c r="BP28" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="BT28" s="3">
         <v>15</v>
@@ -8646,10 +8710,10 @@
         <v>1</v>
       </c>
       <c r="BY28" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CN28" s="3" t="s">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="CO28" s="3">
         <v>0.7</v>
@@ -8660,42 +8724,42 @@
     </row>
     <row r="29">
       <c r="A29" s="3" t="s">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K29" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L29" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="BN29" s="3">
         <v>11</v>
       </c>
       <c r="CX29" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="3" t="s">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC31" s="3">
         <v>2</v>
       </c>
       <c r="AO31" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT31" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX31" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ31" s="3">
         <v>1</v>
@@ -8707,42 +8771,42 @@
         <v>77</v>
       </c>
       <c r="CG31" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CJ31" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CW31" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="CY31" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="3" t="s">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="E32" s="3" t="s">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="G32" s="3">
         <v>3</v>
       </c>
       <c r="J32" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K32" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC32" s="3">
         <v>1</v>
@@ -8763,16 +8827,16 @@
         <v>1</v>
       </c>
       <c r="BY32" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CJ32" s="3" t="s">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="CN32" s="3" t="s">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="CO32" s="3" t="s">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="CR32" s="3">
         <v>30</v>
@@ -8780,22 +8844,22 @@
     </row>
     <row r="34">
       <c r="A34" s="3" t="s">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="C34" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC34" s="3">
         <v>2</v>
       </c>
       <c r="AO34" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT34" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX34" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ34" s="3">
         <v>1</v>
@@ -8807,27 +8871,27 @@
         <v>77</v>
       </c>
       <c r="CG34" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CW34" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="CY34" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="s">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C35" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K35" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L35" s="3" t="s">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="AC35" s="3">
         <v>1</v>
@@ -8839,10 +8903,10 @@
         <v>1</v>
       </c>
       <c r="AI35" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="CN35" s="3" t="s">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="CO35" s="3">
         <v>-1</v>
@@ -8850,28 +8914,28 @@
     </row>
     <row r="36">
       <c r="A36" s="3" t="s">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="C36" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G36" s="3">
         <v>3</v>
       </c>
       <c r="J36" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K36" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="W36" s="3">
         <v>1</v>
@@ -8898,36 +8962,36 @@
         <v>1</v>
       </c>
       <c r="BY36" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CX36" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="s">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="C37" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="G37" s="3">
         <v>3</v>
       </c>
       <c r="J37" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K37" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC37" s="3">
         <v>1</v>
@@ -8939,7 +9003,7 @@
         <v>9</v>
       </c>
       <c r="BO37" s="3" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="BT37" s="3">
         <v>10</v>
@@ -8954,24 +9018,24 @@
         <v>1</v>
       </c>
       <c r="BY37" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CX37" s="3" t="s">
-        <v>549</v>
+        <v>551</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="s">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="C38" s="3" t="s">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="K38" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L38" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AC38" s="3">
         <v>1</v>
@@ -8985,22 +9049,22 @@
     </row>
     <row r="39">
       <c r="A39" s="3" t="s">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="C39" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K39" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L39" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AC39" s="3">
         <v>1</v>
       </c>
       <c r="AI39" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AV39" s="3">
         <v>99</v>
@@ -9009,10 +9073,10 @@
         <v>99</v>
       </c>
       <c r="CN39" s="3" t="s">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="CO39" s="3" t="s">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="CR39" s="3">
         <v>10</v>
@@ -9023,25 +9087,25 @@
     </row>
     <row r="41">
       <c r="A41" s="3" t="s">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="C41" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K41" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AC41" s="3">
         <v>2</v>
       </c>
       <c r="AO41" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT41" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX41" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ41" s="3">
         <v>1</v>
@@ -9050,30 +9114,30 @@
         <v>1</v>
       </c>
       <c r="CB41" s="3" t="s">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="CG41" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CW41" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="CY41" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C42" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K42" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L42" s="3" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="X42" s="3">
         <v>1</v>
@@ -9082,7 +9146,7 @@
         <v>1</v>
       </c>
       <c r="AG42" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="BD42" s="3">
         <v>1</v>
@@ -9093,16 +9157,16 @@
     </row>
     <row r="43">
       <c r="A43" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="C43" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="K43" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L43" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AC43" s="3">
         <v>1</v>
@@ -9116,28 +9180,28 @@
     </row>
     <row r="44">
       <c r="A44" s="3" t="s">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="C44" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="G44" s="3">
         <v>3</v>
       </c>
       <c r="J44" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K44" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="X44" s="3">
         <v>1</v>
@@ -9152,13 +9216,13 @@
         <v>2</v>
       </c>
       <c r="AO44" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT44" s="3" t="s">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AX44" s="3" t="s">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="AZ44" s="3">
         <v>1.7</v>
@@ -9173,7 +9237,7 @@
         <v>0.8</v>
       </c>
       <c r="BO44" s="3" t="s">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="BS44" s="3">
         <v>2.167</v>
@@ -9191,48 +9255,48 @@
         <v>1</v>
       </c>
       <c r="BY44" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CB44" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="CC44" s="3">
         <v>0.5</v>
       </c>
       <c r="CG44" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="CN44" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="CR44" s="3">
         <v>3</v>
       </c>
       <c r="CW44" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="CY44" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="s">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C46" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC46" s="3">
         <v>2</v>
       </c>
       <c r="AO46" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT46" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX46" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ46" s="3">
         <v>1</v>
@@ -9244,42 +9308,42 @@
         <v>77</v>
       </c>
       <c r="CG46" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CW46" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="s">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="C47" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K47" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L47" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AC47" s="3">
         <v>1</v>
       </c>
       <c r="AI47" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BD47" s="3">
         <v>99</v>
       </c>
       <c r="BO47" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="CN47" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="CN47" s="3" t="s">
-        <v>612</v>
-      </c>
       <c r="CO47" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="CR47" s="3">
         <v>99999</v>
@@ -9290,37 +9354,37 @@
     </row>
     <row r="48">
       <c r="A48" s="3" t="s">
+        <v>616</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>531</v>
+      </c>
+      <c r="K48" s="3" t="s">
+        <v>509</v>
+      </c>
+      <c r="L48" s="3" t="s">
+        <v>555</v>
+      </c>
+      <c r="AC48" s="3">
+        <v>1</v>
+      </c>
+      <c r="AF48" s="3">
+        <v>1</v>
+      </c>
+      <c r="AG48" s="3" t="s">
+        <v>618</v>
+      </c>
+      <c r="AI48" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="BD48" s="3">
+        <v>1</v>
+      </c>
+      <c r="CN48" s="3" t="s">
         <v>614</v>
       </c>
-      <c r="C48" s="3" t="s">
-        <v>529</v>
-      </c>
-      <c r="K48" s="3" t="s">
-        <v>507</v>
-      </c>
-      <c r="L48" s="3" t="s">
-        <v>553</v>
-      </c>
-      <c r="AC48" s="3">
-        <v>1</v>
-      </c>
-      <c r="AF48" s="3">
-        <v>1</v>
-      </c>
-      <c r="AG48" s="3" t="s">
-        <v>616</v>
-      </c>
-      <c r="AI48" s="3" t="s">
-        <v>157</v>
-      </c>
-      <c r="BD48" s="3">
-        <v>1</v>
-      </c>
-      <c r="CN48" s="3" t="s">
-        <v>612</v>
-      </c>
       <c r="CO48" s="3" t="s">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="CR48" s="3">
         <v>99999</v>
@@ -9331,16 +9395,16 @@
     </row>
     <row r="49">
       <c r="A49" s="3" t="s">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="C49" s="3" t="s">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="K49" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L49" s="3" t="s">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AC49" s="3">
         <v>2</v>
@@ -9349,36 +9413,36 @@
         <v>1</v>
       </c>
       <c r="AT49" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="CU49" s="3" t="s">
-        <v>620</v>
+        <v>622</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="3" t="s">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="C50" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="G50" s="3">
         <v>3</v>
       </c>
       <c r="J50" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K50" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="W50" s="3">
         <v>1</v>
@@ -9405,48 +9469,48 @@
         <v>1</v>
       </c>
       <c r="BY50" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CX50" s="3" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="3" t="s">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="G51" s="3">
         <v>3</v>
       </c>
       <c r="J51" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K51" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AC51" s="3">
         <v>2</v>
       </c>
       <c r="AO51" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT51" s="3" t="s">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="AX51" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ51" s="3">
         <v>3.4</v>
@@ -9473,54 +9537,54 @@
         <v>3</v>
       </c>
       <c r="BY51" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CB51" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="CG51" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CW51" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="s">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C52" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="G52" s="3">
         <v>3</v>
       </c>
       <c r="J52" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K52" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC52" s="3">
         <v>2</v>
       </c>
       <c r="AO52" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT52" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX52" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ52" s="3">
         <v>3.8</v>
@@ -9529,7 +9593,7 @@
         <v>1</v>
       </c>
       <c r="BO52" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="BT52" s="3">
         <v>25</v>
@@ -9547,19 +9611,19 @@
         <v>1</v>
       </c>
       <c r="BY52" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CA52" s="3" t="s">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="CB52" s="3" t="s">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="CG52" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CN52" s="3" t="s">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="CR52" s="3">
         <v>1.5</v>
@@ -9568,24 +9632,24 @@
         <v>0.4</v>
       </c>
       <c r="CW52" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="CX52" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="s">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C53" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K53" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L53" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AC53" s="3">
         <v>1</v>
@@ -9594,7 +9658,7 @@
         <v>1</v>
       </c>
       <c r="CN53" s="3" t="s">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="CO53" s="3">
         <v>1</v>
@@ -9608,22 +9672,22 @@
     </row>
     <row r="55">
       <c r="A55" s="3" t="s">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="C55" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC55" s="3">
         <v>2</v>
       </c>
       <c r="AO55" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT55" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX55" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ55" s="3">
         <v>1</v>
@@ -9635,33 +9699,33 @@
         <v>77</v>
       </c>
       <c r="CG55" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CX55" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="CY55" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="s">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C56" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I56" s="3">
         <v>1</v>
       </c>
       <c r="K56" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AC56" s="3">
         <v>1</v>
       </c>
       <c r="AI56" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="AV56" s="3">
         <v>99</v>
@@ -9687,34 +9751,34 @@
     </row>
     <row r="57">
       <c r="A57" s="3" t="s">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="C57" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="G57" s="3">
         <v>3</v>
       </c>
       <c r="J57" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K57" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC57" s="3">
         <v>1</v>
       </c>
       <c r="AT57" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="BD57" s="3">
         <v>1</v>
@@ -9738,22 +9802,22 @@
         <v>1</v>
       </c>
       <c r="BY57" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CB57" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="CC57" s="3">
         <v>0</v>
       </c>
       <c r="CE57" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="CG57" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="CN57" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="CP57" s="3">
         <v>-1</v>
@@ -9767,34 +9831,34 @@
     </row>
     <row r="58">
       <c r="A58" s="3" t="s">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C58" s="3" t="s">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="G58" s="3">
         <v>3</v>
       </c>
       <c r="J58" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K58" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC58" s="3">
         <v>1</v>
       </c>
       <c r="AT58" s="3" t="s">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="BD58" s="3">
         <v>1</v>
@@ -9803,7 +9867,7 @@
         <v>16</v>
       </c>
       <c r="BO58" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="BS58" s="3">
         <v>0.01</v>
@@ -9821,22 +9885,22 @@
         <v>1</v>
       </c>
       <c r="BY58" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CB58" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="CC58" s="3">
         <v>0</v>
       </c>
       <c r="CE58" s="3" t="s">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="CG58" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="CN58" s="3" t="s">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="CP58" s="3">
         <v>-1</v>
@@ -9848,21 +9912,21 @@
         <v>1</v>
       </c>
       <c r="DC58" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="s">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="C59" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="J59" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K59" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AB59" s="3">
         <v>1</v>
@@ -9871,10 +9935,10 @@
         <v>1</v>
       </c>
       <c r="AO59" s="3" t="s">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AT59" s="3" t="s">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="AY59" s="3">
         <v>1</v>
@@ -9891,22 +9955,22 @@
     </row>
     <row r="61">
       <c r="A61" s="3" t="s">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="C61" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="AC61" s="3">
         <v>2</v>
       </c>
       <c r="AO61" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT61" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX61" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ61" s="3">
         <v>1</v>
@@ -9915,27 +9979,27 @@
         <v>1</v>
       </c>
       <c r="CB61" s="3" t="s">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="CG61" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CJ61" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="C62" s="3" t="s">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="K62" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L62" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AC62" s="3">
         <v>1</v>
@@ -9947,36 +10011,36 @@
         <v>1</v>
       </c>
       <c r="AI62" s="3" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="BD62" s="3">
         <v>1</v>
       </c>
       <c r="CU62" s="3" t="s">
-        <v>660</v>
+        <v>662</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="3" t="s">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C63" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="J63" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K63" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AC63" s="3">
         <v>1</v>
@@ -9997,13 +10061,13 @@
         <v>1</v>
       </c>
       <c r="BY63" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CN63" s="3" t="s">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="CO63" s="3" t="s">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="CR63" s="3">
         <v>35</v>
@@ -10011,34 +10075,34 @@
     </row>
     <row r="64">
       <c r="A64" s="3" t="s">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="C64" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="J64" s="3" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="K64" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AC64" s="3">
         <v>2</v>
       </c>
       <c r="AT64" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX64" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ64" s="3">
         <v>2</v>
@@ -10065,39 +10129,39 @@
         <v>3</v>
       </c>
       <c r="BY64" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CB64" s="3" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="CG64" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CJ64" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="3" t="s">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="C65" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="J65" s="3" t="s">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="K65" s="3" t="s">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="AB65" s="3">
         <v>1</v>
@@ -10106,10 +10170,10 @@
         <v>2</v>
       </c>
       <c r="AT65" s="3" t="s">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AX65" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ65" s="3">
         <v>1</v>
@@ -10124,7 +10188,7 @@
         <v>0.1</v>
       </c>
       <c r="BO65" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="BT65" s="3">
         <v>20</v>
@@ -10142,30 +10206,30 @@
         <v>1</v>
       </c>
       <c r="BY65" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="CB65" s="3" t="s">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="CG65" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CJ65" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C66" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="K66" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L66" s="3" t="s">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="AC66" s="3">
         <v>1</v>
@@ -10174,10 +10238,10 @@
         <v>1</v>
       </c>
       <c r="CN66" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="CO66" s="3" t="s">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="CR66" s="3">
         <v>20</v>
@@ -10185,42 +10249,42 @@
     </row>
     <row r="68">
       <c r="A68" s="3" t="s">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C68" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="AT68" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="BO68" s="3" t="s">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="CU68" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="3" t="s">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="K69" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AC69" s="3">
         <v>2</v>
       </c>
       <c r="AO69" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT69" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AX69" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ69" s="3">
         <v>1</v>
@@ -10238,39 +10302,39 @@
         <v>77</v>
       </c>
       <c r="CG69" s="3" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="CL69" s="3" t="s">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="CY69" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="3" t="s">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="K70" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L70" s="3" t="s">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="AC70" s="3">
         <v>2</v>
       </c>
       <c r="AO70" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT70" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="AX70" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ70" s="3">
         <v>2</v>
@@ -10285,27 +10349,27 @@
         <v>0.1</v>
       </c>
       <c r="CG70" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="CY70" s="3" t="s">
-        <v>684</v>
+        <v>686</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="s">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I71" s="3">
         <v>1</v>
       </c>
       <c r="K71" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L71" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AC71" s="3">
         <v>1</v>
@@ -10314,16 +10378,16 @@
         <v>1</v>
       </c>
       <c r="AG71" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="BD71" s="3">
         <v>1</v>
       </c>
       <c r="CN71" s="3" t="s">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="CO71" s="3" t="s">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="CR71" s="3">
         <v>99999</v>
@@ -10331,16 +10395,16 @@
     </row>
     <row r="72">
       <c r="A72" s="3" t="s">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="K72" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L72" s="3" t="s">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="AC72" s="3">
         <v>1</v>
@@ -10349,30 +10413,30 @@
         <v>1</v>
       </c>
       <c r="CU72" s="3" t="s">
-        <v>694</v>
+        <v>696</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="3" t="s">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="I77" s="3">
         <v>1</v>
       </c>
       <c r="K77" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AC77" s="3">
         <v>1</v>
       </c>
       <c r="AG77" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AT77" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="BD77" s="3">
         <v>1</v>
@@ -10383,25 +10447,25 @@
     </row>
     <row r="78">
       <c r="A78" s="3" t="s">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="C78" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I78" s="3">
         <v>1</v>
       </c>
       <c r="K78" s="3" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="AC78" s="3">
         <v>2</v>
       </c>
       <c r="AO78" s="3" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="AT78" s="3" t="s">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="BD78" s="3">
         <v>99</v>
@@ -10410,13 +10474,13 @@
         <v>0.01</v>
       </c>
       <c r="CN78" s="3" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="CR78" s="3">
         <v>0.02</v>
       </c>
       <c r="CU78" s="3" t="s">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="DD78" s="3">
         <v>1</v>
@@ -10427,19 +10491,19 @@
     </row>
     <row r="79">
       <c r="A79" s="3" t="s">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="C79" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I79" s="3">
         <v>1</v>
       </c>
       <c r="K79" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L79" s="3" t="s">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="AC79" s="3">
         <v>1</v>
@@ -10448,13 +10512,13 @@
         <v>1</v>
       </c>
       <c r="AJ79" s="3" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="AV79" s="3">
         <v>99</v>
       </c>
       <c r="AX79" s="3" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AZ79" s="3">
         <v>1</v>
@@ -10466,16 +10530,16 @@
         <v>0.02</v>
       </c>
       <c r="CG79" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="CH79" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="CI79" s="3" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="CN79" s="3" t="s">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="CR79" s="3">
         <v>6</v>
@@ -10486,19 +10550,19 @@
     </row>
     <row r="80">
       <c r="A80" s="3" t="s">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="C80" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I80" s="3">
         <v>1</v>
       </c>
       <c r="K80" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L80" s="3" t="s">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="AC80" s="3">
         <v>1</v>
@@ -10507,7 +10571,7 @@
         <v>1</v>
       </c>
       <c r="AG80" s="3" t="s">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AV80" s="3">
         <v>1</v>
@@ -10516,7 +10580,7 @@
         <v>1</v>
       </c>
       <c r="CN80" s="3" t="s">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="CR80" s="3">
         <v>99999</v>
@@ -10530,31 +10594,31 @@
     </row>
     <row r="81">
       <c r="A81" s="3" t="s">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C81" s="3" t="s">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="I81" s="3">
         <v>1</v>
       </c>
       <c r="K81" s="3" t="s">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="L81" s="3" t="s">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AC81" s="3">
         <v>1</v>
       </c>
       <c r="AJ81" s="3" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="AV81" s="3">
         <v>99</v>
       </c>
       <c r="AX81" s="3" t="s">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="AZ81" s="3">
         <v>99999</v>
@@ -10566,7 +10630,7 @@
         <v>1</v>
       </c>
       <c r="CG81" s="3" t="s">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="DD81" s="3">
         <v>1</v>
@@ -10663,37 +10727,37 @@
         <v>21</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="M1" s="3" t="s">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="N1" s="3" t="s">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="O1" s="3" t="s">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="P1" s="3" t="s">
-        <v>716</v>
+        <v>718</v>
       </c>
     </row>
     <row r="2">
@@ -10707,43 +10771,43 @@
         <v>99</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>73</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="N2" s="3" t="s">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="O2" s="3" t="s">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="P2" s="3" t="s">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="Q2" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3">
@@ -10757,51 +10821,51 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>504</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="F3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="H3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>502</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="L3" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="N3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="O3" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="P3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="Q3" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="E4" s="3">
         <v>2</v>
@@ -10816,32 +10880,32 @@
         <v>1</v>
       </c>
       <c r="Q4" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="K5" s="3">
         <v>0.01</v>
       </c>
       <c r="Q5" s="3" t="s">
-        <v>729</v>
+        <v>731</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="G6" s="3">
         <v>1</v>
@@ -10850,18 +10914,18 @@
         <v>0.01</v>
       </c>
       <c r="Q6" s="3" t="s">
-        <v>731</v>
+        <v>733</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J7" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="K7" s="3">
         <v>9999</v>
@@ -10870,40 +10934,40 @@
         <v>1</v>
       </c>
       <c r="Q7" s="3" t="s">
-        <v>733</v>
+        <v>735</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C8" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="J8" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="J9" s="3" t="s">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="Q9" s="3" t="s">
-        <v>738</v>
+        <v>740</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>735</v>
+        <v>737</v>
       </c>
     </row>
   </sheetData>
@@ -10930,7 +10994,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>740</v>
+        <v>742</v>
       </c>
     </row>
     <row r="2">
@@ -10941,10 +11005,10 @@
         <v>67</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3">
@@ -10955,21 +11019,21 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>743</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -10994,7 +11058,7 @@
   <sheetData>
     <row r="1">
       <c r="I1" s="3" t="s">
-        <v>357</v>
+        <v>359</v>
       </c>
     </row>
     <row r="2">
@@ -11008,25 +11072,25 @@
         <v>69</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="E2" s="3" t="s">
         <v>92</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>472</v>
+        <v>474</v>
       </c>
     </row>
     <row r="3">
@@ -11043,39 +11107,39 @@
         <v>2</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="G3" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="I3" s="3" t="s">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="J3" s="3" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="E4" s="3">
         <v>10</v>
       </c>
       <c r="J4" s="3" t="s">
-        <v>750</v>
+        <v>752</v>
       </c>
     </row>
   </sheetData>
@@ -11104,34 +11168,34 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="J1" s="3" t="s">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="K1" s="3" t="s">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="L1" s="3" t="s">
-        <v>760</v>
+        <v>762</v>
       </c>
     </row>
     <row r="2">
@@ -11139,34 +11203,34 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="J2" s="3" t="s">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="K2" s="3" t="s">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="L2" s="3" t="s">
         <v>119</v>
@@ -11180,42 +11244,42 @@
         <v>2</v>
       </c>
       <c r="C3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="D3" s="3" t="s">
+        <v>142</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>2</v>
+      </c>
+      <c r="F3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="G3" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="H3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="J3" s="3" t="s">
+        <v>143</v>
+      </c>
+      <c r="K3" s="3" t="s">
         <v>141</v>
       </c>
-      <c r="D3" s="3" t="s">
-        <v>140</v>
-      </c>
-      <c r="E3" s="3" t="s">
-        <v>2</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="G3" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="H3" s="3" t="s">
+      <c r="L3" s="3" t="s">
         <v>141</v>
-      </c>
-      <c r="I3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="J3" s="3" t="s">
-        <v>141</v>
-      </c>
-      <c r="K3" s="3" t="s">
-        <v>139</v>
-      </c>
-      <c r="L3" s="3" t="s">
-        <v>139</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="s">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="I4" s="3">
         <v>2</v>
@@ -11229,10 +11293,10 @@
     </row>
     <row r="5">
       <c r="A5" s="3" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="I5" s="3">
         <v>2</v>
@@ -11246,13 +11310,13 @@
     </row>
     <row r="6">
       <c r="A6" s="3" t="s">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="F6" s="3">
         <v>1</v>
@@ -11266,10 +11330,10 @@
     </row>
     <row r="7">
       <c r="A7" s="3" t="s">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="I7" s="3">
         <v>2</v>
@@ -11283,10 +11347,10 @@
     </row>
     <row r="8">
       <c r="A8" s="3" t="s">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="I8" s="3">
         <v>2</v>
@@ -11300,10 +11364,10 @@
     </row>
     <row r="9">
       <c r="A9" s="3" t="s">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="I9" s="3">
         <v>2</v>
@@ -11317,10 +11381,10 @@
     </row>
     <row r="10">
       <c r="A10" s="3" t="s">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="H10" s="3">
         <v>2</v>
@@ -11337,10 +11401,10 @@
     </row>
     <row r="11">
       <c r="A11" s="3" t="s">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="I11" s="3">
         <v>2</v>
@@ -11354,10 +11418,10 @@
     </row>
     <row r="12">
       <c r="A12" s="3" t="s">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="H12" s="3">
         <v>2</v>
@@ -11374,10 +11438,10 @@
     </row>
     <row r="13">
       <c r="A13" s="3" t="s">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="I13" s="3">
         <v>2</v>
@@ -11391,13 +11455,13 @@
     </row>
     <row r="14">
       <c r="A14" s="3" t="s">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="E14" s="3" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="H14" s="3">
         <v>2</v>
@@ -11414,13 +11478,13 @@
     </row>
     <row r="15">
       <c r="A15" s="3" t="s">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="F15" s="3">
         <v>1</v>
@@ -11434,18 +11498,18 @@
     </row>
     <row r="16">
       <c r="A16" s="3" t="s">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>785</v>
+        <v>787</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="3" t="s">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="I17" s="3">
         <v>2</v>
@@ -11459,10 +11523,10 @@
     </row>
     <row r="18">
       <c r="A18" s="3" t="s">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="I18" s="3">
         <v>2</v>
@@ -11476,10 +11540,10 @@
     </row>
     <row r="19">
       <c r="A19" s="3" t="s">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="I19" s="3">
         <v>2</v>
@@ -11493,10 +11557,10 @@
     </row>
     <row r="20">
       <c r="A20" s="3" t="s">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="I20" s="3">
         <v>2</v>
@@ -11510,10 +11574,10 @@
     </row>
     <row r="21">
       <c r="A21" s="3" t="s">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="I21" s="3">
         <v>2</v>
@@ -11527,10 +11591,10 @@
     </row>
     <row r="22">
       <c r="A22" s="3" t="s">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="I22" s="3">
         <v>2</v>
@@ -11544,10 +11608,10 @@
     </row>
     <row r="23">
       <c r="A23" s="3" t="s">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="I23" s="3">
         <v>2</v>
@@ -11558,10 +11622,10 @@
     </row>
     <row r="24">
       <c r="A24" s="3" t="s">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="I24" s="3">
         <v>2</v>
@@ -11575,10 +11639,10 @@
     </row>
     <row r="25">
       <c r="A25" s="3" t="s">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>795</v>
+        <v>797</v>
       </c>
       <c r="I25" s="3">
         <v>2</v>
@@ -11592,10 +11656,10 @@
     </row>
     <row r="26">
       <c r="A26" s="3" t="s">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>796</v>
+        <v>798</v>
       </c>
       <c r="I26" s="3">
         <v>2</v>
@@ -11638,28 +11702,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>99</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>797</v>
+        <v>799</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>798</v>
+        <v>800</v>
       </c>
       <c r="F2" s="1" t="s">
         <v>101</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>799</v>
+        <v>801</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>800</v>
+        <v>802</v>
       </c>
       <c r="J2" s="1" t="s">
         <v>74</v>
@@ -11679,22 +11743,22 @@
         <v>2</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>801</v>
+        <v>803</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
     </row>
   </sheetData>
@@ -11725,28 +11789,28 @@
         <v>0</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>802</v>
+        <v>804</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>803</v>
+        <v>805</v>
       </c>
       <c r="D1" s="3" t="s">
-        <v>804</v>
+        <v>806</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>805</v>
+        <v>807</v>
       </c>
       <c r="F1" s="3" t="s">
-        <v>806</v>
+        <v>808</v>
       </c>
       <c r="G1" s="3" t="s">
-        <v>807</v>
+        <v>809</v>
       </c>
       <c r="H1" s="3" t="s">
-        <v>808</v>
+        <v>810</v>
       </c>
       <c r="I1" s="3" t="s">
-        <v>809</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2">
@@ -11754,28 +11818,28 @@
         <v>0</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>810</v>
+        <v>812</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>811</v>
+        <v>813</v>
       </c>
       <c r="D2" s="3" t="s">
-        <v>812</v>
+        <v>814</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>813</v>
+        <v>815</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>814</v>
+        <v>816</v>
       </c>
       <c r="G2" s="3" t="s">
-        <v>815</v>
+        <v>817</v>
       </c>
       <c r="H2" s="3" t="s">
-        <v>816</v>
+        <v>818</v>
       </c>
       <c r="I2" s="3" t="s">
-        <v>817</v>
+        <v>819</v>
       </c>
     </row>
     <row r="3">
@@ -11783,10 +11847,10 @@
         <v>2</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>2</v>
